--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -19299,7 +19299,11 @@
       <c r="B52" s="654" t="s">
         <v>213</v>
       </c>
-      <c r="C52" s="510"/>
+      <c r="C52" s="510" t="inlineStr">
+        <is>
+          <t>M³</t>
+        </is>
+      </c>
       <c r="D52" s="510"/>
       <c r="E52" s="510"/>
       <c r="F52" s="524"/>
@@ -19396,7 +19400,11 @@
       <c r="B58" s="653" t="s">
         <v>231</v>
       </c>
-      <c r="C58" s="510"/>
+      <c r="C58" s="510" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
       <c r="D58" s="510"/>
       <c r="E58" s="510"/>
       <c r="F58" s="398">
@@ -19428,7 +19436,11 @@
       <c r="B60" s="654" t="s">
         <v>237</v>
       </c>
-      <c r="C60" s="510"/>
+      <c r="C60" s="510" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
       <c r="D60" s="510"/>
       <c r="E60" s="510"/>
       <c r="F60" s="524"/>
@@ -19693,7 +19705,11 @@
       <c r="B78" s="654" t="s">
         <v>279</v>
       </c>
-      <c r="C78" s="510"/>
+      <c r="C78" s="510" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
       <c r="D78" s="510"/>
       <c r="E78" s="510"/>
       <c r="F78" s="524"/>
@@ -19857,7 +19873,11 @@
       <c r="B89" s="654" t="s">
         <v>307</v>
       </c>
-      <c r="C89" s="510"/>
+      <c r="C89" s="510" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
       <c r="D89" s="510"/>
       <c r="E89" s="510"/>
       <c r="F89" s="524"/>
@@ -19919,7 +19939,11 @@
       <c r="B94" s="654" t="s">
         <v>315</v>
       </c>
-      <c r="C94" s="510"/>
+      <c r="C94" s="510" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
       <c r="D94" s="510"/>
       <c r="E94" s="510"/>
       <c r="F94" s="524"/>
@@ -19965,7 +19989,11 @@
       <c r="B97" s="653" t="s">
         <v>324</v>
       </c>
-      <c r="C97" s="510"/>
+      <c r="C97" s="510" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
       <c r="D97" s="510"/>
       <c r="E97" s="510"/>
       <c r="F97" s="398">
@@ -20098,7 +20126,11 @@
       <c r="B106" s="653" t="s">
         <v>345</v>
       </c>
-      <c r="C106" s="510"/>
+      <c r="C106" s="510" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
       <c r="D106" s="510"/>
       <c r="E106" s="510"/>
       <c r="F106" s="398">
@@ -20130,7 +20162,11 @@
       <c r="B108" s="654" t="s">
         <v>351</v>
       </c>
-      <c r="C108" s="510"/>
+      <c r="C108" s="510" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
       <c r="D108" s="510"/>
       <c r="E108" s="510"/>
       <c r="F108" s="524"/>
@@ -20243,7 +20279,11 @@
       <c r="B116" s="653" t="s">
         <v>368</v>
       </c>
-      <c r="C116" s="510"/>
+      <c r="C116" s="510" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
       <c r="D116" s="510"/>
       <c r="E116" s="510"/>
       <c r="F116" s="398">
@@ -20308,7 +20348,11 @@
       <c r="B121" s="653" t="s">
         <v>376</v>
       </c>
-      <c r="C121" s="510"/>
+      <c r="C121" s="510" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
       <c r="D121" s="510"/>
       <c r="E121" s="510"/>
       <c r="F121" s="398">
@@ -20340,7 +20384,11 @@
       <c r="B123" s="654" t="s">
         <v>383</v>
       </c>
-      <c r="C123" s="510"/>
+      <c r="C123" s="510" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
       <c r="D123" s="510"/>
       <c r="E123" s="510"/>
       <c r="F123" s="524"/>
@@ -20436,7 +20484,11 @@
       <c r="B130" s="653" t="s">
         <v>398</v>
       </c>
-      <c r="C130" s="510"/>
+      <c r="C130" s="510" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
       <c r="D130" s="510"/>
       <c r="E130" s="510"/>
       <c r="F130" s="398">
@@ -20468,7 +20520,11 @@
       <c r="B132" s="654" t="s">
         <v>404</v>
       </c>
-      <c r="C132" s="510"/>
+      <c r="C132" s="510" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
       <c r="D132" s="510"/>
       <c r="E132" s="510"/>
       <c r="F132" s="524"/>
@@ -20530,7 +20586,11 @@
       <c r="B137" s="653" t="s">
         <v>412</v>
       </c>
-      <c r="C137" s="510"/>
+      <c r="C137" s="510" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
       <c r="D137" s="510"/>
       <c r="E137" s="510"/>
       <c r="F137" s="398">
@@ -20562,7 +20622,11 @@
       <c r="B139" s="653" t="s">
         <v>418</v>
       </c>
-      <c r="C139" s="510"/>
+      <c r="C139" s="510" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
       <c r="D139" s="510"/>
       <c r="E139" s="510"/>
       <c r="F139" s="398">
@@ -22017,18 +22081,14 @@
       <c r="F241" s="362"/>
     </row>
   </sheetData>
-  <mergeCells count="78">
+  <mergeCells count="62">
     <mergeCell ref="B201:E201"/>
-    <mergeCell ref="B139:E139"/>
     <mergeCell ref="B1:B9"/>
     <mergeCell ref="B76:E76"/>
     <mergeCell ref="B180:F180"/>
-    <mergeCell ref="B52:F52"/>
     <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B60:F60"/>
     <mergeCell ref="B109:E109"/>
     <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B108:F108"/>
     <mergeCell ref="B118:F118"/>
     <mergeCell ref="C1:F3"/>
     <mergeCell ref="B178:E178"/>
@@ -22037,7 +22097,6 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="B87:F87"/>
-    <mergeCell ref="B58:E58"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B100:F100"/>
@@ -22048,17 +22107,14 @@
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B106:E106"/>
     <mergeCell ref="B111:F111"/>
     <mergeCell ref="B209:E209"/>
     <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B130:E130"/>
     <mergeCell ref="B117:E117"/>
     <mergeCell ref="B184:E184"/>
     <mergeCell ref="B148:E148"/>
     <mergeCell ref="B164:F164"/>
     <mergeCell ref="B171:E171"/>
-    <mergeCell ref="B123:F123"/>
     <mergeCell ref="B203:F203"/>
     <mergeCell ref="B213:E213"/>
     <mergeCell ref="B196:F196"/>
@@ -22066,36 +22122,28 @@
     <mergeCell ref="B231:E231"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="B116:E116"/>
     <mergeCell ref="B173:F173"/>
     <mergeCell ref="B127:E127"/>
     <mergeCell ref="B150:F150"/>
     <mergeCell ref="B215:F215"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B97:E97"/>
     <mergeCell ref="B136:F136"/>
     <mergeCell ref="B134:E134"/>
     <mergeCell ref="B194:E194"/>
-    <mergeCell ref="B121:E121"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B89:F89"/>
     <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B94:F94"/>
     <mergeCell ref="B65:E65"/>
     <mergeCell ref="B162:E162"/>
     <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B137:E137"/>
     <mergeCell ref="B75:E75"/>
     <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B132:F132"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" scale="53" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -19296,17 +19296,19 @@
       <c r="A52" s="85" t="s">
         <v>1027</v>
       </c>
-      <c r="B52" s="654" t="s">
+      <c r="B52" s="307" t="s">
         <v>213</v>
       </c>
-      <c r="C52" s="510" t="inlineStr">
+      <c r="C52" s="308" t="inlineStr">
         <is>
           <t>M³</t>
         </is>
       </c>
-      <c r="D52" s="510"/>
-      <c r="E52" s="510"/>
-      <c r="F52" s="524"/>
+      <c r="D52" s="309"/>
+      <c r="E52" s="397"/>
+      <c r="F52" s="398">
+        <f>D52*E52</f>
+      </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="85" t="s">
@@ -19397,16 +19399,16 @@
       <c r="A58" s="85" t="s">
         <v>1033</v>
       </c>
-      <c r="B58" s="653" t="s">
+      <c r="B58" s="307" t="s">
         <v>231</v>
       </c>
-      <c r="C58" s="510" t="inlineStr">
+      <c r="C58" s="308" t="inlineStr">
         <is>
           <t>KG</t>
         </is>
       </c>
-      <c r="D58" s="510"/>
-      <c r="E58" s="510"/>
+      <c r="D58" s="309"/>
+      <c r="E58" s="397"/>
       <c r="F58" s="398">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -19433,17 +19435,19 @@
       <c r="A60" s="85" t="s">
         <v>1035</v>
       </c>
-      <c r="B60" s="654" t="s">
+      <c r="B60" s="307" t="s">
         <v>237</v>
       </c>
-      <c r="C60" s="510" t="inlineStr">
+      <c r="C60" s="308" t="inlineStr">
         <is>
           <t>M²</t>
         </is>
       </c>
-      <c r="D60" s="510"/>
-      <c r="E60" s="510"/>
-      <c r="F60" s="524"/>
+      <c r="D60" s="309"/>
+      <c r="E60" s="397"/>
+      <c r="F60" s="398">
+        <f>D60*E60</f>
+      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="85" t="s">
@@ -19702,17 +19706,19 @@
       <c r="A78" s="85" t="s">
         <v>1051</v>
       </c>
-      <c r="B78" s="654" t="s">
+      <c r="B78" s="307" t="s">
         <v>279</v>
       </c>
-      <c r="C78" s="510" t="inlineStr">
+      <c r="C78" s="308" t="inlineStr">
         <is>
           <t>KG</t>
         </is>
       </c>
-      <c r="D78" s="510"/>
-      <c r="E78" s="510"/>
-      <c r="F78" s="524"/>
+      <c r="D78" s="309"/>
+      <c r="E78" s="397"/>
+      <c r="F78" s="398">
+        <f>D78*E78</f>
+      </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="85" t="s">
@@ -19870,17 +19876,19 @@
       <c r="A89" s="85" t="s">
         <v>1061</v>
       </c>
-      <c r="B89" s="654" t="s">
+      <c r="B89" s="307" t="s">
         <v>307</v>
       </c>
-      <c r="C89" s="510" t="inlineStr">
+      <c r="C89" s="308" t="inlineStr">
         <is>
           <t>M²</t>
         </is>
       </c>
-      <c r="D89" s="510"/>
-      <c r="E89" s="510"/>
-      <c r="F89" s="524"/>
+      <c r="D89" s="309"/>
+      <c r="E89" s="397"/>
+      <c r="F89" s="398">
+        <f>D89*E89</f>
+      </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="85" t="s">
@@ -19936,17 +19944,19 @@
       <c r="A94" s="85" t="s">
         <v>1065</v>
       </c>
-      <c r="B94" s="654" t="s">
+      <c r="B94" s="307" t="s">
         <v>315</v>
       </c>
-      <c r="C94" s="510" t="inlineStr">
+      <c r="C94" s="308" t="inlineStr">
         <is>
           <t>M²</t>
         </is>
       </c>
-      <c r="D94" s="510"/>
-      <c r="E94" s="510"/>
-      <c r="F94" s="524"/>
+      <c r="D94" s="309"/>
+      <c r="E94" s="397"/>
+      <c r="F94" s="398">
+        <f>D94*E94</f>
+      </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="85" t="s">
@@ -19986,16 +19996,16 @@
       <c r="A97" s="85" t="s">
         <v>1068</v>
       </c>
-      <c r="B97" s="653" t="s">
+      <c r="B97" s="307" t="s">
         <v>324</v>
       </c>
-      <c r="C97" s="510" t="inlineStr">
+      <c r="C97" s="308" t="inlineStr">
         <is>
           <t>M²</t>
         </is>
       </c>
-      <c r="D97" s="510"/>
-      <c r="E97" s="510"/>
+      <c r="D97" s="309"/>
+      <c r="E97" s="397"/>
       <c r="F97" s="398">
         <f>D97*E97</f>
         <v>0</v>
@@ -20123,16 +20133,16 @@
       <c r="A106" s="85" t="s">
         <v>1076</v>
       </c>
-      <c r="B106" s="653" t="s">
+      <c r="B106" s="307" t="s">
         <v>345</v>
       </c>
-      <c r="C106" s="510" t="inlineStr">
+      <c r="C106" s="308" t="inlineStr">
         <is>
           <t>M²</t>
         </is>
       </c>
-      <c r="D106" s="510"/>
-      <c r="E106" s="510"/>
+      <c r="D106" s="309"/>
+      <c r="E106" s="397"/>
       <c r="F106" s="398">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -20159,17 +20169,19 @@
       <c r="A108" s="85" t="s">
         <v>1078</v>
       </c>
-      <c r="B108" s="654" t="s">
+      <c r="B108" s="307" t="s">
         <v>351</v>
       </c>
-      <c r="C108" s="510" t="inlineStr">
+      <c r="C108" s="308" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="D108" s="510"/>
-      <c r="E108" s="510"/>
-      <c r="F108" s="524"/>
+      <c r="D108" s="309"/>
+      <c r="E108" s="397"/>
+      <c r="F108" s="398">
+        <f>D108*E108</f>
+      </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="86"/>
@@ -20276,16 +20288,16 @@
       <c r="A116" s="85" t="s">
         <v>1085</v>
       </c>
-      <c r="B116" s="653" t="s">
+      <c r="B116" s="307" t="s">
         <v>368</v>
       </c>
-      <c r="C116" s="510" t="inlineStr">
+      <c r="C116" s="308" t="inlineStr">
         <is>
           <t>M²</t>
         </is>
       </c>
-      <c r="D116" s="510"/>
-      <c r="E116" s="510"/>
+      <c r="D116" s="309"/>
+      <c r="E116" s="397"/>
       <c r="F116" s="398">
         <f>D116*E116</f>
         <v>0</v>
@@ -20345,16 +20357,16 @@
       <c r="A121" s="85" t="s">
         <v>1089</v>
       </c>
-      <c r="B121" s="653" t="s">
+      <c r="B121" s="307" t="s">
         <v>376</v>
       </c>
-      <c r="C121" s="510" t="inlineStr">
+      <c r="C121" s="308" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="D121" s="510"/>
-      <c r="E121" s="510"/>
+      <c r="D121" s="309"/>
+      <c r="E121" s="397"/>
       <c r="F121" s="398">
         <f>D121*E121</f>
         <v>0</v>
@@ -20381,17 +20393,19 @@
       <c r="A123" s="85" t="s">
         <v>1091</v>
       </c>
-      <c r="B123" s="654" t="s">
+      <c r="B123" s="307" t="s">
         <v>383</v>
       </c>
-      <c r="C123" s="510" t="inlineStr">
+      <c r="C123" s="308" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="D123" s="510"/>
-      <c r="E123" s="510"/>
-      <c r="F123" s="524"/>
+      <c r="D123" s="309"/>
+      <c r="E123" s="397"/>
+      <c r="F123" s="398">
+        <f>D123*E123</f>
+      </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="85" t="s">
@@ -20481,16 +20495,16 @@
       <c r="A130" s="85" t="s">
         <v>1097</v>
       </c>
-      <c r="B130" s="653" t="s">
+      <c r="B130" s="307" t="s">
         <v>398</v>
       </c>
-      <c r="C130" s="510" t="inlineStr">
+      <c r="C130" s="308" t="inlineStr">
         <is>
           <t>M²</t>
         </is>
       </c>
-      <c r="D130" s="510"/>
-      <c r="E130" s="510"/>
+      <c r="D130" s="309"/>
+      <c r="E130" s="397"/>
       <c r="F130" s="398">
         <f>D130*E130</f>
         <v>0</v>
@@ -20517,17 +20531,19 @@
       <c r="A132" s="85" t="s">
         <v>1099</v>
       </c>
-      <c r="B132" s="654" t="s">
+      <c r="B132" s="307" t="s">
         <v>404</v>
       </c>
-      <c r="C132" s="510" t="inlineStr">
+      <c r="C132" s="308" t="inlineStr">
         <is>
           <t>M²</t>
         </is>
       </c>
-      <c r="D132" s="510"/>
-      <c r="E132" s="510"/>
-      <c r="F132" s="524"/>
+      <c r="D132" s="309"/>
+      <c r="E132" s="397"/>
+      <c r="F132" s="398">
+        <f>D132*E132</f>
+      </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="85" t="s">
@@ -20583,16 +20599,16 @@
       <c r="A137" s="85" t="s">
         <v>1103</v>
       </c>
-      <c r="B137" s="653" t="s">
+      <c r="B137" s="307" t="s">
         <v>412</v>
       </c>
-      <c r="C137" s="510" t="inlineStr">
+      <c r="C137" s="308" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="D137" s="510"/>
-      <c r="E137" s="510"/>
+      <c r="D137" s="309"/>
+      <c r="E137" s="397"/>
       <c r="F137" s="398">
         <f t="shared" ref="F137:F147" si="7">D137*E137</f>
         <v>0</v>
@@ -20619,16 +20635,16 @@
       <c r="A139" s="85" t="s">
         <v>1105</v>
       </c>
-      <c r="B139" s="653" t="s">
+      <c r="B139" s="307" t="s">
         <v>418</v>
       </c>
-      <c r="C139" s="510" t="inlineStr">
+      <c r="C139" s="308" t="inlineStr">
         <is>
           <t>UND</t>
         </is>
       </c>
-      <c r="D139" s="510"/>
-      <c r="E139" s="510"/>
+      <c r="D139" s="309"/>
+      <c r="E139" s="397"/>
       <c r="F139" s="398">
         <f t="shared" si="7"/>
         <v>0</v>

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -16731,7 +16731,6 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="A36:E36"/>
@@ -16743,6 +16742,7 @@
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A31:E31"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="A42:E42"/>
@@ -16761,7 +16761,7 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="B4:C4"/>

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -10531,31 +10531,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -10021,7 +10021,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CO"/>
               </a:p>
@@ -10217,7 +10217,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10308,7 +10308,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10341,7 +10341,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO"/>
         </a:p>
@@ -10736,7 +10736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="42" customWidth="1" style="1223" min="1" max="1"/>
@@ -10836,414 +10836,463 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="1223">
+    <row r="8">
       <c r="A8" s="597" t="inlineStr">
         <is>
+          <t>IDENTIFICACIÓN DEL PROYECTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="99" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+      <c r="B9" s="100" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="99" t="inlineStr">
+        <is>
+          <t>No de Contrato</t>
+        </is>
+      </c>
+      <c r="B10" s="100" t="n"/>
+      <c r="C10" s="99" t="inlineStr">
+        <is>
+          <t>Fecha de Emisión</t>
+        </is>
+      </c>
+      <c r="D10" s="100" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="99" t="inlineStr">
+        <is>
+          <t>Contratista</t>
+        </is>
+      </c>
+      <c r="B11" s="100" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="99" t="inlineStr">
+        <is>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="B12" s="100" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="1223">
+      <c r="A13" s="597" t="inlineStr">
+        <is>
           <t>DATOS GENERALES DEL PROYECTO</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="1223">
-      <c r="A9" s="99" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="1223">
+      <c r="A14" s="99" t="inlineStr">
         <is>
           <t>Número de pisos (torre)</t>
         </is>
       </c>
-      <c r="B9" s="100" t="n"/>
-      <c r="C9" s="593" t="inlineStr">
+      <c r="B14" s="100" t="n"/>
+      <c r="C14" s="593" t="inlineStr">
         <is>
           <t>pisos</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="1223">
-      <c r="A10" s="101" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="1223">
+      <c r="A15" s="101" t="inlineStr">
         <is>
           <t>Número de sótanos (parqueaderos)</t>
         </is>
       </c>
-      <c r="B10" s="102" t="n"/>
-      <c r="C10" s="590" t="inlineStr">
+      <c r="B15" s="102" t="n"/>
+      <c r="C15" s="590" t="inlineStr">
         <is>
           <t>niveles</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="1223">
-      <c r="A11" s="99" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="1223">
+      <c r="A16" s="99" t="inlineStr">
         <is>
           <t>Área del lote</t>
         </is>
       </c>
-      <c r="B11" s="100" t="n"/>
-      <c r="C11" s="593" t="inlineStr">
+      <c r="B16" s="100" t="n"/>
+      <c r="C16" s="593" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="1223">
-      <c r="A12" s="101" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="1223">
+      <c r="A17" s="101" t="inlineStr">
         <is>
           <t>Área construida típica por piso</t>
         </is>
       </c>
-      <c r="B12" s="102" t="n"/>
-      <c r="C12" s="590" t="inlineStr">
+      <c r="B17" s="102" t="n"/>
+      <c r="C17" s="590" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="1223">
-      <c r="A13" s="99" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="1223">
+      <c r="A18" s="99" t="inlineStr">
         <is>
           <t>Área construida - torre (12 pisos)</t>
         </is>
       </c>
-      <c r="B13" s="103">
-        <f>B9*B12</f>
-        <v/>
-      </c>
-      <c r="C13" s="593" t="inlineStr">
+      <c r="B18" s="103">
+        <f>B14*B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="593" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="1223">
-      <c r="A14" s="101" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="1223">
+      <c r="A19" s="101" t="inlineStr">
         <is>
           <t>Área construida - sótanos (2 niveles)</t>
         </is>
       </c>
-      <c r="B14" s="102" t="n"/>
-      <c r="C14" s="590" t="inlineStr">
+      <c r="B19" s="102" t="n"/>
+      <c r="C19" s="590" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="1223">
-      <c r="A15" s="99" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="1223">
+      <c r="A20" s="99" t="inlineStr">
         <is>
           <t>Área cubierta / cuarto de máquinas / tanques</t>
         </is>
       </c>
-      <c r="B15" s="100" t="n"/>
-      <c r="C15" s="593" t="inlineStr">
+      <c r="B20" s="100" t="n"/>
+      <c r="C20" s="593" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="1223">
-      <c r="A16" s="101" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="1223">
+      <c r="A21" s="101" t="inlineStr">
         <is>
           <t>ÁREA TOTAL CONSTRUIDA</t>
         </is>
       </c>
-      <c r="B16" s="104">
-        <f>B13+B14+B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="590" t="inlineStr">
+      <c r="B21" s="104">
+        <f>B18+B19+B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="590" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="1223">
-      <c r="A17" s="99" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="1223">
+      <c r="A22" s="99" t="inlineStr">
         <is>
           <t>Número de apartamentos</t>
         </is>
       </c>
-      <c r="B17" s="100" t="n"/>
-      <c r="C17" s="593" t="inlineStr">
+      <c r="B22" s="100" t="n"/>
+      <c r="C22" s="593" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="1223">
-      <c r="A18" s="101" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="1223">
+      <c r="A23" s="101" t="inlineStr">
         <is>
           <t>Área promedio por apartamento (vendible)</t>
         </is>
       </c>
-      <c r="B18" s="102" t="n"/>
-      <c r="C18" s="590" t="inlineStr">
+      <c r="B23" s="102" t="n"/>
+      <c r="C23" s="590" t="inlineStr">
         <is>
           <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="1223">
-      <c r="A19" s="99" t="inlineStr">
-        <is>
-          <t>Número de parqueaderos</t>
-        </is>
-      </c>
-      <c r="B19" s="100" t="n"/>
-      <c r="C19" s="593" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="1223">
-      <c r="A20" s="101" t="inlineStr">
-        <is>
-          <t>Número de ascensores</t>
-        </is>
-      </c>
-      <c r="B20" s="102" t="n"/>
-      <c r="C20" s="590" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="1223">
-      <c r="A21" s="99" t="inlineStr">
-        <is>
-          <t>Altura total aproximada (sótano a cubierta)</t>
-        </is>
-      </c>
-      <c r="B21" s="100" t="n"/>
-      <c r="C21" s="593" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="592" t="n"/>
-      <c r="B22" s="592" t="n"/>
-      <c r="C22" s="592" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="1223">
-      <c r="A23" s="594" t="inlineStr">
-        <is>
-          <t>PARÁMETROS ECONÓMICOS DEL PRESUPUESTO</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="1223">
       <c r="A24" s="99" t="inlineStr">
         <is>
-          <t>Administración (A)</t>
-        </is>
-      </c>
-      <c r="B24" s="466" t="n">
-        <v>0.1</v>
-      </c>
+          <t>Número de parqueaderos</t>
+        </is>
+      </c>
+      <c r="B24" s="100" t="n"/>
       <c r="C24" s="593" t="inlineStr">
         <is>
-          <t>% s/costo directo</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="1223">
       <c r="A25" s="101" t="inlineStr">
         <is>
-          <t>Imprevistos (I)</t>
-        </is>
-      </c>
-      <c r="B25" s="467" t="n">
-        <v>0.04</v>
-      </c>
+          <t>Número de ascensores</t>
+        </is>
+      </c>
+      <c r="B25" s="102" t="n"/>
       <c r="C25" s="590" t="inlineStr">
         <is>
-          <t>% s/costo directo</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="1223">
       <c r="A26" s="99" t="inlineStr">
         <is>
+          <t>Altura total aproximada (sótano a cubierta)</t>
+        </is>
+      </c>
+      <c r="B26" s="100" t="n"/>
+      <c r="C26" s="593" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="592" t="n"/>
+      <c r="B27" s="592" t="n"/>
+      <c r="C27" s="592" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="1223">
+      <c r="A28" s="594" t="inlineStr">
+        <is>
+          <t>PARÁMETROS ECONÓMICOS DEL PRESUPUESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="1223">
+      <c r="A29" s="99" t="inlineStr">
+        <is>
+          <t>Administración (A)</t>
+        </is>
+      </c>
+      <c r="B29" s="466" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C29" s="593" t="inlineStr">
+        <is>
+          <t>% s/costo directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="1223">
+      <c r="A30" s="101" t="inlineStr">
+        <is>
+          <t>Imprevistos (I)</t>
+        </is>
+      </c>
+      <c r="B30" s="467" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C30" s="590" t="inlineStr">
+        <is>
+          <t>% s/costo directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="1223">
+      <c r="A31" s="99" t="inlineStr">
+        <is>
           <t>Utilidad (U)</t>
         </is>
       </c>
-      <c r="B26" s="466" t="n">
+      <c r="B31" s="466" t="n">
         <v>0.12</v>
       </c>
-      <c r="C26" s="593" t="inlineStr">
+      <c r="C31" s="593" t="inlineStr">
         <is>
           <t>% s/costo directo</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="1223">
-      <c r="A27" s="101" t="inlineStr">
+    <row r="32" ht="15" customHeight="1" s="1223">
+      <c r="A32" s="101" t="inlineStr">
         <is>
           <t>IVA sobre Utilidad</t>
         </is>
       </c>
-      <c r="B27" s="467" t="n">
+      <c r="B32" s="467" t="n">
         <v>0.19</v>
       </c>
-      <c r="C27" s="590" t="inlineStr">
+      <c r="C32" s="590" t="inlineStr">
         <is>
           <t>% s/utilidad (Ley 1943 / práctica AIU en Colombia)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="592" t="n"/>
-      <c r="B28" s="592" t="n"/>
-      <c r="C28" s="592" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="1223">
-      <c r="A29" s="105" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="592" t="n"/>
+      <c r="B33" s="592" t="n"/>
+      <c r="C33" s="592" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="1223">
+      <c r="A34" s="105" t="inlineStr">
         <is>
           <t>AIU TOTAL (A+I+U)</t>
         </is>
       </c>
-      <c r="B29" s="468">
-        <f>B24+B25+B26</f>
-        <v/>
-      </c>
-      <c r="C29" s="592" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="592" t="n"/>
-      <c r="B30" s="592" t="n"/>
-      <c r="C30" s="592" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="1223">
-      <c r="A31" s="594" t="inlineStr">
+      <c r="B34" s="468">
+        <f>B29+B30+B31</f>
+        <v/>
+      </c>
+      <c r="C34" s="592" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="592" t="n"/>
+      <c r="B35" s="592" t="n"/>
+      <c r="C35" s="592" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="1223">
+      <c r="A36" s="594" t="inlineStr">
         <is>
           <t>FUENTES Y NOTAS METODOLÓGICAS</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customFormat="1" customHeight="1" s="202">
-      <c r="A32" s="203" t="inlineStr">
+    <row r="37" ht="15" customFormat="1" customHeight="1" s="202">
+      <c r="A37" s="203" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="B32" s="201" t="n"/>
-      <c r="C32" s="201" t="n"/>
-      <c r="D32" s="201" t="n"/>
-      <c r="E32" s="342">
+      <c r="B37" s="201" t="n"/>
+      <c r="C37" s="201" t="n"/>
+      <c r="D37" s="201" t="n"/>
+      <c r="E37" s="342">
         <f>E4</f>
         <v/>
-      </c>
-    </row>
-    <row r="33" ht="25.5" customHeight="1" s="1223">
-      <c r="A33" s="591" t="inlineStr">
-        <is>
-          <t>1. Precios de referencia investigados para Bogotá D.C., 2026 (2° semestre). Son precios promedio de mercado; cada obra requiere cotización formal con proveedores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="25.5" customHeight="1" s="1223">
-      <c r="A34" s="591" t="inlineStr">
-        <is>
-          <t>2. Rango de costo directo de construcción en Bogotá 2026 según fuentes de mercado: $2.200.000 - $3.800.000 COP/m² (Aliados de Obras, 2026); promedio de estabilización Ene-Abr 2026: ~$3.050.000 COP/m².</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="25.5" customHeight="1" s="1223">
-      <c r="A35" s="591" t="inlineStr">
-        <is>
-          <t>3. Concreto 3000 PSI para estructura con formaletería: referencia ~$868.306 COP/m³ (Listado de Precios Unitarios, Secretaría de Infraestructura / Fidubogotá, ajustado a 2026).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="25.5" customHeight="1" s="1223">
-      <c r="A36" s="591" t="inlineStr">
-        <is>
-          <t>4. Acero de refuerzo figurado e instalado: referencia ~$6.500-7.000 COP/kg (Comando Construcciones, 2026; incremento por alza del 23,7% en el SMMLV 2026 según DANE-ICOCED).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="25.5" customHeight="1" s="1223">
-      <c r="A37" s="591" t="inlineStr">
-        <is>
-          <t>5. Ascensor eléctrico para edificio de 10+ pisos, alta velocidad, instalado: $450M-$750M COP por unidad (OTA Vertical, 2026). Se tomó valor medio.</t>
-        </is>
       </c>
     </row>
     <row r="38" ht="25.5" customHeight="1" s="1223">
       <c r="A38" s="591" t="inlineStr">
         <is>
-          <t>6. Índice de Costos de la Construcción de Edificaciones (ICOCED-DANE): variación interanual ene.2025-ene.2026 de +8,7% en Bogotá, impulsada por incremento salarial.</t>
+          <t>1. Precios de referencia investigados para Bogotá D.C., 2026 (2° semestre). Son precios promedio de mercado; cada obra requiere cotización formal con proveedores.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="25.5" customHeight="1" s="1223">
       <c r="A39" s="591" t="inlineStr">
         <is>
-          <t>7. AIU recomendado para edificaciones en Colombia: 25%-30% sobre costos directos (Administración 10-12%, Imprevistos 3-5%, Utilidad 10-15%). Se usó 26% (10%+4%+12%).</t>
+          <t>2. Rango de costo directo de construcción en Bogotá 2026 según fuentes de mercado: $2.200.000 - $3.800.000 COP/m² (Aliados de Obras, 2026); promedio de estabilización Ene-Abr 2026: ~$3.050.000 COP/m².</t>
         </is>
       </c>
     </row>
     <row r="40" ht="25.5" customHeight="1" s="1223">
       <c r="A40" s="591" t="inlineStr">
         <is>
-          <t>8. IVA: en Colombia, para contratos de obra el IVA se causa típicamente sobre el componente de Utilidad (AIU), no sobre el costo directo de materiales de construcción de vivienda (parcialmente exentos). Verificar con contador/tributarista para el régimen aplicable a cada proyecto.</t>
+          <t>3. Concreto 3000 PSI para estructura con formaletería: referencia ~$868.306 COP/m³ (Listado de Precios Unitarios, Secretaría de Infraestructura / Fidubogotá, ajustado a 2026).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="25.5" customHeight="1" s="1223">
       <c r="A41" s="591" t="inlineStr">
         <is>
-          <t>9. Este documento es una ESTIMACIÓN DE PRESUPUESTO (clase de precisión ±15-20%), útil para prefactibilidad y anteproyecto. No reemplaza un presupuesto detallado con cubicación (cantidades de obra) tomada de planos definitivos y cotizaciones de proveedores.</t>
+          <t>4. Acero de refuerzo figurado e instalado: referencia ~$6.500-7.000 COP/kg (Comando Construcciones, 2026; incremento por alza del 23,7% en el SMMLV 2026 según DANE-ICOCED).</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25.5" customHeight="1" s="1223">
       <c r="A42" s="591" t="inlineStr">
         <is>
+          <t>5. Ascensor eléctrico para edificio de 10+ pisos, alta velocidad, instalado: $450M-$750M COP por unidad (OTA Vertical, 2026). Se tomó valor medio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="25.5" customHeight="1" s="1223">
+      <c r="A43" s="591" t="inlineStr">
+        <is>
+          <t>6. Índice de Costos de la Construcción de Edificaciones (ICOCED-DANE): variación interanual ene.2025-ene.2026 de +8,7% en Bogotá, impulsada por incremento salarial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="25.5" customHeight="1" s="1223">
+      <c r="A44" s="591" t="inlineStr">
+        <is>
+          <t>7. AIU recomendado para edificaciones en Colombia: 25%-30% sobre costos directos (Administración 10-12%, Imprevistos 3-5%, Utilidad 10-15%). Se usó 26% (10%+4%+12%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="25.5" customHeight="1" s="1223">
+      <c r="A45" s="591" t="inlineStr">
+        <is>
+          <t>8. IVA: en Colombia, para contratos de obra el IVA se causa típicamente sobre el componente de Utilidad (AIU), no sobre el costo directo de materiales de construcción de vivienda (parcialmente exentos). Verificar con contador/tributarista para el régimen aplicable a cada proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="25.5" customHeight="1" s="1223">
+      <c r="A46" s="591" t="inlineStr">
+        <is>
+          <t>9. Este documento es una ESTIMACIÓN DE PRESUPUESTO (clase de precisión ±15-20%), útil para prefactibilidad y anteproyecto. No reemplaza un presupuesto detallado con cubicación (cantidades de obra) tomada de planos definitivos y cotizaciones de proveedores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="25.5" customHeight="1" s="1223">
+      <c r="A47" s="591" t="inlineStr">
+        <is>
           <t>10. Celdas en color AZUL = dato de entrada editable. Celdas en NEGRO = fórmula (se recalculan automáticamente). Cambie cantidades y precios unitarios en la hoja 'Presupuesto' según su proyecto real.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="43">
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A45:E45"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C11:E11"/>
     <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C23:E23"/>
     <mergeCell ref="A41:E41"/>
     <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="C32:E32"/>
     <mergeCell ref="C19:E19"/>
+    <mergeCell ref="B12:E12"/>
     <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A33:E33"/>
     <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B11:E11"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A8:E8"/>
     <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C34:E34"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C24:E24"/>
-    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="C33:E33"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="C29:E29"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -15956,7 +16005,7 @@
       <c r="C241" s="681" t="n"/>
       <c r="D241" s="681" t="n"/>
       <c r="E241" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$24</f>
+        <f>'Ficha Técnica del Proyecto'!$B$29</f>
         <v/>
       </c>
       <c r="F241" s="482">
@@ -15974,7 +16023,7 @@
       <c r="C242" s="681" t="n"/>
       <c r="D242" s="681" t="n"/>
       <c r="E242" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$25</f>
+        <f>'Ficha Técnica del Proyecto'!$B$30</f>
         <v/>
       </c>
       <c r="F242" s="482">
@@ -15992,7 +16041,7 @@
       <c r="C243" s="681" t="n"/>
       <c r="D243" s="681" t="n"/>
       <c r="E243" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$26</f>
+        <f>'Ficha Técnica del Proyecto'!$B$31</f>
         <v/>
       </c>
       <c r="F243" s="482">
@@ -16040,7 +16089,7 @@
       <c r="C246" s="681" t="n"/>
       <c r="D246" s="681" t="n"/>
       <c r="E246" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$27</f>
+        <f>'Ficha Técnica del Proyecto'!$B$32</f>
         <v/>
       </c>
       <c r="F246" s="482">
@@ -16105,7 +16154,7 @@
       <c r="D251" s="91" t="n"/>
       <c r="E251" s="91" t="n"/>
       <c r="F251" s="484">
-        <f>F239/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>F239/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
     </row>
@@ -16120,7 +16169,7 @@
       <c r="D252" s="93" t="n"/>
       <c r="E252" s="93" t="n"/>
       <c r="F252" s="485">
-        <f>F248/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>F248/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
     </row>
@@ -16427,7 +16476,7 @@
         <v/>
       </c>
       <c r="E12" s="686">
-        <f>C12/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C12/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F12" s="605" t="n"/>
@@ -16452,7 +16501,7 @@
         <v/>
       </c>
       <c r="E13" s="686">
-        <f>C13/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C13/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F13" s="605" t="n"/>
@@ -16477,7 +16526,7 @@
         <v/>
       </c>
       <c r="E14" s="686">
-        <f>C14/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C14/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F14" s="605" t="n"/>
@@ -16502,7 +16551,7 @@
         <v/>
       </c>
       <c r="E15" s="686">
-        <f>C15/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C15/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F15" s="605" t="n"/>
@@ -16527,7 +16576,7 @@
         <v/>
       </c>
       <c r="E16" s="686">
-        <f>C16/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C16/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F16" s="605" t="n"/>
@@ -16552,7 +16601,7 @@
         <v/>
       </c>
       <c r="E17" s="686">
-        <f>C17/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C17/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F17" s="605" t="n"/>
@@ -16577,7 +16626,7 @@
         <v/>
       </c>
       <c r="E18" s="686">
-        <f>C18/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C18/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F18" s="605" t="n"/>
@@ -16602,7 +16651,7 @@
         <v/>
       </c>
       <c r="E19" s="686">
-        <f>C19/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C19/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F19" s="605" t="n"/>
@@ -16627,7 +16676,7 @@
         <v/>
       </c>
       <c r="E20" s="686">
-        <f>C20/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C20/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F20" s="605" t="n"/>
@@ -16652,7 +16701,7 @@
         <v/>
       </c>
       <c r="E21" s="686">
-        <f>C21/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C21/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F21" s="605" t="n"/>
@@ -16677,7 +16726,7 @@
         <v/>
       </c>
       <c r="E22" s="686">
-        <f>C22/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C22/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F22" s="605" t="n"/>
@@ -16702,7 +16751,7 @@
         <v/>
       </c>
       <c r="E23" s="686">
-        <f>C23/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C23/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F23" s="605" t="n"/>
@@ -16727,7 +16776,7 @@
         <v/>
       </c>
       <c r="E24" s="686">
-        <f>C24/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C24/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F24" s="605" t="n"/>
@@ -16752,7 +16801,7 @@
         <v/>
       </c>
       <c r="E25" s="686">
-        <f>C25/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C25/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F25" s="605" t="n"/>
@@ -16777,7 +16826,7 @@
         <v/>
       </c>
       <c r="E26" s="686">
-        <f>C26/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C26/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F26" s="605" t="n"/>
@@ -16802,7 +16851,7 @@
         <v/>
       </c>
       <c r="E27" s="686">
-        <f>C27/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C27/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F27" s="605" t="n"/>
@@ -16827,7 +16876,7 @@
         <v/>
       </c>
       <c r="E28" s="686">
-        <f>C28/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C28/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F28" s="605" t="n"/>
@@ -16852,7 +16901,7 @@
         <v/>
       </c>
       <c r="E29" s="686">
-        <f>C29/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C29/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F29" s="605" t="n"/>
@@ -16877,7 +16926,7 @@
         <v/>
       </c>
       <c r="E30" s="686">
-        <f>C30/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C30/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F30" s="605" t="n"/>
@@ -16902,7 +16951,7 @@
         <v/>
       </c>
       <c r="E31" s="686">
-        <f>C31/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C31/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F31" s="605" t="n"/>
@@ -16927,7 +16976,7 @@
         <v/>
       </c>
       <c r="E32" s="686">
-        <f>C32/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C32/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F32" s="605" t="n"/>
@@ -16952,7 +17001,7 @@
         <v/>
       </c>
       <c r="E33" s="687">
-        <f>C33/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C33/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F33" s="543" t="n"/>
@@ -16973,7 +17022,7 @@
         <v/>
       </c>
       <c r="E34" s="695">
-        <f>C34/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C34/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="F34" s="605" t="n"/>
@@ -17073,7 +17122,7 @@
         </is>
       </c>
       <c r="C42" s="491">
-        <f>C40/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>C40/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
       <c r="D42" s="5" t="n"/>

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
   </numFmts>
-  <fonts count="168">
+  <fonts count="169">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1231,6 +1231,11 @@
       <color rgb="FF8A8F99"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="76">
     <fill>
@@ -6575,7 +6580,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1307">
+  <cellXfs count="1308">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9800,6 +9805,9 @@
     </xf>
     <xf numFmtId="165" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10849,7 +10857,7 @@
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B9" s="100" t="n"/>
+      <c r="B9" s="1307" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="99" t="inlineStr">
@@ -10857,13 +10865,13 @@
           <t>No de Contrato</t>
         </is>
       </c>
-      <c r="B10" s="100" t="n"/>
+      <c r="B10" s="1307" t="n"/>
       <c r="C10" s="99" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="D10" s="100" t="n"/>
+      <c r="D10" s="1307" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="99" t="inlineStr">
@@ -10871,7 +10879,7 @@
           <t>Contratista</t>
         </is>
       </c>
-      <c r="B11" s="100" t="n"/>
+      <c r="B11" s="1307" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="99" t="inlineStr">
@@ -10879,7 +10887,7 @@
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="B12" s="100" t="n"/>
+      <c r="B12" s="1307" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="1223">
       <c r="A13" s="597" t="inlineStr">
@@ -11284,13 +11292,13 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
   </mergeCells>
@@ -11519,12 +11527,12 @@
       </c>
       <c r="B15" s="373" t="inlineStr">
         <is>
-          <t>Replanteo general de ejes y niveles</t>
+          <t>Localización y Replanteo</t>
         </is>
       </c>
       <c r="C15" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D15" s="262" t="n"/>

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
   </numFmts>
-  <fonts count="169">
+  <fonts count="170">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1236,6 +1236,10 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <color rgb="008A8F99"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="76">
     <fill>
@@ -6580,7 +6584,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1308">
+  <cellXfs count="1309">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9809,6 +9813,7 @@
     <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11315,7 +11320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F258"/>
+  <dimension ref="A1:F259"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" style="586" min="1" max="1"/>
@@ -12643,76 +12648,76 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="82" t="n"/>
-      <c r="B68" s="674" t="inlineStr">
+      <c r="A68" s="81" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="B68" s="373" t="inlineStr">
+        <is>
+          <t>Concreto premezclado o de planta (suministro)</t>
+        </is>
+      </c>
+      <c r="C68" s="261" t="inlineStr">
+        <is>
+          <t>M³</t>
+        </is>
+      </c>
+      <c r="D68" s="262" t="n"/>
+      <c r="E68" s="477" t="n"/>
+      <c r="F68" s="478">
+        <f>D68*E68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="82" t="n"/>
+      <c r="B69" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 4 - ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C68" s="530" t="n"/>
-      <c r="D68" s="530" t="n"/>
-      <c r="E68" s="530" t="n"/>
-      <c r="F68" s="479">
-        <f>SUM(F52:F67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="83" t="n"/>
-      <c r="B69" s="681" t="n"/>
-      <c r="C69" s="681" t="n"/>
-      <c r="D69" s="681" t="n"/>
-      <c r="E69" s="681" t="n"/>
-      <c r="F69" s="675" t="n"/>
+      <c r="C69" s="530" t="n"/>
+      <c r="D69" s="530" t="n"/>
+      <c r="E69" s="530" t="n"/>
+      <c r="F69" s="479">
+        <f>SUM(F51:F68)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="185" t="inlineStr">
+      <c r="A70" s="83" t="n"/>
+      <c r="B70" s="681" t="n"/>
+      <c r="C70" s="681" t="n"/>
+      <c r="D70" s="681" t="n"/>
+      <c r="E70" s="681" t="n"/>
+      <c r="F70" s="675" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="185" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B70" s="680" t="inlineStr">
+      <c r="B71" s="680" t="inlineStr">
         <is>
           <t>MAMPOSTERÍA</t>
         </is>
       </c>
-      <c r="C70" s="581" t="n"/>
-      <c r="D70" s="581" t="n"/>
-      <c r="E70" s="581" t="n"/>
-      <c r="F70" s="582" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="81" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="B71" s="373" t="inlineStr">
-        <is>
-          <t>Mampostería en bloque de concreto</t>
-        </is>
-      </c>
-      <c r="C71" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D71" s="262" t="n"/>
-      <c r="E71" s="477" t="n"/>
-      <c r="F71" s="478">
-        <f>D71*E71</f>
-        <v/>
-      </c>
+      <c r="C71" s="581" t="n"/>
+      <c r="D71" s="581" t="n"/>
+      <c r="E71" s="581" t="n"/>
+      <c r="F71" s="582" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="81" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B72" s="373" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo</t>
+          <t>Mampostería en bloque de concreto</t>
         </is>
       </c>
       <c r="C72" s="261" t="inlineStr">
@@ -12730,12 +12735,12 @@
     <row r="73">
       <c r="A73" s="81" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B73" s="373" t="inlineStr">
         <is>
-          <t>Mampostería estructural</t>
+          <t>Mampostería en ladrillo</t>
         </is>
       </c>
       <c r="C73" s="261" t="inlineStr">
@@ -12753,12 +12758,12 @@
     <row r="74">
       <c r="A74" s="81" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B74" s="373" t="inlineStr">
         <is>
-          <t>Muros en sistema liviano / drywall</t>
+          <t>Mampostería estructural</t>
         </is>
       </c>
       <c r="C74" s="261" t="inlineStr">
@@ -12776,17 +12781,17 @@
     <row r="75">
       <c r="A75" s="81" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="B75" s="373" t="inlineStr">
         <is>
-          <t>Dinteles sobre vanos</t>
+          <t>Muros en sistema liviano / drywall</t>
         </is>
       </c>
       <c r="C75" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D75" s="262" t="n"/>
@@ -12799,12 +12804,12 @@
     <row r="76">
       <c r="A76" s="81" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="B76" s="373" t="inlineStr">
         <is>
-          <t>Alfajías y remates</t>
+          <t>Dinteles sobre vanos</t>
         </is>
       </c>
       <c r="C76" s="261" t="inlineStr">
@@ -12822,17 +12827,17 @@
     <row r="77">
       <c r="A77" s="81" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="B77" s="373" t="inlineStr">
         <is>
-          <t>Anclajes y refuerzos de mampostería</t>
+          <t>Alfajías y remates</t>
         </is>
       </c>
       <c r="C77" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D77" s="262" t="n"/>
@@ -12845,17 +12850,17 @@
     <row r="78">
       <c r="A78" s="81" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="B78" s="373" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
+          <t>Anclajes y refuerzos de mampostería</t>
         </is>
       </c>
       <c r="C78" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D78" s="262" t="n"/>
@@ -12868,12 +12873,12 @@
     <row r="79">
       <c r="A79" s="81" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="B79" s="373" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
+          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
         </is>
       </c>
       <c r="C79" s="261" t="inlineStr">
@@ -12889,74 +12894,76 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="82" t="n"/>
-      <c r="B80" s="674" t="inlineStr">
+      <c r="A80" s="81" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="B80" s="373" t="inlineStr">
+        <is>
+          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
+        </is>
+      </c>
+      <c r="C80" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D80" s="262" t="n"/>
+      <c r="E80" s="477" t="n"/>
+      <c r="F80" s="478">
+        <f>D80*E80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="82" t="n"/>
+      <c r="B81" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 5 - MAMPOSTERÍA</t>
         </is>
       </c>
-      <c r="C80" s="530" t="n"/>
-      <c r="D80" s="530" t="n"/>
-      <c r="E80" s="530" t="n"/>
-      <c r="F80" s="479">
-        <f>SUM(F71:F79)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="83" t="n"/>
-      <c r="B81" s="681" t="n"/>
       <c r="C81" s="530" t="n"/>
       <c r="D81" s="530" t="n"/>
       <c r="E81" s="530" t="n"/>
-      <c r="F81" s="675" t="n"/>
+      <c r="F81" s="479">
+        <f>SUM(F72:F80)</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="185" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B82" s="682" t="inlineStr">
-        <is>
-          <t>CUBIERTAS</t>
-        </is>
-      </c>
+      <c r="A82" s="83" t="n"/>
+      <c r="B82" s="681" t="n"/>
       <c r="C82" s="530" t="n"/>
       <c r="D82" s="530" t="n"/>
       <c r="E82" s="530" t="n"/>
-      <c r="F82" s="530" t="n"/>
+      <c r="F82" s="675" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="81" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B83" s="374" t="inlineStr">
-        <is>
-          <t>Estructura metálica o de madera para cubierta</t>
-        </is>
-      </c>
-      <c r="C83" s="261" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="F83">
-        <f>D83*E83</f>
-        <v/>
-      </c>
+      <c r="A83" s="185" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B83" s="682" t="inlineStr">
+        <is>
+          <t>CUBIERTAS</t>
+        </is>
+      </c>
+      <c r="C83" s="530" t="n"/>
+      <c r="D83" s="530" t="n"/>
+      <c r="E83" s="530" t="n"/>
+      <c r="F83" s="530" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="81" t="inlineStr">
         <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="B84" s="373" t="inlineStr">
-        <is>
-          <t>Cerchas y elementos estructurales</t>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B84" s="374" t="inlineStr">
+        <is>
+          <t>Estructura metálica o de madera para cubierta</t>
         </is>
       </c>
       <c r="C84" s="261" t="inlineStr">
@@ -12964,9 +12971,7 @@
           <t>KG</t>
         </is>
       </c>
-      <c r="D84" s="262" t="n"/>
-      <c r="E84" s="477" t="n"/>
-      <c r="F84" s="478">
+      <c r="F84">
         <f>D84*E84</f>
         <v/>
       </c>
@@ -12974,17 +12979,17 @@
     <row r="85">
       <c r="A85" s="81" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B85" s="373" t="inlineStr">
         <is>
-          <t>Suministro e instalación de teja</t>
+          <t>Cerchas y elementos estructurales</t>
         </is>
       </c>
       <c r="C85" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D85" s="262" t="n"/>
@@ -12997,12 +13002,12 @@
     <row r="86">
       <c r="A86" s="81" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B86" s="373" t="inlineStr">
         <is>
-          <t>Impermeabilización de cubierta</t>
+          <t>Suministro e instalación de teja</t>
         </is>
       </c>
       <c r="C86" s="261" t="inlineStr">
@@ -13020,12 +13025,12 @@
     <row r="87">
       <c r="A87" s="81" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="B87" s="373" t="inlineStr">
         <is>
-          <t>Aislamiento térmico/acústico</t>
+          <t>Impermeabilización de cubierta</t>
         </is>
       </c>
       <c r="C87" s="261" t="inlineStr">
@@ -13043,17 +13048,17 @@
     <row r="88">
       <c r="A88" s="81" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="B88" s="373" t="inlineStr">
         <is>
-          <t>Canales de aguas lluvias</t>
+          <t>Aislamiento térmico/acústico</t>
         </is>
       </c>
       <c r="C88" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D88" s="262" t="n"/>
@@ -13066,12 +13071,12 @@
     <row r="89">
       <c r="A89" s="81" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="B89" s="373" t="inlineStr">
         <is>
-          <t>Bajantes de aguas lluvias</t>
+          <t>Canales de aguas lluvias</t>
         </is>
       </c>
       <c r="C89" s="261" t="inlineStr">
@@ -13089,17 +13094,17 @@
     <row r="90">
       <c r="A90" s="81" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="B90" s="373" t="inlineStr">
         <is>
-          <t>Cielo raso Dry Wall</t>
+          <t>Bajantes de aguas lluvias</t>
         </is>
       </c>
       <c r="C90" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D90" s="262" t="n"/>
@@ -13112,12 +13117,12 @@
     <row r="91">
       <c r="A91" s="81" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="B91" s="373" t="inlineStr">
         <is>
-          <t>Cielo raso en lámina acústica de fibra mineral</t>
+          <t>Cielo raso Dry Wall</t>
         </is>
       </c>
       <c r="C91" s="261" t="inlineStr">
@@ -13133,76 +13138,76 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="82" t="n"/>
-      <c r="B92" s="674" t="inlineStr">
+      <c r="A92" s="81" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="B92" s="373" t="inlineStr">
+        <is>
+          <t>Cielo raso en lámina acústica de fibra mineral</t>
+        </is>
+      </c>
+      <c r="C92" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D92" s="262" t="n"/>
+      <c r="E92" s="477" t="n"/>
+      <c r="F92" s="478">
+        <f>D92*E92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="82" t="n"/>
+      <c r="B93" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 6 - CUBIERTAS</t>
         </is>
       </c>
-      <c r="C92" s="530" t="n"/>
-      <c r="D92" s="530" t="n"/>
-      <c r="E92" s="530" t="n"/>
-      <c r="F92" s="479">
-        <f>SUM(F83:F91)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="83" t="n"/>
-      <c r="B93" s="681" t="n"/>
-      <c r="C93" s="681" t="n"/>
-      <c r="D93" s="681" t="n"/>
-      <c r="E93" s="681" t="n"/>
-      <c r="F93" s="675" t="n"/>
+      <c r="C93" s="530" t="n"/>
+      <c r="D93" s="530" t="n"/>
+      <c r="E93" s="530" t="n"/>
+      <c r="F93" s="479">
+        <f>SUM(F84:F92)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="185" t="inlineStr">
+      <c r="A94" s="83" t="n"/>
+      <c r="B94" s="681" t="n"/>
+      <c r="C94" s="681" t="n"/>
+      <c r="D94" s="681" t="n"/>
+      <c r="E94" s="681" t="n"/>
+      <c r="F94" s="675" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="185" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B94" s="677" t="inlineStr">
+      <c r="B95" s="677" t="inlineStr">
         <is>
           <t>IMPERMEABILIZACIONES</t>
         </is>
       </c>
-      <c r="C94" s="530" t="n"/>
-      <c r="D94" s="530" t="n"/>
-      <c r="E94" s="530" t="n"/>
-      <c r="F94" s="530" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="81" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="B95" s="373" t="inlineStr">
-        <is>
-          <t>Impermeabilización de losas y terrazas</t>
-        </is>
-      </c>
-      <c r="C95" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D95" s="262" t="n"/>
-      <c r="E95" s="477" t="n"/>
-      <c r="F95" s="478">
-        <f>D95*E95</f>
-        <v/>
-      </c>
+      <c r="C95" s="530" t="n"/>
+      <c r="D95" s="530" t="n"/>
+      <c r="E95" s="530" t="n"/>
+      <c r="F95" s="530" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="81" t="inlineStr">
         <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B96" s="374" t="inlineStr">
-        <is>
-          <t>Impermeabilización de muros</t>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="B96" s="373" t="inlineStr">
+        <is>
+          <t>Impermeabilización de losas y terrazas</t>
         </is>
       </c>
       <c r="C96" s="261" t="inlineStr">
@@ -13210,7 +13215,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="D96" s="262" t="n"/>
+      <c r="E96" s="477" t="n"/>
+      <c r="F96" s="478">
         <f>D96*E96</f>
         <v/>
       </c>
@@ -13218,12 +13225,12 @@
     <row r="97">
       <c r="A97" s="81" t="inlineStr">
         <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="B97" s="373" t="inlineStr">
-        <is>
-          <t>Impermeabilización de zonas húmedas</t>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B97" s="374" t="inlineStr">
+        <is>
+          <t>Impermeabilización de muros</t>
         </is>
       </c>
       <c r="C97" s="261" t="inlineStr">
@@ -13231,9 +13238,7 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D97" s="262" t="n"/>
-      <c r="E97" s="477" t="n"/>
-      <c r="F97" s="478">
+      <c r="F97">
         <f>D97*E97</f>
         <v/>
       </c>
@@ -13241,12 +13246,12 @@
     <row r="98">
       <c r="A98" s="81" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B98" s="373" t="inlineStr">
         <is>
-          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
+          <t>Impermeabilización de zonas húmedas</t>
         </is>
       </c>
       <c r="C98" s="261" t="inlineStr">
@@ -13262,74 +13267,76 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="82" t="n"/>
-      <c r="B99" s="674" t="inlineStr">
+      <c r="A99" s="81" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="B99" s="373" t="inlineStr">
+        <is>
+          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
+        </is>
+      </c>
+      <c r="C99" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D99" s="262" t="n"/>
+      <c r="E99" s="477" t="n"/>
+      <c r="F99" s="478">
+        <f>D99*E99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="82" t="n"/>
+      <c r="B100" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 7 - IMPERMEABILIZACIONES</t>
         </is>
       </c>
-      <c r="C99" s="530" t="n"/>
-      <c r="D99" s="530" t="n"/>
-      <c r="E99" s="530" t="n"/>
-      <c r="F99" s="479">
-        <f>SUM(F95:F98)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="83" t="n"/>
-      <c r="B100" s="681" t="n"/>
       <c r="C100" s="530" t="n"/>
       <c r="D100" s="530" t="n"/>
       <c r="E100" s="530" t="n"/>
-      <c r="F100" s="675" t="n"/>
+      <c r="F100" s="479">
+        <f>SUM(F96:F99)</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="185" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B101" s="677" t="inlineStr">
-        <is>
-          <t>PAÑETES Y REVOQUES</t>
-        </is>
-      </c>
+      <c r="A101" s="83" t="n"/>
+      <c r="B101" s="681" t="n"/>
       <c r="C101" s="530" t="n"/>
       <c r="D101" s="530" t="n"/>
       <c r="E101" s="530" t="n"/>
-      <c r="F101" s="530" t="n"/>
+      <c r="F101" s="675" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="81" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="B102" s="374" t="inlineStr">
-        <is>
-          <t>Pañete / revoque interior</t>
-        </is>
-      </c>
-      <c r="C102" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="F102">
-        <f>D102*E102</f>
-        <v/>
-      </c>
+      <c r="A102" s="185" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B102" s="677" t="inlineStr">
+        <is>
+          <t>PAÑETES Y REVOQUES</t>
+        </is>
+      </c>
+      <c r="C102" s="530" t="n"/>
+      <c r="D102" s="530" t="n"/>
+      <c r="E102" s="530" t="n"/>
+      <c r="F102" s="530" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="81" t="inlineStr">
         <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="B103" s="373" t="inlineStr">
-        <is>
-          <t>Pañete / revoque exterior</t>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B103" s="374" t="inlineStr">
+        <is>
+          <t>Pañete / revoque interior</t>
         </is>
       </c>
       <c r="C103" s="261" t="inlineStr">
@@ -13337,9 +13344,7 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D103" s="262" t="n"/>
-      <c r="E103" s="477" t="n"/>
-      <c r="F103" s="478">
+      <c r="F103">
         <f>D103*E103</f>
         <v/>
       </c>
@@ -13347,12 +13352,12 @@
     <row r="104">
       <c r="A104" s="81" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="B104" s="373" t="inlineStr">
         <is>
-          <t>Pañete impermeabilizado</t>
+          <t>Pañete / revoque exterior</t>
         </is>
       </c>
       <c r="C104" s="261" t="inlineStr">
@@ -13370,12 +13375,12 @@
     <row r="105">
       <c r="A105" s="81" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="B105" s="373" t="inlineStr">
         <is>
-          <t>Estuco plástico o tradicional</t>
+          <t>Pañete impermeabilizado</t>
         </is>
       </c>
       <c r="C105" s="261" t="inlineStr">
@@ -13383,82 +13388,82 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D105" s="262" t="n"/>
+      <c r="E105" s="477" t="n"/>
       <c r="F105" s="478">
         <f>D105*E105</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="82" t="n"/>
-      <c r="B106" s="674" t="inlineStr">
+      <c r="A106" s="81" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="B106" s="373" t="inlineStr">
+        <is>
+          <t>Estuco plástico o tradicional</t>
+        </is>
+      </c>
+      <c r="C106" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F106" s="478">
+        <f>D106*E106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="82" t="n"/>
+      <c r="B107" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 8 - PAÑETES Y REVOQUES</t>
         </is>
       </c>
-      <c r="C106" s="530" t="n"/>
-      <c r="D106" s="530" t="n"/>
-      <c r="E106" s="530" t="n"/>
-      <c r="F106" s="479">
-        <f>SUM(F102:F105)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="83" t="n"/>
-      <c r="B107" s="675" t="n"/>
       <c r="C107" s="530" t="n"/>
       <c r="D107" s="530" t="n"/>
       <c r="E107" s="530" t="n"/>
-      <c r="F107" s="579" t="n"/>
+      <c r="F107" s="479">
+        <f>SUM(F103:F106)</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="185" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B108" s="677" t="inlineStr">
-        <is>
-          <t>PISOS Y ENCHAPES</t>
-        </is>
-      </c>
+      <c r="A108" s="83" t="n"/>
+      <c r="B108" s="675" t="n"/>
       <c r="C108" s="530" t="n"/>
       <c r="D108" s="530" t="n"/>
       <c r="E108" s="530" t="n"/>
-      <c r="F108" s="530" t="n"/>
+      <c r="F108" s="579" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="81" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="B109" s="373" t="inlineStr">
-        <is>
-          <t>Mortero de nivelación</t>
-        </is>
-      </c>
-      <c r="C109" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D109" s="262" t="n"/>
-      <c r="E109" s="477" t="n"/>
-      <c r="F109" s="478">
-        <f>D109*E109</f>
-        <v/>
-      </c>
+      <c r="A109" s="185" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B109" s="677" t="inlineStr">
+        <is>
+          <t>PISOS Y ENCHAPES</t>
+        </is>
+      </c>
+      <c r="C109" s="530" t="n"/>
+      <c r="D109" s="530" t="n"/>
+      <c r="E109" s="530" t="n"/>
+      <c r="F109" s="530" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="81" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="B110" s="373" t="inlineStr">
         <is>
-          <t>Piso cerámico</t>
+          <t>Mortero de nivelación</t>
         </is>
       </c>
       <c r="C110" s="261" t="inlineStr">
@@ -13476,12 +13481,12 @@
     <row r="111">
       <c r="A111" s="81" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="B111" s="373" t="inlineStr">
         <is>
-          <t>Piso en porcelanato</t>
+          <t>Piso cerámico</t>
         </is>
       </c>
       <c r="C111" s="261" t="inlineStr">
@@ -13499,12 +13504,12 @@
     <row r="112">
       <c r="A112" s="81" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="B112" s="373" t="inlineStr">
         <is>
-          <t>Piso vinílico</t>
+          <t>Piso en porcelanato</t>
         </is>
       </c>
       <c r="C112" s="261" t="inlineStr">
@@ -13522,12 +13527,12 @@
     <row r="113">
       <c r="A113" s="81" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="B113" s="373" t="inlineStr">
         <is>
-          <t>Piso laminado</t>
+          <t>Piso vinílico</t>
         </is>
       </c>
       <c r="C113" s="261" t="inlineStr">
@@ -13545,12 +13550,12 @@
     <row r="114">
       <c r="A114" s="81" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="B114" s="373" t="inlineStr">
         <is>
-          <t>Enchape cerámico en muros</t>
+          <t>Piso laminado</t>
         </is>
       </c>
       <c r="C114" s="261" t="inlineStr">
@@ -13558,6 +13563,8 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D114" s="262" t="n"/>
+      <c r="E114" s="477" t="n"/>
       <c r="F114" s="478">
         <f>D114*E114</f>
         <v/>
@@ -13566,21 +13573,19 @@
     <row r="115">
       <c r="A115" s="81" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="B115" s="373" t="inlineStr">
         <is>
-          <t>Guardaescoba</t>
+          <t>Enchape cerámico en muros</t>
         </is>
       </c>
       <c r="C115" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D115" s="262" t="n"/>
-      <c r="E115" s="477" t="n"/>
+          <t>M²</t>
+        </is>
+      </c>
       <c r="F115" s="478">
         <f>D115*E115</f>
         <v/>
@@ -13589,12 +13594,12 @@
     <row r="116">
       <c r="A116" s="81" t="inlineStr">
         <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="B116" s="374" t="inlineStr">
-        <is>
-          <t>Juntas de dilatación / construcción</t>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="B116" s="373" t="inlineStr">
+        <is>
+          <t>Guardaescoba</t>
         </is>
       </c>
       <c r="C116" s="261" t="inlineStr">
@@ -13602,7 +13607,9 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="F116">
+      <c r="D116" s="262" t="n"/>
+      <c r="E116" s="477" t="n"/>
+      <c r="F116" s="478">
         <f>D116*E116</f>
         <v/>
       </c>
@@ -13610,17 +13617,17 @@
     <row r="117">
       <c r="A117" s="81" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="B117" s="374" t="inlineStr">
         <is>
-          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
+          <t>Juntas de dilatación / construcción</t>
         </is>
       </c>
       <c r="C117" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F117">
@@ -13631,12 +13638,12 @@
     <row r="118">
       <c r="A118" s="81" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="B118" s="374" t="inlineStr">
         <is>
-          <t>Baldosa de granito</t>
+          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
         </is>
       </c>
       <c r="C118" s="261" t="inlineStr">
@@ -13652,12 +13659,12 @@
     <row r="119">
       <c r="A119" s="81" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="B119" s="374" t="inlineStr">
         <is>
-          <t>Enchape en granito pulido</t>
+          <t>Baldosa de granito</t>
         </is>
       </c>
       <c r="C119" s="261" t="inlineStr">
@@ -13671,76 +13678,74 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="82" t="n"/>
-      <c r="B120" s="674" t="inlineStr">
+      <c r="A120" s="81" t="inlineStr">
+        <is>
+          <t>9.11</t>
+        </is>
+      </c>
+      <c r="B120" s="374" t="inlineStr">
+        <is>
+          <t>Enchape en granito pulido</t>
+        </is>
+      </c>
+      <c r="C120" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F120">
+        <f>D120*E120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="82" t="n"/>
+      <c r="B121" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 9 - PISOS Y ENCHAPES</t>
         </is>
       </c>
-      <c r="C120" s="530" t="n"/>
-      <c r="D120" s="530" t="n"/>
-      <c r="E120" s="530" t="n"/>
-      <c r="F120" s="479">
-        <f>SUM(F109:F119)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="83" t="n"/>
-      <c r="B121" s="681" t="n"/>
-      <c r="C121" s="681" t="n"/>
-      <c r="D121" s="681" t="n"/>
-      <c r="E121" s="681" t="n"/>
-      <c r="F121" s="675" t="n"/>
+      <c r="C121" s="530" t="n"/>
+      <c r="D121" s="530" t="n"/>
+      <c r="E121" s="530" t="n"/>
+      <c r="F121" s="479">
+        <f>SUM(F110:F120)</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="185" t="inlineStr">
+      <c r="A122" s="83" t="n"/>
+      <c r="B122" s="681" t="n"/>
+      <c r="C122" s="681" t="n"/>
+      <c r="D122" s="681" t="n"/>
+      <c r="E122" s="681" t="n"/>
+      <c r="F122" s="675" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="185" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B122" s="677" t="inlineStr">
+      <c r="B123" s="677" t="inlineStr">
         <is>
           <t>PINTURA</t>
         </is>
       </c>
-      <c r="C122" s="530" t="n"/>
-      <c r="D122" s="530" t="n"/>
-      <c r="E122" s="530" t="n"/>
-      <c r="F122" s="530" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="81" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="B123" s="373" t="inlineStr">
-        <is>
-          <t>Pintura vinílica interior</t>
-        </is>
-      </c>
-      <c r="C123" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D123" s="262" t="n"/>
-      <c r="E123" s="477" t="n"/>
-      <c r="F123" s="478">
-        <f>D123*E123</f>
-        <v/>
-      </c>
+      <c r="C123" s="530" t="n"/>
+      <c r="D123" s="530" t="n"/>
+      <c r="E123" s="530" t="n"/>
+      <c r="F123" s="530" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="81" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="B124" s="373" t="inlineStr">
         <is>
-          <t>Pintura exterior</t>
+          <t>Pintura vinílica interior</t>
         </is>
       </c>
       <c r="C124" s="261" t="inlineStr">
@@ -13758,12 +13763,12 @@
     <row r="125">
       <c r="A125" s="81" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="B125" s="373" t="inlineStr">
         <is>
-          <t>Pintura esmalte en superficies metálicas/madera</t>
+          <t>Pintura exterior</t>
         </is>
       </c>
       <c r="C125" s="261" t="inlineStr">
@@ -13781,12 +13786,12 @@
     <row r="126">
       <c r="A126" s="81" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="B126" s="373" t="inlineStr">
         <is>
-          <t>Pintura anticorrosiva</t>
+          <t>Pintura esmalte en superficies metálicas/madera</t>
         </is>
       </c>
       <c r="C126" s="261" t="inlineStr">
@@ -13804,12 +13809,12 @@
     <row r="127">
       <c r="A127" s="81" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="B127" s="373" t="inlineStr">
         <is>
-          <t>Sellador / imprimante</t>
+          <t>Pintura anticorrosiva</t>
         </is>
       </c>
       <c r="C127" s="261" t="inlineStr">
@@ -13817,89 +13822,91 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D127" s="262" t="n"/>
+      <c r="E127" s="477" t="n"/>
       <c r="F127" s="478">
         <f>D127*E127</f>
         <v/>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="82" t="n"/>
-      <c r="B128" s="674" t="inlineStr">
+      <c r="A128" s="81" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="B128" s="373" t="inlineStr">
+        <is>
+          <t>Sellador / imprimante</t>
+        </is>
+      </c>
+      <c r="C128" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F128" s="478">
+        <f>D128*E128</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="82" t="n"/>
+      <c r="B129" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 10 - PINTURA</t>
         </is>
       </c>
-      <c r="C128" s="530" t="n"/>
-      <c r="D128" s="530" t="n"/>
-      <c r="E128" s="530" t="n"/>
-      <c r="F128" s="479">
-        <f>SUM(F123:F127)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="83" t="n"/>
-      <c r="B129" s="675" t="n"/>
       <c r="C129" s="530" t="n"/>
       <c r="D129" s="530" t="n"/>
       <c r="E129" s="530" t="n"/>
-      <c r="F129" s="579" t="n"/>
+      <c r="F129" s="479">
+        <f>SUM(F124:F128)</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="185" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B130" s="677" t="inlineStr">
-        <is>
-          <t>CARPINTERÍA</t>
-        </is>
-      </c>
+      <c r="A130" s="83" t="n"/>
+      <c r="B130" s="675" t="n"/>
       <c r="C130" s="530" t="n"/>
       <c r="D130" s="530" t="n"/>
       <c r="E130" s="530" t="n"/>
-      <c r="F130" s="530" t="n"/>
+      <c r="F130" s="579" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="81" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="B131" s="373" t="inlineStr">
-        <is>
-          <t>Puertas de madera</t>
-        </is>
-      </c>
-      <c r="C131" s="261" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D131" s="262" t="n"/>
-      <c r="E131" s="477" t="n"/>
-      <c r="F131" s="478">
-        <f>D131*E131</f>
-        <v/>
-      </c>
+      <c r="A131" s="185" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B131" s="677" t="inlineStr">
+        <is>
+          <t>CARPINTERÍA</t>
+        </is>
+      </c>
+      <c r="C131" s="530" t="n"/>
+      <c r="D131" s="530" t="n"/>
+      <c r="E131" s="530" t="n"/>
+      <c r="F131" s="530" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="81" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="B132" s="373" t="inlineStr">
         <is>
-          <t>Muebles fijos de madera</t>
+          <t>Puertas de madera</t>
         </is>
       </c>
       <c r="C132" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D132" s="262" t="n"/>
+      <c r="E132" s="477" t="n"/>
       <c r="F132" s="478">
         <f>D132*E132</f>
         <v/>
@@ -13908,21 +13915,19 @@
     <row r="133">
       <c r="A133" s="81" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="B133" s="373" t="inlineStr">
         <is>
-          <t>Puertas metálicas</t>
+          <t>Muebles fijos de madera</t>
         </is>
       </c>
       <c r="C133" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D133" s="262" t="n"/>
-      <c r="E133" s="477" t="n"/>
+          <t>ML</t>
+        </is>
+      </c>
       <c r="F133" s="478">
         <f>D133*E133</f>
         <v/>
@@ -13931,20 +13936,22 @@
     <row r="134">
       <c r="A134" s="81" t="inlineStr">
         <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="B134" s="374" t="inlineStr">
-        <is>
-          <t>Barandas metálicas</t>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="B134" s="373" t="inlineStr">
+        <is>
+          <t>Puertas metálicas</t>
         </is>
       </c>
       <c r="C134" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F134">
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D134" s="262" t="n"/>
+      <c r="E134" s="477" t="n"/>
+      <c r="F134" s="478">
         <f>D134*E134</f>
         <v/>
       </c>
@@ -13952,12 +13959,12 @@
     <row r="135">
       <c r="A135" s="81" t="inlineStr">
         <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="B135" s="373" t="inlineStr">
-        <is>
-          <t>Pasamanos</t>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="B135" s="374" t="inlineStr">
+        <is>
+          <t>Barandas metálicas</t>
         </is>
       </c>
       <c r="C135" s="261" t="inlineStr">
@@ -13965,9 +13972,7 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D135" s="262" t="n"/>
-      <c r="E135" s="477" t="n"/>
-      <c r="F135" s="478">
+      <c r="F135">
         <f>D135*E135</f>
         <v/>
       </c>
@@ -13975,17 +13980,17 @@
     <row r="136">
       <c r="A136" s="81" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="B136" s="373" t="inlineStr">
         <is>
-          <t>Ventanas de aluminio</t>
+          <t>Pasamanos</t>
         </is>
       </c>
       <c r="C136" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D136" s="262" t="n"/>
@@ -13998,12 +14003,12 @@
     <row r="137">
       <c r="A137" s="81" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="B137" s="373" t="inlineStr">
         <is>
-          <t>Divisiones de aluminio</t>
+          <t>Ventanas de aluminio</t>
         </is>
       </c>
       <c r="C137" s="261" t="inlineStr">
@@ -14021,17 +14026,17 @@
     <row r="138">
       <c r="A138" s="81" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="B138" s="373" t="inlineStr">
         <is>
-          <t>Puerta antipánico</t>
+          <t>Divisiones de aluminio</t>
         </is>
       </c>
       <c r="C138" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D138" s="262" t="n"/>
@@ -14042,74 +14047,76 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="82" t="n"/>
-      <c r="B139" s="674" t="inlineStr">
+      <c r="A139" s="81" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="B139" s="373" t="inlineStr">
+        <is>
+          <t>Puerta antipánico</t>
+        </is>
+      </c>
+      <c r="C139" s="261" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D139" s="262" t="n"/>
+      <c r="E139" s="477" t="n"/>
+      <c r="F139" s="478">
+        <f>D139*E139</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="82" t="n"/>
+      <c r="B140" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 11 - CARPINTERÍA</t>
         </is>
       </c>
-      <c r="C139" s="530" t="n"/>
-      <c r="D139" s="530" t="n"/>
-      <c r="E139" s="530" t="n"/>
-      <c r="F139" s="479">
-        <f>SUM(F131:F138)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="83" t="n"/>
-      <c r="B140" s="681" t="n"/>
-      <c r="C140" s="681" t="n"/>
-      <c r="D140" s="681" t="n"/>
-      <c r="E140" s="681" t="n"/>
-      <c r="F140" s="675" t="n"/>
+      <c r="C140" s="530" t="n"/>
+      <c r="D140" s="530" t="n"/>
+      <c r="E140" s="530" t="n"/>
+      <c r="F140" s="479">
+        <f>SUM(F132:F139)</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" s="185" t="inlineStr">
+      <c r="A141" s="83" t="n"/>
+      <c r="B141" s="681" t="n"/>
+      <c r="C141" s="681" t="n"/>
+      <c r="D141" s="681" t="n"/>
+      <c r="E141" s="681" t="n"/>
+      <c r="F141" s="675" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="185" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B141" s="677" t="inlineStr">
+      <c r="B142" s="677" t="inlineStr">
         <is>
           <t>VIDRIOS</t>
         </is>
       </c>
-      <c r="C141" s="530" t="n"/>
-      <c r="D141" s="530" t="n"/>
-      <c r="E141" s="530" t="n"/>
-      <c r="F141" s="530" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="81" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="B142" s="373" t="inlineStr">
-        <is>
-          <t>Vidrio templado</t>
-        </is>
-      </c>
-      <c r="C142" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="F142" s="478">
-        <f>D142*E142</f>
-        <v/>
-      </c>
+      <c r="C142" s="530" t="n"/>
+      <c r="D142" s="530" t="n"/>
+      <c r="E142" s="530" t="n"/>
+      <c r="F142" s="530" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="81" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="B143" s="373" t="inlineStr">
         <is>
-          <t>Vidrio laminado</t>
+          <t>Vidrio templado</t>
         </is>
       </c>
       <c r="C143" s="261" t="inlineStr">
@@ -14117,8 +14124,6 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D143" s="262" t="n"/>
-      <c r="E143" s="477" t="n"/>
       <c r="F143" s="478">
         <f>D143*E143</f>
         <v/>
@@ -14127,12 +14132,12 @@
     <row r="144">
       <c r="A144" s="81" t="inlineStr">
         <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="B144" s="374" t="inlineStr">
-        <is>
-          <t>Espejos</t>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B144" s="373" t="inlineStr">
+        <is>
+          <t>Vidrio laminado</t>
         </is>
       </c>
       <c r="C144" s="261" t="inlineStr">
@@ -14140,7 +14145,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="F144">
+      <c r="D144" s="262" t="n"/>
+      <c r="E144" s="477" t="n"/>
+      <c r="F144" s="478">
         <f>D144*E144</f>
         <v/>
       </c>
@@ -14148,95 +14155,95 @@
     <row r="145">
       <c r="A145" s="81" t="inlineStr">
         <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="B145" s="374" t="inlineStr">
+        <is>
+          <t>Espejos</t>
+        </is>
+      </c>
+      <c r="C145" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F145">
+        <f>D145*E145</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="81" t="inlineStr">
+        <is>
           <t>12.4</t>
         </is>
       </c>
-      <c r="B145" s="373" t="inlineStr">
+      <c r="B146" s="373" t="inlineStr">
         <is>
           <t>Sellos y silicona</t>
         </is>
       </c>
-      <c r="C145" s="261" t="inlineStr">
+      <c r="C146" s="261" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="D145" s="262" t="n"/>
-      <c r="E145" s="477" t="n"/>
-      <c r="F145" s="478">
-        <f>D145*E145</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="82" t="n"/>
-      <c r="B146" s="674" t="inlineStr">
+      <c r="D146" s="262" t="n"/>
+      <c r="E146" s="477" t="n"/>
+      <c r="F146" s="478">
+        <f>D146*E146</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="82" t="n"/>
+      <c r="B147" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 12 - VIDRIOS</t>
         </is>
       </c>
-      <c r="C146" s="530" t="n"/>
-      <c r="D146" s="530" t="n"/>
-      <c r="E146" s="530" t="n"/>
-      <c r="F146" s="479">
-        <f>SUM(F142:F145)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="83" t="n"/>
-      <c r="B147" s="681" t="n"/>
-      <c r="C147" s="681" t="n"/>
-      <c r="D147" s="681" t="n"/>
-      <c r="E147" s="681" t="n"/>
-      <c r="F147" s="675" t="n"/>
+      <c r="C147" s="530" t="n"/>
+      <c r="D147" s="530" t="n"/>
+      <c r="E147" s="530" t="n"/>
+      <c r="F147" s="479">
+        <f>SUM(F143:F146)</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="185" t="inlineStr">
+      <c r="A148" s="83" t="n"/>
+      <c r="B148" s="681" t="n"/>
+      <c r="C148" s="681" t="n"/>
+      <c r="D148" s="681" t="n"/>
+      <c r="E148" s="681" t="n"/>
+      <c r="F148" s="675" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="185" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B148" s="677" t="inlineStr">
+      <c r="B149" s="677" t="inlineStr">
         <is>
           <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
-      <c r="C148" s="530" t="n"/>
-      <c r="D148" s="530" t="n"/>
-      <c r="E148" s="530" t="n"/>
-      <c r="F148" s="530" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="81" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="B149" s="373" t="inlineStr">
-        <is>
-          <t>Tubería de agua fría</t>
-        </is>
-      </c>
-      <c r="C149" s="261" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F149" s="478">
-        <f>D149*E149</f>
-        <v/>
-      </c>
+      <c r="C149" s="530" t="n"/>
+      <c r="D149" s="530" t="n"/>
+      <c r="E149" s="530" t="n"/>
+      <c r="F149" s="530" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="81" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="B150" s="373" t="inlineStr">
         <is>
-          <t>Tubería de agua caliente</t>
+          <t>Tubería de agua fría</t>
         </is>
       </c>
       <c r="C150" s="261" t="inlineStr">
@@ -14244,8 +14251,6 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D150" s="262" t="n"/>
-      <c r="E150" s="477" t="n"/>
       <c r="F150" s="478">
         <f>D150*E150</f>
         <v/>
@@ -14254,19 +14259,21 @@
     <row r="151">
       <c r="A151" s="81" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="B151" s="373" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios</t>
+          <t>Tubería de agua caliente</t>
         </is>
       </c>
       <c r="C151" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D151" s="262" t="n"/>
+      <c r="E151" s="477" t="n"/>
       <c r="F151" s="478">
         <f>D151*E151</f>
         <v/>
@@ -14275,21 +14282,19 @@
     <row r="152">
       <c r="A152" s="81" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="B152" s="373" t="inlineStr">
         <is>
-          <t>Tubería sanitaria</t>
+          <t>Válvulas y accesorios</t>
         </is>
       </c>
       <c r="C152" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D152" s="262" t="n"/>
-      <c r="E152" s="477" t="n"/>
+          <t>UND</t>
+        </is>
+      </c>
       <c r="F152" s="478">
         <f>D152*E152</f>
         <v/>
@@ -14298,12 +14303,12 @@
     <row r="153">
       <c r="A153" s="81" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="B153" s="373" t="inlineStr">
         <is>
-          <t>Tubería de aguas lluvias</t>
+          <t>Tubería sanitaria</t>
         </is>
       </c>
       <c r="C153" s="261" t="inlineStr">
@@ -14321,17 +14326,17 @@
     <row r="154">
       <c r="A154" s="81" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="B154" s="373" t="inlineStr">
         <is>
-          <t>Cajas de inspección</t>
+          <t>Tubería de aguas lluvias</t>
         </is>
       </c>
       <c r="C154" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D154" s="262" t="n"/>
@@ -14344,12 +14349,12 @@
     <row r="155">
       <c r="A155" s="81" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="B155" s="373" t="inlineStr">
         <is>
-          <t>Aparatos sanitarios</t>
+          <t>Cajas de inspección</t>
         </is>
       </c>
       <c r="C155" s="261" t="inlineStr">
@@ -14367,12 +14372,12 @@
     <row r="156">
       <c r="A156" s="81" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="B156" s="373" t="inlineStr">
         <is>
-          <t>Lavamanos</t>
+          <t>Aparatos sanitarios</t>
         </is>
       </c>
       <c r="C156" s="261" t="inlineStr">
@@ -14390,12 +14395,12 @@
     <row r="157">
       <c r="A157" s="81" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="B157" s="373" t="inlineStr">
         <is>
-          <t>Griferías</t>
+          <t>Lavamanos</t>
         </is>
       </c>
       <c r="C157" s="261" t="inlineStr">
@@ -14413,12 +14418,12 @@
     <row r="158">
       <c r="A158" s="81" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="B158" s="373" t="inlineStr">
         <is>
-          <t>Duchas</t>
+          <t>Griferías</t>
         </is>
       </c>
       <c r="C158" s="261" t="inlineStr">
@@ -14436,17 +14441,17 @@
     <row r="159">
       <c r="A159" s="81" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="B159" s="373" t="inlineStr">
         <is>
-          <t>Pruebas hidráulicas y de estanqueidad</t>
+          <t>Duchas</t>
         </is>
       </c>
       <c r="C159" s="261" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D159" s="262" t="n"/>
@@ -14459,17 +14464,17 @@
     <row r="160">
       <c r="A160" s="81" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="B160" s="373" t="inlineStr">
         <is>
-          <t>Orinal institucional</t>
+          <t>Pruebas hidráulicas y de estanqueidad</t>
         </is>
       </c>
       <c r="C160" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D160" s="262" t="n"/>
@@ -14480,76 +14485,76 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="82" t="n"/>
-      <c r="B161" s="674" t="inlineStr">
+      <c r="A161" s="81" t="inlineStr">
+        <is>
+          <t>13.12</t>
+        </is>
+      </c>
+      <c r="B161" s="373" t="inlineStr">
+        <is>
+          <t>Orinal institucional</t>
+        </is>
+      </c>
+      <c r="C161" s="261" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D161" s="262" t="n"/>
+      <c r="E161" s="477" t="n"/>
+      <c r="F161" s="478">
+        <f>D161*E161</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="82" t="n"/>
+      <c r="B162" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 13 - INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
-      <c r="C161" s="530" t="n"/>
-      <c r="D161" s="530" t="n"/>
-      <c r="E161" s="530" t="n"/>
-      <c r="F161" s="479">
-        <f>SUM(F149:F160)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="83" t="n"/>
-      <c r="B162" s="681" t="n"/>
-      <c r="C162" s="681" t="n"/>
-      <c r="D162" s="681" t="n"/>
-      <c r="E162" s="681" t="n"/>
-      <c r="F162" s="675" t="n"/>
+      <c r="C162" s="530" t="n"/>
+      <c r="D162" s="530" t="n"/>
+      <c r="E162" s="530" t="n"/>
+      <c r="F162" s="479">
+        <f>SUM(F150:F161)</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="185" t="inlineStr">
+      <c r="A163" s="83" t="n"/>
+      <c r="B163" s="681" t="n"/>
+      <c r="C163" s="681" t="n"/>
+      <c r="D163" s="681" t="n"/>
+      <c r="E163" s="681" t="n"/>
+      <c r="F163" s="675" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="185" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B163" s="677" t="inlineStr">
+      <c r="B164" s="677" t="inlineStr">
         <is>
           <t>INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
-      <c r="C163" s="530" t="n"/>
-      <c r="D163" s="530" t="n"/>
-      <c r="E163" s="530" t="n"/>
-      <c r="F163" s="530" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="81" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="B164" s="373" t="inlineStr">
-        <is>
-          <t>Tubería/conduit eléctrica</t>
-        </is>
-      </c>
-      <c r="C164" s="261" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D164" s="262" t="n"/>
-      <c r="E164" s="477" t="n"/>
-      <c r="F164" s="478">
-        <f>D164*E164</f>
-        <v/>
-      </c>
+      <c r="C164" s="530" t="n"/>
+      <c r="D164" s="530" t="n"/>
+      <c r="E164" s="530" t="n"/>
+      <c r="F164" s="530" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="81" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="B165" s="373" t="inlineStr">
         <is>
-          <t>Bandejas portacables</t>
+          <t>Tubería/conduit eléctrica</t>
         </is>
       </c>
       <c r="C165" s="261" t="inlineStr">
@@ -14567,17 +14572,17 @@
     <row r="166">
       <c r="A166" s="81" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="B166" s="373" t="inlineStr">
         <is>
-          <t>Cajas eléctricas</t>
+          <t>Bandejas portacables</t>
         </is>
       </c>
       <c r="C166" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D166" s="262" t="n"/>
@@ -14590,17 +14595,17 @@
     <row r="167">
       <c r="A167" s="81" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="B167" s="373" t="inlineStr">
         <is>
-          <t>Cableado de fuerza</t>
+          <t>Cajas eléctricas</t>
         </is>
       </c>
       <c r="C167" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D167" s="262" t="n"/>
@@ -14613,12 +14618,12 @@
     <row r="168">
       <c r="A168" s="81" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="B168" s="373" t="inlineStr">
         <is>
-          <t>Cableado de iluminación</t>
+          <t>Cableado de fuerza</t>
         </is>
       </c>
       <c r="C168" s="261" t="inlineStr">
@@ -14636,17 +14641,17 @@
     <row r="169">
       <c r="A169" s="81" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="B169" s="373" t="inlineStr">
         <is>
-          <t>Tableros eléctricos</t>
+          <t>Cableado de iluminación</t>
         </is>
       </c>
       <c r="C169" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D169" s="262" t="n"/>
@@ -14659,12 +14664,12 @@
     <row r="170">
       <c r="A170" s="81" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="B170" s="373" t="inlineStr">
         <is>
-          <t>Tomacorrientes</t>
+          <t>Tableros eléctricos</t>
         </is>
       </c>
       <c r="C170" s="261" t="inlineStr">
@@ -14682,12 +14687,12 @@
     <row r="171">
       <c r="A171" s="81" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="B171" s="373" t="inlineStr">
         <is>
-          <t>Interruptores</t>
+          <t>Tomacorrientes</t>
         </is>
       </c>
       <c r="C171" s="261" t="inlineStr">
@@ -14705,12 +14710,12 @@
     <row r="172">
       <c r="A172" s="81" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="B172" s="373" t="inlineStr">
         <is>
-          <t>Luminarias</t>
+          <t>Interruptores</t>
         </is>
       </c>
       <c r="C172" s="261" t="inlineStr">
@@ -14728,17 +14733,17 @@
     <row r="173">
       <c r="A173" s="81" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="B173" s="373" t="inlineStr">
         <is>
-          <t>Sistema de puesta a tierra</t>
+          <t>Luminarias</t>
         </is>
       </c>
       <c r="C173" s="261" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D173" s="262" t="n"/>
@@ -14751,12 +14756,12 @@
     <row r="174">
       <c r="A174" s="81" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="B174" s="373" t="inlineStr">
         <is>
-          <t>Pruebas y certificaciones</t>
+          <t>Sistema de puesta a tierra</t>
         </is>
       </c>
       <c r="C174" s="261" t="inlineStr">
@@ -14772,81 +14777,81 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="82" t="n"/>
-      <c r="B175" s="674" t="inlineStr">
+      <c r="A175" s="81" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="B175" s="373" t="inlineStr">
+        <is>
+          <t>Pruebas y certificaciones</t>
+        </is>
+      </c>
+      <c r="C175" s="261" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D175" s="262" t="n"/>
+      <c r="E175" s="477" t="n"/>
+      <c r="F175" s="478">
+        <f>D175*E175</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="82" t="n"/>
+      <c r="B176" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 14 - INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
-      <c r="C175" s="530" t="n"/>
-      <c r="D175" s="530" t="n"/>
-      <c r="E175" s="530" t="n"/>
-      <c r="F175" s="479">
-        <f>SUM(F164:F174)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="83" t="n"/>
-      <c r="B176" s="681" t="n"/>
-      <c r="C176" s="681" t="n"/>
-      <c r="D176" s="681" t="n"/>
-      <c r="E176" s="681" t="n"/>
-      <c r="F176" s="675" t="n"/>
+      <c r="C176" s="530" t="n"/>
+      <c r="D176" s="530" t="n"/>
+      <c r="E176" s="530" t="n"/>
+      <c r="F176" s="479">
+        <f>SUM(F165:F175)</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
-      <c r="A177" s="185" t="inlineStr">
+      <c r="A177" s="83" t="n"/>
+      <c r="B177" s="681" t="n"/>
+      <c r="C177" s="681" t="n"/>
+      <c r="D177" s="681" t="n"/>
+      <c r="E177" s="681" t="n"/>
+      <c r="F177" s="675" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="185" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B177" s="677" t="inlineStr">
+      <c r="B178" s="677" t="inlineStr">
         <is>
           <t>COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
-      <c r="C177" s="530" t="n"/>
-      <c r="D177" s="530" t="n"/>
-      <c r="E177" s="530" t="n"/>
-      <c r="F177" s="530" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="81" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="B178" s="373" t="inlineStr">
-        <is>
-          <t>Cableado estructurado de datos</t>
-        </is>
-      </c>
-      <c r="C178" s="261" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D178" s="262" t="n"/>
-      <c r="E178" s="477" t="n"/>
-      <c r="F178" s="478">
-        <f>D178*E178</f>
-        <v/>
-      </c>
+      <c r="C178" s="530" t="n"/>
+      <c r="D178" s="530" t="n"/>
+      <c r="E178" s="530" t="n"/>
+      <c r="F178" s="530" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="81" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="B179" s="373" t="inlineStr">
         <is>
-          <t>Rack de comunicaciones</t>
+          <t>Cableado estructurado de datos</t>
         </is>
       </c>
       <c r="C179" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D179" s="262" t="n"/>
@@ -14859,12 +14864,12 @@
     <row r="180">
       <c r="A180" s="81" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="B180" s="373" t="inlineStr">
         <is>
-          <t>Cámaras y sistema CCTV</t>
+          <t>Rack de comunicaciones</t>
         </is>
       </c>
       <c r="C180" s="261" t="inlineStr">
@@ -14882,12 +14887,12 @@
     <row r="181">
       <c r="A181" s="81" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="B181" s="373" t="inlineStr">
         <is>
-          <t>Control de acceso</t>
+          <t>Cámaras y sistema CCTV</t>
         </is>
       </c>
       <c r="C181" s="261" t="inlineStr">
@@ -14905,12 +14910,12 @@
     <row r="182">
       <c r="A182" s="81" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="B182" s="373" t="inlineStr">
         <is>
-          <t>Sistema de citofonía</t>
+          <t>Control de acceso</t>
         </is>
       </c>
       <c r="C182" s="261" t="inlineStr">
@@ -14928,17 +14933,17 @@
     <row r="183">
       <c r="A183" s="81" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="B183" s="373" t="inlineStr">
         <is>
-          <t>Sistema de detección de incendios</t>
+          <t>Sistema de citofonía</t>
         </is>
       </c>
       <c r="C183" s="261" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D183" s="262" t="n"/>
@@ -14949,81 +14954,81 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="82" t="n"/>
-      <c r="B184" s="674" t="inlineStr">
+      <c r="A184" s="81" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="B184" s="373" t="inlineStr">
+        <is>
+          <t>Sistema de detección de incendios</t>
+        </is>
+      </c>
+      <c r="C184" s="261" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D184" s="262" t="n"/>
+      <c r="E184" s="477" t="n"/>
+      <c r="F184" s="478">
+        <f>D184*E184</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="82" t="n"/>
+      <c r="B185" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 15 - COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
-      <c r="C184" s="530" t="n"/>
-      <c r="D184" s="530" t="n"/>
-      <c r="E184" s="530" t="n"/>
-      <c r="F184" s="479">
-        <f>SUM(F178:F183)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="83" t="n"/>
-      <c r="B185" s="681" t="n"/>
-      <c r="C185" s="681" t="n"/>
-      <c r="D185" s="681" t="n"/>
-      <c r="E185" s="681" t="n"/>
-      <c r="F185" s="675" t="n"/>
+      <c r="C185" s="530" t="n"/>
+      <c r="D185" s="530" t="n"/>
+      <c r="E185" s="530" t="n"/>
+      <c r="F185" s="479">
+        <f>SUM(F179:F184)</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
-      <c r="A186" s="185" t="inlineStr">
+      <c r="A186" s="83" t="n"/>
+      <c r="B186" s="681" t="n"/>
+      <c r="C186" s="681" t="n"/>
+      <c r="D186" s="681" t="n"/>
+      <c r="E186" s="681" t="n"/>
+      <c r="F186" s="675" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="185" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B186" s="677" t="inlineStr">
+      <c r="B187" s="677" t="inlineStr">
         <is>
           <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
-      <c r="C186" s="530" t="n"/>
-      <c r="D186" s="530" t="n"/>
-      <c r="E186" s="530" t="n"/>
-      <c r="F186" s="530" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="81" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="B187" s="373" t="inlineStr">
-        <is>
-          <t>Equipos de aire acondicionado</t>
-        </is>
-      </c>
-      <c r="C187" s="261" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D187" s="262" t="n"/>
-      <c r="E187" s="477" t="n"/>
-      <c r="F187" s="478">
-        <f>D187*E187</f>
-        <v/>
-      </c>
+      <c r="C187" s="530" t="n"/>
+      <c r="D187" s="530" t="n"/>
+      <c r="E187" s="530" t="n"/>
+      <c r="F187" s="530" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="81" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="B188" s="373" t="inlineStr">
         <is>
-          <t>Ductos de ventilación</t>
+          <t>Equipos de aire acondicionado</t>
         </is>
       </c>
       <c r="C188" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D188" s="262" t="n"/>
@@ -15036,17 +15041,17 @@
     <row r="189">
       <c r="A189" s="81" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="B189" s="373" t="inlineStr">
         <is>
-          <t>Tubería de refrigerante</t>
+          <t>Ductos de ventilación</t>
         </is>
       </c>
       <c r="C189" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D189" s="262" t="n"/>
@@ -15059,17 +15064,17 @@
     <row r="190">
       <c r="A190" s="81" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="B190" s="373" t="inlineStr">
         <is>
-          <t>Rejillas y difusores</t>
+          <t>Tubería de refrigerante</t>
         </is>
       </c>
       <c r="C190" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D190" s="262" t="n"/>
@@ -15080,81 +15085,81 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="82" t="n"/>
-      <c r="B191" s="674" t="inlineStr">
+      <c r="A191" s="81" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="B191" s="373" t="inlineStr">
+        <is>
+          <t>Rejillas y difusores</t>
+        </is>
+      </c>
+      <c r="C191" s="261" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D191" s="262" t="n"/>
+      <c r="E191" s="477" t="n"/>
+      <c r="F191" s="478">
+        <f>D191*E191</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="82" t="n"/>
+      <c r="B192" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 16 - CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
-      <c r="C191" s="530" t="n"/>
-      <c r="D191" s="530" t="n"/>
-      <c r="E191" s="530" t="n"/>
-      <c r="F191" s="479">
-        <f>SUM(F187:F190)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="83" t="n"/>
-      <c r="B192" s="681" t="n"/>
-      <c r="C192" s="681" t="n"/>
-      <c r="D192" s="681" t="n"/>
-      <c r="E192" s="681" t="n"/>
-      <c r="F192" s="675" t="n"/>
+      <c r="C192" s="530" t="n"/>
+      <c r="D192" s="530" t="n"/>
+      <c r="E192" s="530" t="n"/>
+      <c r="F192" s="479">
+        <f>SUM(F188:F191)</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
-      <c r="A193" s="185" t="inlineStr">
+      <c r="A193" s="83" t="n"/>
+      <c r="B193" s="681" t="n"/>
+      <c r="C193" s="681" t="n"/>
+      <c r="D193" s="681" t="n"/>
+      <c r="E193" s="681" t="n"/>
+      <c r="F193" s="675" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="185" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B193" s="677" t="inlineStr">
+      <c r="B194" s="677" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="C193" s="530" t="n"/>
-      <c r="D193" s="530" t="n"/>
-      <c r="E193" s="530" t="n"/>
-      <c r="F193" s="530" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="81" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="B194" s="373" t="inlineStr">
-        <is>
-          <t>Red interna de gas</t>
-        </is>
-      </c>
-      <c r="C194" s="261" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D194" s="262" t="n"/>
-      <c r="E194" s="477" t="n"/>
-      <c r="F194" s="478">
-        <f>D194*E194</f>
-        <v/>
-      </c>
+      <c r="C194" s="530" t="n"/>
+      <c r="D194" s="530" t="n"/>
+      <c r="E194" s="530" t="n"/>
+      <c r="F194" s="530" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="81" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="B195" s="373" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios</t>
+          <t>Red interna de gas</t>
         </is>
       </c>
       <c r="C195" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D195" s="262" t="n"/>
@@ -15167,17 +15172,17 @@
     <row r="196">
       <c r="A196" s="81" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="B196" s="373" t="inlineStr">
         <is>
-          <t>Pruebas y certificación</t>
+          <t>Válvulas y accesorios</t>
         </is>
       </c>
       <c r="C196" s="261" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D196" s="262" t="n"/>
@@ -15188,81 +15193,81 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="82" t="n"/>
-      <c r="B197" s="674" t="inlineStr">
+      <c r="A197" s="81" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="B197" s="373" t="inlineStr">
+        <is>
+          <t>Pruebas y certificación</t>
+        </is>
+      </c>
+      <c r="C197" s="261" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D197" s="262" t="n"/>
+      <c r="E197" s="477" t="n"/>
+      <c r="F197" s="478">
+        <f>D197*E197</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="82" t="n"/>
+      <c r="B198" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 17 - GAS</t>
         </is>
       </c>
-      <c r="C197" s="530" t="n"/>
-      <c r="D197" s="530" t="n"/>
-      <c r="E197" s="530" t="n"/>
-      <c r="F197" s="479">
-        <f>SUM(F194:F196)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="83" t="n"/>
-      <c r="B198" s="681" t="n"/>
-      <c r="C198" s="681" t="n"/>
-      <c r="D198" s="681" t="n"/>
-      <c r="E198" s="681" t="n"/>
-      <c r="F198" s="675" t="n"/>
+      <c r="C198" s="530" t="n"/>
+      <c r="D198" s="530" t="n"/>
+      <c r="E198" s="530" t="n"/>
+      <c r="F198" s="479">
+        <f>SUM(F195:F197)</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
-      <c r="A199" s="185" t="inlineStr">
+      <c r="A199" s="83" t="n"/>
+      <c r="B199" s="681" t="n"/>
+      <c r="C199" s="681" t="n"/>
+      <c r="D199" s="681" t="n"/>
+      <c r="E199" s="681" t="n"/>
+      <c r="F199" s="675" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="185" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B199" s="677" t="inlineStr">
+      <c r="B200" s="677" t="inlineStr">
         <is>
           <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
-      <c r="C199" s="530" t="n"/>
-      <c r="D199" s="530" t="n"/>
-      <c r="E199" s="530" t="n"/>
-      <c r="F199" s="530" t="n"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="81" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="B200" s="373" t="inlineStr">
-        <is>
-          <t>Construcción de andenes</t>
-        </is>
-      </c>
-      <c r="C200" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D200" s="262" t="n"/>
-      <c r="E200" s="477" t="n"/>
-      <c r="F200" s="478">
-        <f>D200*E200</f>
-        <v/>
-      </c>
+      <c r="C200" s="530" t="n"/>
+      <c r="D200" s="530" t="n"/>
+      <c r="E200" s="530" t="n"/>
+      <c r="F200" s="530" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="81" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="B201" s="373" t="inlineStr">
         <is>
-          <t>Placas de concreto exteriores</t>
+          <t>Construcción de andenes</t>
         </is>
       </c>
       <c r="C201" s="261" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D201" s="262" t="n"/>
@@ -15275,17 +15280,17 @@
     <row r="202">
       <c r="A202" s="81" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="B202" s="373" t="inlineStr">
         <is>
-          <t>Pavimento en adoquín</t>
+          <t>Placas de concreto exteriores</t>
         </is>
       </c>
       <c r="C202" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D202" s="262" t="n"/>
@@ -15298,17 +15303,17 @@
     <row r="203">
       <c r="A203" s="81" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="B203" s="373" t="inlineStr">
         <is>
-          <t>Sardineles y bordillos</t>
+          <t>Pavimento en adoquín</t>
         </is>
       </c>
       <c r="C203" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D203" s="262" t="n"/>
@@ -15321,17 +15326,17 @@
     <row r="204">
       <c r="A204" s="81" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="B204" s="373" t="inlineStr">
         <is>
-          <t>Sumideros exteriores</t>
+          <t>Sardineles y bordillos</t>
         </is>
       </c>
       <c r="C204" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D204" s="262" t="n"/>
@@ -15344,17 +15349,17 @@
     <row r="205">
       <c r="A205" s="81" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="B205" s="373" t="inlineStr">
         <is>
-          <t>Suministro y extendido de tierra vegetal</t>
+          <t>Sumideros exteriores</t>
         </is>
       </c>
       <c r="C205" s="261" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D205" s="262" t="n"/>
@@ -15367,17 +15372,17 @@
     <row r="206">
       <c r="A206" s="81" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="B206" s="373" t="inlineStr">
         <is>
-          <t>Siembra y jardinería</t>
+          <t>Suministro y extendido de tierra vegetal</t>
         </is>
       </c>
       <c r="C206" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D206" s="262" t="n"/>
@@ -15390,12 +15395,12 @@
     <row r="207">
       <c r="A207" s="81" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="B207" s="373" t="inlineStr">
         <is>
-          <t>Geotextil para drenaje y filtración</t>
+          <t>Siembra y jardinería</t>
         </is>
       </c>
       <c r="C207" s="261" t="inlineStr">
@@ -15413,17 +15418,17 @@
     <row r="208">
       <c r="A208" s="81" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="B208" s="373" t="inlineStr">
         <is>
-          <t>Gaviones para obras de contención</t>
+          <t>Geotextil para drenaje y filtración</t>
         </is>
       </c>
       <c r="C208" s="261" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D208" s="262" t="n"/>
@@ -15436,17 +15441,17 @@
     <row r="209">
       <c r="A209" s="81" t="inlineStr">
         <is>
-          <t>18.10</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="B209" s="373" t="inlineStr">
         <is>
-          <t>Filtro francés (drenaje de terrenos)</t>
+          <t>Gaviones para obras de contención</t>
         </is>
       </c>
       <c r="C209" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D209" s="262" t="n"/>
@@ -15459,17 +15464,17 @@
     <row r="210">
       <c r="A210" s="81" t="inlineStr">
         <is>
-          <t>18.11</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="B210" s="373" t="inlineStr">
         <is>
-          <t>Revegetalización / empradización</t>
+          <t>Filtro francés (drenaje de terrenos)</t>
         </is>
       </c>
       <c r="C210" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D210" s="262" t="n"/>
@@ -15480,81 +15485,81 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="82" t="n"/>
-      <c r="B211" s="674" t="inlineStr">
+      <c r="A211" s="81" t="inlineStr">
+        <is>
+          <t>18.11</t>
+        </is>
+      </c>
+      <c r="B211" s="373" t="inlineStr">
+        <is>
+          <t>Revegetalización / empradización</t>
+        </is>
+      </c>
+      <c r="C211" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D211" s="262" t="n"/>
+      <c r="E211" s="477" t="n"/>
+      <c r="F211" s="478">
+        <f>D211*E211</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="82" t="n"/>
+      <c r="B212" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 18 - URBANISMO Y EXTERIORES</t>
         </is>
       </c>
-      <c r="C211" s="530" t="n"/>
-      <c r="D211" s="530" t="n"/>
-      <c r="E211" s="530" t="n"/>
-      <c r="F211" s="479">
-        <f>SUM(F200:F210)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="83" t="n"/>
-      <c r="B212" s="681" t="n"/>
-      <c r="C212" s="681" t="n"/>
-      <c r="D212" s="681" t="n"/>
-      <c r="E212" s="681" t="n"/>
-      <c r="F212" s="675" t="n"/>
+      <c r="C212" s="530" t="n"/>
+      <c r="D212" s="530" t="n"/>
+      <c r="E212" s="530" t="n"/>
+      <c r="F212" s="479">
+        <f>SUM(F201:F211)</f>
+        <v/>
+      </c>
     </row>
     <row r="213">
-      <c r="A213" s="185" t="inlineStr">
+      <c r="A213" s="83" t="n"/>
+      <c r="B213" s="681" t="n"/>
+      <c r="C213" s="681" t="n"/>
+      <c r="D213" s="681" t="n"/>
+      <c r="E213" s="681" t="n"/>
+      <c r="F213" s="675" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="185" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B213" s="677" t="inlineStr">
+      <c r="B214" s="677" t="inlineStr">
         <is>
           <t>OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
-      <c r="C213" s="530" t="n"/>
-      <c r="D213" s="530" t="n"/>
-      <c r="E213" s="530" t="n"/>
-      <c r="F213" s="530" t="n"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="81" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="B214" s="373" t="inlineStr">
-        <is>
-          <t>Rejas metálicas</t>
-        </is>
-      </c>
-      <c r="C214" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D214" s="262" t="n"/>
-      <c r="E214" s="477" t="n"/>
-      <c r="F214" s="478">
-        <f>D214*E214</f>
-        <v/>
-      </c>
+      <c r="C214" s="530" t="n"/>
+      <c r="D214" s="530" t="n"/>
+      <c r="E214" s="530" t="n"/>
+      <c r="F214" s="530" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="81" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="B215" s="373" t="inlineStr">
         <is>
-          <t>Escaleras metálicas</t>
+          <t>Rejas metálicas</t>
         </is>
       </c>
       <c r="C215" s="261" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D215" s="262" t="n"/>
@@ -15567,12 +15572,12 @@
     <row r="216">
       <c r="A216" s="81" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="B216" s="373" t="inlineStr">
         <is>
-          <t>Elementos metálicos especiales</t>
+          <t>Escaleras metálicas</t>
         </is>
       </c>
       <c r="C216" s="261" t="inlineStr">
@@ -15590,17 +15595,17 @@
     <row r="217">
       <c r="A217" s="81" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="B217" s="373" t="inlineStr">
         <is>
-          <t>Mobiliario fijo de obra</t>
+          <t>Elementos metálicos especiales</t>
         </is>
       </c>
       <c r="C217" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D217" s="262" t="n"/>
@@ -15611,76 +15616,76 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="82" t="n"/>
-      <c r="B218" s="674" t="inlineStr">
+      <c r="A218" s="81" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="B218" s="373" t="inlineStr">
+        <is>
+          <t>Mobiliario fijo de obra</t>
+        </is>
+      </c>
+      <c r="C218" s="261" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D218" s="262" t="n"/>
+      <c r="E218" s="477" t="n"/>
+      <c r="F218" s="478">
+        <f>D218*E218</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="82" t="n"/>
+      <c r="B219" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 19 - OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
-      <c r="C218" s="530" t="n"/>
-      <c r="D218" s="530" t="n"/>
-      <c r="E218" s="530" t="n"/>
-      <c r="F218" s="479">
-        <f>SUM(F214:F217)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="83" t="n"/>
-      <c r="B219" s="681" t="n"/>
-      <c r="C219" s="681" t="n"/>
-      <c r="D219" s="681" t="n"/>
-      <c r="E219" s="681" t="n"/>
-      <c r="F219" s="675" t="n"/>
+      <c r="C219" s="530" t="n"/>
+      <c r="D219" s="530" t="n"/>
+      <c r="E219" s="530" t="n"/>
+      <c r="F219" s="479">
+        <f>SUM(F215:F218)</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
-      <c r="A220" s="185" t="inlineStr">
+      <c r="A220" s="83" t="n"/>
+      <c r="B220" s="681" t="n"/>
+      <c r="C220" s="681" t="n"/>
+      <c r="D220" s="681" t="n"/>
+      <c r="E220" s="681" t="n"/>
+      <c r="F220" s="675" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="185" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B220" s="677" t="inlineStr">
+      <c r="B221" s="677" t="inlineStr">
         <is>
           <t>ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
-      <c r="C220" s="530" t="n"/>
-      <c r="D220" s="530" t="n"/>
-      <c r="E220" s="530" t="n"/>
-      <c r="F220" s="530" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="81" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="B221" s="373" t="inlineStr">
-        <is>
-          <t>Limpieza gruesa y fina de obra</t>
-        </is>
-      </c>
-      <c r="C221" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D221" s="262" t="n"/>
-      <c r="E221" s="477" t="n"/>
-      <c r="F221" s="478">
-        <f>D221*E221</f>
-        <v/>
-      </c>
+      <c r="C221" s="530" t="n"/>
+      <c r="D221" s="530" t="n"/>
+      <c r="E221" s="530" t="n"/>
+      <c r="F221" s="530" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="81" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="B222" s="373" t="inlineStr">
         <is>
-          <t>Limpieza final para entrega</t>
+          <t>Limpieza gruesa y fina de obra</t>
         </is>
       </c>
       <c r="C222" s="261" t="inlineStr">
@@ -15698,17 +15703,17 @@
     <row r="223">
       <c r="A223" s="81" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="B223" s="373" t="inlineStr">
         <is>
-          <t>Pruebas, puesta en marcha y ajustes</t>
+          <t>Limpieza final para entrega</t>
         </is>
       </c>
       <c r="C223" s="261" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D223" s="262" t="n"/>
@@ -15721,12 +15726,12 @@
     <row r="224">
       <c r="A224" s="81" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="B224" s="373" t="inlineStr">
         <is>
-          <t>Actualización de planos récord / as-built</t>
+          <t>Pruebas, puesta en marcha y ajustes</t>
         </is>
       </c>
       <c r="C224" s="261" t="inlineStr">
@@ -15744,12 +15749,12 @@
     <row r="225">
       <c r="A225" s="81" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="B225" s="373" t="inlineStr">
         <is>
-          <t>Entrega, manuales y acta de recibo</t>
+          <t>Actualización de planos récord / as-built</t>
         </is>
       </c>
       <c r="C225" s="261" t="inlineStr">
@@ -15765,138 +15770,138 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="82" t="n"/>
-      <c r="B226" s="674" t="inlineStr">
+      <c r="A226" s="81" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="B226" s="373" t="inlineStr">
+        <is>
+          <t>Entrega, manuales y acta de recibo</t>
+        </is>
+      </c>
+      <c r="C226" s="261" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D226" s="262" t="n"/>
+      <c r="E226" s="477" t="n"/>
+      <c r="F226" s="478">
+        <f>D226*E226</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="82" t="n"/>
+      <c r="B227" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 20 - ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
-      <c r="C226" s="530" t="n"/>
-      <c r="D226" s="530" t="n"/>
-      <c r="E226" s="530" t="n"/>
-      <c r="F226" s="479">
-        <f>SUM(F221:F225)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="83" t="n"/>
-      <c r="B227" s="681" t="n"/>
-      <c r="C227" s="681" t="n"/>
-      <c r="D227" s="681" t="n"/>
-      <c r="E227" s="681" t="n"/>
-      <c r="F227" s="675" t="n"/>
+      <c r="C227" s="530" t="n"/>
+      <c r="D227" s="530" t="n"/>
+      <c r="E227" s="530" t="n"/>
+      <c r="F227" s="479">
+        <f>SUM(F222:F226)</f>
+        <v/>
+      </c>
     </row>
     <row r="228">
-      <c r="A228" s="185" t="inlineStr">
+      <c r="A228" s="83" t="n"/>
+      <c r="B228" s="681" t="n"/>
+      <c r="C228" s="681" t="n"/>
+      <c r="D228" s="681" t="n"/>
+      <c r="E228" s="681" t="n"/>
+      <c r="F228" s="675" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="185" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B228" s="677" t="inlineStr">
+      <c r="B229" s="677" t="inlineStr">
         <is>
           <t>ASCENSORES</t>
         </is>
       </c>
-      <c r="C228" s="530" t="n"/>
-      <c r="D228" s="530" t="n"/>
-      <c r="E228" s="530" t="n"/>
-      <c r="F228" s="530" t="n"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="81" t="inlineStr">
+      <c r="C229" s="530" t="n"/>
+      <c r="D229" s="530" t="n"/>
+      <c r="E229" s="530" t="n"/>
+      <c r="F229" s="530" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="81" t="inlineStr">
         <is>
           <t>21.1</t>
         </is>
       </c>
-      <c r="B229" s="373" t="inlineStr">
+      <c r="B230" s="373" t="inlineStr">
         <is>
           <t>Suministro e instalación de ascensor eléctrico</t>
         </is>
       </c>
-      <c r="C229" s="261" t="inlineStr">
+      <c r="C230" s="261" t="inlineStr">
         <is>
           <t>UND</t>
         </is>
       </c>
-      <c r="D229" s="262" t="n"/>
-      <c r="E229" s="477" t="n"/>
-      <c r="F229" s="478">
-        <f>D229*E229</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="82" t="n"/>
-      <c r="B230" s="674" t="inlineStr">
+      <c r="D230" s="262" t="n"/>
+      <c r="E230" s="477" t="n"/>
+      <c r="F230" s="478">
+        <f>D230*E230</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="82" t="n"/>
+      <c r="B231" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 21 - ASCENSORES</t>
         </is>
       </c>
-      <c r="C230" s="530" t="n"/>
-      <c r="D230" s="530" t="n"/>
-      <c r="E230" s="530" t="n"/>
-      <c r="F230" s="479">
-        <f>SUM(F229:F229)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="83" t="n"/>
-      <c r="B231" s="681" t="n"/>
-      <c r="C231" s="681" t="n"/>
-      <c r="D231" s="681" t="n"/>
-      <c r="E231" s="681" t="n"/>
-      <c r="F231" s="675" t="n"/>
+      <c r="C231" s="530" t="n"/>
+      <c r="D231" s="530" t="n"/>
+      <c r="E231" s="530" t="n"/>
+      <c r="F231" s="479">
+        <f>SUM(F230:F230)</f>
+        <v/>
+      </c>
     </row>
     <row r="232">
-      <c r="A232" s="185" t="inlineStr">
+      <c r="A232" s="83" t="n"/>
+      <c r="B232" s="681" t="n"/>
+      <c r="C232" s="681" t="n"/>
+      <c r="D232" s="681" t="n"/>
+      <c r="E232" s="681" t="n"/>
+      <c r="F232" s="675" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="185" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B232" s="677" t="inlineStr">
+      <c r="B233" s="677" t="inlineStr">
         <is>
           <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
-      <c r="C232" s="530" t="n"/>
-      <c r="D232" s="530" t="n"/>
-      <c r="E232" s="530" t="n"/>
-      <c r="F232" s="530" t="n"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="81" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="B233" s="373" t="inlineStr">
-        <is>
-          <t>Estudio de suelos y geotecnia</t>
-        </is>
-      </c>
-      <c r="C233" s="261" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D233" s="262" t="n"/>
-      <c r="E233" s="477" t="n"/>
-      <c r="F233" s="478">
-        <f>D233*E233</f>
-        <v/>
-      </c>
+      <c r="C233" s="530" t="n"/>
+      <c r="D233" s="530" t="n"/>
+      <c r="E233" s="530" t="n"/>
+      <c r="F233" s="530" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="81" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="B234" s="373" t="inlineStr">
         <is>
-          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
+          <t>Estudio de suelos y geotecnia</t>
         </is>
       </c>
       <c r="C234" s="261" t="inlineStr">
@@ -15914,12 +15919,12 @@
     <row r="235">
       <c r="A235" s="81" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="B235" s="373" t="inlineStr">
         <is>
-          <t>Licencia de construcción y trámites de curaduría urbana</t>
+          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
         </is>
       </c>
       <c r="C235" s="261" t="inlineStr">
@@ -15937,12 +15942,12 @@
     <row r="236">
       <c r="A236" s="81" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="B236" s="373" t="inlineStr">
         <is>
-          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
+          <t>Licencia de construcción y trámites de curaduría urbana</t>
         </is>
       </c>
       <c r="C236" s="261" t="inlineStr">
@@ -15958,84 +15963,89 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="82" t="n"/>
-      <c r="B237" s="674" t="inlineStr">
+      <c r="A237" s="81" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="B237" s="373" t="inlineStr">
+        <is>
+          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
+        </is>
+      </c>
+      <c r="C237" s="261" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D237" s="262" t="n"/>
+      <c r="E237" s="477" t="n"/>
+      <c r="F237" s="478">
+        <f>D237*E237</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="82" t="n"/>
+      <c r="B238" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 22 - GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
-      <c r="C237" s="530" t="n"/>
-      <c r="D237" s="530" t="n"/>
-      <c r="E237" s="530" t="n"/>
-      <c r="F237" s="479">
-        <f>SUM(F233:F236)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="83" t="n"/>
-      <c r="B238" s="681" t="n"/>
-      <c r="C238" s="681" t="n"/>
-      <c r="D238" s="681" t="n"/>
-      <c r="E238" s="681" t="n"/>
-      <c r="F238" s="675" t="n"/>
-    </row>
-    <row r="239" ht="15" customHeight="1" s="1223">
-      <c r="A239" s="84" t="n"/>
-      <c r="B239" s="676" t="inlineStr">
+      <c r="C238" s="530" t="n"/>
+      <c r="D238" s="530" t="n"/>
+      <c r="E238" s="530" t="n"/>
+      <c r="F238" s="479">
+        <f>SUM(F234:F237)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="83" t="n"/>
+      <c r="B239" s="681" t="n"/>
+      <c r="C239" s="681" t="n"/>
+      <c r="D239" s="681" t="n"/>
+      <c r="E239" s="681" t="n"/>
+      <c r="F239" s="675" t="n"/>
+    </row>
+    <row r="240" ht="15" customHeight="1" s="1223">
+      <c r="A240" s="84" t="n"/>
+      <c r="B240" s="676" t="inlineStr">
         <is>
           <t>COSTO DIRECTO TOTAL (suma de capítulos 1 a 22)</t>
         </is>
       </c>
-      <c r="C239" s="530" t="n"/>
-      <c r="D239" s="530" t="n"/>
-      <c r="E239" s="530" t="n"/>
-      <c r="F239" s="480">
-        <f>F25+F39+F49+F68+F80+F92+F99+F106+F120+F128+F139+F146+F161+F175+F184+F191+F197+F211+F218+F226+F230+F237</f>
-        <v/>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="85" t="n"/>
-      <c r="B240" s="28" t="n"/>
-      <c r="C240" s="28" t="n"/>
-      <c r="D240" s="28" t="n"/>
-      <c r="E240" s="28" t="n"/>
-      <c r="F240" s="86" t="n"/>
-    </row>
-    <row r="241" ht="15" customHeight="1" s="1223">
-      <c r="A241" s="83" t="n"/>
-      <c r="B241" s="46" t="inlineStr">
-        <is>
-          <t>Administración (A)</t>
-        </is>
-      </c>
-      <c r="C241" s="681" t="n"/>
-      <c r="D241" s="681" t="n"/>
-      <c r="E241" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$29</f>
-        <v/>
-      </c>
-      <c r="F241" s="482">
-        <f>F239*E241</f>
-        <v/>
-      </c>
+      <c r="C240" s="530" t="n"/>
+      <c r="D240" s="530" t="n"/>
+      <c r="E240" s="530" t="n"/>
+      <c r="F240" s="480">
+        <f>F25+F39+F49+F69+F81+F93+F100+F107+F121+F129+F140+F147+F162+F176+F185+F192+F198+F212+F219+F227+F231+F238</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="85" t="n"/>
+      <c r="B241" s="28" t="n"/>
+      <c r="C241" s="28" t="n"/>
+      <c r="D241" s="28" t="n"/>
+      <c r="E241" s="28" t="n"/>
+      <c r="F241" s="86" t="n"/>
     </row>
     <row r="242" ht="15" customHeight="1" s="1223">
       <c r="A242" s="83" t="n"/>
       <c r="B242" s="46" t="inlineStr">
         <is>
-          <t>Imprevistos (I)</t>
+          <t>Administración (A)</t>
         </is>
       </c>
       <c r="C242" s="681" t="n"/>
       <c r="D242" s="681" t="n"/>
       <c r="E242" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$30</f>
+        <f>'Ficha Técnica del Proyecto'!$B$29</f>
         <v/>
       </c>
       <c r="F242" s="482">
-        <f>F239*E242</f>
+        <f>F240*E242</f>
         <v/>
       </c>
     </row>
@@ -16043,47 +16053,50 @@
       <c r="A243" s="83" t="n"/>
       <c r="B243" s="46" t="inlineStr">
         <is>
-          <t>Utilidad (U)</t>
+          <t>Imprevistos (I)</t>
         </is>
       </c>
       <c r="C243" s="681" t="n"/>
       <c r="D243" s="681" t="n"/>
       <c r="E243" s="481">
+        <f>'Ficha Técnica del Proyecto'!$B$30</f>
+        <v/>
+      </c>
+      <c r="F243" s="482">
+        <f>F240*E243</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244" ht="15" customHeight="1" s="1223">
+      <c r="A244" s="83" t="n"/>
+      <c r="B244" s="46" t="inlineStr">
+        <is>
+          <t>Utilidad (U)</t>
+        </is>
+      </c>
+      <c r="C244" s="681" t="n"/>
+      <c r="D244" s="681" t="n"/>
+      <c r="E244" s="481">
         <f>'Ficha Técnica del Proyecto'!$B$31</f>
         <v/>
       </c>
-      <c r="F243" s="482">
-        <f>F239*E243</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244" ht="15" customHeight="1" s="1223">
-      <c r="A244" s="82" t="n"/>
-      <c r="B244" s="674" t="inlineStr">
+      <c r="F244" s="482">
+        <f>F240*E244</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245" ht="15" customHeight="1" s="1223">
+      <c r="A245" s="82" t="n"/>
+      <c r="B245" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL AIU (A+I+U)</t>
         </is>
       </c>
-      <c r="C244" s="29" t="n"/>
-      <c r="D244" s="29" t="n"/>
-      <c r="E244" s="30" t="n"/>
-      <c r="F244" s="479">
-        <f>F241+F242+F243</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245" ht="15" customHeight="1" s="1223">
-      <c r="A245" s="83" t="n"/>
-      <c r="B245" s="46" t="inlineStr">
-        <is>
-          <t>COSTO DIRECTO + AIU</t>
-        </is>
-      </c>
-      <c r="C245" s="681" t="n"/>
-      <c r="D245" s="681" t="n"/>
-      <c r="E245" s="47" t="n"/>
-      <c r="F245" s="482">
-        <f>F239+F244</f>
+      <c r="C245" s="29" t="n"/>
+      <c r="D245" s="29" t="n"/>
+      <c r="E245" s="30" t="n"/>
+      <c r="F245" s="479">
+        <f>F242+F243+F244</f>
         <v/>
       </c>
     </row>
@@ -16091,103 +16104,110 @@
       <c r="A246" s="83" t="n"/>
       <c r="B246" s="46" t="inlineStr">
         <is>
-          <t>IVA sobre Utilidad (19%)</t>
+          <t>COSTO DIRECTO + AIU</t>
         </is>
       </c>
       <c r="C246" s="681" t="n"/>
       <c r="D246" s="681" t="n"/>
-      <c r="E246" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$32</f>
-        <v/>
-      </c>
+      <c r="E246" s="47" t="n"/>
       <c r="F246" s="482">
-        <f>F243*E246</f>
-        <v/>
-      </c>
-    </row>
-    <row r="247">
+        <f>F240+F245</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247" ht="15" customHeight="1" s="1223">
       <c r="A247" s="83" t="n"/>
-      <c r="B247" s="681" t="n"/>
+      <c r="B247" s="46" t="inlineStr">
+        <is>
+          <t>IVA sobre Utilidad (19%)</t>
+        </is>
+      </c>
       <c r="C247" s="681" t="n"/>
       <c r="D247" s="681" t="n"/>
-      <c r="E247" s="681" t="n"/>
-      <c r="F247" s="675" t="n"/>
-    </row>
-    <row r="248" ht="24" customHeight="1" s="1223">
-      <c r="A248" s="87" t="n"/>
-      <c r="B248" s="677" t="inlineStr">
+      <c r="E247" s="481">
+        <f>'Ficha Técnica del Proyecto'!$B$32</f>
+        <v/>
+      </c>
+      <c r="F247" s="482">
+        <f>F244*E247</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="83" t="n"/>
+      <c r="B248" s="681" t="n"/>
+      <c r="C248" s="681" t="n"/>
+      <c r="D248" s="681" t="n"/>
+      <c r="E248" s="681" t="n"/>
+      <c r="F248" s="675" t="n"/>
+    </row>
+    <row r="249" ht="24" customHeight="1" s="1223">
+      <c r="A249" s="87" t="n"/>
+      <c r="B249" s="677" t="inlineStr">
         <is>
           <t>PRESUPUESTO TOTAL DE OBRA</t>
         </is>
       </c>
-      <c r="C248" s="530" t="n"/>
-      <c r="D248" s="530" t="n"/>
-      <c r="E248" s="530" t="n"/>
-      <c r="F248" s="483">
-        <f>F245+F246</f>
-        <v/>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="88" t="n"/>
-      <c r="B249" s="206" t="inlineStr">
-        <is>
-          <t>REV. 10/09/2026</t>
-        </is>
-      </c>
-      <c r="C249" s="281" t="n"/>
-      <c r="D249" s="281" t="n"/>
-      <c r="E249" s="281" t="n"/>
-      <c r="F249" s="350">
-        <f>F6</f>
+      <c r="C249" s="530" t="n"/>
+      <c r="D249" s="530" t="n"/>
+      <c r="E249" s="530" t="n"/>
+      <c r="F249" s="483">
+        <f>F246+F247</f>
         <v/>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="88" t="n"/>
-      <c r="B250" s="206" t="n"/>
+      <c r="B250" s="206" t="inlineStr">
+        <is>
+          <t>REV. 10/09/2026</t>
+        </is>
+      </c>
       <c r="C250" s="281" t="n"/>
       <c r="D250" s="281" t="n"/>
       <c r="E250" s="281" t="n"/>
-      <c r="F250" s="204" t="n"/>
-    </row>
-    <row r="251" ht="15" customHeight="1" s="1223">
+      <c r="F250" s="350">
+        <f>F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251">
       <c r="A251" s="88" t="n"/>
-      <c r="B251" s="90" t="inlineStr">
+      <c r="B251" s="206" t="n"/>
+      <c r="C251" s="281" t="n"/>
+      <c r="D251" s="281" t="n"/>
+      <c r="E251" s="281" t="n"/>
+      <c r="F251" s="204" t="n"/>
+    </row>
+    <row r="252" ht="15" customHeight="1" s="1223">
+      <c r="A252" s="88" t="n"/>
+      <c r="B252" s="90" t="inlineStr">
         <is>
           <t>Costo por m² construido (sobre Costo Directo Total)</t>
         </is>
       </c>
-      <c r="C251" s="91" t="n"/>
-      <c r="D251" s="91" t="n"/>
-      <c r="E251" s="91" t="n"/>
-      <c r="F251" s="484">
-        <f>F239/'Ficha Técnica del Proyecto'!$B$21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252" ht="15" customHeight="1" s="1223">
-      <c r="A252" s="89" t="n"/>
-      <c r="B252" s="92" t="inlineStr">
+      <c r="C252" s="91" t="n"/>
+      <c r="D252" s="91" t="n"/>
+      <c r="E252" s="91" t="n"/>
+      <c r="F252" s="484">
+        <f>F240/'Ficha Técnica del Proyecto'!$B$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" ht="15" customHeight="1" s="1223">
+      <c r="A253" s="89" t="n"/>
+      <c r="B253" s="92" t="inlineStr">
         <is>
           <t>Costo por m² construido (sobre Presupuesto Total)</t>
         </is>
       </c>
-      <c r="C252" s="93" t="n"/>
-      <c r="D252" s="93" t="n"/>
-      <c r="E252" s="93" t="n"/>
-      <c r="F252" s="485">
-        <f>F248/'Ficha Técnica del Proyecto'!$B$21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="27" t="n"/>
-      <c r="B253" s="281" t="n"/>
-      <c r="C253" s="281" t="n"/>
-      <c r="D253" s="281" t="n"/>
-      <c r="E253" s="281" t="n"/>
-      <c r="F253" s="281" t="n"/>
+      <c r="C253" s="93" t="n"/>
+      <c r="D253" s="93" t="n"/>
+      <c r="E253" s="93" t="n"/>
+      <c r="F253" s="485">
+        <f>F249/'Ficha Técnica del Proyecto'!$B$21</f>
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="27" t="n"/>
@@ -16229,69 +16249,77 @@
       <c r="E258" s="281" t="n"/>
       <c r="F258" s="281" t="n"/>
     </row>
+    <row r="259">
+      <c r="A259" s="27" t="n"/>
+      <c r="B259" s="281" t="n"/>
+      <c r="C259" s="281" t="n"/>
+      <c r="D259" s="281" t="n"/>
+      <c r="E259" s="281" t="n"/>
+      <c r="F259" s="281" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B211:E211"/>
-    <mergeCell ref="B226:E226"/>
-    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B233:F233"/>
+    <mergeCell ref="B109:F109"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B232:F232"/>
-    <mergeCell ref="B141:F141"/>
-    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B200:F200"/>
+    <mergeCell ref="B194:F194"/>
+    <mergeCell ref="B192:E192"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="B199:F199"/>
-    <mergeCell ref="B68:E68"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B193:F193"/>
-    <mergeCell ref="B139:E139"/>
-    <mergeCell ref="B122:F122"/>
-    <mergeCell ref="B80:E80"/>
-    <mergeCell ref="B220:F220"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B214:F214"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B102:F102"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B70:F70"/>
     <mergeCell ref="B130:F130"/>
-    <mergeCell ref="B197:E197"/>
-    <mergeCell ref="B228:F228"/>
-    <mergeCell ref="B237:E237"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B129:E129"/>
     <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B229:F229"/>
+    <mergeCell ref="B227:E227"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B185:E185"/>
     <mergeCell ref="B81:E81"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B148:F148"/>
-    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B93:E93"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B184:E184"/>
+    <mergeCell ref="B140:E140"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="B248:E248"/>
-    <mergeCell ref="B161:E161"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B219:E219"/>
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B187:F187"/>
     <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B83:F83"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B175:E175"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="C1:F3"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B249:E249"/>
+    <mergeCell ref="B162:E162"/>
     <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B191:E191"/>
-    <mergeCell ref="B213:F213"/>
-    <mergeCell ref="B94:F94"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B221:F221"/>
+    <mergeCell ref="B41:F41"/>
   </mergeCells>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.5118110236220472" footer="0.5118110236220472"/>
   <pageSetup orientation="portrait" paperSize="9" scale="53" horizontalDpi="300" verticalDpi="300"/>
@@ -16480,7 +16508,7 @@
         <v/>
       </c>
       <c r="D12" s="487">
-        <f>C12/'Presupuesto '!$F$239</f>
+        <f>C12/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E12" s="686">
@@ -16505,7 +16533,7 @@
         <v/>
       </c>
       <c r="D13" s="487">
-        <f>C13/'Presupuesto '!$F$239</f>
+        <f>C13/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E13" s="686">
@@ -16530,7 +16558,7 @@
         <v/>
       </c>
       <c r="D14" s="487">
-        <f>C14/'Presupuesto '!$F$239</f>
+        <f>C14/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E14" s="686">
@@ -16551,11 +16579,11 @@
         </is>
       </c>
       <c r="C15" s="486">
-        <f>'Presupuesto '!F68</f>
+        <f>'Presupuesto '!F69</f>
         <v/>
       </c>
       <c r="D15" s="487">
-        <f>C15/'Presupuesto '!$F$239</f>
+        <f>C15/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E15" s="686">
@@ -16576,11 +16604,11 @@
         </is>
       </c>
       <c r="C16" s="486">
-        <f>'Presupuesto '!F80</f>
+        <f>'Presupuesto '!F81</f>
         <v/>
       </c>
       <c r="D16" s="487">
-        <f>C16/'Presupuesto '!$F$239</f>
+        <f>C16/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E16" s="686">
@@ -16601,11 +16629,11 @@
         </is>
       </c>
       <c r="C17" s="486">
-        <f>'Presupuesto '!F92</f>
+        <f>'Presupuesto '!F93</f>
         <v/>
       </c>
       <c r="D17" s="487">
-        <f>C17/'Presupuesto '!$F$239</f>
+        <f>C17/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E17" s="686">
@@ -16626,11 +16654,11 @@
         </is>
       </c>
       <c r="C18" s="486">
-        <f>'Presupuesto '!F99</f>
+        <f>'Presupuesto '!F100</f>
         <v/>
       </c>
       <c r="D18" s="487">
-        <f>C18/'Presupuesto '!$F$239</f>
+        <f>C18/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E18" s="686">
@@ -16651,11 +16679,11 @@
         </is>
       </c>
       <c r="C19" s="486">
-        <f>'Presupuesto '!F106</f>
+        <f>'Presupuesto '!F107</f>
         <v/>
       </c>
       <c r="D19" s="487">
-        <f>C19/'Presupuesto '!$F$239</f>
+        <f>C19/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E19" s="686">
@@ -16676,11 +16704,11 @@
         </is>
       </c>
       <c r="C20" s="486">
-        <f>'Presupuesto '!F120</f>
+        <f>'Presupuesto '!F121</f>
         <v/>
       </c>
       <c r="D20" s="487">
-        <f>C20/'Presupuesto '!$F$239</f>
+        <f>C20/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E20" s="686">
@@ -16701,11 +16729,11 @@
         </is>
       </c>
       <c r="C21" s="486">
-        <f>'Presupuesto '!F128</f>
+        <f>'Presupuesto '!F129</f>
         <v/>
       </c>
       <c r="D21" s="487">
-        <f>C21/'Presupuesto '!$F$239</f>
+        <f>C21/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E21" s="686">
@@ -16726,11 +16754,11 @@
         </is>
       </c>
       <c r="C22" s="486">
-        <f>'Presupuesto '!F139</f>
+        <f>'Presupuesto '!F140</f>
         <v/>
       </c>
       <c r="D22" s="487">
-        <f>C22/'Presupuesto '!$F$239</f>
+        <f>C22/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E22" s="686">
@@ -16751,11 +16779,11 @@
         </is>
       </c>
       <c r="C23" s="486">
-        <f>'Presupuesto '!F146</f>
+        <f>'Presupuesto '!F147</f>
         <v/>
       </c>
       <c r="D23" s="487">
-        <f>C23/'Presupuesto '!$F$239</f>
+        <f>C23/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E23" s="686">
@@ -16776,11 +16804,11 @@
         </is>
       </c>
       <c r="C24" s="486">
-        <f>'Presupuesto '!F248</f>
+        <f>'Presupuesto '!F249</f>
         <v/>
       </c>
       <c r="D24" s="487">
-        <f>C24/'Presupuesto '!$F$239</f>
+        <f>C24/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E24" s="686">
@@ -16801,11 +16829,11 @@
         </is>
       </c>
       <c r="C25" s="486">
-        <f>'Presupuesto '!F175</f>
+        <f>'Presupuesto '!F176</f>
         <v/>
       </c>
       <c r="D25" s="487">
-        <f>C25/'Presupuesto '!$F$239</f>
+        <f>C25/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E25" s="686">
@@ -16826,11 +16854,11 @@
         </is>
       </c>
       <c r="C26" s="486">
-        <f>'Presupuesto '!F184</f>
+        <f>'Presupuesto '!F185</f>
         <v/>
       </c>
       <c r="D26" s="487">
-        <f>C26/'Presupuesto '!$F$239</f>
+        <f>C26/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E26" s="686">
@@ -16851,11 +16879,11 @@
         </is>
       </c>
       <c r="C27" s="486">
-        <f>'Presupuesto '!F191</f>
+        <f>'Presupuesto '!F192</f>
         <v/>
       </c>
       <c r="D27" s="487">
-        <f>C27/'Presupuesto '!$F$239</f>
+        <f>C27/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E27" s="686">
@@ -16876,11 +16904,11 @@
         </is>
       </c>
       <c r="C28" s="486">
-        <f>'Presupuesto '!F197</f>
+        <f>'Presupuesto '!F198</f>
         <v/>
       </c>
       <c r="D28" s="487">
-        <f>C28/'Presupuesto '!$F$239</f>
+        <f>C28/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E28" s="686">
@@ -16901,11 +16929,11 @@
         </is>
       </c>
       <c r="C29" s="486">
-        <f>'Presupuesto '!F211</f>
+        <f>'Presupuesto '!F212</f>
         <v/>
       </c>
       <c r="D29" s="487">
-        <f>C29/'Presupuesto '!$F$239</f>
+        <f>C29/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E29" s="686">
@@ -16926,11 +16954,11 @@
         </is>
       </c>
       <c r="C30" s="486">
-        <f>'Presupuesto '!F218</f>
+        <f>'Presupuesto '!F219</f>
         <v/>
       </c>
       <c r="D30" s="487">
-        <f>C30/'Presupuesto '!$F$239</f>
+        <f>C30/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E30" s="686">
@@ -16951,11 +16979,11 @@
         </is>
       </c>
       <c r="C31" s="486">
-        <f>'Presupuesto '!F226</f>
+        <f>'Presupuesto '!F227</f>
         <v/>
       </c>
       <c r="D31" s="487">
-        <f>C31/'Presupuesto '!$F$239</f>
+        <f>C31/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E31" s="686">
@@ -16976,11 +17004,11 @@
         </is>
       </c>
       <c r="C32" s="486">
-        <f>'Presupuesto '!F230</f>
+        <f>'Presupuesto '!F231</f>
         <v/>
       </c>
       <c r="D32" s="487">
-        <f>C32/'Presupuesto '!$F$239</f>
+        <f>C32/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E32" s="686">
@@ -17001,11 +17029,11 @@
         </is>
       </c>
       <c r="C33" s="486">
-        <f>'Presupuesto '!F237</f>
+        <f>'Presupuesto '!F238</f>
         <v/>
       </c>
       <c r="D33" s="487">
-        <f>C33/'Presupuesto '!$F$239</f>
+        <f>C33/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E33" s="687">
@@ -17026,7 +17054,7 @@
         <v/>
       </c>
       <c r="D34" s="489">
-        <f>C34/'Presupuesto '!$F$239</f>
+        <f>C34/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E34" s="695">
@@ -17104,7 +17132,7 @@
         </is>
       </c>
       <c r="C40" s="490">
-        <f>'Presupuesto '!F248</f>
+        <f>'Presupuesto '!F249</f>
         <v/>
       </c>
       <c r="D40" s="182" t="n"/>

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -16,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
@@ -25,6 +25,7 @@
     <numFmt numFmtId="169" formatCode="&quot;$ &quot;#,##0"/>
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
+    <numFmt numFmtId="172" formatCode="$ #,##0"/>
   </numFmts>
   <fonts count="170">
     <font>
@@ -1690,7 +1691,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="411">
+  <borders count="412">
     <border>
       <left/>
       <right/>
@@ -6575,6 +6576,20 @@
       </top>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="5">
@@ -6584,7 +6599,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1309">
+  <cellXfs count="1313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9814,6 +9829,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="28" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10746,7 +10773,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E47"/>
@@ -11317,7 +11343,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F259"/>
@@ -16331,7 +16356,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F42"/>

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -10405,31 +10405,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -6599,7 +6599,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1313">
+  <cellXfs count="1319">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9841,6 +9841,16 @@
     <xf numFmtId="0" fontId="124" fillId="28" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="48" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="36" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10748,6 +10758,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E47"/>
@@ -11267,6 +11278,7 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11299,9 +11311,8 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="C35:E35"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
@@ -11318,6 +11329,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F259"/>
@@ -16331,6 +16343,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F42"/>

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -10758,7 +10758,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E47"/>
@@ -11329,7 +11328,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F259"/>
@@ -16343,7 +16341,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F42"/>

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ficha Técnica del Proyecto" sheetId="1" r:id="rId1"/>
-    <sheet name="Presupuesto " sheetId="2" r:id="rId12"/>
-    <sheet name="Resumen" sheetId="3" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ficha Técnica del Proyecto" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Presupuesto " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -6685,7 +6686,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1447">
+  <cellXfs count="1449">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -10285,6 +10286,8 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="166" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10461,7 +10464,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -11206,7 +11209,6 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11239,8 +11241,9 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
@@ -11253,7 +11256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
@@ -12263,6 +12266,8 @@
           <t>M³</t>
         </is>
       </c>
+      <c r="D53" s="1447" t="n"/>
+      <c r="E53" s="1448" t="n"/>
       <c r="F53">
         <f>D53*E53</f>
         <v/>
@@ -12399,6 +12404,8 @@
           <t>KG</t>
         </is>
       </c>
+      <c r="D59" s="1447" t="n"/>
+      <c r="E59" s="1448" t="n"/>
       <c r="F59" s="1311">
         <f>D59*E59</f>
         <v/>
@@ -12443,6 +12450,8 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D61" s="1447" t="n"/>
+      <c r="E61" s="1448" t="n"/>
       <c r="F61">
         <f>D61*E61</f>
         <v/>
@@ -12910,6 +12919,8 @@
           <t>KG</t>
         </is>
       </c>
+      <c r="D84" s="1447" t="n"/>
+      <c r="E84" s="1448" t="n"/>
       <c r="F84">
         <f>D84*E84</f>
         <v/>
@@ -13177,6 +13188,8 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D97" s="1447" t="n"/>
+      <c r="E97" s="1448" t="n"/>
       <c r="F97">
         <f>D97*E97</f>
         <v/>
@@ -13283,6 +13296,8 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D103" s="1447" t="n"/>
+      <c r="E103" s="1448" t="n"/>
       <c r="F103">
         <f>D103*E103</f>
         <v/>
@@ -13350,6 +13365,8 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D106" s="1447" t="n"/>
+      <c r="E106" s="1448" t="n"/>
       <c r="F106" s="1311">
         <f>D106*E106</f>
         <v/>
@@ -13525,6 +13542,8 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D115" s="1447" t="n"/>
+      <c r="E115" s="1448" t="n"/>
       <c r="F115" s="1311">
         <f>D115*E115</f>
         <v/>
@@ -13569,6 +13588,8 @@
           <t>ML</t>
         </is>
       </c>
+      <c r="D117" s="1447" t="n"/>
+      <c r="E117" s="1448" t="n"/>
       <c r="F117">
         <f>D117*E117</f>
         <v/>
@@ -13590,6 +13611,8 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D118" s="1447" t="n"/>
+      <c r="E118" s="1448" t="n"/>
       <c r="F118">
         <f>D118*E118</f>
         <v/>
@@ -13611,6 +13634,8 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D119" s="1447" t="n"/>
+      <c r="E119" s="1448" t="n"/>
       <c r="F119">
         <f>D119*E119</f>
         <v/>
@@ -13632,6 +13657,8 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D120" s="1447" t="n"/>
+      <c r="E120" s="1448" t="n"/>
       <c r="F120">
         <f>D120*E120</f>
         <v/>
@@ -13784,6 +13811,8 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D128" s="1447" t="n"/>
+      <c r="E128" s="1448" t="n"/>
       <c r="F128" s="1311">
         <f>D128*E128</f>
         <v/>
@@ -13867,6 +13896,8 @@
           <t>ML</t>
         </is>
       </c>
+      <c r="D133" s="1447" t="n"/>
+      <c r="E133" s="1448" t="n"/>
       <c r="F133" s="1311">
         <f>D133*E133</f>
         <v/>
@@ -13911,6 +13942,8 @@
           <t>ML</t>
         </is>
       </c>
+      <c r="D135" s="1447" t="n"/>
+      <c r="E135" s="1448" t="n"/>
       <c r="F135">
         <f>D135*E135</f>
         <v/>
@@ -14063,6 +14096,8 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D143" s="1447" t="n"/>
+      <c r="E143" s="1448" t="n"/>
       <c r="F143" s="1311">
         <f>D143*E143</f>
         <v/>
@@ -14107,6 +14142,8 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D145" s="1447" t="n"/>
+      <c r="E145" s="1448" t="n"/>
       <c r="F145">
         <f>D145*E145</f>
         <v/>
@@ -14190,6 +14227,8 @@
           <t>ML</t>
         </is>
       </c>
+      <c r="D150" s="1447" t="n"/>
+      <c r="E150" s="1448" t="n"/>
       <c r="F150" s="1311">
         <f>D150*E150</f>
         <v/>
@@ -14234,6 +14273,8 @@
           <t>UND</t>
         </is>
       </c>
+      <c r="D152" s="1447" t="n"/>
+      <c r="E152" s="1448" t="n"/>
       <c r="F152" s="1311">
         <f>D152*E152</f>
         <v/>
@@ -16266,7 +16307,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -17,7 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="&quot;$ &quot;#,##0"/>
@@ -27,8 +27,9 @@
     <numFmt numFmtId="170" formatCode="&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="\$\ #,##0"/>
     <numFmt numFmtId="172" formatCode="$ #,##0"/>
+    <numFmt numFmtId="173" formatCode="&quot;$ &quot;#,##0.00"/>
   </numFmts>
-  <fonts count="167">
+  <fonts count="168">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1221,6 +1222,11 @@
       <color rgb="008A8F99"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="76">
     <fill>
@@ -6686,7 +6692,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1449">
+  <cellXfs count="1453">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -10288,6 +10294,12 @@
     <xf numFmtId="0" fontId="166" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="167" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="167" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="167" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11209,6 +11221,7 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11241,9 +11254,8 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="C35:E35"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
@@ -11483,7 +11495,7 @@
         </is>
       </c>
       <c r="D15" s="258" t="n"/>
-      <c r="E15" s="1310" t="n"/>
+      <c r="E15" s="1451" t="n"/>
       <c r="F15" s="1311">
         <f>D15*E15</f>
         <v/>
@@ -11506,7 +11518,7 @@
         </is>
       </c>
       <c r="D16" s="258" t="n"/>
-      <c r="E16" s="1310" t="n"/>
+      <c r="E16" s="1451" t="n"/>
       <c r="F16" s="1311">
         <f>D16*E16</f>
         <v/>
@@ -11529,7 +11541,7 @@
         </is>
       </c>
       <c r="D17" s="258" t="n"/>
-      <c r="E17" s="1310" t="n"/>
+      <c r="E17" s="1451" t="n"/>
       <c r="F17" s="1311">
         <f>D17*E17</f>
         <v/>
@@ -11552,7 +11564,7 @@
         </is>
       </c>
       <c r="D18" s="258" t="n"/>
-      <c r="E18" s="1310" t="n"/>
+      <c r="E18" s="1451" t="n"/>
       <c r="F18" s="1311">
         <f>D18*E18</f>
         <v/>
@@ -11575,7 +11587,7 @@
         </is>
       </c>
       <c r="D19" s="258" t="n"/>
-      <c r="E19" s="1310" t="n"/>
+      <c r="E19" s="1451" t="n"/>
       <c r="F19" s="1311">
         <f>D19*E19</f>
         <v/>
@@ -11598,7 +11610,7 @@
         </is>
       </c>
       <c r="D20" s="258" t="n"/>
-      <c r="E20" s="1310" t="n"/>
+      <c r="E20" s="1451" t="n"/>
       <c r="F20" s="1311">
         <f>D20*E20</f>
         <v/>
@@ -11621,7 +11633,7 @@
         </is>
       </c>
       <c r="D21" s="258" t="n"/>
-      <c r="E21" s="1310" t="n"/>
+      <c r="E21" s="1451" t="n"/>
       <c r="F21" s="1311">
         <f>D21*E21</f>
         <v/>
@@ -11644,7 +11656,7 @@
         </is>
       </c>
       <c r="D22" s="258" t="n"/>
-      <c r="E22" s="1310" t="n"/>
+      <c r="E22" s="1451" t="n"/>
       <c r="F22" s="1311">
         <f>D22*E22</f>
         <v/>
@@ -11667,7 +11679,7 @@
         </is>
       </c>
       <c r="D23" s="258" t="n"/>
-      <c r="E23" s="1310" t="n"/>
+      <c r="E23" s="1451" t="n"/>
       <c r="F23" s="1311">
         <f>D23*E23</f>
         <v/>
@@ -11690,7 +11702,7 @@
         </is>
       </c>
       <c r="D24" s="258" t="n"/>
-      <c r="E24" s="1310" t="n"/>
+      <c r="E24" s="1451" t="n"/>
       <c r="F24" s="1311">
         <f>D24*E24</f>
         <v/>
@@ -11752,7 +11764,7 @@
         </is>
       </c>
       <c r="D28" s="258" t="n"/>
-      <c r="E28" s="1310" t="n"/>
+      <c r="E28" s="1451" t="n"/>
       <c r="F28" s="1311">
         <f>D28*E28</f>
         <v/>
@@ -11775,7 +11787,7 @@
         </is>
       </c>
       <c r="D29" s="258" t="n"/>
-      <c r="E29" s="1310" t="n"/>
+      <c r="E29" s="1451" t="n"/>
       <c r="F29" s="1311">
         <f>D29*E29</f>
         <v/>
@@ -11798,7 +11810,7 @@
         </is>
       </c>
       <c r="D30" s="258" t="n"/>
-      <c r="E30" s="1310" t="n"/>
+      <c r="E30" s="1451" t="n"/>
       <c r="F30" s="1311">
         <f>D30*E30</f>
         <v/>
@@ -11821,7 +11833,7 @@
         </is>
       </c>
       <c r="D31" s="258" t="n"/>
-      <c r="E31" s="1310" t="n"/>
+      <c r="E31" s="1451" t="n"/>
       <c r="F31" s="1311">
         <f>D31*E31</f>
         <v/>
@@ -11844,7 +11856,7 @@
         </is>
       </c>
       <c r="D32" s="258" t="n"/>
-      <c r="E32" s="1310" t="n"/>
+      <c r="E32" s="1451" t="n"/>
       <c r="F32" s="1311">
         <f>D32*E32</f>
         <v/>
@@ -11867,7 +11879,7 @@
         </is>
       </c>
       <c r="D33" s="258" t="n"/>
-      <c r="E33" s="1310" t="n"/>
+      <c r="E33" s="1451" t="n"/>
       <c r="F33" s="1311">
         <f>D33*E33</f>
         <v/>
@@ -11890,7 +11902,7 @@
         </is>
       </c>
       <c r="D34" s="258" t="n"/>
-      <c r="E34" s="1310" t="n"/>
+      <c r="E34" s="1451" t="n"/>
       <c r="F34" s="1311">
         <f>D34*E34</f>
         <v/>
@@ -11913,7 +11925,7 @@
         </is>
       </c>
       <c r="D35" s="258" t="n"/>
-      <c r="E35" s="1310" t="n"/>
+      <c r="E35" s="1451" t="n"/>
       <c r="F35" s="1311">
         <f>D35*E35</f>
         <v/>
@@ -11936,7 +11948,7 @@
         </is>
       </c>
       <c r="D36" s="258" t="n"/>
-      <c r="E36" s="1310" t="n"/>
+      <c r="E36" s="1451" t="n"/>
       <c r="F36" s="1311">
         <f>D36*E36</f>
         <v/>
@@ -11959,7 +11971,7 @@
         </is>
       </c>
       <c r="D37" s="258" t="n"/>
-      <c r="E37" s="1310" t="n"/>
+      <c r="E37" s="1451" t="n"/>
       <c r="F37" s="1311">
         <f>D37*E37</f>
         <v/>
@@ -11982,7 +11994,7 @@
         </is>
       </c>
       <c r="D38" s="258" t="n"/>
-      <c r="E38" s="1310" t="n"/>
+      <c r="E38" s="1451" t="n"/>
       <c r="F38" s="1311">
         <f>D38*E38</f>
         <v/>
@@ -12044,7 +12056,7 @@
         </is>
       </c>
       <c r="D42" s="258" t="n"/>
-      <c r="E42" s="1310" t="n"/>
+      <c r="E42" s="1451" t="n"/>
       <c r="F42" s="1311">
         <f>D42*E42</f>
         <v/>
@@ -12067,7 +12079,7 @@
         </is>
       </c>
       <c r="D43" s="258" t="n"/>
-      <c r="E43" s="1310" t="n"/>
+      <c r="E43" s="1451" t="n"/>
       <c r="F43" s="1311">
         <f>D43*E43</f>
         <v/>
@@ -12090,7 +12102,7 @@
         </is>
       </c>
       <c r="D44" s="258" t="n"/>
-      <c r="E44" s="1310" t="n"/>
+      <c r="E44" s="1451" t="n"/>
       <c r="F44" s="1311">
         <f>D44*E44</f>
         <v/>
@@ -12113,7 +12125,7 @@
         </is>
       </c>
       <c r="D45" s="258" t="n"/>
-      <c r="E45" s="1310" t="n"/>
+      <c r="E45" s="1451" t="n"/>
       <c r="F45" s="1311">
         <f>D45*E45</f>
         <v/>
@@ -12136,7 +12148,7 @@
         </is>
       </c>
       <c r="D46" s="258" t="n"/>
-      <c r="E46" s="1310" t="n"/>
+      <c r="E46" s="1451" t="n"/>
       <c r="F46" s="1311">
         <f>D46*E46</f>
         <v/>
@@ -12159,7 +12171,7 @@
         </is>
       </c>
       <c r="D47" s="258" t="n"/>
-      <c r="E47" s="1310" t="n"/>
+      <c r="E47" s="1451" t="n"/>
       <c r="F47" s="1311">
         <f>D47*E47</f>
         <v/>
@@ -12182,7 +12194,7 @@
         </is>
       </c>
       <c r="D48" s="258" t="n"/>
-      <c r="E48" s="1310" t="n"/>
+      <c r="E48" s="1451" t="n"/>
       <c r="F48" s="1311">
         <f>D48*E48</f>
         <v/>
@@ -12244,7 +12256,7 @@
         </is>
       </c>
       <c r="D52" s="258" t="n"/>
-      <c r="E52" s="1310" t="n"/>
+      <c r="E52" s="1451" t="n"/>
       <c r="F52" s="1311">
         <f>D52*E52</f>
         <v/>
@@ -12266,9 +12278,9 @@
           <t>M³</t>
         </is>
       </c>
-      <c r="D53" s="1447" t="n"/>
-      <c r="E53" s="1448" t="n"/>
-      <c r="F53">
+      <c r="D53" s="1449" t="n"/>
+      <c r="E53" s="1452" t="n"/>
+      <c r="F53" s="1448">
         <f>D53*E53</f>
         <v/>
       </c>
@@ -12290,7 +12302,7 @@
         </is>
       </c>
       <c r="D54" s="258" t="n"/>
-      <c r="E54" s="1310" t="n"/>
+      <c r="E54" s="1451" t="n"/>
       <c r="F54" s="1311">
         <f>D54*E54</f>
         <v/>
@@ -12313,7 +12325,7 @@
         </is>
       </c>
       <c r="D55" s="258" t="n"/>
-      <c r="E55" s="1310" t="n"/>
+      <c r="E55" s="1451" t="n"/>
       <c r="F55" s="1311">
         <f>D55*E55</f>
         <v/>
@@ -12336,7 +12348,7 @@
         </is>
       </c>
       <c r="D56" s="258" t="n"/>
-      <c r="E56" s="1310" t="n"/>
+      <c r="E56" s="1451" t="n"/>
       <c r="F56" s="1311">
         <f>D56*E56</f>
         <v/>
@@ -12359,7 +12371,7 @@
         </is>
       </c>
       <c r="D57" s="258" t="n"/>
-      <c r="E57" s="1310" t="n"/>
+      <c r="E57" s="1451" t="n"/>
       <c r="F57" s="1311">
         <f>D57*E57</f>
         <v/>
@@ -12382,7 +12394,7 @@
         </is>
       </c>
       <c r="D58" s="258" t="n"/>
-      <c r="E58" s="1310" t="n"/>
+      <c r="E58" s="1451" t="n"/>
       <c r="F58" s="1311">
         <f>D58*E58</f>
         <v/>
@@ -12404,8 +12416,8 @@
           <t>KG</t>
         </is>
       </c>
-      <c r="D59" s="1447" t="n"/>
-      <c r="E59" s="1448" t="n"/>
+      <c r="D59" s="1449" t="n"/>
+      <c r="E59" s="1452" t="n"/>
       <c r="F59" s="1311">
         <f>D59*E59</f>
         <v/>
@@ -12428,7 +12440,7 @@
         </is>
       </c>
       <c r="D60" s="258" t="n"/>
-      <c r="E60" s="1310" t="n"/>
+      <c r="E60" s="1451" t="n"/>
       <c r="F60" s="1311">
         <f>D60*E60</f>
         <v/>
@@ -12450,9 +12462,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D61" s="1447" t="n"/>
-      <c r="E61" s="1448" t="n"/>
-      <c r="F61">
+      <c r="D61" s="1449" t="n"/>
+      <c r="E61" s="1452" t="n"/>
+      <c r="F61" s="1448">
         <f>D61*E61</f>
         <v/>
       </c>
@@ -12474,7 +12486,7 @@
         </is>
       </c>
       <c r="D62" s="258" t="n"/>
-      <c r="E62" s="1310" t="n"/>
+      <c r="E62" s="1451" t="n"/>
       <c r="F62" s="1311">
         <f>D62*E62</f>
         <v/>
@@ -12497,7 +12509,7 @@
         </is>
       </c>
       <c r="D63" s="258" t="n"/>
-      <c r="E63" s="1310" t="n"/>
+      <c r="E63" s="1451" t="n"/>
       <c r="F63" s="1311">
         <f>D63*E63</f>
         <v/>
@@ -12520,7 +12532,7 @@
         </is>
       </c>
       <c r="D64" s="258" t="n"/>
-      <c r="E64" s="1310" t="n"/>
+      <c r="E64" s="1451" t="n"/>
       <c r="F64" s="1311">
         <f>D64*E64</f>
         <v/>
@@ -12543,7 +12555,7 @@
         </is>
       </c>
       <c r="D65" s="258" t="n"/>
-      <c r="E65" s="1310" t="n"/>
+      <c r="E65" s="1451" t="n"/>
       <c r="F65" s="1311">
         <f>D65*E65</f>
         <v/>
@@ -12566,7 +12578,7 @@
         </is>
       </c>
       <c r="D66" s="258" t="n"/>
-      <c r="E66" s="1310" t="n"/>
+      <c r="E66" s="1451" t="n"/>
       <c r="F66" s="1311">
         <f>D66*E66</f>
         <v/>
@@ -12589,7 +12601,7 @@
         </is>
       </c>
       <c r="D67" s="258" t="n"/>
-      <c r="E67" s="1310" t="n"/>
+      <c r="E67" s="1451" t="n"/>
       <c r="F67" s="1311">
         <f>D67*E67</f>
         <v/>
@@ -12612,7 +12624,7 @@
         </is>
       </c>
       <c r="D68" s="258" t="n"/>
-      <c r="E68" s="1310" t="n"/>
+      <c r="E68" s="1451" t="n"/>
       <c r="F68" s="1311">
         <f>D68*E68</f>
         <v/>
@@ -12674,7 +12686,7 @@
         </is>
       </c>
       <c r="D72" s="258" t="n"/>
-      <c r="E72" s="1310" t="n"/>
+      <c r="E72" s="1451" t="n"/>
       <c r="F72" s="1311">
         <f>D72*E72</f>
         <v/>
@@ -12697,7 +12709,7 @@
         </is>
       </c>
       <c r="D73" s="258" t="n"/>
-      <c r="E73" s="1310" t="n"/>
+      <c r="E73" s="1451" t="n"/>
       <c r="F73" s="1311">
         <f>D73*E73</f>
         <v/>
@@ -12720,7 +12732,7 @@
         </is>
       </c>
       <c r="D74" s="258" t="n"/>
-      <c r="E74" s="1310" t="n"/>
+      <c r="E74" s="1451" t="n"/>
       <c r="F74" s="1311">
         <f>D74*E74</f>
         <v/>
@@ -12743,7 +12755,7 @@
         </is>
       </c>
       <c r="D75" s="258" t="n"/>
-      <c r="E75" s="1310" t="n"/>
+      <c r="E75" s="1451" t="n"/>
       <c r="F75" s="1311">
         <f>D75*E75</f>
         <v/>
@@ -12766,7 +12778,7 @@
         </is>
       </c>
       <c r="D76" s="258" t="n"/>
-      <c r="E76" s="1310" t="n"/>
+      <c r="E76" s="1451" t="n"/>
       <c r="F76" s="1311">
         <f>D76*E76</f>
         <v/>
@@ -12789,7 +12801,7 @@
         </is>
       </c>
       <c r="D77" s="258" t="n"/>
-      <c r="E77" s="1310" t="n"/>
+      <c r="E77" s="1451" t="n"/>
       <c r="F77" s="1311">
         <f>D77*E77</f>
         <v/>
@@ -12812,7 +12824,7 @@
         </is>
       </c>
       <c r="D78" s="258" t="n"/>
-      <c r="E78" s="1310" t="n"/>
+      <c r="E78" s="1451" t="n"/>
       <c r="F78" s="1311">
         <f>D78*E78</f>
         <v/>
@@ -12835,7 +12847,7 @@
         </is>
       </c>
       <c r="D79" s="258" t="n"/>
-      <c r="E79" s="1310" t="n"/>
+      <c r="E79" s="1451" t="n"/>
       <c r="F79" s="1311">
         <f>D79*E79</f>
         <v/>
@@ -12858,7 +12870,7 @@
         </is>
       </c>
       <c r="D80" s="258" t="n"/>
-      <c r="E80" s="1310" t="n"/>
+      <c r="E80" s="1451" t="n"/>
       <c r="F80" s="1311">
         <f>D80*E80</f>
         <v/>
@@ -12919,9 +12931,9 @@
           <t>KG</t>
         </is>
       </c>
-      <c r="D84" s="1447" t="n"/>
-      <c r="E84" s="1448" t="n"/>
-      <c r="F84">
+      <c r="D84" s="1449" t="n"/>
+      <c r="E84" s="1452" t="n"/>
+      <c r="F84" s="1448">
         <f>D84*E84</f>
         <v/>
       </c>
@@ -12943,7 +12955,7 @@
         </is>
       </c>
       <c r="D85" s="258" t="n"/>
-      <c r="E85" s="1310" t="n"/>
+      <c r="E85" s="1451" t="n"/>
       <c r="F85" s="1311">
         <f>D85*E85</f>
         <v/>
@@ -12966,7 +12978,7 @@
         </is>
       </c>
       <c r="D86" s="258" t="n"/>
-      <c r="E86" s="1310" t="n"/>
+      <c r="E86" s="1451" t="n"/>
       <c r="F86" s="1311">
         <f>D86*E86</f>
         <v/>
@@ -12989,7 +13001,7 @@
         </is>
       </c>
       <c r="D87" s="258" t="n"/>
-      <c r="E87" s="1310" t="n"/>
+      <c r="E87" s="1451" t="n"/>
       <c r="F87" s="1311">
         <f>D87*E87</f>
         <v/>
@@ -13012,7 +13024,7 @@
         </is>
       </c>
       <c r="D88" s="258" t="n"/>
-      <c r="E88" s="1310" t="n"/>
+      <c r="E88" s="1451" t="n"/>
       <c r="F88" s="1311">
         <f>D88*E88</f>
         <v/>
@@ -13035,7 +13047,7 @@
         </is>
       </c>
       <c r="D89" s="258" t="n"/>
-      <c r="E89" s="1310" t="n"/>
+      <c r="E89" s="1451" t="n"/>
       <c r="F89" s="1311">
         <f>D89*E89</f>
         <v/>
@@ -13058,7 +13070,7 @@
         </is>
       </c>
       <c r="D90" s="258" t="n"/>
-      <c r="E90" s="1310" t="n"/>
+      <c r="E90" s="1451" t="n"/>
       <c r="F90" s="1311">
         <f>D90*E90</f>
         <v/>
@@ -13081,7 +13093,7 @@
         </is>
       </c>
       <c r="D91" s="258" t="n"/>
-      <c r="E91" s="1310" t="n"/>
+      <c r="E91" s="1451" t="n"/>
       <c r="F91" s="1311">
         <f>D91*E91</f>
         <v/>
@@ -13104,7 +13116,7 @@
         </is>
       </c>
       <c r="D92" s="258" t="n"/>
-      <c r="E92" s="1310" t="n"/>
+      <c r="E92" s="1451" t="n"/>
       <c r="F92" s="1311">
         <f>D92*E92</f>
         <v/>
@@ -13166,7 +13178,7 @@
         </is>
       </c>
       <c r="D96" s="258" t="n"/>
-      <c r="E96" s="1310" t="n"/>
+      <c r="E96" s="1451" t="n"/>
       <c r="F96" s="1311">
         <f>D96*E96</f>
         <v/>
@@ -13188,9 +13200,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D97" s="1447" t="n"/>
-      <c r="E97" s="1448" t="n"/>
-      <c r="F97">
+      <c r="D97" s="1449" t="n"/>
+      <c r="E97" s="1452" t="n"/>
+      <c r="F97" s="1448">
         <f>D97*E97</f>
         <v/>
       </c>
@@ -13212,7 +13224,7 @@
         </is>
       </c>
       <c r="D98" s="258" t="n"/>
-      <c r="E98" s="1310" t="n"/>
+      <c r="E98" s="1451" t="n"/>
       <c r="F98" s="1311">
         <f>D98*E98</f>
         <v/>
@@ -13235,7 +13247,7 @@
         </is>
       </c>
       <c r="D99" s="258" t="n"/>
-      <c r="E99" s="1310" t="n"/>
+      <c r="E99" s="1451" t="n"/>
       <c r="F99" s="1311">
         <f>D99*E99</f>
         <v/>
@@ -13296,9 +13308,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D103" s="1447" t="n"/>
-      <c r="E103" s="1448" t="n"/>
-      <c r="F103">
+      <c r="D103" s="1449" t="n"/>
+      <c r="E103" s="1452" t="n"/>
+      <c r="F103" s="1448">
         <f>D103*E103</f>
         <v/>
       </c>
@@ -13320,7 +13332,7 @@
         </is>
       </c>
       <c r="D104" s="258" t="n"/>
-      <c r="E104" s="1310" t="n"/>
+      <c r="E104" s="1451" t="n"/>
       <c r="F104" s="1311">
         <f>D104*E104</f>
         <v/>
@@ -13343,7 +13355,7 @@
         </is>
       </c>
       <c r="D105" s="258" t="n"/>
-      <c r="E105" s="1310" t="n"/>
+      <c r="E105" s="1451" t="n"/>
       <c r="F105" s="1311">
         <f>D105*E105</f>
         <v/>
@@ -13365,8 +13377,8 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D106" s="1447" t="n"/>
-      <c r="E106" s="1448" t="n"/>
+      <c r="D106" s="1449" t="n"/>
+      <c r="E106" s="1452" t="n"/>
       <c r="F106" s="1311">
         <f>D106*E106</f>
         <v/>
@@ -13428,7 +13440,7 @@
         </is>
       </c>
       <c r="D110" s="258" t="n"/>
-      <c r="E110" s="1310" t="n"/>
+      <c r="E110" s="1451" t="n"/>
       <c r="F110" s="1311">
         <f>D110*E110</f>
         <v/>
@@ -13451,7 +13463,7 @@
         </is>
       </c>
       <c r="D111" s="258" t="n"/>
-      <c r="E111" s="1310" t="n"/>
+      <c r="E111" s="1451" t="n"/>
       <c r="F111" s="1311">
         <f>D111*E111</f>
         <v/>
@@ -13474,7 +13486,7 @@
         </is>
       </c>
       <c r="D112" s="258" t="n"/>
-      <c r="E112" s="1310" t="n"/>
+      <c r="E112" s="1451" t="n"/>
       <c r="F112" s="1311">
         <f>D112*E112</f>
         <v/>
@@ -13497,7 +13509,7 @@
         </is>
       </c>
       <c r="D113" s="258" t="n"/>
-      <c r="E113" s="1310" t="n"/>
+      <c r="E113" s="1451" t="n"/>
       <c r="F113" s="1311">
         <f>D113*E113</f>
         <v/>
@@ -13520,7 +13532,7 @@
         </is>
       </c>
       <c r="D114" s="258" t="n"/>
-      <c r="E114" s="1310" t="n"/>
+      <c r="E114" s="1451" t="n"/>
       <c r="F114" s="1311">
         <f>D114*E114</f>
         <v/>
@@ -13542,8 +13554,8 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D115" s="1447" t="n"/>
-      <c r="E115" s="1448" t="n"/>
+      <c r="D115" s="1449" t="n"/>
+      <c r="E115" s="1452" t="n"/>
       <c r="F115" s="1311">
         <f>D115*E115</f>
         <v/>
@@ -13566,7 +13578,7 @@
         </is>
       </c>
       <c r="D116" s="258" t="n"/>
-      <c r="E116" s="1310" t="n"/>
+      <c r="E116" s="1451" t="n"/>
       <c r="F116" s="1311">
         <f>D116*E116</f>
         <v/>
@@ -13588,9 +13600,9 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D117" s="1447" t="n"/>
-      <c r="E117" s="1448" t="n"/>
-      <c r="F117">
+      <c r="D117" s="1449" t="n"/>
+      <c r="E117" s="1452" t="n"/>
+      <c r="F117" s="1448">
         <f>D117*E117</f>
         <v/>
       </c>
@@ -13611,9 +13623,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D118" s="1447" t="n"/>
-      <c r="E118" s="1448" t="n"/>
-      <c r="F118">
+      <c r="D118" s="1449" t="n"/>
+      <c r="E118" s="1452" t="n"/>
+      <c r="F118" s="1448">
         <f>D118*E118</f>
         <v/>
       </c>
@@ -13634,9 +13646,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D119" s="1447" t="n"/>
-      <c r="E119" s="1448" t="n"/>
-      <c r="F119">
+      <c r="D119" s="1449" t="n"/>
+      <c r="E119" s="1452" t="n"/>
+      <c r="F119" s="1448">
         <f>D119*E119</f>
         <v/>
       </c>
@@ -13657,9 +13669,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D120" s="1447" t="n"/>
-      <c r="E120" s="1448" t="n"/>
-      <c r="F120">
+      <c r="D120" s="1449" t="n"/>
+      <c r="E120" s="1452" t="n"/>
+      <c r="F120" s="1448">
         <f>D120*E120</f>
         <v/>
       </c>
@@ -13720,7 +13732,7 @@
         </is>
       </c>
       <c r="D124" s="258" t="n"/>
-      <c r="E124" s="1310" t="n"/>
+      <c r="E124" s="1451" t="n"/>
       <c r="F124" s="1311">
         <f>D124*E124</f>
         <v/>
@@ -13743,7 +13755,7 @@
         </is>
       </c>
       <c r="D125" s="258" t="n"/>
-      <c r="E125" s="1310" t="n"/>
+      <c r="E125" s="1451" t="n"/>
       <c r="F125" s="1311">
         <f>D125*E125</f>
         <v/>
@@ -13766,7 +13778,7 @@
         </is>
       </c>
       <c r="D126" s="258" t="n"/>
-      <c r="E126" s="1310" t="n"/>
+      <c r="E126" s="1451" t="n"/>
       <c r="F126" s="1311">
         <f>D126*E126</f>
         <v/>
@@ -13789,7 +13801,7 @@
         </is>
       </c>
       <c r="D127" s="258" t="n"/>
-      <c r="E127" s="1310" t="n"/>
+      <c r="E127" s="1451" t="n"/>
       <c r="F127" s="1311">
         <f>D127*E127</f>
         <v/>
@@ -13811,8 +13823,8 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D128" s="1447" t="n"/>
-      <c r="E128" s="1448" t="n"/>
+      <c r="D128" s="1449" t="n"/>
+      <c r="E128" s="1452" t="n"/>
       <c r="F128" s="1311">
         <f>D128*E128</f>
         <v/>
@@ -13874,7 +13886,7 @@
         </is>
       </c>
       <c r="D132" s="258" t="n"/>
-      <c r="E132" s="1310" t="n"/>
+      <c r="E132" s="1451" t="n"/>
       <c r="F132" s="1311">
         <f>D132*E132</f>
         <v/>
@@ -13896,8 +13908,8 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D133" s="1447" t="n"/>
-      <c r="E133" s="1448" t="n"/>
+      <c r="D133" s="1449" t="n"/>
+      <c r="E133" s="1452" t="n"/>
       <c r="F133" s="1311">
         <f>D133*E133</f>
         <v/>
@@ -13920,7 +13932,7 @@
         </is>
       </c>
       <c r="D134" s="258" t="n"/>
-      <c r="E134" s="1310" t="n"/>
+      <c r="E134" s="1451" t="n"/>
       <c r="F134" s="1311">
         <f>D134*E134</f>
         <v/>
@@ -13942,9 +13954,9 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D135" s="1447" t="n"/>
-      <c r="E135" s="1448" t="n"/>
-      <c r="F135">
+      <c r="D135" s="1449" t="n"/>
+      <c r="E135" s="1452" t="n"/>
+      <c r="F135" s="1448">
         <f>D135*E135</f>
         <v/>
       </c>
@@ -13966,7 +13978,7 @@
         </is>
       </c>
       <c r="D136" s="258" t="n"/>
-      <c r="E136" s="1310" t="n"/>
+      <c r="E136" s="1451" t="n"/>
       <c r="F136" s="1311">
         <f>D136*E136</f>
         <v/>
@@ -13989,7 +14001,7 @@
         </is>
       </c>
       <c r="D137" s="258" t="n"/>
-      <c r="E137" s="1310" t="n"/>
+      <c r="E137" s="1451" t="n"/>
       <c r="F137" s="1311">
         <f>D137*E137</f>
         <v/>
@@ -14012,7 +14024,7 @@
         </is>
       </c>
       <c r="D138" s="258" t="n"/>
-      <c r="E138" s="1310" t="n"/>
+      <c r="E138" s="1451" t="n"/>
       <c r="F138" s="1311">
         <f>D138*E138</f>
         <v/>
@@ -14035,7 +14047,7 @@
         </is>
       </c>
       <c r="D139" s="258" t="n"/>
-      <c r="E139" s="1310" t="n"/>
+      <c r="E139" s="1451" t="n"/>
       <c r="F139" s="1311">
         <f>D139*E139</f>
         <v/>
@@ -14096,8 +14108,8 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D143" s="1447" t="n"/>
-      <c r="E143" s="1448" t="n"/>
+      <c r="D143" s="1449" t="n"/>
+      <c r="E143" s="1452" t="n"/>
       <c r="F143" s="1311">
         <f>D143*E143</f>
         <v/>
@@ -14120,7 +14132,7 @@
         </is>
       </c>
       <c r="D144" s="258" t="n"/>
-      <c r="E144" s="1310" t="n"/>
+      <c r="E144" s="1451" t="n"/>
       <c r="F144" s="1311">
         <f>D144*E144</f>
         <v/>
@@ -14142,9 +14154,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D145" s="1447" t="n"/>
-      <c r="E145" s="1448" t="n"/>
-      <c r="F145">
+      <c r="D145" s="1449" t="n"/>
+      <c r="E145" s="1452" t="n"/>
+      <c r="F145" s="1448">
         <f>D145*E145</f>
         <v/>
       </c>
@@ -14166,7 +14178,7 @@
         </is>
       </c>
       <c r="D146" s="258" t="n"/>
-      <c r="E146" s="1310" t="n"/>
+      <c r="E146" s="1451" t="n"/>
       <c r="F146" s="1311">
         <f>D146*E146</f>
         <v/>
@@ -14227,8 +14239,8 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D150" s="1447" t="n"/>
-      <c r="E150" s="1448" t="n"/>
+      <c r="D150" s="1449" t="n"/>
+      <c r="E150" s="1452" t="n"/>
       <c r="F150" s="1311">
         <f>D150*E150</f>
         <v/>
@@ -14251,7 +14263,7 @@
         </is>
       </c>
       <c r="D151" s="258" t="n"/>
-      <c r="E151" s="1310" t="n"/>
+      <c r="E151" s="1451" t="n"/>
       <c r="F151" s="1311">
         <f>D151*E151</f>
         <v/>
@@ -14273,8 +14285,8 @@
           <t>UND</t>
         </is>
       </c>
-      <c r="D152" s="1447" t="n"/>
-      <c r="E152" s="1448" t="n"/>
+      <c r="D152" s="1449" t="n"/>
+      <c r="E152" s="1452" t="n"/>
       <c r="F152" s="1311">
         <f>D152*E152</f>
         <v/>
@@ -14297,7 +14309,7 @@
         </is>
       </c>
       <c r="D153" s="258" t="n"/>
-      <c r="E153" s="1310" t="n"/>
+      <c r="E153" s="1451" t="n"/>
       <c r="F153" s="1311">
         <f>D153*E153</f>
         <v/>
@@ -14320,7 +14332,7 @@
         </is>
       </c>
       <c r="D154" s="258" t="n"/>
-      <c r="E154" s="1310" t="n"/>
+      <c r="E154" s="1451" t="n"/>
       <c r="F154" s="1311">
         <f>D154*E154</f>
         <v/>
@@ -14343,7 +14355,7 @@
         </is>
       </c>
       <c r="D155" s="258" t="n"/>
-      <c r="E155" s="1310" t="n"/>
+      <c r="E155" s="1451" t="n"/>
       <c r="F155" s="1311">
         <f>D155*E155</f>
         <v/>
@@ -14366,7 +14378,7 @@
         </is>
       </c>
       <c r="D156" s="258" t="n"/>
-      <c r="E156" s="1310" t="n"/>
+      <c r="E156" s="1451" t="n"/>
       <c r="F156" s="1311">
         <f>D156*E156</f>
         <v/>
@@ -14389,7 +14401,7 @@
         </is>
       </c>
       <c r="D157" s="258" t="n"/>
-      <c r="E157" s="1310" t="n"/>
+      <c r="E157" s="1451" t="n"/>
       <c r="F157" s="1311">
         <f>D157*E157</f>
         <v/>
@@ -14412,7 +14424,7 @@
         </is>
       </c>
       <c r="D158" s="258" t="n"/>
-      <c r="E158" s="1310" t="n"/>
+      <c r="E158" s="1451" t="n"/>
       <c r="F158" s="1311">
         <f>D158*E158</f>
         <v/>
@@ -14435,7 +14447,7 @@
         </is>
       </c>
       <c r="D159" s="258" t="n"/>
-      <c r="E159" s="1310" t="n"/>
+      <c r="E159" s="1451" t="n"/>
       <c r="F159" s="1311">
         <f>D159*E159</f>
         <v/>
@@ -14458,7 +14470,7 @@
         </is>
       </c>
       <c r="D160" s="258" t="n"/>
-      <c r="E160" s="1310" t="n"/>
+      <c r="E160" s="1451" t="n"/>
       <c r="F160" s="1311">
         <f>D160*E160</f>
         <v/>
@@ -14481,7 +14493,7 @@
         </is>
       </c>
       <c r="D161" s="258" t="n"/>
-      <c r="E161" s="1310" t="n"/>
+      <c r="E161" s="1451" t="n"/>
       <c r="F161" s="1311">
         <f>D161*E161</f>
         <v/>
@@ -14543,7 +14555,7 @@
         </is>
       </c>
       <c r="D165" s="258" t="n"/>
-      <c r="E165" s="1310" t="n"/>
+      <c r="E165" s="1451" t="n"/>
       <c r="F165" s="1311">
         <f>D165*E165</f>
         <v/>
@@ -14566,7 +14578,7 @@
         </is>
       </c>
       <c r="D166" s="258" t="n"/>
-      <c r="E166" s="1310" t="n"/>
+      <c r="E166" s="1451" t="n"/>
       <c r="F166" s="1311">
         <f>D166*E166</f>
         <v/>
@@ -14589,7 +14601,7 @@
         </is>
       </c>
       <c r="D167" s="258" t="n"/>
-      <c r="E167" s="1310" t="n"/>
+      <c r="E167" s="1451" t="n"/>
       <c r="F167" s="1311">
         <f>D167*E167</f>
         <v/>
@@ -14612,7 +14624,7 @@
         </is>
       </c>
       <c r="D168" s="258" t="n"/>
-      <c r="E168" s="1310" t="n"/>
+      <c r="E168" s="1451" t="n"/>
       <c r="F168" s="1311">
         <f>D168*E168</f>
         <v/>
@@ -14635,7 +14647,7 @@
         </is>
       </c>
       <c r="D169" s="258" t="n"/>
-      <c r="E169" s="1310" t="n"/>
+      <c r="E169" s="1451" t="n"/>
       <c r="F169" s="1311">
         <f>D169*E169</f>
         <v/>
@@ -14658,7 +14670,7 @@
         </is>
       </c>
       <c r="D170" s="258" t="n"/>
-      <c r="E170" s="1310" t="n"/>
+      <c r="E170" s="1451" t="n"/>
       <c r="F170" s="1311">
         <f>D170*E170</f>
         <v/>
@@ -14681,7 +14693,7 @@
         </is>
       </c>
       <c r="D171" s="258" t="n"/>
-      <c r="E171" s="1310" t="n"/>
+      <c r="E171" s="1451" t="n"/>
       <c r="F171" s="1311">
         <f>D171*E171</f>
         <v/>
@@ -14704,7 +14716,7 @@
         </is>
       </c>
       <c r="D172" s="258" t="n"/>
-      <c r="E172" s="1310" t="n"/>
+      <c r="E172" s="1451" t="n"/>
       <c r="F172" s="1311">
         <f>D172*E172</f>
         <v/>
@@ -14727,7 +14739,7 @@
         </is>
       </c>
       <c r="D173" s="258" t="n"/>
-      <c r="E173" s="1310" t="n"/>
+      <c r="E173" s="1451" t="n"/>
       <c r="F173" s="1311">
         <f>D173*E173</f>
         <v/>
@@ -14750,7 +14762,7 @@
         </is>
       </c>
       <c r="D174" s="258" t="n"/>
-      <c r="E174" s="1310" t="n"/>
+      <c r="E174" s="1451" t="n"/>
       <c r="F174" s="1311">
         <f>D174*E174</f>
         <v/>
@@ -14773,7 +14785,7 @@
         </is>
       </c>
       <c r="D175" s="258" t="n"/>
-      <c r="E175" s="1310" t="n"/>
+      <c r="E175" s="1451" t="n"/>
       <c r="F175" s="1311">
         <f>D175*E175</f>
         <v/>
@@ -14835,7 +14847,7 @@
         </is>
       </c>
       <c r="D179" s="258" t="n"/>
-      <c r="E179" s="1310" t="n"/>
+      <c r="E179" s="1451" t="n"/>
       <c r="F179" s="1311">
         <f>D179*E179</f>
         <v/>
@@ -14858,7 +14870,7 @@
         </is>
       </c>
       <c r="D180" s="258" t="n"/>
-      <c r="E180" s="1310" t="n"/>
+      <c r="E180" s="1451" t="n"/>
       <c r="F180" s="1311">
         <f>D180*E180</f>
         <v/>
@@ -14881,7 +14893,7 @@
         </is>
       </c>
       <c r="D181" s="258" t="n"/>
-      <c r="E181" s="1310" t="n"/>
+      <c r="E181" s="1451" t="n"/>
       <c r="F181" s="1311">
         <f>D181*E181</f>
         <v/>
@@ -14904,7 +14916,7 @@
         </is>
       </c>
       <c r="D182" s="258" t="n"/>
-      <c r="E182" s="1310" t="n"/>
+      <c r="E182" s="1451" t="n"/>
       <c r="F182" s="1311">
         <f>D182*E182</f>
         <v/>
@@ -14927,7 +14939,7 @@
         </is>
       </c>
       <c r="D183" s="258" t="n"/>
-      <c r="E183" s="1310" t="n"/>
+      <c r="E183" s="1451" t="n"/>
       <c r="F183" s="1311">
         <f>D183*E183</f>
         <v/>
@@ -14950,7 +14962,7 @@
         </is>
       </c>
       <c r="D184" s="258" t="n"/>
-      <c r="E184" s="1310" t="n"/>
+      <c r="E184" s="1451" t="n"/>
       <c r="F184" s="1311">
         <f>D184*E184</f>
         <v/>
@@ -15012,7 +15024,7 @@
         </is>
       </c>
       <c r="D188" s="258" t="n"/>
-      <c r="E188" s="1310" t="n"/>
+      <c r="E188" s="1451" t="n"/>
       <c r="F188" s="1311">
         <f>D188*E188</f>
         <v/>
@@ -15035,7 +15047,7 @@
         </is>
       </c>
       <c r="D189" s="258" t="n"/>
-      <c r="E189" s="1310" t="n"/>
+      <c r="E189" s="1451" t="n"/>
       <c r="F189" s="1311">
         <f>D189*E189</f>
         <v/>
@@ -15058,7 +15070,7 @@
         </is>
       </c>
       <c r="D190" s="258" t="n"/>
-      <c r="E190" s="1310" t="n"/>
+      <c r="E190" s="1451" t="n"/>
       <c r="F190" s="1311">
         <f>D190*E190</f>
         <v/>
@@ -15081,7 +15093,7 @@
         </is>
       </c>
       <c r="D191" s="258" t="n"/>
-      <c r="E191" s="1310" t="n"/>
+      <c r="E191" s="1451" t="n"/>
       <c r="F191" s="1311">
         <f>D191*E191</f>
         <v/>
@@ -15143,7 +15155,7 @@
         </is>
       </c>
       <c r="D195" s="258" t="n"/>
-      <c r="E195" s="1310" t="n"/>
+      <c r="E195" s="1451" t="n"/>
       <c r="F195" s="1311">
         <f>D195*E195</f>
         <v/>
@@ -15166,7 +15178,7 @@
         </is>
       </c>
       <c r="D196" s="258" t="n"/>
-      <c r="E196" s="1310" t="n"/>
+      <c r="E196" s="1451" t="n"/>
       <c r="F196" s="1311">
         <f>D196*E196</f>
         <v/>
@@ -15189,7 +15201,7 @@
         </is>
       </c>
       <c r="D197" s="258" t="n"/>
-      <c r="E197" s="1310" t="n"/>
+      <c r="E197" s="1451" t="n"/>
       <c r="F197" s="1311">
         <f>D197*E197</f>
         <v/>
@@ -15251,7 +15263,7 @@
         </is>
       </c>
       <c r="D201" s="258" t="n"/>
-      <c r="E201" s="1310" t="n"/>
+      <c r="E201" s="1451" t="n"/>
       <c r="F201" s="1311">
         <f>D201*E201</f>
         <v/>
@@ -15274,7 +15286,7 @@
         </is>
       </c>
       <c r="D202" s="258" t="n"/>
-      <c r="E202" s="1310" t="n"/>
+      <c r="E202" s="1451" t="n"/>
       <c r="F202" s="1311">
         <f>D202*E202</f>
         <v/>
@@ -15297,7 +15309,7 @@
         </is>
       </c>
       <c r="D203" s="258" t="n"/>
-      <c r="E203" s="1310" t="n"/>
+      <c r="E203" s="1451" t="n"/>
       <c r="F203" s="1311">
         <f>D203*E203</f>
         <v/>
@@ -15320,7 +15332,7 @@
         </is>
       </c>
       <c r="D204" s="258" t="n"/>
-      <c r="E204" s="1310" t="n"/>
+      <c r="E204" s="1451" t="n"/>
       <c r="F204" s="1311">
         <f>D204*E204</f>
         <v/>
@@ -15343,7 +15355,7 @@
         </is>
       </c>
       <c r="D205" s="258" t="n"/>
-      <c r="E205" s="1310" t="n"/>
+      <c r="E205" s="1451" t="n"/>
       <c r="F205" s="1311">
         <f>D205*E205</f>
         <v/>
@@ -15366,7 +15378,7 @@
         </is>
       </c>
       <c r="D206" s="258" t="n"/>
-      <c r="E206" s="1310" t="n"/>
+      <c r="E206" s="1451" t="n"/>
       <c r="F206" s="1311">
         <f>D206*E206</f>
         <v/>
@@ -15389,7 +15401,7 @@
         </is>
       </c>
       <c r="D207" s="258" t="n"/>
-      <c r="E207" s="1310" t="n"/>
+      <c r="E207" s="1451" t="n"/>
       <c r="F207" s="1311">
         <f>D207*E207</f>
         <v/>
@@ -15412,7 +15424,7 @@
         </is>
       </c>
       <c r="D208" s="258" t="n"/>
-      <c r="E208" s="1310" t="n"/>
+      <c r="E208" s="1451" t="n"/>
       <c r="F208" s="1311">
         <f>D208*E208</f>
         <v/>
@@ -15435,7 +15447,7 @@
         </is>
       </c>
       <c r="D209" s="258" t="n"/>
-      <c r="E209" s="1310" t="n"/>
+      <c r="E209" s="1451" t="n"/>
       <c r="F209" s="1311">
         <f>D209*E209</f>
         <v/>
@@ -15458,7 +15470,7 @@
         </is>
       </c>
       <c r="D210" s="258" t="n"/>
-      <c r="E210" s="1310" t="n"/>
+      <c r="E210" s="1451" t="n"/>
       <c r="F210" s="1311">
         <f>D210*E210</f>
         <v/>
@@ -15481,7 +15493,7 @@
         </is>
       </c>
       <c r="D211" s="258" t="n"/>
-      <c r="E211" s="1310" t="n"/>
+      <c r="E211" s="1451" t="n"/>
       <c r="F211" s="1311">
         <f>D211*E211</f>
         <v/>
@@ -15543,7 +15555,7 @@
         </is>
       </c>
       <c r="D215" s="258" t="n"/>
-      <c r="E215" s="1310" t="n"/>
+      <c r="E215" s="1451" t="n"/>
       <c r="F215" s="1311">
         <f>D215*E215</f>
         <v/>
@@ -15566,7 +15578,7 @@
         </is>
       </c>
       <c r="D216" s="258" t="n"/>
-      <c r="E216" s="1310" t="n"/>
+      <c r="E216" s="1451" t="n"/>
       <c r="F216" s="1311">
         <f>D216*E216</f>
         <v/>
@@ -15589,7 +15601,7 @@
         </is>
       </c>
       <c r="D217" s="258" t="n"/>
-      <c r="E217" s="1310" t="n"/>
+      <c r="E217" s="1451" t="n"/>
       <c r="F217" s="1311">
         <f>D217*E217</f>
         <v/>
@@ -15612,7 +15624,7 @@
         </is>
       </c>
       <c r="D218" s="258" t="n"/>
-      <c r="E218" s="1310" t="n"/>
+      <c r="E218" s="1451" t="n"/>
       <c r="F218" s="1311">
         <f>D218*E218</f>
         <v/>
@@ -15674,7 +15686,7 @@
         </is>
       </c>
       <c r="D222" s="258" t="n"/>
-      <c r="E222" s="1310" t="n"/>
+      <c r="E222" s="1451" t="n"/>
       <c r="F222" s="1311">
         <f>D222*E222</f>
         <v/>
@@ -15697,7 +15709,7 @@
         </is>
       </c>
       <c r="D223" s="258" t="n"/>
-      <c r="E223" s="1310" t="n"/>
+      <c r="E223" s="1451" t="n"/>
       <c r="F223" s="1311">
         <f>D223*E223</f>
         <v/>
@@ -15720,7 +15732,7 @@
         </is>
       </c>
       <c r="D224" s="258" t="n"/>
-      <c r="E224" s="1310" t="n"/>
+      <c r="E224" s="1451" t="n"/>
       <c r="F224" s="1311">
         <f>D224*E224</f>
         <v/>
@@ -15743,7 +15755,7 @@
         </is>
       </c>
       <c r="D225" s="258" t="n"/>
-      <c r="E225" s="1310" t="n"/>
+      <c r="E225" s="1451" t="n"/>
       <c r="F225" s="1311">
         <f>D225*E225</f>
         <v/>
@@ -15766,7 +15778,7 @@
         </is>
       </c>
       <c r="D226" s="258" t="n"/>
-      <c r="E226" s="1310" t="n"/>
+      <c r="E226" s="1451" t="n"/>
       <c r="F226" s="1311">
         <f>D226*E226</f>
         <v/>
@@ -15828,7 +15840,7 @@
         </is>
       </c>
       <c r="D230" s="258" t="n"/>
-      <c r="E230" s="1310" t="n"/>
+      <c r="E230" s="1451" t="n"/>
       <c r="F230" s="1311">
         <f>D230*E230</f>
         <v/>
@@ -15890,7 +15902,7 @@
         </is>
       </c>
       <c r="D234" s="258" t="n"/>
-      <c r="E234" s="1310" t="n"/>
+      <c r="E234" s="1451" t="n"/>
       <c r="F234" s="1311">
         <f>D234*E234</f>
         <v/>
@@ -15913,7 +15925,7 @@
         </is>
       </c>
       <c r="D235" s="258" t="n"/>
-      <c r="E235" s="1310" t="n"/>
+      <c r="E235" s="1451" t="n"/>
       <c r="F235" s="1311">
         <f>D235*E235</f>
         <v/>
@@ -15936,7 +15948,7 @@
         </is>
       </c>
       <c r="D236" s="258" t="n"/>
-      <c r="E236" s="1310" t="n"/>
+      <c r="E236" s="1451" t="n"/>
       <c r="F236" s="1311">
         <f>D236*E236</f>
         <v/>
@@ -15959,7 +15971,7 @@
         </is>
       </c>
       <c r="D237" s="258" t="n"/>
-      <c r="E237" s="1310" t="n"/>
+      <c r="E237" s="1451" t="n"/>
       <c r="F237" s="1311">
         <f>D237*E237</f>
         <v/>

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -6692,7 +6692,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1453">
+  <cellXfs count="1469">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -10300,6 +10300,36 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="173" fontId="167" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="49" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="55" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="87" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="87" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="62" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="62" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="49" fillId="3" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="55" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11221,7 +11251,6 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11253,12 +11282,13 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
   </mergeCells>
@@ -11496,7 +11526,7 @@
       </c>
       <c r="D15" s="258" t="n"/>
       <c r="E15" s="1451" t="n"/>
-      <c r="F15" s="1311">
+      <c r="F15" s="1453">
         <f>D15*E15</f>
         <v/>
       </c>
@@ -11519,7 +11549,7 @@
       </c>
       <c r="D16" s="258" t="n"/>
       <c r="E16" s="1451" t="n"/>
-      <c r="F16" s="1311">
+      <c r="F16" s="1453">
         <f>D16*E16</f>
         <v/>
       </c>
@@ -11542,7 +11572,7 @@
       </c>
       <c r="D17" s="258" t="n"/>
       <c r="E17" s="1451" t="n"/>
-      <c r="F17" s="1311">
+      <c r="F17" s="1453">
         <f>D17*E17</f>
         <v/>
       </c>
@@ -11565,7 +11595,7 @@
       </c>
       <c r="D18" s="258" t="n"/>
       <c r="E18" s="1451" t="n"/>
-      <c r="F18" s="1311">
+      <c r="F18" s="1453">
         <f>D18*E18</f>
         <v/>
       </c>
@@ -11588,7 +11618,7 @@
       </c>
       <c r="D19" s="258" t="n"/>
       <c r="E19" s="1451" t="n"/>
-      <c r="F19" s="1311">
+      <c r="F19" s="1453">
         <f>D19*E19</f>
         <v/>
       </c>
@@ -11611,7 +11641,7 @@
       </c>
       <c r="D20" s="258" t="n"/>
       <c r="E20" s="1451" t="n"/>
-      <c r="F20" s="1311">
+      <c r="F20" s="1453">
         <f>D20*E20</f>
         <v/>
       </c>
@@ -11634,7 +11664,7 @@
       </c>
       <c r="D21" s="258" t="n"/>
       <c r="E21" s="1451" t="n"/>
-      <c r="F21" s="1311">
+      <c r="F21" s="1453">
         <f>D21*E21</f>
         <v/>
       </c>
@@ -11657,7 +11687,7 @@
       </c>
       <c r="D22" s="258" t="n"/>
       <c r="E22" s="1451" t="n"/>
-      <c r="F22" s="1311">
+      <c r="F22" s="1453">
         <f>D22*E22</f>
         <v/>
       </c>
@@ -11680,7 +11710,7 @@
       </c>
       <c r="D23" s="258" t="n"/>
       <c r="E23" s="1451" t="n"/>
-      <c r="F23" s="1311">
+      <c r="F23" s="1453">
         <f>D23*E23</f>
         <v/>
       </c>
@@ -11703,7 +11733,7 @@
       </c>
       <c r="D24" s="258" t="n"/>
       <c r="E24" s="1451" t="n"/>
-      <c r="F24" s="1311">
+      <c r="F24" s="1453">
         <f>D24*E24</f>
         <v/>
       </c>
@@ -11718,7 +11748,7 @@
       <c r="C25" s="567" t="n"/>
       <c r="D25" s="567" t="n"/>
       <c r="E25" s="567" t="n"/>
-      <c r="F25" s="1312">
+      <c r="F25" s="1454">
         <f>SUM(F15:F24)</f>
         <v/>
       </c>
@@ -11765,7 +11795,7 @@
       </c>
       <c r="D28" s="258" t="n"/>
       <c r="E28" s="1451" t="n"/>
-      <c r="F28" s="1311">
+      <c r="F28" s="1453">
         <f>D28*E28</f>
         <v/>
       </c>
@@ -11788,7 +11818,7 @@
       </c>
       <c r="D29" s="258" t="n"/>
       <c r="E29" s="1451" t="n"/>
-      <c r="F29" s="1311">
+      <c r="F29" s="1453">
         <f>D29*E29</f>
         <v/>
       </c>
@@ -11811,7 +11841,7 @@
       </c>
       <c r="D30" s="258" t="n"/>
       <c r="E30" s="1451" t="n"/>
-      <c r="F30" s="1311">
+      <c r="F30" s="1453">
         <f>D30*E30</f>
         <v/>
       </c>
@@ -11834,7 +11864,7 @@
       </c>
       <c r="D31" s="258" t="n"/>
       <c r="E31" s="1451" t="n"/>
-      <c r="F31" s="1311">
+      <c r="F31" s="1453">
         <f>D31*E31</f>
         <v/>
       </c>
@@ -11857,7 +11887,7 @@
       </c>
       <c r="D32" s="258" t="n"/>
       <c r="E32" s="1451" t="n"/>
-      <c r="F32" s="1311">
+      <c r="F32" s="1453">
         <f>D32*E32</f>
         <v/>
       </c>
@@ -11880,7 +11910,7 @@
       </c>
       <c r="D33" s="258" t="n"/>
       <c r="E33" s="1451" t="n"/>
-      <c r="F33" s="1311">
+      <c r="F33" s="1453">
         <f>D33*E33</f>
         <v/>
       </c>
@@ -11903,7 +11933,7 @@
       </c>
       <c r="D34" s="258" t="n"/>
       <c r="E34" s="1451" t="n"/>
-      <c r="F34" s="1311">
+      <c r="F34" s="1453">
         <f>D34*E34</f>
         <v/>
       </c>
@@ -11926,7 +11956,7 @@
       </c>
       <c r="D35" s="258" t="n"/>
       <c r="E35" s="1451" t="n"/>
-      <c r="F35" s="1311">
+      <c r="F35" s="1453">
         <f>D35*E35</f>
         <v/>
       </c>
@@ -11949,7 +11979,7 @@
       </c>
       <c r="D36" s="258" t="n"/>
       <c r="E36" s="1451" t="n"/>
-      <c r="F36" s="1311">
+      <c r="F36" s="1453">
         <f>D36*E36</f>
         <v/>
       </c>
@@ -11972,7 +12002,7 @@
       </c>
       <c r="D37" s="258" t="n"/>
       <c r="E37" s="1451" t="n"/>
-      <c r="F37" s="1311">
+      <c r="F37" s="1453">
         <f>D37*E37</f>
         <v/>
       </c>
@@ -11995,7 +12025,7 @@
       </c>
       <c r="D38" s="258" t="n"/>
       <c r="E38" s="1451" t="n"/>
-      <c r="F38" s="1311">
+      <c r="F38" s="1453">
         <f>D38*E38</f>
         <v/>
       </c>
@@ -12010,7 +12040,7 @@
       <c r="C39" s="567" t="n"/>
       <c r="D39" s="567" t="n"/>
       <c r="E39" s="567" t="n"/>
-      <c r="F39" s="1312">
+      <c r="F39" s="1454">
         <f>SUM(F28:F38)</f>
         <v/>
       </c>
@@ -12057,7 +12087,7 @@
       </c>
       <c r="D42" s="258" t="n"/>
       <c r="E42" s="1451" t="n"/>
-      <c r="F42" s="1311">
+      <c r="F42" s="1453">
         <f>D42*E42</f>
         <v/>
       </c>
@@ -12080,7 +12110,7 @@
       </c>
       <c r="D43" s="258" t="n"/>
       <c r="E43" s="1451" t="n"/>
-      <c r="F43" s="1311">
+      <c r="F43" s="1453">
         <f>D43*E43</f>
         <v/>
       </c>
@@ -12103,7 +12133,7 @@
       </c>
       <c r="D44" s="258" t="n"/>
       <c r="E44" s="1451" t="n"/>
-      <c r="F44" s="1311">
+      <c r="F44" s="1453">
         <f>D44*E44</f>
         <v/>
       </c>
@@ -12126,7 +12156,7 @@
       </c>
       <c r="D45" s="258" t="n"/>
       <c r="E45" s="1451" t="n"/>
-      <c r="F45" s="1311">
+      <c r="F45" s="1453">
         <f>D45*E45</f>
         <v/>
       </c>
@@ -12149,7 +12179,7 @@
       </c>
       <c r="D46" s="258" t="n"/>
       <c r="E46" s="1451" t="n"/>
-      <c r="F46" s="1311">
+      <c r="F46" s="1453">
         <f>D46*E46</f>
         <v/>
       </c>
@@ -12172,7 +12202,7 @@
       </c>
       <c r="D47" s="258" t="n"/>
       <c r="E47" s="1451" t="n"/>
-      <c r="F47" s="1311">
+      <c r="F47" s="1453">
         <f>D47*E47</f>
         <v/>
       </c>
@@ -12195,7 +12225,7 @@
       </c>
       <c r="D48" s="258" t="n"/>
       <c r="E48" s="1451" t="n"/>
-      <c r="F48" s="1311">
+      <c r="F48" s="1453">
         <f>D48*E48</f>
         <v/>
       </c>
@@ -12210,7 +12240,7 @@
       <c r="C49" s="567" t="n"/>
       <c r="D49" s="567" t="n"/>
       <c r="E49" s="567" t="n"/>
-      <c r="F49" s="1312">
+      <c r="F49" s="1454">
         <f>SUM(F42:F48)</f>
         <v/>
       </c>
@@ -12257,7 +12287,7 @@
       </c>
       <c r="D52" s="258" t="n"/>
       <c r="E52" s="1451" t="n"/>
-      <c r="F52" s="1311">
+      <c r="F52" s="1453">
         <f>D52*E52</f>
         <v/>
       </c>
@@ -12280,7 +12310,7 @@
       </c>
       <c r="D53" s="1449" t="n"/>
       <c r="E53" s="1452" t="n"/>
-      <c r="F53" s="1448">
+      <c r="F53" s="1455">
         <f>D53*E53</f>
         <v/>
       </c>
@@ -12303,7 +12333,7 @@
       </c>
       <c r="D54" s="258" t="n"/>
       <c r="E54" s="1451" t="n"/>
-      <c r="F54" s="1311">
+      <c r="F54" s="1453">
         <f>D54*E54</f>
         <v/>
       </c>
@@ -12326,7 +12356,7 @@
       </c>
       <c r="D55" s="258" t="n"/>
       <c r="E55" s="1451" t="n"/>
-      <c r="F55" s="1311">
+      <c r="F55" s="1453">
         <f>D55*E55</f>
         <v/>
       </c>
@@ -12349,7 +12379,7 @@
       </c>
       <c r="D56" s="258" t="n"/>
       <c r="E56" s="1451" t="n"/>
-      <c r="F56" s="1311">
+      <c r="F56" s="1453">
         <f>D56*E56</f>
         <v/>
       </c>
@@ -12372,7 +12402,7 @@
       </c>
       <c r="D57" s="258" t="n"/>
       <c r="E57" s="1451" t="n"/>
-      <c r="F57" s="1311">
+      <c r="F57" s="1453">
         <f>D57*E57</f>
         <v/>
       </c>
@@ -12395,7 +12425,7 @@
       </c>
       <c r="D58" s="258" t="n"/>
       <c r="E58" s="1451" t="n"/>
-      <c r="F58" s="1311">
+      <c r="F58" s="1453">
         <f>D58*E58</f>
         <v/>
       </c>
@@ -12418,7 +12448,7 @@
       </c>
       <c r="D59" s="1449" t="n"/>
       <c r="E59" s="1452" t="n"/>
-      <c r="F59" s="1311">
+      <c r="F59" s="1453">
         <f>D59*E59</f>
         <v/>
       </c>
@@ -12441,7 +12471,7 @@
       </c>
       <c r="D60" s="258" t="n"/>
       <c r="E60" s="1451" t="n"/>
-      <c r="F60" s="1311">
+      <c r="F60" s="1453">
         <f>D60*E60</f>
         <v/>
       </c>
@@ -12464,7 +12494,7 @@
       </c>
       <c r="D61" s="1449" t="n"/>
       <c r="E61" s="1452" t="n"/>
-      <c r="F61" s="1448">
+      <c r="F61" s="1455">
         <f>D61*E61</f>
         <v/>
       </c>
@@ -12487,7 +12517,7 @@
       </c>
       <c r="D62" s="258" t="n"/>
       <c r="E62" s="1451" t="n"/>
-      <c r="F62" s="1311">
+      <c r="F62" s="1453">
         <f>D62*E62</f>
         <v/>
       </c>
@@ -12510,7 +12540,7 @@
       </c>
       <c r="D63" s="258" t="n"/>
       <c r="E63" s="1451" t="n"/>
-      <c r="F63" s="1311">
+      <c r="F63" s="1453">
         <f>D63*E63</f>
         <v/>
       </c>
@@ -12533,7 +12563,7 @@
       </c>
       <c r="D64" s="258" t="n"/>
       <c r="E64" s="1451" t="n"/>
-      <c r="F64" s="1311">
+      <c r="F64" s="1453">
         <f>D64*E64</f>
         <v/>
       </c>
@@ -12556,7 +12586,7 @@
       </c>
       <c r="D65" s="258" t="n"/>
       <c r="E65" s="1451" t="n"/>
-      <c r="F65" s="1311">
+      <c r="F65" s="1453">
         <f>D65*E65</f>
         <v/>
       </c>
@@ -12579,7 +12609,7 @@
       </c>
       <c r="D66" s="258" t="n"/>
       <c r="E66" s="1451" t="n"/>
-      <c r="F66" s="1311">
+      <c r="F66" s="1453">
         <f>D66*E66</f>
         <v/>
       </c>
@@ -12602,7 +12632,7 @@
       </c>
       <c r="D67" s="258" t="n"/>
       <c r="E67" s="1451" t="n"/>
-      <c r="F67" s="1311">
+      <c r="F67" s="1453">
         <f>D67*E67</f>
         <v/>
       </c>
@@ -12625,7 +12655,7 @@
       </c>
       <c r="D68" s="258" t="n"/>
       <c r="E68" s="1451" t="n"/>
-      <c r="F68" s="1311">
+      <c r="F68" s="1453">
         <f>D68*E68</f>
         <v/>
       </c>
@@ -12640,7 +12670,7 @@
       <c r="C69" s="567" t="n"/>
       <c r="D69" s="567" t="n"/>
       <c r="E69" s="567" t="n"/>
-      <c r="F69" s="1312">
+      <c r="F69" s="1454">
         <f>SUM(F51:F68)</f>
         <v/>
       </c>
@@ -12687,7 +12717,7 @@
       </c>
       <c r="D72" s="258" t="n"/>
       <c r="E72" s="1451" t="n"/>
-      <c r="F72" s="1311">
+      <c r="F72" s="1453">
         <f>D72*E72</f>
         <v/>
       </c>
@@ -12710,7 +12740,7 @@
       </c>
       <c r="D73" s="258" t="n"/>
       <c r="E73" s="1451" t="n"/>
-      <c r="F73" s="1311">
+      <c r="F73" s="1453">
         <f>D73*E73</f>
         <v/>
       </c>
@@ -12733,7 +12763,7 @@
       </c>
       <c r="D74" s="258" t="n"/>
       <c r="E74" s="1451" t="n"/>
-      <c r="F74" s="1311">
+      <c r="F74" s="1453">
         <f>D74*E74</f>
         <v/>
       </c>
@@ -12756,7 +12786,7 @@
       </c>
       <c r="D75" s="258" t="n"/>
       <c r="E75" s="1451" t="n"/>
-      <c r="F75" s="1311">
+      <c r="F75" s="1453">
         <f>D75*E75</f>
         <v/>
       </c>
@@ -12779,7 +12809,7 @@
       </c>
       <c r="D76" s="258" t="n"/>
       <c r="E76" s="1451" t="n"/>
-      <c r="F76" s="1311">
+      <c r="F76" s="1453">
         <f>D76*E76</f>
         <v/>
       </c>
@@ -12802,7 +12832,7 @@
       </c>
       <c r="D77" s="258" t="n"/>
       <c r="E77" s="1451" t="n"/>
-      <c r="F77" s="1311">
+      <c r="F77" s="1453">
         <f>D77*E77</f>
         <v/>
       </c>
@@ -12825,7 +12855,7 @@
       </c>
       <c r="D78" s="258" t="n"/>
       <c r="E78" s="1451" t="n"/>
-      <c r="F78" s="1311">
+      <c r="F78" s="1453">
         <f>D78*E78</f>
         <v/>
       </c>
@@ -12848,7 +12878,7 @@
       </c>
       <c r="D79" s="258" t="n"/>
       <c r="E79" s="1451" t="n"/>
-      <c r="F79" s="1311">
+      <c r="F79" s="1453">
         <f>D79*E79</f>
         <v/>
       </c>
@@ -12871,7 +12901,7 @@
       </c>
       <c r="D80" s="258" t="n"/>
       <c r="E80" s="1451" t="n"/>
-      <c r="F80" s="1311">
+      <c r="F80" s="1453">
         <f>D80*E80</f>
         <v/>
       </c>
@@ -12886,7 +12916,7 @@
       <c r="C81" s="567" t="n"/>
       <c r="D81" s="567" t="n"/>
       <c r="E81" s="567" t="n"/>
-      <c r="F81" s="1312">
+      <c r="F81" s="1454">
         <f>SUM(F72:F80)</f>
         <v/>
       </c>
@@ -12933,7 +12963,7 @@
       </c>
       <c r="D84" s="1449" t="n"/>
       <c r="E84" s="1452" t="n"/>
-      <c r="F84" s="1448">
+      <c r="F84" s="1455">
         <f>D84*E84</f>
         <v/>
       </c>
@@ -12956,7 +12986,7 @@
       </c>
       <c r="D85" s="258" t="n"/>
       <c r="E85" s="1451" t="n"/>
-      <c r="F85" s="1311">
+      <c r="F85" s="1453">
         <f>D85*E85</f>
         <v/>
       </c>
@@ -12979,7 +13009,7 @@
       </c>
       <c r="D86" s="258" t="n"/>
       <c r="E86" s="1451" t="n"/>
-      <c r="F86" s="1311">
+      <c r="F86" s="1453">
         <f>D86*E86</f>
         <v/>
       </c>
@@ -13002,7 +13032,7 @@
       </c>
       <c r="D87" s="258" t="n"/>
       <c r="E87" s="1451" t="n"/>
-      <c r="F87" s="1311">
+      <c r="F87" s="1453">
         <f>D87*E87</f>
         <v/>
       </c>
@@ -13025,7 +13055,7 @@
       </c>
       <c r="D88" s="258" t="n"/>
       <c r="E88" s="1451" t="n"/>
-      <c r="F88" s="1311">
+      <c r="F88" s="1453">
         <f>D88*E88</f>
         <v/>
       </c>
@@ -13048,7 +13078,7 @@
       </c>
       <c r="D89" s="258" t="n"/>
       <c r="E89" s="1451" t="n"/>
-      <c r="F89" s="1311">
+      <c r="F89" s="1453">
         <f>D89*E89</f>
         <v/>
       </c>
@@ -13071,7 +13101,7 @@
       </c>
       <c r="D90" s="258" t="n"/>
       <c r="E90" s="1451" t="n"/>
-      <c r="F90" s="1311">
+      <c r="F90" s="1453">
         <f>D90*E90</f>
         <v/>
       </c>
@@ -13094,7 +13124,7 @@
       </c>
       <c r="D91" s="258" t="n"/>
       <c r="E91" s="1451" t="n"/>
-      <c r="F91" s="1311">
+      <c r="F91" s="1453">
         <f>D91*E91</f>
         <v/>
       </c>
@@ -13117,7 +13147,7 @@
       </c>
       <c r="D92" s="258" t="n"/>
       <c r="E92" s="1451" t="n"/>
-      <c r="F92" s="1311">
+      <c r="F92" s="1453">
         <f>D92*E92</f>
         <v/>
       </c>
@@ -13132,7 +13162,7 @@
       <c r="C93" s="567" t="n"/>
       <c r="D93" s="567" t="n"/>
       <c r="E93" s="567" t="n"/>
-      <c r="F93" s="1312">
+      <c r="F93" s="1454">
         <f>SUM(F84:F92)</f>
         <v/>
       </c>
@@ -13179,7 +13209,7 @@
       </c>
       <c r="D96" s="258" t="n"/>
       <c r="E96" s="1451" t="n"/>
-      <c r="F96" s="1311">
+      <c r="F96" s="1453">
         <f>D96*E96</f>
         <v/>
       </c>
@@ -13202,7 +13232,7 @@
       </c>
       <c r="D97" s="1449" t="n"/>
       <c r="E97" s="1452" t="n"/>
-      <c r="F97" s="1448">
+      <c r="F97" s="1455">
         <f>D97*E97</f>
         <v/>
       </c>
@@ -13225,7 +13255,7 @@
       </c>
       <c r="D98" s="258" t="n"/>
       <c r="E98" s="1451" t="n"/>
-      <c r="F98" s="1311">
+      <c r="F98" s="1453">
         <f>D98*E98</f>
         <v/>
       </c>
@@ -13248,7 +13278,7 @@
       </c>
       <c r="D99" s="258" t="n"/>
       <c r="E99" s="1451" t="n"/>
-      <c r="F99" s="1311">
+      <c r="F99" s="1453">
         <f>D99*E99</f>
         <v/>
       </c>
@@ -13263,7 +13293,7 @@
       <c r="C100" s="567" t="n"/>
       <c r="D100" s="567" t="n"/>
       <c r="E100" s="567" t="n"/>
-      <c r="F100" s="1312">
+      <c r="F100" s="1454">
         <f>SUM(F96:F99)</f>
         <v/>
       </c>
@@ -13310,7 +13340,7 @@
       </c>
       <c r="D103" s="1449" t="n"/>
       <c r="E103" s="1452" t="n"/>
-      <c r="F103" s="1448">
+      <c r="F103" s="1455">
         <f>D103*E103</f>
         <v/>
       </c>
@@ -13333,7 +13363,7 @@
       </c>
       <c r="D104" s="258" t="n"/>
       <c r="E104" s="1451" t="n"/>
-      <c r="F104" s="1311">
+      <c r="F104" s="1453">
         <f>D104*E104</f>
         <v/>
       </c>
@@ -13356,7 +13386,7 @@
       </c>
       <c r="D105" s="258" t="n"/>
       <c r="E105" s="1451" t="n"/>
-      <c r="F105" s="1311">
+      <c r="F105" s="1453">
         <f>D105*E105</f>
         <v/>
       </c>
@@ -13379,7 +13409,7 @@
       </c>
       <c r="D106" s="1449" t="n"/>
       <c r="E106" s="1452" t="n"/>
-      <c r="F106" s="1311">
+      <c r="F106" s="1453">
         <f>D106*E106</f>
         <v/>
       </c>
@@ -13394,7 +13424,7 @@
       <c r="C107" s="567" t="n"/>
       <c r="D107" s="567" t="n"/>
       <c r="E107" s="567" t="n"/>
-      <c r="F107" s="1312">
+      <c r="F107" s="1454">
         <f>SUM(F103:F106)</f>
         <v/>
       </c>
@@ -13441,7 +13471,7 @@
       </c>
       <c r="D110" s="258" t="n"/>
       <c r="E110" s="1451" t="n"/>
-      <c r="F110" s="1311">
+      <c r="F110" s="1453">
         <f>D110*E110</f>
         <v/>
       </c>
@@ -13464,7 +13494,7 @@
       </c>
       <c r="D111" s="258" t="n"/>
       <c r="E111" s="1451" t="n"/>
-      <c r="F111" s="1311">
+      <c r="F111" s="1453">
         <f>D111*E111</f>
         <v/>
       </c>
@@ -13487,7 +13517,7 @@
       </c>
       <c r="D112" s="258" t="n"/>
       <c r="E112" s="1451" t="n"/>
-      <c r="F112" s="1311">
+      <c r="F112" s="1453">
         <f>D112*E112</f>
         <v/>
       </c>
@@ -13510,7 +13540,7 @@
       </c>
       <c r="D113" s="258" t="n"/>
       <c r="E113" s="1451" t="n"/>
-      <c r="F113" s="1311">
+      <c r="F113" s="1453">
         <f>D113*E113</f>
         <v/>
       </c>
@@ -13533,7 +13563,7 @@
       </c>
       <c r="D114" s="258" t="n"/>
       <c r="E114" s="1451" t="n"/>
-      <c r="F114" s="1311">
+      <c r="F114" s="1453">
         <f>D114*E114</f>
         <v/>
       </c>
@@ -13556,7 +13586,7 @@
       </c>
       <c r="D115" s="1449" t="n"/>
       <c r="E115" s="1452" t="n"/>
-      <c r="F115" s="1311">
+      <c r="F115" s="1453">
         <f>D115*E115</f>
         <v/>
       </c>
@@ -13579,7 +13609,7 @@
       </c>
       <c r="D116" s="258" t="n"/>
       <c r="E116" s="1451" t="n"/>
-      <c r="F116" s="1311">
+      <c r="F116" s="1453">
         <f>D116*E116</f>
         <v/>
       </c>
@@ -13602,7 +13632,7 @@
       </c>
       <c r="D117" s="1449" t="n"/>
       <c r="E117" s="1452" t="n"/>
-      <c r="F117" s="1448">
+      <c r="F117" s="1455">
         <f>D117*E117</f>
         <v/>
       </c>
@@ -13625,7 +13655,7 @@
       </c>
       <c r="D118" s="1449" t="n"/>
       <c r="E118" s="1452" t="n"/>
-      <c r="F118" s="1448">
+      <c r="F118" s="1455">
         <f>D118*E118</f>
         <v/>
       </c>
@@ -13648,7 +13678,7 @@
       </c>
       <c r="D119" s="1449" t="n"/>
       <c r="E119" s="1452" t="n"/>
-      <c r="F119" s="1448">
+      <c r="F119" s="1455">
         <f>D119*E119</f>
         <v/>
       </c>
@@ -13671,7 +13701,7 @@
       </c>
       <c r="D120" s="1449" t="n"/>
       <c r="E120" s="1452" t="n"/>
-      <c r="F120" s="1448">
+      <c r="F120" s="1455">
         <f>D120*E120</f>
         <v/>
       </c>
@@ -13686,7 +13716,7 @@
       <c r="C121" s="567" t="n"/>
       <c r="D121" s="567" t="n"/>
       <c r="E121" s="567" t="n"/>
-      <c r="F121" s="1312">
+      <c r="F121" s="1454">
         <f>SUM(F110:F120)</f>
         <v/>
       </c>
@@ -13733,7 +13763,7 @@
       </c>
       <c r="D124" s="258" t="n"/>
       <c r="E124" s="1451" t="n"/>
-      <c r="F124" s="1311">
+      <c r="F124" s="1453">
         <f>D124*E124</f>
         <v/>
       </c>
@@ -13756,7 +13786,7 @@
       </c>
       <c r="D125" s="258" t="n"/>
       <c r="E125" s="1451" t="n"/>
-      <c r="F125" s="1311">
+      <c r="F125" s="1453">
         <f>D125*E125</f>
         <v/>
       </c>
@@ -13779,7 +13809,7 @@
       </c>
       <c r="D126" s="258" t="n"/>
       <c r="E126" s="1451" t="n"/>
-      <c r="F126" s="1311">
+      <c r="F126" s="1453">
         <f>D126*E126</f>
         <v/>
       </c>
@@ -13802,7 +13832,7 @@
       </c>
       <c r="D127" s="258" t="n"/>
       <c r="E127" s="1451" t="n"/>
-      <c r="F127" s="1311">
+      <c r="F127" s="1453">
         <f>D127*E127</f>
         <v/>
       </c>
@@ -13825,7 +13855,7 @@
       </c>
       <c r="D128" s="1449" t="n"/>
       <c r="E128" s="1452" t="n"/>
-      <c r="F128" s="1311">
+      <c r="F128" s="1453">
         <f>D128*E128</f>
         <v/>
       </c>
@@ -13840,7 +13870,7 @@
       <c r="C129" s="567" t="n"/>
       <c r="D129" s="567" t="n"/>
       <c r="E129" s="567" t="n"/>
-      <c r="F129" s="1312">
+      <c r="F129" s="1454">
         <f>SUM(F124:F128)</f>
         <v/>
       </c>
@@ -13887,7 +13917,7 @@
       </c>
       <c r="D132" s="258" t="n"/>
       <c r="E132" s="1451" t="n"/>
-      <c r="F132" s="1311">
+      <c r="F132" s="1453">
         <f>D132*E132</f>
         <v/>
       </c>
@@ -13910,7 +13940,7 @@
       </c>
       <c r="D133" s="1449" t="n"/>
       <c r="E133" s="1452" t="n"/>
-      <c r="F133" s="1311">
+      <c r="F133" s="1453">
         <f>D133*E133</f>
         <v/>
       </c>
@@ -13933,7 +13963,7 @@
       </c>
       <c r="D134" s="258" t="n"/>
       <c r="E134" s="1451" t="n"/>
-      <c r="F134" s="1311">
+      <c r="F134" s="1453">
         <f>D134*E134</f>
         <v/>
       </c>
@@ -13956,7 +13986,7 @@
       </c>
       <c r="D135" s="1449" t="n"/>
       <c r="E135" s="1452" t="n"/>
-      <c r="F135" s="1448">
+      <c r="F135" s="1455">
         <f>D135*E135</f>
         <v/>
       </c>
@@ -13979,7 +14009,7 @@
       </c>
       <c r="D136" s="258" t="n"/>
       <c r="E136" s="1451" t="n"/>
-      <c r="F136" s="1311">
+      <c r="F136" s="1453">
         <f>D136*E136</f>
         <v/>
       </c>
@@ -14002,7 +14032,7 @@
       </c>
       <c r="D137" s="258" t="n"/>
       <c r="E137" s="1451" t="n"/>
-      <c r="F137" s="1311">
+      <c r="F137" s="1453">
         <f>D137*E137</f>
         <v/>
       </c>
@@ -14025,7 +14055,7 @@
       </c>
       <c r="D138" s="258" t="n"/>
       <c r="E138" s="1451" t="n"/>
-      <c r="F138" s="1311">
+      <c r="F138" s="1453">
         <f>D138*E138</f>
         <v/>
       </c>
@@ -14048,7 +14078,7 @@
       </c>
       <c r="D139" s="258" t="n"/>
       <c r="E139" s="1451" t="n"/>
-      <c r="F139" s="1311">
+      <c r="F139" s="1453">
         <f>D139*E139</f>
         <v/>
       </c>
@@ -14063,7 +14093,7 @@
       <c r="C140" s="567" t="n"/>
       <c r="D140" s="567" t="n"/>
       <c r="E140" s="567" t="n"/>
-      <c r="F140" s="1312">
+      <c r="F140" s="1454">
         <f>SUM(F132:F139)</f>
         <v/>
       </c>
@@ -14110,7 +14140,7 @@
       </c>
       <c r="D143" s="1449" t="n"/>
       <c r="E143" s="1452" t="n"/>
-      <c r="F143" s="1311">
+      <c r="F143" s="1453">
         <f>D143*E143</f>
         <v/>
       </c>
@@ -14133,7 +14163,7 @@
       </c>
       <c r="D144" s="258" t="n"/>
       <c r="E144" s="1451" t="n"/>
-      <c r="F144" s="1311">
+      <c r="F144" s="1453">
         <f>D144*E144</f>
         <v/>
       </c>
@@ -14156,7 +14186,7 @@
       </c>
       <c r="D145" s="1449" t="n"/>
       <c r="E145" s="1452" t="n"/>
-      <c r="F145" s="1448">
+      <c r="F145" s="1455">
         <f>D145*E145</f>
         <v/>
       </c>
@@ -14179,7 +14209,7 @@
       </c>
       <c r="D146" s="258" t="n"/>
       <c r="E146" s="1451" t="n"/>
-      <c r="F146" s="1311">
+      <c r="F146" s="1453">
         <f>D146*E146</f>
         <v/>
       </c>
@@ -14194,7 +14224,7 @@
       <c r="C147" s="567" t="n"/>
       <c r="D147" s="567" t="n"/>
       <c r="E147" s="567" t="n"/>
-      <c r="F147" s="1312">
+      <c r="F147" s="1454">
         <f>SUM(F143:F146)</f>
         <v/>
       </c>
@@ -14241,7 +14271,7 @@
       </c>
       <c r="D150" s="1449" t="n"/>
       <c r="E150" s="1452" t="n"/>
-      <c r="F150" s="1311">
+      <c r="F150" s="1453">
         <f>D150*E150</f>
         <v/>
       </c>
@@ -14264,7 +14294,7 @@
       </c>
       <c r="D151" s="258" t="n"/>
       <c r="E151" s="1451" t="n"/>
-      <c r="F151" s="1311">
+      <c r="F151" s="1453">
         <f>D151*E151</f>
         <v/>
       </c>
@@ -14287,7 +14317,7 @@
       </c>
       <c r="D152" s="1449" t="n"/>
       <c r="E152" s="1452" t="n"/>
-      <c r="F152" s="1311">
+      <c r="F152" s="1453">
         <f>D152*E152</f>
         <v/>
       </c>
@@ -14310,7 +14340,7 @@
       </c>
       <c r="D153" s="258" t="n"/>
       <c r="E153" s="1451" t="n"/>
-      <c r="F153" s="1311">
+      <c r="F153" s="1453">
         <f>D153*E153</f>
         <v/>
       </c>
@@ -14333,7 +14363,7 @@
       </c>
       <c r="D154" s="258" t="n"/>
       <c r="E154" s="1451" t="n"/>
-      <c r="F154" s="1311">
+      <c r="F154" s="1453">
         <f>D154*E154</f>
         <v/>
       </c>
@@ -14356,7 +14386,7 @@
       </c>
       <c r="D155" s="258" t="n"/>
       <c r="E155" s="1451" t="n"/>
-      <c r="F155" s="1311">
+      <c r="F155" s="1453">
         <f>D155*E155</f>
         <v/>
       </c>
@@ -14379,7 +14409,7 @@
       </c>
       <c r="D156" s="258" t="n"/>
       <c r="E156" s="1451" t="n"/>
-      <c r="F156" s="1311">
+      <c r="F156" s="1453">
         <f>D156*E156</f>
         <v/>
       </c>
@@ -14402,7 +14432,7 @@
       </c>
       <c r="D157" s="258" t="n"/>
       <c r="E157" s="1451" t="n"/>
-      <c r="F157" s="1311">
+      <c r="F157" s="1453">
         <f>D157*E157</f>
         <v/>
       </c>
@@ -14425,7 +14455,7 @@
       </c>
       <c r="D158" s="258" t="n"/>
       <c r="E158" s="1451" t="n"/>
-      <c r="F158" s="1311">
+      <c r="F158" s="1453">
         <f>D158*E158</f>
         <v/>
       </c>
@@ -14448,7 +14478,7 @@
       </c>
       <c r="D159" s="258" t="n"/>
       <c r="E159" s="1451" t="n"/>
-      <c r="F159" s="1311">
+      <c r="F159" s="1453">
         <f>D159*E159</f>
         <v/>
       </c>
@@ -14471,7 +14501,7 @@
       </c>
       <c r="D160" s="258" t="n"/>
       <c r="E160" s="1451" t="n"/>
-      <c r="F160" s="1311">
+      <c r="F160" s="1453">
         <f>D160*E160</f>
         <v/>
       </c>
@@ -14494,7 +14524,7 @@
       </c>
       <c r="D161" s="258" t="n"/>
       <c r="E161" s="1451" t="n"/>
-      <c r="F161" s="1311">
+      <c r="F161" s="1453">
         <f>D161*E161</f>
         <v/>
       </c>
@@ -14509,7 +14539,7 @@
       <c r="C162" s="567" t="n"/>
       <c r="D162" s="567" t="n"/>
       <c r="E162" s="567" t="n"/>
-      <c r="F162" s="1312">
+      <c r="F162" s="1454">
         <f>SUM(F150:F161)</f>
         <v/>
       </c>
@@ -14556,7 +14586,7 @@
       </c>
       <c r="D165" s="258" t="n"/>
       <c r="E165" s="1451" t="n"/>
-      <c r="F165" s="1311">
+      <c r="F165" s="1453">
         <f>D165*E165</f>
         <v/>
       </c>
@@ -14579,7 +14609,7 @@
       </c>
       <c r="D166" s="258" t="n"/>
       <c r="E166" s="1451" t="n"/>
-      <c r="F166" s="1311">
+      <c r="F166" s="1453">
         <f>D166*E166</f>
         <v/>
       </c>
@@ -14602,7 +14632,7 @@
       </c>
       <c r="D167" s="258" t="n"/>
       <c r="E167" s="1451" t="n"/>
-      <c r="F167" s="1311">
+      <c r="F167" s="1453">
         <f>D167*E167</f>
         <v/>
       </c>
@@ -14625,7 +14655,7 @@
       </c>
       <c r="D168" s="258" t="n"/>
       <c r="E168" s="1451" t="n"/>
-      <c r="F168" s="1311">
+      <c r="F168" s="1453">
         <f>D168*E168</f>
         <v/>
       </c>
@@ -14648,7 +14678,7 @@
       </c>
       <c r="D169" s="258" t="n"/>
       <c r="E169" s="1451" t="n"/>
-      <c r="F169" s="1311">
+      <c r="F169" s="1453">
         <f>D169*E169</f>
         <v/>
       </c>
@@ -14671,7 +14701,7 @@
       </c>
       <c r="D170" s="258" t="n"/>
       <c r="E170" s="1451" t="n"/>
-      <c r="F170" s="1311">
+      <c r="F170" s="1453">
         <f>D170*E170</f>
         <v/>
       </c>
@@ -14694,7 +14724,7 @@
       </c>
       <c r="D171" s="258" t="n"/>
       <c r="E171" s="1451" t="n"/>
-      <c r="F171" s="1311">
+      <c r="F171" s="1453">
         <f>D171*E171</f>
         <v/>
       </c>
@@ -14717,7 +14747,7 @@
       </c>
       <c r="D172" s="258" t="n"/>
       <c r="E172" s="1451" t="n"/>
-      <c r="F172" s="1311">
+      <c r="F172" s="1453">
         <f>D172*E172</f>
         <v/>
       </c>
@@ -14740,7 +14770,7 @@
       </c>
       <c r="D173" s="258" t="n"/>
       <c r="E173" s="1451" t="n"/>
-      <c r="F173" s="1311">
+      <c r="F173" s="1453">
         <f>D173*E173</f>
         <v/>
       </c>
@@ -14763,7 +14793,7 @@
       </c>
       <c r="D174" s="258" t="n"/>
       <c r="E174" s="1451" t="n"/>
-      <c r="F174" s="1311">
+      <c r="F174" s="1453">
         <f>D174*E174</f>
         <v/>
       </c>
@@ -14786,7 +14816,7 @@
       </c>
       <c r="D175" s="258" t="n"/>
       <c r="E175" s="1451" t="n"/>
-      <c r="F175" s="1311">
+      <c r="F175" s="1453">
         <f>D175*E175</f>
         <v/>
       </c>
@@ -14801,7 +14831,7 @@
       <c r="C176" s="567" t="n"/>
       <c r="D176" s="567" t="n"/>
       <c r="E176" s="567" t="n"/>
-      <c r="F176" s="1312">
+      <c r="F176" s="1454">
         <f>SUM(F165:F175)</f>
         <v/>
       </c>
@@ -14848,7 +14878,7 @@
       </c>
       <c r="D179" s="258" t="n"/>
       <c r="E179" s="1451" t="n"/>
-      <c r="F179" s="1311">
+      <c r="F179" s="1453">
         <f>D179*E179</f>
         <v/>
       </c>
@@ -14871,7 +14901,7 @@
       </c>
       <c r="D180" s="258" t="n"/>
       <c r="E180" s="1451" t="n"/>
-      <c r="F180" s="1311">
+      <c r="F180" s="1453">
         <f>D180*E180</f>
         <v/>
       </c>
@@ -14894,7 +14924,7 @@
       </c>
       <c r="D181" s="258" t="n"/>
       <c r="E181" s="1451" t="n"/>
-      <c r="F181" s="1311">
+      <c r="F181" s="1453">
         <f>D181*E181</f>
         <v/>
       </c>
@@ -14917,7 +14947,7 @@
       </c>
       <c r="D182" s="258" t="n"/>
       <c r="E182" s="1451" t="n"/>
-      <c r="F182" s="1311">
+      <c r="F182" s="1453">
         <f>D182*E182</f>
         <v/>
       </c>
@@ -14940,7 +14970,7 @@
       </c>
       <c r="D183" s="258" t="n"/>
       <c r="E183" s="1451" t="n"/>
-      <c r="F183" s="1311">
+      <c r="F183" s="1453">
         <f>D183*E183</f>
         <v/>
       </c>
@@ -14963,7 +14993,7 @@
       </c>
       <c r="D184" s="258" t="n"/>
       <c r="E184" s="1451" t="n"/>
-      <c r="F184" s="1311">
+      <c r="F184" s="1453">
         <f>D184*E184</f>
         <v/>
       </c>
@@ -14978,7 +15008,7 @@
       <c r="C185" s="567" t="n"/>
       <c r="D185" s="567" t="n"/>
       <c r="E185" s="567" t="n"/>
-      <c r="F185" s="1312">
+      <c r="F185" s="1454">
         <f>SUM(F179:F184)</f>
         <v/>
       </c>
@@ -15025,7 +15055,7 @@
       </c>
       <c r="D188" s="258" t="n"/>
       <c r="E188" s="1451" t="n"/>
-      <c r="F188" s="1311">
+      <c r="F188" s="1453">
         <f>D188*E188</f>
         <v/>
       </c>
@@ -15048,7 +15078,7 @@
       </c>
       <c r="D189" s="258" t="n"/>
       <c r="E189" s="1451" t="n"/>
-      <c r="F189" s="1311">
+      <c r="F189" s="1453">
         <f>D189*E189</f>
         <v/>
       </c>
@@ -15071,7 +15101,7 @@
       </c>
       <c r="D190" s="258" t="n"/>
       <c r="E190" s="1451" t="n"/>
-      <c r="F190" s="1311">
+      <c r="F190" s="1453">
         <f>D190*E190</f>
         <v/>
       </c>
@@ -15094,7 +15124,7 @@
       </c>
       <c r="D191" s="258" t="n"/>
       <c r="E191" s="1451" t="n"/>
-      <c r="F191" s="1311">
+      <c r="F191" s="1453">
         <f>D191*E191</f>
         <v/>
       </c>
@@ -15109,7 +15139,7 @@
       <c r="C192" s="567" t="n"/>
       <c r="D192" s="567" t="n"/>
       <c r="E192" s="567" t="n"/>
-      <c r="F192" s="1312">
+      <c r="F192" s="1454">
         <f>SUM(F188:F191)</f>
         <v/>
       </c>
@@ -15156,7 +15186,7 @@
       </c>
       <c r="D195" s="258" t="n"/>
       <c r="E195" s="1451" t="n"/>
-      <c r="F195" s="1311">
+      <c r="F195" s="1453">
         <f>D195*E195</f>
         <v/>
       </c>
@@ -15179,7 +15209,7 @@
       </c>
       <c r="D196" s="258" t="n"/>
       <c r="E196" s="1451" t="n"/>
-      <c r="F196" s="1311">
+      <c r="F196" s="1453">
         <f>D196*E196</f>
         <v/>
       </c>
@@ -15202,7 +15232,7 @@
       </c>
       <c r="D197" s="258" t="n"/>
       <c r="E197" s="1451" t="n"/>
-      <c r="F197" s="1311">
+      <c r="F197" s="1453">
         <f>D197*E197</f>
         <v/>
       </c>
@@ -15217,7 +15247,7 @@
       <c r="C198" s="567" t="n"/>
       <c r="D198" s="567" t="n"/>
       <c r="E198" s="567" t="n"/>
-      <c r="F198" s="1312">
+      <c r="F198" s="1454">
         <f>SUM(F195:F197)</f>
         <v/>
       </c>
@@ -15264,7 +15294,7 @@
       </c>
       <c r="D201" s="258" t="n"/>
       <c r="E201" s="1451" t="n"/>
-      <c r="F201" s="1311">
+      <c r="F201" s="1453">
         <f>D201*E201</f>
         <v/>
       </c>
@@ -15287,7 +15317,7 @@
       </c>
       <c r="D202" s="258" t="n"/>
       <c r="E202" s="1451" t="n"/>
-      <c r="F202" s="1311">
+      <c r="F202" s="1453">
         <f>D202*E202</f>
         <v/>
       </c>
@@ -15310,7 +15340,7 @@
       </c>
       <c r="D203" s="258" t="n"/>
       <c r="E203" s="1451" t="n"/>
-      <c r="F203" s="1311">
+      <c r="F203" s="1453">
         <f>D203*E203</f>
         <v/>
       </c>
@@ -15333,7 +15363,7 @@
       </c>
       <c r="D204" s="258" t="n"/>
       <c r="E204" s="1451" t="n"/>
-      <c r="F204" s="1311">
+      <c r="F204" s="1453">
         <f>D204*E204</f>
         <v/>
       </c>
@@ -15356,7 +15386,7 @@
       </c>
       <c r="D205" s="258" t="n"/>
       <c r="E205" s="1451" t="n"/>
-      <c r="F205" s="1311">
+      <c r="F205" s="1453">
         <f>D205*E205</f>
         <v/>
       </c>
@@ -15379,7 +15409,7 @@
       </c>
       <c r="D206" s="258" t="n"/>
       <c r="E206" s="1451" t="n"/>
-      <c r="F206" s="1311">
+      <c r="F206" s="1453">
         <f>D206*E206</f>
         <v/>
       </c>
@@ -15402,7 +15432,7 @@
       </c>
       <c r="D207" s="258" t="n"/>
       <c r="E207" s="1451" t="n"/>
-      <c r="F207" s="1311">
+      <c r="F207" s="1453">
         <f>D207*E207</f>
         <v/>
       </c>
@@ -15425,7 +15455,7 @@
       </c>
       <c r="D208" s="258" t="n"/>
       <c r="E208" s="1451" t="n"/>
-      <c r="F208" s="1311">
+      <c r="F208" s="1453">
         <f>D208*E208</f>
         <v/>
       </c>
@@ -15448,7 +15478,7 @@
       </c>
       <c r="D209" s="258" t="n"/>
       <c r="E209" s="1451" t="n"/>
-      <c r="F209" s="1311">
+      <c r="F209" s="1453">
         <f>D209*E209</f>
         <v/>
       </c>
@@ -15471,7 +15501,7 @@
       </c>
       <c r="D210" s="258" t="n"/>
       <c r="E210" s="1451" t="n"/>
-      <c r="F210" s="1311">
+      <c r="F210" s="1453">
         <f>D210*E210</f>
         <v/>
       </c>
@@ -15494,7 +15524,7 @@
       </c>
       <c r="D211" s="258" t="n"/>
       <c r="E211" s="1451" t="n"/>
-      <c r="F211" s="1311">
+      <c r="F211" s="1453">
         <f>D211*E211</f>
         <v/>
       </c>
@@ -15509,7 +15539,7 @@
       <c r="C212" s="567" t="n"/>
       <c r="D212" s="567" t="n"/>
       <c r="E212" s="567" t="n"/>
-      <c r="F212" s="1312">
+      <c r="F212" s="1454">
         <f>SUM(F201:F211)</f>
         <v/>
       </c>
@@ -15556,7 +15586,7 @@
       </c>
       <c r="D215" s="258" t="n"/>
       <c r="E215" s="1451" t="n"/>
-      <c r="F215" s="1311">
+      <c r="F215" s="1453">
         <f>D215*E215</f>
         <v/>
       </c>
@@ -15579,7 +15609,7 @@
       </c>
       <c r="D216" s="258" t="n"/>
       <c r="E216" s="1451" t="n"/>
-      <c r="F216" s="1311">
+      <c r="F216" s="1453">
         <f>D216*E216</f>
         <v/>
       </c>
@@ -15602,7 +15632,7 @@
       </c>
       <c r="D217" s="258" t="n"/>
       <c r="E217" s="1451" t="n"/>
-      <c r="F217" s="1311">
+      <c r="F217" s="1453">
         <f>D217*E217</f>
         <v/>
       </c>
@@ -15625,7 +15655,7 @@
       </c>
       <c r="D218" s="258" t="n"/>
       <c r="E218" s="1451" t="n"/>
-      <c r="F218" s="1311">
+      <c r="F218" s="1453">
         <f>D218*E218</f>
         <v/>
       </c>
@@ -15640,7 +15670,7 @@
       <c r="C219" s="567" t="n"/>
       <c r="D219" s="567" t="n"/>
       <c r="E219" s="567" t="n"/>
-      <c r="F219" s="1312">
+      <c r="F219" s="1454">
         <f>SUM(F215:F218)</f>
         <v/>
       </c>
@@ -15687,7 +15717,7 @@
       </c>
       <c r="D222" s="258" t="n"/>
       <c r="E222" s="1451" t="n"/>
-      <c r="F222" s="1311">
+      <c r="F222" s="1453">
         <f>D222*E222</f>
         <v/>
       </c>
@@ -15710,7 +15740,7 @@
       </c>
       <c r="D223" s="258" t="n"/>
       <c r="E223" s="1451" t="n"/>
-      <c r="F223" s="1311">
+      <c r="F223" s="1453">
         <f>D223*E223</f>
         <v/>
       </c>
@@ -15733,7 +15763,7 @@
       </c>
       <c r="D224" s="258" t="n"/>
       <c r="E224" s="1451" t="n"/>
-      <c r="F224" s="1311">
+      <c r="F224" s="1453">
         <f>D224*E224</f>
         <v/>
       </c>
@@ -15756,7 +15786,7 @@
       </c>
       <c r="D225" s="258" t="n"/>
       <c r="E225" s="1451" t="n"/>
-      <c r="F225" s="1311">
+      <c r="F225" s="1453">
         <f>D225*E225</f>
         <v/>
       </c>
@@ -15779,7 +15809,7 @@
       </c>
       <c r="D226" s="258" t="n"/>
       <c r="E226" s="1451" t="n"/>
-      <c r="F226" s="1311">
+      <c r="F226" s="1453">
         <f>D226*E226</f>
         <v/>
       </c>
@@ -15794,7 +15824,7 @@
       <c r="C227" s="567" t="n"/>
       <c r="D227" s="567" t="n"/>
       <c r="E227" s="567" t="n"/>
-      <c r="F227" s="1312">
+      <c r="F227" s="1454">
         <f>SUM(F222:F226)</f>
         <v/>
       </c>
@@ -15841,7 +15871,7 @@
       </c>
       <c r="D230" s="258" t="n"/>
       <c r="E230" s="1451" t="n"/>
-      <c r="F230" s="1311">
+      <c r="F230" s="1453">
         <f>D230*E230</f>
         <v/>
       </c>
@@ -15856,7 +15886,7 @@
       <c r="C231" s="567" t="n"/>
       <c r="D231" s="567" t="n"/>
       <c r="E231" s="567" t="n"/>
-      <c r="F231" s="1312">
+      <c r="F231" s="1454">
         <f>SUM(F230:F230)</f>
         <v/>
       </c>
@@ -15903,7 +15933,7 @@
       </c>
       <c r="D234" s="258" t="n"/>
       <c r="E234" s="1451" t="n"/>
-      <c r="F234" s="1311">
+      <c r="F234" s="1453">
         <f>D234*E234</f>
         <v/>
       </c>
@@ -15926,7 +15956,7 @@
       </c>
       <c r="D235" s="258" t="n"/>
       <c r="E235" s="1451" t="n"/>
-      <c r="F235" s="1311">
+      <c r="F235" s="1453">
         <f>D235*E235</f>
         <v/>
       </c>
@@ -15949,7 +15979,7 @@
       </c>
       <c r="D236" s="258" t="n"/>
       <c r="E236" s="1451" t="n"/>
-      <c r="F236" s="1311">
+      <c r="F236" s="1453">
         <f>D236*E236</f>
         <v/>
       </c>
@@ -15972,7 +16002,7 @@
       </c>
       <c r="D237" s="258" t="n"/>
       <c r="E237" s="1451" t="n"/>
-      <c r="F237" s="1311">
+      <c r="F237" s="1453">
         <f>D237*E237</f>
         <v/>
       </c>
@@ -15987,7 +16017,7 @@
       <c r="C238" s="567" t="n"/>
       <c r="D238" s="567" t="n"/>
       <c r="E238" s="567" t="n"/>
-      <c r="F238" s="1312">
+      <c r="F238" s="1454">
         <f>SUM(F234:F237)</f>
         <v/>
       </c>
@@ -16010,7 +16040,7 @@
       <c r="C240" s="567" t="n"/>
       <c r="D240" s="567" t="n"/>
       <c r="E240" s="567" t="n"/>
-      <c r="F240" s="1313">
+      <c r="F240" s="1456">
         <f>F25+F39+F49+F69+F81+F93+F100+F107+F121+F129+F140+F147+F162+F176+F185+F192+F198+F212+F219+F227+F231+F238</f>
         <v/>
       </c>
@@ -16036,7 +16066,7 @@
         <f>'Ficha Técnica del Proyecto'!$B$29</f>
         <v/>
       </c>
-      <c r="F242" s="1315">
+      <c r="F242" s="1457">
         <f>F240*E242</f>
         <v/>
       </c>
@@ -16054,7 +16084,7 @@
         <f>'Ficha Técnica del Proyecto'!$B$30</f>
         <v/>
       </c>
-      <c r="F243" s="1315">
+      <c r="F243" s="1457">
         <f>F240*E243</f>
         <v/>
       </c>
@@ -16072,7 +16102,7 @@
         <f>'Ficha Técnica del Proyecto'!$B$31</f>
         <v/>
       </c>
-      <c r="F244" s="1315">
+      <c r="F244" s="1457">
         <f>F240*E244</f>
         <v/>
       </c>
@@ -16087,7 +16117,7 @@
       <c r="C245" s="29" t="n"/>
       <c r="D245" s="29" t="n"/>
       <c r="E245" s="30" t="n"/>
-      <c r="F245" s="1312">
+      <c r="F245" s="1454">
         <f>F242+F243+F244</f>
         <v/>
       </c>
@@ -16102,7 +16132,7 @@
       <c r="C246" s="716" t="n"/>
       <c r="D246" s="716" t="n"/>
       <c r="E246" s="47" t="n"/>
-      <c r="F246" s="1315">
+      <c r="F246" s="1457">
         <f>F240+F245</f>
         <v/>
       </c>
@@ -16120,7 +16150,7 @@
         <f>'Ficha Técnica del Proyecto'!$B$32</f>
         <v/>
       </c>
-      <c r="F247" s="1315">
+      <c r="F247" s="1457">
         <f>F244*E247</f>
         <v/>
       </c>
@@ -16143,7 +16173,7 @@
       <c r="C249" s="567" t="n"/>
       <c r="D249" s="567" t="n"/>
       <c r="E249" s="567" t="n"/>
-      <c r="F249" s="1316">
+      <c r="F249" s="1458">
         <f>F246+F247</f>
         <v/>
       </c>
@@ -16181,7 +16211,7 @@
       <c r="C252" s="90" t="n"/>
       <c r="D252" s="90" t="n"/>
       <c r="E252" s="90" t="n"/>
-      <c r="F252" s="1317">
+      <c r="F252" s="1459">
         <f>F240/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16196,7 +16226,7 @@
       <c r="C253" s="92" t="n"/>
       <c r="D253" s="92" t="n"/>
       <c r="E253" s="92" t="n"/>
-      <c r="F253" s="1318">
+      <c r="F253" s="1460">
         <f>F249/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16494,7 +16524,7 @@
           <t>PRELIMINARES</t>
         </is>
       </c>
-      <c r="C12" s="1319">
+      <c r="C12" s="1461">
         <f>'Presupuesto '!F25</f>
         <v/>
       </c>
@@ -16502,7 +16532,7 @@
         <f>C12/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E12" s="1321">
+      <c r="E12" s="1462">
         <f>C12/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16519,7 +16549,7 @@
           <t>MOVIMIENTO DE TIERRAS</t>
         </is>
       </c>
-      <c r="C13" s="1319">
+      <c r="C13" s="1461">
         <f>'Presupuesto '!F39</f>
         <v/>
       </c>
@@ -16527,7 +16557,7 @@
         <f>C13/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E13" s="1321">
+      <c r="E13" s="1462">
         <f>C13/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16544,7 +16574,7 @@
           <t>CIMENTACIONES</t>
         </is>
       </c>
-      <c r="C14" s="1319">
+      <c r="C14" s="1461">
         <f>'Presupuesto '!F49</f>
         <v/>
       </c>
@@ -16552,7 +16582,7 @@
         <f>C14/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E14" s="1321">
+      <c r="E14" s="1462">
         <f>C14/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16569,7 +16599,7 @@
           <t>ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C15" s="1319">
+      <c r="C15" s="1461">
         <f>'Presupuesto '!F69</f>
         <v/>
       </c>
@@ -16577,7 +16607,7 @@
         <f>C15/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E15" s="1321">
+      <c r="E15" s="1462">
         <f>C15/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16594,7 +16624,7 @@
           <t>MAMPOSTERÍA</t>
         </is>
       </c>
-      <c r="C16" s="1319">
+      <c r="C16" s="1461">
         <f>'Presupuesto '!F81</f>
         <v/>
       </c>
@@ -16602,7 +16632,7 @@
         <f>C16/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E16" s="1321">
+      <c r="E16" s="1462">
         <f>C16/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16619,7 +16649,7 @@
           <t>CUBIERTAS</t>
         </is>
       </c>
-      <c r="C17" s="1319">
+      <c r="C17" s="1461">
         <f>'Presupuesto '!F93</f>
         <v/>
       </c>
@@ -16627,7 +16657,7 @@
         <f>C17/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E17" s="1321">
+      <c r="E17" s="1462">
         <f>C17/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16644,7 +16674,7 @@
           <t>IMPERMEABILIZACIONES</t>
         </is>
       </c>
-      <c r="C18" s="1319">
+      <c r="C18" s="1461">
         <f>'Presupuesto '!F100</f>
         <v/>
       </c>
@@ -16652,7 +16682,7 @@
         <f>C18/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E18" s="1321">
+      <c r="E18" s="1462">
         <f>C18/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16669,7 +16699,7 @@
           <t>PAÑETES Y REVOQUES</t>
         </is>
       </c>
-      <c r="C19" s="1319">
+      <c r="C19" s="1461">
         <f>'Presupuesto '!F107</f>
         <v/>
       </c>
@@ -16677,7 +16707,7 @@
         <f>C19/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E19" s="1321">
+      <c r="E19" s="1462">
         <f>C19/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16694,7 +16724,7 @@
           <t>PISOS Y ENCHAPES</t>
         </is>
       </c>
-      <c r="C20" s="1319">
+      <c r="C20" s="1461">
         <f>'Presupuesto '!F121</f>
         <v/>
       </c>
@@ -16702,7 +16732,7 @@
         <f>C20/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E20" s="1321">
+      <c r="E20" s="1462">
         <f>C20/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16719,7 +16749,7 @@
           <t>PINTURA</t>
         </is>
       </c>
-      <c r="C21" s="1319">
+      <c r="C21" s="1461">
         <f>'Presupuesto '!F129</f>
         <v/>
       </c>
@@ -16727,7 +16757,7 @@
         <f>C21/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E21" s="1321">
+      <c r="E21" s="1462">
         <f>C21/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16744,7 +16774,7 @@
           <t>CARPINTERÍA</t>
         </is>
       </c>
-      <c r="C22" s="1319">
+      <c r="C22" s="1461">
         <f>'Presupuesto '!F140</f>
         <v/>
       </c>
@@ -16752,7 +16782,7 @@
         <f>C22/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E22" s="1321">
+      <c r="E22" s="1462">
         <f>C22/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16769,7 +16799,7 @@
           <t>VIDRIOS</t>
         </is>
       </c>
-      <c r="C23" s="1319">
+      <c r="C23" s="1461">
         <f>'Presupuesto '!F147</f>
         <v/>
       </c>
@@ -16777,7 +16807,7 @@
         <f>C23/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E23" s="1321">
+      <c r="E23" s="1462">
         <f>C23/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16794,7 +16824,7 @@
           <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
-      <c r="C24" s="1319">
+      <c r="C24" s="1461">
         <f>'Presupuesto '!F249</f>
         <v/>
       </c>
@@ -16802,7 +16832,7 @@
         <f>C24/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E24" s="1321">
+      <c r="E24" s="1462">
         <f>C24/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16819,7 +16849,7 @@
           <t>INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
-      <c r="C25" s="1319">
+      <c r="C25" s="1461">
         <f>'Presupuesto '!F176</f>
         <v/>
       </c>
@@ -16827,7 +16857,7 @@
         <f>C25/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E25" s="1321">
+      <c r="E25" s="1462">
         <f>C25/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16844,7 +16874,7 @@
           <t>COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
-      <c r="C26" s="1319">
+      <c r="C26" s="1461">
         <f>'Presupuesto '!F185</f>
         <v/>
       </c>
@@ -16852,7 +16882,7 @@
         <f>C26/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E26" s="1321">
+      <c r="E26" s="1462">
         <f>C26/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16869,7 +16899,7 @@
           <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
-      <c r="C27" s="1319">
+      <c r="C27" s="1461">
         <f>'Presupuesto '!F192</f>
         <v/>
       </c>
@@ -16877,7 +16907,7 @@
         <f>C27/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E27" s="1321">
+      <c r="E27" s="1462">
         <f>C27/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16894,7 +16924,7 @@
           <t>GAS</t>
         </is>
       </c>
-      <c r="C28" s="1319">
+      <c r="C28" s="1461">
         <f>'Presupuesto '!F198</f>
         <v/>
       </c>
@@ -16902,7 +16932,7 @@
         <f>C28/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E28" s="1321">
+      <c r="E28" s="1462">
         <f>C28/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16919,7 +16949,7 @@
           <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
-      <c r="C29" s="1319">
+      <c r="C29" s="1461">
         <f>'Presupuesto '!F212</f>
         <v/>
       </c>
@@ -16927,7 +16957,7 @@
         <f>C29/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E29" s="1321">
+      <c r="E29" s="1462">
         <f>C29/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16944,7 +16974,7 @@
           <t>OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
-      <c r="C30" s="1319">
+      <c r="C30" s="1461">
         <f>'Presupuesto '!F219</f>
         <v/>
       </c>
@@ -16952,7 +16982,7 @@
         <f>C30/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E30" s="1321">
+      <c r="E30" s="1462">
         <f>C30/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16969,7 +16999,7 @@
           <t>ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
-      <c r="C31" s="1319">
+      <c r="C31" s="1461">
         <f>'Presupuesto '!F227</f>
         <v/>
       </c>
@@ -16977,7 +17007,7 @@
         <f>C31/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E31" s="1321">
+      <c r="E31" s="1462">
         <f>C31/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -16994,7 +17024,7 @@
           <t>ASCENSORES</t>
         </is>
       </c>
-      <c r="C32" s="1319">
+      <c r="C32" s="1461">
         <f>'Presupuesto '!F231</f>
         <v/>
       </c>
@@ -17002,7 +17032,7 @@
         <f>C32/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E32" s="1321">
+      <c r="E32" s="1462">
         <f>C32/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -17019,7 +17049,7 @@
           <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
-      <c r="C33" s="1319">
+      <c r="C33" s="1461">
         <f>'Presupuesto '!F238</f>
         <v/>
       </c>
@@ -17027,7 +17057,7 @@
         <f>C33/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E33" s="1322">
+      <c r="E33" s="1463">
         <f>C33/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -17040,7 +17070,7 @@
           <t>COSTO DIRECTO TOTAL</t>
         </is>
       </c>
-      <c r="C34" s="1323">
+      <c r="C34" s="1464">
         <f>SUM(C12:C33)</f>
         <v/>
       </c>
@@ -17048,7 +17078,7 @@
         <f>C34/'Presupuesto '!$F$240</f>
         <v/>
       </c>
-      <c r="E34" s="1325">
+      <c r="E34" s="1465">
         <f>C34/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
@@ -17059,7 +17089,7 @@
       <c r="B35" s="274" t="n"/>
       <c r="C35" s="274" t="n"/>
       <c r="D35" s="274" t="n"/>
-      <c r="E35" s="1326" t="n"/>
+      <c r="E35" s="1466" t="n"/>
       <c r="F35" s="625" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="550">
@@ -17069,7 +17099,7 @@
           <t>Subtotal AIU (A+I+U)</t>
         </is>
       </c>
-      <c r="C36" s="1319">
+      <c r="C36" s="1461">
         <f>'Presupuesto '!F227</f>
         <v/>
       </c>
@@ -17084,7 +17114,7 @@
           <t>Costo Directo + AIU</t>
         </is>
       </c>
-      <c r="C37" s="1319">
+      <c r="C37" s="1461">
         <f>'Presupuesto '!F228</f>
         <v/>
       </c>
@@ -17099,7 +17129,7 @@
           <t>IVA sobre Utilidad</t>
         </is>
       </c>
-      <c r="C38" s="1319">
+      <c r="C38" s="1461">
         <f>'Presupuesto '!F229</f>
         <v/>
       </c>
@@ -17122,7 +17152,7 @@
           <t>PRESUPUESTO TOTAL DE OBRA</t>
         </is>
       </c>
-      <c r="C40" s="1327">
+      <c r="C40" s="1467">
         <f>'Presupuesto '!F249</f>
         <v/>
       </c>
@@ -17148,7 +17178,7 @@
           <t>Costo por m² construido (Presupuesto Total)</t>
         </is>
       </c>
-      <c r="C42" s="1328">
+      <c r="C42" s="1468">
         <f>C40/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -11282,13 +11282,13 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
   </mergeCells>
@@ -11304,7 +11304,7 @@
     <tabColor rgb="FF2E7D32"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F259"/>
+  <dimension ref="A1:F260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" style="614" min="1" max="1"/>
@@ -13392,76 +13392,76 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="80" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="B106" s="364" t="inlineStr">
-        <is>
-          <t>Estuco plástico o tradicional</t>
-        </is>
-      </c>
-      <c r="C106" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D106" s="1449" t="n"/>
-      <c r="E106" s="1452" t="n"/>
-      <c r="F106" s="1453">
-        <f>D106*E106</f>
+      <c r="A106" s="81" t="n"/>
+      <c r="B106" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 8 - PAÑETES Y REVOQUES</t>
+        </is>
+      </c>
+      <c r="C106" s="567" t="n"/>
+      <c r="D106" s="567" t="n"/>
+      <c r="E106" s="567" t="n"/>
+      <c r="F106" s="1454">
+        <f>SUM(F103:F105)</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="81" t="n"/>
-      <c r="B107" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 8 - PAÑETES Y REVOQUES</t>
-        </is>
-      </c>
+      <c r="A107" s="82" t="n"/>
+      <c r="B107" s="708" t="n"/>
       <c r="C107" s="567" t="n"/>
       <c r="D107" s="567" t="n"/>
       <c r="E107" s="567" t="n"/>
-      <c r="F107" s="1454">
-        <f>SUM(F103:F106)</f>
-        <v/>
-      </c>
+      <c r="F107" s="607" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="82" t="n"/>
-      <c r="B108" s="708" t="n"/>
+      <c r="A108" s="182" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B108" s="703" t="inlineStr">
+        <is>
+          <t>PISOS Y ENCHAPES</t>
+        </is>
+      </c>
       <c r="C108" s="567" t="n"/>
       <c r="D108" s="567" t="n"/>
       <c r="E108" s="567" t="n"/>
-      <c r="F108" s="607" t="n"/>
+      <c r="F108" s="567" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="182" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B109" s="703" t="inlineStr">
-        <is>
-          <t>PISOS Y ENCHAPES</t>
-        </is>
-      </c>
-      <c r="C109" s="567" t="n"/>
-      <c r="D109" s="567" t="n"/>
-      <c r="E109" s="567" t="n"/>
-      <c r="F109" s="567" t="n"/>
+      <c r="A109" s="80" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B109" s="364" t="inlineStr">
+        <is>
+          <t>Mortero de nivelación</t>
+        </is>
+      </c>
+      <c r="C109" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D109" s="258" t="n"/>
+      <c r="E109" s="1451" t="n"/>
+      <c r="F109" s="1453">
+        <f>D109*E109</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="80" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="B110" s="364" t="inlineStr">
         <is>
-          <t>Mortero de nivelación</t>
+          <t>Piso cerámico</t>
         </is>
       </c>
       <c r="C110" s="257" t="inlineStr">
@@ -13479,12 +13479,12 @@
     <row r="111">
       <c r="A111" s="80" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="B111" s="364" t="inlineStr">
         <is>
-          <t>Piso cerámico</t>
+          <t>Piso en porcelanato</t>
         </is>
       </c>
       <c r="C111" s="257" t="inlineStr">
@@ -13502,12 +13502,12 @@
     <row r="112">
       <c r="A112" s="80" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="B112" s="364" t="inlineStr">
         <is>
-          <t>Piso en porcelanato</t>
+          <t>Piso vinílico</t>
         </is>
       </c>
       <c r="C112" s="257" t="inlineStr">
@@ -13525,12 +13525,12 @@
     <row r="113">
       <c r="A113" s="80" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="B113" s="364" t="inlineStr">
         <is>
-          <t>Piso vinílico</t>
+          <t>Piso laminado</t>
         </is>
       </c>
       <c r="C113" s="257" t="inlineStr">
@@ -13548,12 +13548,12 @@
     <row r="114">
       <c r="A114" s="80" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="B114" s="364" t="inlineStr">
         <is>
-          <t>Piso laminado</t>
+          <t>Enchape cerámico en muros</t>
         </is>
       </c>
       <c r="C114" s="257" t="inlineStr">
@@ -13561,8 +13561,8 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D114" s="258" t="n"/>
-      <c r="E114" s="1451" t="n"/>
+      <c r="D114" s="1449" t="n"/>
+      <c r="E114" s="1452" t="n"/>
       <c r="F114" s="1453">
         <f>D114*E114</f>
         <v/>
@@ -13571,21 +13571,21 @@
     <row r="115">
       <c r="A115" s="80" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="B115" s="364" t="inlineStr">
         <is>
-          <t>Enchape cerámico en muros</t>
+          <t>Guardaescoba</t>
         </is>
       </c>
       <c r="C115" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D115" s="1449" t="n"/>
-      <c r="E115" s="1452" t="n"/>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D115" s="258" t="n"/>
+      <c r="E115" s="1451" t="n"/>
       <c r="F115" s="1453">
         <f>D115*E115</f>
         <v/>
@@ -13594,12 +13594,12 @@
     <row r="116">
       <c r="A116" s="80" t="inlineStr">
         <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="B116" s="364" t="inlineStr">
-        <is>
-          <t>Guardaescoba</t>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="B116" s="365" t="inlineStr">
+        <is>
+          <t>Juntas de dilatación / construcción</t>
         </is>
       </c>
       <c r="C116" s="257" t="inlineStr">
@@ -13607,9 +13607,9 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D116" s="258" t="n"/>
-      <c r="E116" s="1451" t="n"/>
-      <c r="F116" s="1453">
+      <c r="D116" s="1449" t="n"/>
+      <c r="E116" s="1452" t="n"/>
+      <c r="F116" s="1455">
         <f>D116*E116</f>
         <v/>
       </c>
@@ -13617,17 +13617,17 @@
     <row r="117">
       <c r="A117" s="80" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="B117" s="365" t="inlineStr">
         <is>
-          <t>Juntas de dilatación / construcción</t>
+          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
         </is>
       </c>
       <c r="C117" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D117" s="1449" t="n"/>
@@ -13640,12 +13640,12 @@
     <row r="118">
       <c r="A118" s="80" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="B118" s="365" t="inlineStr">
         <is>
-          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
+          <t>Baldosa de granito</t>
         </is>
       </c>
       <c r="C118" s="257" t="inlineStr">
@@ -13663,12 +13663,12 @@
     <row r="119">
       <c r="A119" s="80" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="B119" s="365" t="inlineStr">
         <is>
-          <t>Baldosa de granito</t>
+          <t>Enchape en granito pulido</t>
         </is>
       </c>
       <c r="C119" s="257" t="inlineStr">
@@ -13684,76 +13684,76 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="80" t="inlineStr">
-        <is>
-          <t>9.11</t>
-        </is>
-      </c>
-      <c r="B120" s="365" t="inlineStr">
-        <is>
-          <t>Enchape en granito pulido</t>
-        </is>
-      </c>
-      <c r="C120" s="257" t="inlineStr">
+      <c r="A120" s="81" t="n"/>
+      <c r="B120" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 9 - PISOS Y ENCHAPES</t>
+        </is>
+      </c>
+      <c r="C120" s="567" t="n"/>
+      <c r="D120" s="567" t="n"/>
+      <c r="E120" s="567" t="n"/>
+      <c r="F120" s="1454">
+        <f>SUM(F109:F119)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="82" t="n"/>
+      <c r="B121" s="716" t="n"/>
+      <c r="C121" s="716" t="n"/>
+      <c r="D121" s="716" t="n"/>
+      <c r="E121" s="716" t="n"/>
+      <c r="F121" s="708" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="182" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B122" s="703" t="inlineStr">
+        <is>
+          <t>PINTURA</t>
+        </is>
+      </c>
+      <c r="C122" s="567" t="n"/>
+      <c r="D122" s="567" t="n"/>
+      <c r="E122" s="567" t="n"/>
+      <c r="F122" s="567" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="80" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="B123" s="364" t="inlineStr">
+        <is>
+          <t>Pintura vinílica interior</t>
+        </is>
+      </c>
+      <c r="C123" s="257" t="inlineStr">
         <is>
           <t>M²</t>
         </is>
       </c>
-      <c r="D120" s="1449" t="n"/>
-      <c r="E120" s="1452" t="n"/>
-      <c r="F120" s="1455">
-        <f>D120*E120</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="81" t="n"/>
-      <c r="B121" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 9 - PISOS Y ENCHAPES</t>
-        </is>
-      </c>
-      <c r="C121" s="567" t="n"/>
-      <c r="D121" s="567" t="n"/>
-      <c r="E121" s="567" t="n"/>
-      <c r="F121" s="1454">
-        <f>SUM(F110:F120)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="82" t="n"/>
-      <c r="B122" s="716" t="n"/>
-      <c r="C122" s="716" t="n"/>
-      <c r="D122" s="716" t="n"/>
-      <c r="E122" s="716" t="n"/>
-      <c r="F122" s="708" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="182" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B123" s="703" t="inlineStr">
-        <is>
-          <t>PINTURA</t>
-        </is>
-      </c>
-      <c r="C123" s="567" t="n"/>
-      <c r="D123" s="567" t="n"/>
-      <c r="E123" s="567" t="n"/>
-      <c r="F123" s="567" t="n"/>
+      <c r="D123" s="258" t="n"/>
+      <c r="E123" s="1451" t="n"/>
+      <c r="F123" s="1453">
+        <f>D123*E123</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="80" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="B124" s="364" t="inlineStr">
         <is>
-          <t>Pintura vinílica interior</t>
+          <t>Pintura exterior</t>
         </is>
       </c>
       <c r="C124" s="257" t="inlineStr">
@@ -13771,12 +13771,12 @@
     <row r="125">
       <c r="A125" s="80" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="B125" s="364" t="inlineStr">
         <is>
-          <t>Pintura exterior</t>
+          <t>Pintura esmalte en superficies metálicas/madera</t>
         </is>
       </c>
       <c r="C125" s="257" t="inlineStr">
@@ -13794,12 +13794,12 @@
     <row r="126">
       <c r="A126" s="80" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="B126" s="364" t="inlineStr">
         <is>
-          <t>Pintura esmalte en superficies metálicas/madera</t>
+          <t>Pintura anticorrosiva</t>
         </is>
       </c>
       <c r="C126" s="257" t="inlineStr">
@@ -13817,12 +13817,12 @@
     <row r="127">
       <c r="A127" s="80" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="B127" s="364" t="inlineStr">
         <is>
-          <t>Pintura anticorrosiva</t>
+          <t>Sellador / imprimante</t>
         </is>
       </c>
       <c r="C127" s="257" t="inlineStr">
@@ -13830,8 +13830,8 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D127" s="258" t="n"/>
-      <c r="E127" s="1451" t="n"/>
+      <c r="D127" s="1449" t="n"/>
+      <c r="E127" s="1452" t="n"/>
       <c r="F127" s="1453">
         <f>D127*E127</f>
         <v/>
@@ -13840,12 +13840,12 @@
     <row r="128">
       <c r="A128" s="80" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="B128" s="364" t="inlineStr">
         <is>
-          <t>Sellador / imprimante</t>
+          <t>Estuco plástico</t>
         </is>
       </c>
       <c r="C128" s="257" t="inlineStr">
@@ -13861,85 +13861,85 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="81" t="n"/>
-      <c r="B129" s="704" t="inlineStr">
+      <c r="A129" s="80" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="B129" s="364" t="inlineStr">
+        <is>
+          <t>Estuco tradicional</t>
+        </is>
+      </c>
+      <c r="C129" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D129" s="1449" t="n"/>
+      <c r="E129" s="1452" t="n"/>
+      <c r="F129" s="1453">
+        <f>D129*E129</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="81" t="n"/>
+      <c r="B130" s="704" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 10 - PINTURA</t>
         </is>
       </c>
-      <c r="C129" s="567" t="n"/>
-      <c r="D129" s="567" t="n"/>
-      <c r="E129" s="567" t="n"/>
-      <c r="F129" s="1454">
-        <f>SUM(F124:F128)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="82" t="n"/>
-      <c r="B130" s="708" t="n"/>
       <c r="C130" s="567" t="n"/>
       <c r="D130" s="567" t="n"/>
       <c r="E130" s="567" t="n"/>
-      <c r="F130" s="607" t="n"/>
+      <c r="F130" s="1454">
+        <f>SUM(F123:F129)</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="182" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B131" s="703" t="inlineStr">
-        <is>
-          <t>CARPINTERÍA</t>
-        </is>
-      </c>
+      <c r="A131" s="82" t="n"/>
+      <c r="B131" s="708" t="n"/>
       <c r="C131" s="567" t="n"/>
       <c r="D131" s="567" t="n"/>
       <c r="E131" s="567" t="n"/>
-      <c r="F131" s="567" t="n"/>
+      <c r="F131" s="607" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="80" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="B132" s="364" t="inlineStr">
-        <is>
-          <t>Puertas de madera</t>
-        </is>
-      </c>
-      <c r="C132" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D132" s="258" t="n"/>
-      <c r="E132" s="1451" t="n"/>
-      <c r="F132" s="1453">
-        <f>D132*E132</f>
-        <v/>
-      </c>
+      <c r="A132" s="182" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B132" s="703" t="inlineStr">
+        <is>
+          <t>CARPINTERÍA</t>
+        </is>
+      </c>
+      <c r="C132" s="567" t="n"/>
+      <c r="D132" s="567" t="n"/>
+      <c r="E132" s="567" t="n"/>
+      <c r="F132" s="567" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="80" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="B133" s="364" t="inlineStr">
         <is>
-          <t>Muebles fijos de madera</t>
+          <t>Puertas de madera</t>
         </is>
       </c>
       <c r="C133" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D133" s="1449" t="n"/>
-      <c r="E133" s="1452" t="n"/>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D133" s="258" t="n"/>
+      <c r="E133" s="1451" t="n"/>
       <c r="F133" s="1453">
         <f>D133*E133</f>
         <v/>
@@ -13948,21 +13948,21 @@
     <row r="134">
       <c r="A134" s="80" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="B134" s="364" t="inlineStr">
         <is>
-          <t>Puertas metálicas</t>
+          <t>Muebles fijos de madera</t>
         </is>
       </c>
       <c r="C134" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D134" s="258" t="n"/>
-      <c r="E134" s="1451" t="n"/>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D134" s="1449" t="n"/>
+      <c r="E134" s="1452" t="n"/>
       <c r="F134" s="1453">
         <f>D134*E134</f>
         <v/>
@@ -13971,22 +13971,22 @@
     <row r="135">
       <c r="A135" s="80" t="inlineStr">
         <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="B135" s="365" t="inlineStr">
-        <is>
-          <t>Barandas metálicas</t>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="B135" s="364" t="inlineStr">
+        <is>
+          <t>Puertas metálicas</t>
         </is>
       </c>
       <c r="C135" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D135" s="1449" t="n"/>
-      <c r="E135" s="1452" t="n"/>
-      <c r="F135" s="1455">
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D135" s="258" t="n"/>
+      <c r="E135" s="1451" t="n"/>
+      <c r="F135" s="1453">
         <f>D135*E135</f>
         <v/>
       </c>
@@ -13994,12 +13994,12 @@
     <row r="136">
       <c r="A136" s="80" t="inlineStr">
         <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="B136" s="364" t="inlineStr">
-        <is>
-          <t>Pasamanos</t>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="B136" s="365" t="inlineStr">
+        <is>
+          <t>Barandas metálicas</t>
         </is>
       </c>
       <c r="C136" s="257" t="inlineStr">
@@ -14007,9 +14007,9 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D136" s="258" t="n"/>
-      <c r="E136" s="1451" t="n"/>
-      <c r="F136" s="1453">
+      <c r="D136" s="1449" t="n"/>
+      <c r="E136" s="1452" t="n"/>
+      <c r="F136" s="1455">
         <f>D136*E136</f>
         <v/>
       </c>
@@ -14017,17 +14017,17 @@
     <row r="137">
       <c r="A137" s="80" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="B137" s="364" t="inlineStr">
         <is>
-          <t>Ventanas de aluminio</t>
+          <t>Pasamanos</t>
         </is>
       </c>
       <c r="C137" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D137" s="258" t="n"/>
@@ -14040,12 +14040,12 @@
     <row r="138">
       <c r="A138" s="80" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="B138" s="364" t="inlineStr">
         <is>
-          <t>Divisiones de aluminio</t>
+          <t>Ventanas de aluminio</t>
         </is>
       </c>
       <c r="C138" s="257" t="inlineStr">
@@ -14063,17 +14063,17 @@
     <row r="139">
       <c r="A139" s="80" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="B139" s="364" t="inlineStr">
         <is>
-          <t>Puerta antipánico</t>
+          <t>Divisiones de aluminio</t>
         </is>
       </c>
       <c r="C139" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D139" s="258" t="n"/>
@@ -14084,76 +14084,76 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="81" t="n"/>
-      <c r="B140" s="704" t="inlineStr">
+      <c r="A140" s="80" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="B140" s="364" t="inlineStr">
+        <is>
+          <t>Puerta antipánico</t>
+        </is>
+      </c>
+      <c r="C140" s="257" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D140" s="258" t="n"/>
+      <c r="E140" s="1451" t="n"/>
+      <c r="F140" s="1453">
+        <f>D140*E140</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="81" t="n"/>
+      <c r="B141" s="704" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 11 - CARPINTERÍA</t>
         </is>
       </c>
-      <c r="C140" s="567" t="n"/>
-      <c r="D140" s="567" t="n"/>
-      <c r="E140" s="567" t="n"/>
-      <c r="F140" s="1454">
-        <f>SUM(F132:F139)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="82" t="n"/>
-      <c r="B141" s="716" t="n"/>
-      <c r="C141" s="716" t="n"/>
-      <c r="D141" s="716" t="n"/>
-      <c r="E141" s="716" t="n"/>
-      <c r="F141" s="708" t="n"/>
+      <c r="C141" s="567" t="n"/>
+      <c r="D141" s="567" t="n"/>
+      <c r="E141" s="567" t="n"/>
+      <c r="F141" s="1454">
+        <f>SUM(F133:F140)</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="182" t="inlineStr">
+      <c r="A142" s="82" t="n"/>
+      <c r="B142" s="716" t="n"/>
+      <c r="C142" s="716" t="n"/>
+      <c r="D142" s="716" t="n"/>
+      <c r="E142" s="716" t="n"/>
+      <c r="F142" s="708" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="182" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B142" s="703" t="inlineStr">
+      <c r="B143" s="703" t="inlineStr">
         <is>
           <t>VIDRIOS</t>
         </is>
       </c>
-      <c r="C142" s="567" t="n"/>
-      <c r="D142" s="567" t="n"/>
-      <c r="E142" s="567" t="n"/>
-      <c r="F142" s="567" t="n"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="80" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="B143" s="364" t="inlineStr">
-        <is>
-          <t>Vidrio templado</t>
-        </is>
-      </c>
-      <c r="C143" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D143" s="1449" t="n"/>
-      <c r="E143" s="1452" t="n"/>
-      <c r="F143" s="1453">
-        <f>D143*E143</f>
-        <v/>
-      </c>
+      <c r="C143" s="567" t="n"/>
+      <c r="D143" s="567" t="n"/>
+      <c r="E143" s="567" t="n"/>
+      <c r="F143" s="567" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="80" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="B144" s="364" t="inlineStr">
         <is>
-          <t>Vidrio laminado</t>
+          <t>Vidrio templado</t>
         </is>
       </c>
       <c r="C144" s="257" t="inlineStr">
@@ -14161,8 +14161,8 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D144" s="258" t="n"/>
-      <c r="E144" s="1451" t="n"/>
+      <c r="D144" s="1449" t="n"/>
+      <c r="E144" s="1452" t="n"/>
       <c r="F144" s="1453">
         <f>D144*E144</f>
         <v/>
@@ -14171,12 +14171,12 @@
     <row r="145">
       <c r="A145" s="80" t="inlineStr">
         <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="B145" s="365" t="inlineStr">
-        <is>
-          <t>Espejos</t>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B145" s="364" t="inlineStr">
+        <is>
+          <t>Vidrio laminado</t>
         </is>
       </c>
       <c r="C145" s="257" t="inlineStr">
@@ -14184,9 +14184,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D145" s="1449" t="n"/>
-      <c r="E145" s="1452" t="n"/>
-      <c r="F145" s="1455">
+      <c r="D145" s="258" t="n"/>
+      <c r="E145" s="1451" t="n"/>
+      <c r="F145" s="1453">
         <f>D145*E145</f>
         <v/>
       </c>
@@ -14194,97 +14194,97 @@
     <row r="146">
       <c r="A146" s="80" t="inlineStr">
         <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="B146" s="365" t="inlineStr">
+        <is>
+          <t>Espejos</t>
+        </is>
+      </c>
+      <c r="C146" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D146" s="1449" t="n"/>
+      <c r="E146" s="1452" t="n"/>
+      <c r="F146" s="1455">
+        <f>D146*E146</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="80" t="inlineStr">
+        <is>
           <t>12.4</t>
         </is>
       </c>
-      <c r="B146" s="364" t="inlineStr">
+      <c r="B147" s="364" t="inlineStr">
         <is>
           <t>Sellos y silicona</t>
         </is>
       </c>
-      <c r="C146" s="257" t="inlineStr">
+      <c r="C147" s="257" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="D146" s="258" t="n"/>
-      <c r="E146" s="1451" t="n"/>
-      <c r="F146" s="1453">
-        <f>D146*E146</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="81" t="n"/>
-      <c r="B147" s="704" t="inlineStr">
+      <c r="D147" s="258" t="n"/>
+      <c r="E147" s="1451" t="n"/>
+      <c r="F147" s="1453">
+        <f>D147*E147</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="81" t="n"/>
+      <c r="B148" s="704" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 12 - VIDRIOS</t>
         </is>
       </c>
-      <c r="C147" s="567" t="n"/>
-      <c r="D147" s="567" t="n"/>
-      <c r="E147" s="567" t="n"/>
-      <c r="F147" s="1454">
-        <f>SUM(F143:F146)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="82" t="n"/>
-      <c r="B148" s="716" t="n"/>
-      <c r="C148" s="716" t="n"/>
-      <c r="D148" s="716" t="n"/>
-      <c r="E148" s="716" t="n"/>
-      <c r="F148" s="708" t="n"/>
+      <c r="C148" s="567" t="n"/>
+      <c r="D148" s="567" t="n"/>
+      <c r="E148" s="567" t="n"/>
+      <c r="F148" s="1454">
+        <f>SUM(F144:F147)</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="182" t="inlineStr">
+      <c r="A149" s="82" t="n"/>
+      <c r="B149" s="716" t="n"/>
+      <c r="C149" s="716" t="n"/>
+      <c r="D149" s="716" t="n"/>
+      <c r="E149" s="716" t="n"/>
+      <c r="F149" s="708" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="182" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B149" s="703" t="inlineStr">
+      <c r="B150" s="703" t="inlineStr">
         <is>
           <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
-      <c r="C149" s="567" t="n"/>
-      <c r="D149" s="567" t="n"/>
-      <c r="E149" s="567" t="n"/>
-      <c r="F149" s="567" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="80" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="B150" s="364" t="inlineStr">
-        <is>
-          <t>Tubería de agua fría</t>
-        </is>
-      </c>
-      <c r="C150" s="257" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D150" s="1449" t="n"/>
-      <c r="E150" s="1452" t="n"/>
-      <c r="F150" s="1453">
-        <f>D150*E150</f>
-        <v/>
-      </c>
+      <c r="C150" s="567" t="n"/>
+      <c r="D150" s="567" t="n"/>
+      <c r="E150" s="567" t="n"/>
+      <c r="F150" s="567" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="80" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="B151" s="364" t="inlineStr">
         <is>
-          <t>Tubería de agua caliente</t>
+          <t>Tubería de agua fría</t>
         </is>
       </c>
       <c r="C151" s="257" t="inlineStr">
@@ -14292,8 +14292,8 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D151" s="258" t="n"/>
-      <c r="E151" s="1451" t="n"/>
+      <c r="D151" s="1449" t="n"/>
+      <c r="E151" s="1452" t="n"/>
       <c r="F151" s="1453">
         <f>D151*E151</f>
         <v/>
@@ -14302,21 +14302,21 @@
     <row r="152">
       <c r="A152" s="80" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="B152" s="364" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios hidrosanitarios</t>
+          <t>Tubería de agua caliente</t>
         </is>
       </c>
       <c r="C152" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D152" s="1449" t="n"/>
-      <c r="E152" s="1452" t="n"/>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D152" s="258" t="n"/>
+      <c r="E152" s="1451" t="n"/>
       <c r="F152" s="1453">
         <f>D152*E152</f>
         <v/>
@@ -14325,21 +14325,21 @@
     <row r="153">
       <c r="A153" s="80" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="B153" s="364" t="inlineStr">
         <is>
-          <t>Tubería sanitaria</t>
+          <t>Válvulas y accesorios hidrosanitarios</t>
         </is>
       </c>
       <c r="C153" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D153" s="258" t="n"/>
-      <c r="E153" s="1451" t="n"/>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D153" s="1449" t="n"/>
+      <c r="E153" s="1452" t="n"/>
       <c r="F153" s="1453">
         <f>D153*E153</f>
         <v/>
@@ -14348,12 +14348,12 @@
     <row r="154">
       <c r="A154" s="80" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="B154" s="364" t="inlineStr">
         <is>
-          <t>Tubería de aguas lluvias</t>
+          <t>Tubería sanitaria</t>
         </is>
       </c>
       <c r="C154" s="257" t="inlineStr">
@@ -14371,17 +14371,17 @@
     <row r="155">
       <c r="A155" s="80" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="B155" s="364" t="inlineStr">
         <is>
-          <t>Cajas de inspección</t>
+          <t>Tubería de aguas lluvias</t>
         </is>
       </c>
       <c r="C155" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D155" s="258" t="n"/>
@@ -14394,12 +14394,12 @@
     <row r="156">
       <c r="A156" s="80" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="B156" s="364" t="inlineStr">
         <is>
-          <t>Aparatos sanitarios</t>
+          <t>Cajas de inspección</t>
         </is>
       </c>
       <c r="C156" s="257" t="inlineStr">
@@ -14417,12 +14417,12 @@
     <row r="157">
       <c r="A157" s="80" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="B157" s="364" t="inlineStr">
         <is>
-          <t>Lavamanos</t>
+          <t>Aparatos sanitarios</t>
         </is>
       </c>
       <c r="C157" s="257" t="inlineStr">
@@ -14440,12 +14440,12 @@
     <row r="158">
       <c r="A158" s="80" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="B158" s="364" t="inlineStr">
         <is>
-          <t>Griferías</t>
+          <t>Lavamanos</t>
         </is>
       </c>
       <c r="C158" s="257" t="inlineStr">
@@ -14463,12 +14463,12 @@
     <row r="159">
       <c r="A159" s="80" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="B159" s="364" t="inlineStr">
         <is>
-          <t>Duchas</t>
+          <t>Griferías</t>
         </is>
       </c>
       <c r="C159" s="257" t="inlineStr">
@@ -14486,17 +14486,17 @@
     <row r="160">
       <c r="A160" s="80" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="B160" s="364" t="inlineStr">
         <is>
-          <t>Pruebas hidráulicas y de estanqueidad</t>
+          <t>Duchas</t>
         </is>
       </c>
       <c r="C160" s="257" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D160" s="258" t="n"/>
@@ -14509,17 +14509,17 @@
     <row r="161">
       <c r="A161" s="80" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="B161" s="364" t="inlineStr">
         <is>
-          <t>Orinal institucional</t>
+          <t>Pruebas hidráulicas y de estanqueidad</t>
         </is>
       </c>
       <c r="C161" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D161" s="258" t="n"/>
@@ -14530,76 +14530,76 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="81" t="n"/>
-      <c r="B162" s="704" t="inlineStr">
+      <c r="A162" s="80" t="inlineStr">
+        <is>
+          <t>13.12</t>
+        </is>
+      </c>
+      <c r="B162" s="364" t="inlineStr">
+        <is>
+          <t>Orinal institucional</t>
+        </is>
+      </c>
+      <c r="C162" s="257" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D162" s="258" t="n"/>
+      <c r="E162" s="1451" t="n"/>
+      <c r="F162" s="1453">
+        <f>D162*E162</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="81" t="n"/>
+      <c r="B163" s="704" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 13 - INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
-      <c r="C162" s="567" t="n"/>
-      <c r="D162" s="567" t="n"/>
-      <c r="E162" s="567" t="n"/>
-      <c r="F162" s="1454">
-        <f>SUM(F150:F161)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="82" t="n"/>
-      <c r="B163" s="716" t="n"/>
-      <c r="C163" s="716" t="n"/>
-      <c r="D163" s="716" t="n"/>
-      <c r="E163" s="716" t="n"/>
-      <c r="F163" s="708" t="n"/>
+      <c r="C163" s="567" t="n"/>
+      <c r="D163" s="567" t="n"/>
+      <c r="E163" s="567" t="n"/>
+      <c r="F163" s="1454">
+        <f>SUM(F151:F162)</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="182" t="inlineStr">
+      <c r="A164" s="82" t="n"/>
+      <c r="B164" s="716" t="n"/>
+      <c r="C164" s="716" t="n"/>
+      <c r="D164" s="716" t="n"/>
+      <c r="E164" s="716" t="n"/>
+      <c r="F164" s="708" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="182" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B164" s="703" t="inlineStr">
+      <c r="B165" s="703" t="inlineStr">
         <is>
           <t>INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
-      <c r="C164" s="567" t="n"/>
-      <c r="D164" s="567" t="n"/>
-      <c r="E164" s="567" t="n"/>
-      <c r="F164" s="567" t="n"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="80" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="B165" s="364" t="inlineStr">
-        <is>
-          <t>Tubería/conduit eléctrica</t>
-        </is>
-      </c>
-      <c r="C165" s="257" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D165" s="258" t="n"/>
-      <c r="E165" s="1451" t="n"/>
-      <c r="F165" s="1453">
-        <f>D165*E165</f>
-        <v/>
-      </c>
+      <c r="C165" s="567" t="n"/>
+      <c r="D165" s="567" t="n"/>
+      <c r="E165" s="567" t="n"/>
+      <c r="F165" s="567" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="80" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="B166" s="364" t="inlineStr">
         <is>
-          <t>Bandejas portacables</t>
+          <t>Tubería/conduit eléctrica</t>
         </is>
       </c>
       <c r="C166" s="257" t="inlineStr">
@@ -14617,17 +14617,17 @@
     <row r="167">
       <c r="A167" s="80" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="B167" s="364" t="inlineStr">
         <is>
-          <t>Cajas eléctricas</t>
+          <t>Bandejas portacables</t>
         </is>
       </c>
       <c r="C167" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D167" s="258" t="n"/>
@@ -14640,17 +14640,17 @@
     <row r="168">
       <c r="A168" s="80" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="B168" s="364" t="inlineStr">
         <is>
-          <t>Cableado de fuerza</t>
+          <t>Cajas eléctricas</t>
         </is>
       </c>
       <c r="C168" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D168" s="258" t="n"/>
@@ -14663,12 +14663,12 @@
     <row r="169">
       <c r="A169" s="80" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="B169" s="364" t="inlineStr">
         <is>
-          <t>Cableado de iluminación</t>
+          <t>Cableado de fuerza</t>
         </is>
       </c>
       <c r="C169" s="257" t="inlineStr">
@@ -14686,17 +14686,17 @@
     <row r="170">
       <c r="A170" s="80" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="B170" s="364" t="inlineStr">
         <is>
-          <t>Tableros eléctricos</t>
+          <t>Cableado de iluminación</t>
         </is>
       </c>
       <c r="C170" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D170" s="258" t="n"/>
@@ -14709,12 +14709,12 @@
     <row r="171">
       <c r="A171" s="80" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="B171" s="364" t="inlineStr">
         <is>
-          <t>Tomacorrientes</t>
+          <t>Tableros eléctricos</t>
         </is>
       </c>
       <c r="C171" s="257" t="inlineStr">
@@ -14732,12 +14732,12 @@
     <row r="172">
       <c r="A172" s="80" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="B172" s="364" t="inlineStr">
         <is>
-          <t>Interruptores</t>
+          <t>Tomacorrientes</t>
         </is>
       </c>
       <c r="C172" s="257" t="inlineStr">
@@ -14755,12 +14755,12 @@
     <row r="173">
       <c r="A173" s="80" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="B173" s="364" t="inlineStr">
         <is>
-          <t>Luminarias</t>
+          <t>Interruptores</t>
         </is>
       </c>
       <c r="C173" s="257" t="inlineStr">
@@ -14778,17 +14778,17 @@
     <row r="174">
       <c r="A174" s="80" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="B174" s="364" t="inlineStr">
         <is>
-          <t>Sistema de puesta a tierra</t>
+          <t>Luminarias</t>
         </is>
       </c>
       <c r="C174" s="257" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D174" s="258" t="n"/>
@@ -14801,12 +14801,12 @@
     <row r="175">
       <c r="A175" s="80" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="B175" s="364" t="inlineStr">
         <is>
-          <t>Pruebas y certificaciones</t>
+          <t>Sistema de puesta a tierra</t>
         </is>
       </c>
       <c r="C175" s="257" t="inlineStr">
@@ -14822,81 +14822,81 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="81" t="n"/>
-      <c r="B176" s="704" t="inlineStr">
+      <c r="A176" s="80" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="B176" s="364" t="inlineStr">
+        <is>
+          <t>Pruebas y certificaciones</t>
+        </is>
+      </c>
+      <c r="C176" s="257" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D176" s="258" t="n"/>
+      <c r="E176" s="1451" t="n"/>
+      <c r="F176" s="1453">
+        <f>D176*E176</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="81" t="n"/>
+      <c r="B177" s="704" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 14 - INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
-      <c r="C176" s="567" t="n"/>
-      <c r="D176" s="567" t="n"/>
-      <c r="E176" s="567" t="n"/>
-      <c r="F176" s="1454">
-        <f>SUM(F165:F175)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="82" t="n"/>
-      <c r="B177" s="716" t="n"/>
-      <c r="C177" s="716" t="n"/>
-      <c r="D177" s="716" t="n"/>
-      <c r="E177" s="716" t="n"/>
-      <c r="F177" s="708" t="n"/>
+      <c r="C177" s="567" t="n"/>
+      <c r="D177" s="567" t="n"/>
+      <c r="E177" s="567" t="n"/>
+      <c r="F177" s="1454">
+        <f>SUM(F166:F176)</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
-      <c r="A178" s="182" t="inlineStr">
+      <c r="A178" s="82" t="n"/>
+      <c r="B178" s="716" t="n"/>
+      <c r="C178" s="716" t="n"/>
+      <c r="D178" s="716" t="n"/>
+      <c r="E178" s="716" t="n"/>
+      <c r="F178" s="708" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="182" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B178" s="703" t="inlineStr">
+      <c r="B179" s="703" t="inlineStr">
         <is>
           <t>COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
-      <c r="C178" s="567" t="n"/>
-      <c r="D178" s="567" t="n"/>
-      <c r="E178" s="567" t="n"/>
-      <c r="F178" s="567" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="80" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="B179" s="364" t="inlineStr">
-        <is>
-          <t>Cableado estructurado de datos</t>
-        </is>
-      </c>
-      <c r="C179" s="257" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D179" s="258" t="n"/>
-      <c r="E179" s="1451" t="n"/>
-      <c r="F179" s="1453">
-        <f>D179*E179</f>
-        <v/>
-      </c>
+      <c r="C179" s="567" t="n"/>
+      <c r="D179" s="567" t="n"/>
+      <c r="E179" s="567" t="n"/>
+      <c r="F179" s="567" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="80" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="B180" s="364" t="inlineStr">
         <is>
-          <t>Rack de comunicaciones</t>
+          <t>Cableado estructurado de datos</t>
         </is>
       </c>
       <c r="C180" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D180" s="258" t="n"/>
@@ -14909,12 +14909,12 @@
     <row r="181">
       <c r="A181" s="80" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="B181" s="364" t="inlineStr">
         <is>
-          <t>Cámaras y sistema CCTV</t>
+          <t>Rack de comunicaciones</t>
         </is>
       </c>
       <c r="C181" s="257" t="inlineStr">
@@ -14932,12 +14932,12 @@
     <row r="182">
       <c r="A182" s="80" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="B182" s="364" t="inlineStr">
         <is>
-          <t>Control de acceso</t>
+          <t>Cámaras y sistema CCTV</t>
         </is>
       </c>
       <c r="C182" s="257" t="inlineStr">
@@ -14955,12 +14955,12 @@
     <row r="183">
       <c r="A183" s="80" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="B183" s="364" t="inlineStr">
         <is>
-          <t>Sistema de citofonía</t>
+          <t>Control de acceso</t>
         </is>
       </c>
       <c r="C183" s="257" t="inlineStr">
@@ -14978,17 +14978,17 @@
     <row r="184">
       <c r="A184" s="80" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="B184" s="364" t="inlineStr">
         <is>
-          <t>Sistema de detección de incendios</t>
+          <t>Sistema de citofonía</t>
         </is>
       </c>
       <c r="C184" s="257" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D184" s="258" t="n"/>
@@ -14999,81 +14999,81 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="81" t="n"/>
-      <c r="B185" s="704" t="inlineStr">
+      <c r="A185" s="80" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="B185" s="364" t="inlineStr">
+        <is>
+          <t>Sistema de detección de incendios</t>
+        </is>
+      </c>
+      <c r="C185" s="257" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D185" s="258" t="n"/>
+      <c r="E185" s="1451" t="n"/>
+      <c r="F185" s="1453">
+        <f>D185*E185</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="81" t="n"/>
+      <c r="B186" s="704" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 15 - COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
-      <c r="C185" s="567" t="n"/>
-      <c r="D185" s="567" t="n"/>
-      <c r="E185" s="567" t="n"/>
-      <c r="F185" s="1454">
-        <f>SUM(F179:F184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="82" t="n"/>
-      <c r="B186" s="716" t="n"/>
-      <c r="C186" s="716" t="n"/>
-      <c r="D186" s="716" t="n"/>
-      <c r="E186" s="716" t="n"/>
-      <c r="F186" s="708" t="n"/>
+      <c r="C186" s="567" t="n"/>
+      <c r="D186" s="567" t="n"/>
+      <c r="E186" s="567" t="n"/>
+      <c r="F186" s="1454">
+        <f>SUM(F180:F185)</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
-      <c r="A187" s="182" t="inlineStr">
+      <c r="A187" s="82" t="n"/>
+      <c r="B187" s="716" t="n"/>
+      <c r="C187" s="716" t="n"/>
+      <c r="D187" s="716" t="n"/>
+      <c r="E187" s="716" t="n"/>
+      <c r="F187" s="708" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="182" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B187" s="703" t="inlineStr">
+      <c r="B188" s="703" t="inlineStr">
         <is>
           <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
-      <c r="C187" s="567" t="n"/>
-      <c r="D187" s="567" t="n"/>
-      <c r="E187" s="567" t="n"/>
-      <c r="F187" s="567" t="n"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="80" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="B188" s="364" t="inlineStr">
-        <is>
-          <t>Equipos de aire acondicionado</t>
-        </is>
-      </c>
-      <c r="C188" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D188" s="258" t="n"/>
-      <c r="E188" s="1451" t="n"/>
-      <c r="F188" s="1453">
-        <f>D188*E188</f>
-        <v/>
-      </c>
+      <c r="C188" s="567" t="n"/>
+      <c r="D188" s="567" t="n"/>
+      <c r="E188" s="567" t="n"/>
+      <c r="F188" s="567" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="80" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="B189" s="364" t="inlineStr">
         <is>
-          <t>Ductos de ventilación</t>
+          <t>Equipos de aire acondicionado</t>
         </is>
       </c>
       <c r="C189" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D189" s="258" t="n"/>
@@ -15086,17 +15086,17 @@
     <row r="190">
       <c r="A190" s="80" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="B190" s="364" t="inlineStr">
         <is>
-          <t>Tubería de refrigerante</t>
+          <t>Ductos de ventilación</t>
         </is>
       </c>
       <c r="C190" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D190" s="258" t="n"/>
@@ -15109,17 +15109,17 @@
     <row r="191">
       <c r="A191" s="80" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="B191" s="364" t="inlineStr">
         <is>
-          <t>Rejillas y difusores</t>
+          <t>Tubería de refrigerante</t>
         </is>
       </c>
       <c r="C191" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D191" s="258" t="n"/>
@@ -15130,81 +15130,81 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="81" t="n"/>
-      <c r="B192" s="704" t="inlineStr">
+      <c r="A192" s="80" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="B192" s="364" t="inlineStr">
+        <is>
+          <t>Rejillas y difusores</t>
+        </is>
+      </c>
+      <c r="C192" s="257" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D192" s="258" t="n"/>
+      <c r="E192" s="1451" t="n"/>
+      <c r="F192" s="1453">
+        <f>D192*E192</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="81" t="n"/>
+      <c r="B193" s="704" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 16 - CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
-      <c r="C192" s="567" t="n"/>
-      <c r="D192" s="567" t="n"/>
-      <c r="E192" s="567" t="n"/>
-      <c r="F192" s="1454">
-        <f>SUM(F188:F191)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="82" t="n"/>
-      <c r="B193" s="716" t="n"/>
-      <c r="C193" s="716" t="n"/>
-      <c r="D193" s="716" t="n"/>
-      <c r="E193" s="716" t="n"/>
-      <c r="F193" s="708" t="n"/>
+      <c r="C193" s="567" t="n"/>
+      <c r="D193" s="567" t="n"/>
+      <c r="E193" s="567" t="n"/>
+      <c r="F193" s="1454">
+        <f>SUM(F189:F192)</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
-      <c r="A194" s="182" t="inlineStr">
+      <c r="A194" s="82" t="n"/>
+      <c r="B194" s="716" t="n"/>
+      <c r="C194" s="716" t="n"/>
+      <c r="D194" s="716" t="n"/>
+      <c r="E194" s="716" t="n"/>
+      <c r="F194" s="708" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="182" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B194" s="703" t="inlineStr">
+      <c r="B195" s="703" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="C194" s="567" t="n"/>
-      <c r="D194" s="567" t="n"/>
-      <c r="E194" s="567" t="n"/>
-      <c r="F194" s="567" t="n"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="80" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="B195" s="364" t="inlineStr">
-        <is>
-          <t>Red interna de gas</t>
-        </is>
-      </c>
-      <c r="C195" s="257" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D195" s="258" t="n"/>
-      <c r="E195" s="1451" t="n"/>
-      <c r="F195" s="1453">
-        <f>D195*E195</f>
-        <v/>
-      </c>
+      <c r="C195" s="567" t="n"/>
+      <c r="D195" s="567" t="n"/>
+      <c r="E195" s="567" t="n"/>
+      <c r="F195" s="567" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="80" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="B196" s="364" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios de gas</t>
+          <t>Red interna de gas</t>
         </is>
       </c>
       <c r="C196" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D196" s="258" t="n"/>
@@ -15217,17 +15217,17 @@
     <row r="197">
       <c r="A197" s="80" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="B197" s="364" t="inlineStr">
         <is>
-          <t>Pruebas y certificación</t>
+          <t>Válvulas y accesorios de gas</t>
         </is>
       </c>
       <c r="C197" s="257" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D197" s="258" t="n"/>
@@ -15238,81 +15238,81 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="81" t="n"/>
-      <c r="B198" s="704" t="inlineStr">
+      <c r="A198" s="80" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="B198" s="364" t="inlineStr">
+        <is>
+          <t>Pruebas y certificación</t>
+        </is>
+      </c>
+      <c r="C198" s="257" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D198" s="258" t="n"/>
+      <c r="E198" s="1451" t="n"/>
+      <c r="F198" s="1453">
+        <f>D198*E198</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="81" t="n"/>
+      <c r="B199" s="704" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 17 - GAS</t>
         </is>
       </c>
-      <c r="C198" s="567" t="n"/>
-      <c r="D198" s="567" t="n"/>
-      <c r="E198" s="567" t="n"/>
-      <c r="F198" s="1454">
-        <f>SUM(F195:F197)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="82" t="n"/>
-      <c r="B199" s="716" t="n"/>
-      <c r="C199" s="716" t="n"/>
-      <c r="D199" s="716" t="n"/>
-      <c r="E199" s="716" t="n"/>
-      <c r="F199" s="708" t="n"/>
+      <c r="C199" s="567" t="n"/>
+      <c r="D199" s="567" t="n"/>
+      <c r="E199" s="567" t="n"/>
+      <c r="F199" s="1454">
+        <f>SUM(F196:F198)</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
-      <c r="A200" s="182" t="inlineStr">
+      <c r="A200" s="82" t="n"/>
+      <c r="B200" s="716" t="n"/>
+      <c r="C200" s="716" t="n"/>
+      <c r="D200" s="716" t="n"/>
+      <c r="E200" s="716" t="n"/>
+      <c r="F200" s="708" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="182" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B200" s="703" t="inlineStr">
+      <c r="B201" s="703" t="inlineStr">
         <is>
           <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
-      <c r="C200" s="567" t="n"/>
-      <c r="D200" s="567" t="n"/>
-      <c r="E200" s="567" t="n"/>
-      <c r="F200" s="567" t="n"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="80" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="B201" s="364" t="inlineStr">
-        <is>
-          <t>Construcción de andenes</t>
-        </is>
-      </c>
-      <c r="C201" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D201" s="258" t="n"/>
-      <c r="E201" s="1451" t="n"/>
-      <c r="F201" s="1453">
-        <f>D201*E201</f>
-        <v/>
-      </c>
+      <c r="C201" s="567" t="n"/>
+      <c r="D201" s="567" t="n"/>
+      <c r="E201" s="567" t="n"/>
+      <c r="F201" s="567" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="80" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="B202" s="364" t="inlineStr">
         <is>
-          <t>Placas de concreto exteriores</t>
+          <t>Construcción de andenes</t>
         </is>
       </c>
       <c r="C202" s="257" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D202" s="258" t="n"/>
@@ -15325,17 +15325,17 @@
     <row r="203">
       <c r="A203" s="80" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="B203" s="364" t="inlineStr">
         <is>
-          <t>Pavimento en adoquín</t>
+          <t>Placas de concreto exteriores</t>
         </is>
       </c>
       <c r="C203" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D203" s="258" t="n"/>
@@ -15348,17 +15348,17 @@
     <row r="204">
       <c r="A204" s="80" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="B204" s="364" t="inlineStr">
         <is>
-          <t>Sardineles y bordillos</t>
+          <t>Pavimento en adoquín</t>
         </is>
       </c>
       <c r="C204" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D204" s="258" t="n"/>
@@ -15371,17 +15371,17 @@
     <row r="205">
       <c r="A205" s="80" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="B205" s="364" t="inlineStr">
         <is>
-          <t>Sumideros exteriores</t>
+          <t>Sardineles y bordillos</t>
         </is>
       </c>
       <c r="C205" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D205" s="258" t="n"/>
@@ -15394,17 +15394,17 @@
     <row r="206">
       <c r="A206" s="80" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="B206" s="364" t="inlineStr">
         <is>
-          <t>Suministro y extendido de tierra vegetal</t>
+          <t>Sumideros exteriores</t>
         </is>
       </c>
       <c r="C206" s="257" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D206" s="258" t="n"/>
@@ -15417,17 +15417,17 @@
     <row r="207">
       <c r="A207" s="80" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="B207" s="364" t="inlineStr">
         <is>
-          <t>Siembra y jardinería</t>
+          <t>Suministro y extendido de tierra vegetal</t>
         </is>
       </c>
       <c r="C207" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D207" s="258" t="n"/>
@@ -15440,12 +15440,12 @@
     <row r="208">
       <c r="A208" s="80" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="B208" s="364" t="inlineStr">
         <is>
-          <t>Geotextil para drenaje y filtración</t>
+          <t>Siembra y jardinería</t>
         </is>
       </c>
       <c r="C208" s="257" t="inlineStr">
@@ -15463,17 +15463,17 @@
     <row r="209">
       <c r="A209" s="80" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="B209" s="364" t="inlineStr">
         <is>
-          <t>Gaviones para obras de contención</t>
+          <t>Geotextil para drenaje y filtración</t>
         </is>
       </c>
       <c r="C209" s="257" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D209" s="258" t="n"/>
@@ -15486,17 +15486,17 @@
     <row r="210">
       <c r="A210" s="80" t="inlineStr">
         <is>
-          <t>18.10</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="B210" s="364" t="inlineStr">
         <is>
-          <t>Filtro francés (drenaje de terrenos)</t>
+          <t>Gaviones para obras de contención</t>
         </is>
       </c>
       <c r="C210" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D210" s="258" t="n"/>
@@ -15509,17 +15509,17 @@
     <row r="211">
       <c r="A211" s="80" t="inlineStr">
         <is>
-          <t>18.11</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="B211" s="364" t="inlineStr">
         <is>
-          <t>Revegetalización / empradización</t>
+          <t>Filtro francés (drenaje de terrenos)</t>
         </is>
       </c>
       <c r="C211" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D211" s="258" t="n"/>
@@ -15530,81 +15530,81 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="81" t="n"/>
-      <c r="B212" s="704" t="inlineStr">
+      <c r="A212" s="80" t="inlineStr">
+        <is>
+          <t>18.11</t>
+        </is>
+      </c>
+      <c r="B212" s="364" t="inlineStr">
+        <is>
+          <t>Revegetalización / empradización</t>
+        </is>
+      </c>
+      <c r="C212" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D212" s="258" t="n"/>
+      <c r="E212" s="1451" t="n"/>
+      <c r="F212" s="1453">
+        <f>D212*E212</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="81" t="n"/>
+      <c r="B213" s="704" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 18 - URBANISMO Y EXTERIORES</t>
         </is>
       </c>
-      <c r="C212" s="567" t="n"/>
-      <c r="D212" s="567" t="n"/>
-      <c r="E212" s="567" t="n"/>
-      <c r="F212" s="1454">
-        <f>SUM(F201:F211)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="82" t="n"/>
-      <c r="B213" s="716" t="n"/>
-      <c r="C213" s="716" t="n"/>
-      <c r="D213" s="716" t="n"/>
-      <c r="E213" s="716" t="n"/>
-      <c r="F213" s="708" t="n"/>
+      <c r="C213" s="567" t="n"/>
+      <c r="D213" s="567" t="n"/>
+      <c r="E213" s="567" t="n"/>
+      <c r="F213" s="1454">
+        <f>SUM(F202:F212)</f>
+        <v/>
+      </c>
     </row>
     <row r="214">
-      <c r="A214" s="182" t="inlineStr">
+      <c r="A214" s="82" t="n"/>
+      <c r="B214" s="716" t="n"/>
+      <c r="C214" s="716" t="n"/>
+      <c r="D214" s="716" t="n"/>
+      <c r="E214" s="716" t="n"/>
+      <c r="F214" s="708" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="182" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B214" s="703" t="inlineStr">
+      <c r="B215" s="703" t="inlineStr">
         <is>
           <t>OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
-      <c r="C214" s="567" t="n"/>
-      <c r="D214" s="567" t="n"/>
-      <c r="E214" s="567" t="n"/>
-      <c r="F214" s="567" t="n"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="80" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="B215" s="364" t="inlineStr">
-        <is>
-          <t>Rejas metálicas</t>
-        </is>
-      </c>
-      <c r="C215" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D215" s="258" t="n"/>
-      <c r="E215" s="1451" t="n"/>
-      <c r="F215" s="1453">
-        <f>D215*E215</f>
-        <v/>
-      </c>
+      <c r="C215" s="567" t="n"/>
+      <c r="D215" s="567" t="n"/>
+      <c r="E215" s="567" t="n"/>
+      <c r="F215" s="567" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="80" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="B216" s="364" t="inlineStr">
         <is>
-          <t>Escaleras metálicas</t>
+          <t>Rejas metálicas</t>
         </is>
       </c>
       <c r="C216" s="257" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D216" s="258" t="n"/>
@@ -15617,12 +15617,12 @@
     <row r="217">
       <c r="A217" s="80" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="B217" s="364" t="inlineStr">
         <is>
-          <t>Elementos metálicos especiales</t>
+          <t>Escaleras metálicas</t>
         </is>
       </c>
       <c r="C217" s="257" t="inlineStr">
@@ -15640,17 +15640,17 @@
     <row r="218">
       <c r="A218" s="80" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="B218" s="364" t="inlineStr">
         <is>
-          <t>Mobiliario fijo de obra</t>
+          <t>Elementos metálicos especiales</t>
         </is>
       </c>
       <c r="C218" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D218" s="258" t="n"/>
@@ -15661,76 +15661,76 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="81" t="n"/>
-      <c r="B219" s="704" t="inlineStr">
+      <c r="A219" s="80" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="B219" s="364" t="inlineStr">
+        <is>
+          <t>Mobiliario fijo de obra</t>
+        </is>
+      </c>
+      <c r="C219" s="257" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D219" s="258" t="n"/>
+      <c r="E219" s="1451" t="n"/>
+      <c r="F219" s="1453">
+        <f>D219*E219</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="81" t="n"/>
+      <c r="B220" s="704" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 19 - OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
-      <c r="C219" s="567" t="n"/>
-      <c r="D219" s="567" t="n"/>
-      <c r="E219" s="567" t="n"/>
-      <c r="F219" s="1454">
-        <f>SUM(F215:F218)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="82" t="n"/>
-      <c r="B220" s="716" t="n"/>
-      <c r="C220" s="716" t="n"/>
-      <c r="D220" s="716" t="n"/>
-      <c r="E220" s="716" t="n"/>
-      <c r="F220" s="708" t="n"/>
+      <c r="C220" s="567" t="n"/>
+      <c r="D220" s="567" t="n"/>
+      <c r="E220" s="567" t="n"/>
+      <c r="F220" s="1454">
+        <f>SUM(F216:F219)</f>
+        <v/>
+      </c>
     </row>
     <row r="221">
-      <c r="A221" s="182" t="inlineStr">
+      <c r="A221" s="82" t="n"/>
+      <c r="B221" s="716" t="n"/>
+      <c r="C221" s="716" t="n"/>
+      <c r="D221" s="716" t="n"/>
+      <c r="E221" s="716" t="n"/>
+      <c r="F221" s="708" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="182" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B221" s="703" t="inlineStr">
+      <c r="B222" s="703" t="inlineStr">
         <is>
           <t>ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
-      <c r="C221" s="567" t="n"/>
-      <c r="D221" s="567" t="n"/>
-      <c r="E221" s="567" t="n"/>
-      <c r="F221" s="567" t="n"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="80" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="B222" s="364" t="inlineStr">
-        <is>
-          <t>Limpieza gruesa y fina de obra</t>
-        </is>
-      </c>
-      <c r="C222" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D222" s="258" t="n"/>
-      <c r="E222" s="1451" t="n"/>
-      <c r="F222" s="1453">
-        <f>D222*E222</f>
-        <v/>
-      </c>
+      <c r="C222" s="567" t="n"/>
+      <c r="D222" s="567" t="n"/>
+      <c r="E222" s="567" t="n"/>
+      <c r="F222" s="567" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="80" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="B223" s="364" t="inlineStr">
         <is>
-          <t>Limpieza final para entrega</t>
+          <t>Limpieza gruesa y fina de obra</t>
         </is>
       </c>
       <c r="C223" s="257" t="inlineStr">
@@ -15748,17 +15748,17 @@
     <row r="224">
       <c r="A224" s="80" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="B224" s="364" t="inlineStr">
         <is>
-          <t>Pruebas, puesta en marcha y ajustes</t>
+          <t>Limpieza final para entrega</t>
         </is>
       </c>
       <c r="C224" s="257" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D224" s="258" t="n"/>
@@ -15771,12 +15771,12 @@
     <row r="225">
       <c r="A225" s="80" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="B225" s="364" t="inlineStr">
         <is>
-          <t>Actualización de planos récord / as-built</t>
+          <t>Pruebas, puesta en marcha y ajustes</t>
         </is>
       </c>
       <c r="C225" s="257" t="inlineStr">
@@ -15794,12 +15794,12 @@
     <row r="226">
       <c r="A226" s="80" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="B226" s="364" t="inlineStr">
         <is>
-          <t>Entrega, manuales y acta de recibo</t>
+          <t>Actualización de planos récord / as-built</t>
         </is>
       </c>
       <c r="C226" s="257" t="inlineStr">
@@ -15815,138 +15815,138 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="81" t="n"/>
-      <c r="B227" s="704" t="inlineStr">
+      <c r="A227" s="80" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="B227" s="364" t="inlineStr">
+        <is>
+          <t>Entrega, manuales y acta de recibo</t>
+        </is>
+      </c>
+      <c r="C227" s="257" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D227" s="258" t="n"/>
+      <c r="E227" s="1451" t="n"/>
+      <c r="F227" s="1453">
+        <f>D227*E227</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="81" t="n"/>
+      <c r="B228" s="704" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 20 - ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
-      <c r="C227" s="567" t="n"/>
-      <c r="D227" s="567" t="n"/>
-      <c r="E227" s="567" t="n"/>
-      <c r="F227" s="1454">
-        <f>SUM(F222:F226)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="82" t="n"/>
-      <c r="B228" s="716" t="n"/>
-      <c r="C228" s="716" t="n"/>
-      <c r="D228" s="716" t="n"/>
-      <c r="E228" s="716" t="n"/>
-      <c r="F228" s="708" t="n"/>
+      <c r="C228" s="567" t="n"/>
+      <c r="D228" s="567" t="n"/>
+      <c r="E228" s="567" t="n"/>
+      <c r="F228" s="1454">
+        <f>SUM(F223:F227)</f>
+        <v/>
+      </c>
     </row>
     <row r="229">
-      <c r="A229" s="182" t="inlineStr">
+      <c r="A229" s="82" t="n"/>
+      <c r="B229" s="716" t="n"/>
+      <c r="C229" s="716" t="n"/>
+      <c r="D229" s="716" t="n"/>
+      <c r="E229" s="716" t="n"/>
+      <c r="F229" s="708" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="182" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B229" s="703" t="inlineStr">
+      <c r="B230" s="703" t="inlineStr">
         <is>
           <t>ASCENSORES</t>
         </is>
       </c>
-      <c r="C229" s="567" t="n"/>
-      <c r="D229" s="567" t="n"/>
-      <c r="E229" s="567" t="n"/>
-      <c r="F229" s="567" t="n"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="80" t="inlineStr">
+      <c r="C230" s="567" t="n"/>
+      <c r="D230" s="567" t="n"/>
+      <c r="E230" s="567" t="n"/>
+      <c r="F230" s="567" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="80" t="inlineStr">
         <is>
           <t>21.1</t>
         </is>
       </c>
-      <c r="B230" s="364" t="inlineStr">
+      <c r="B231" s="364" t="inlineStr">
         <is>
           <t>Suministro e instalación de ascensor eléctrico</t>
         </is>
       </c>
-      <c r="C230" s="257" t="inlineStr">
+      <c r="C231" s="257" t="inlineStr">
         <is>
           <t>UND</t>
         </is>
       </c>
-      <c r="D230" s="258" t="n"/>
-      <c r="E230" s="1451" t="n"/>
-      <c r="F230" s="1453">
-        <f>D230*E230</f>
-        <v/>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="81" t="n"/>
-      <c r="B231" s="704" t="inlineStr">
+      <c r="D231" s="258" t="n"/>
+      <c r="E231" s="1451" t="n"/>
+      <c r="F231" s="1453">
+        <f>D231*E231</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="81" t="n"/>
+      <c r="B232" s="704" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 21 - ASCENSORES</t>
         </is>
       </c>
-      <c r="C231" s="567" t="n"/>
-      <c r="D231" s="567" t="n"/>
-      <c r="E231" s="567" t="n"/>
-      <c r="F231" s="1454">
-        <f>SUM(F230:F230)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="82" t="n"/>
-      <c r="B232" s="716" t="n"/>
-      <c r="C232" s="716" t="n"/>
-      <c r="D232" s="716" t="n"/>
-      <c r="E232" s="716" t="n"/>
-      <c r="F232" s="708" t="n"/>
+      <c r="C232" s="567" t="n"/>
+      <c r="D232" s="567" t="n"/>
+      <c r="E232" s="567" t="n"/>
+      <c r="F232" s="1454">
+        <f>SUM(F231:F231)</f>
+        <v/>
+      </c>
     </row>
     <row r="233">
-      <c r="A233" s="182" t="inlineStr">
+      <c r="A233" s="82" t="n"/>
+      <c r="B233" s="716" t="n"/>
+      <c r="C233" s="716" t="n"/>
+      <c r="D233" s="716" t="n"/>
+      <c r="E233" s="716" t="n"/>
+      <c r="F233" s="708" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="182" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B233" s="703" t="inlineStr">
+      <c r="B234" s="703" t="inlineStr">
         <is>
           <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
-      <c r="C233" s="567" t="n"/>
-      <c r="D233" s="567" t="n"/>
-      <c r="E233" s="567" t="n"/>
-      <c r="F233" s="567" t="n"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="80" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="B234" s="364" t="inlineStr">
-        <is>
-          <t>Estudio de suelos y geotecnia</t>
-        </is>
-      </c>
-      <c r="C234" s="257" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D234" s="258" t="n"/>
-      <c r="E234" s="1451" t="n"/>
-      <c r="F234" s="1453">
-        <f>D234*E234</f>
-        <v/>
-      </c>
+      <c r="C234" s="567" t="n"/>
+      <c r="D234" s="567" t="n"/>
+      <c r="E234" s="567" t="n"/>
+      <c r="F234" s="567" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="80" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="B235" s="364" t="inlineStr">
         <is>
-          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
+          <t>Estudio de suelos y geotecnia</t>
         </is>
       </c>
       <c r="C235" s="257" t="inlineStr">
@@ -15964,12 +15964,12 @@
     <row r="236">
       <c r="A236" s="80" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="B236" s="364" t="inlineStr">
         <is>
-          <t>Licencia de construcción y trámites de curaduría urbana</t>
+          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
         </is>
       </c>
       <c r="C236" s="257" t="inlineStr">
@@ -15987,12 +15987,12 @@
     <row r="237">
       <c r="A237" s="80" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="B237" s="364" t="inlineStr">
         <is>
-          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
+          <t>Licencia de construcción y trámites de curaduría urbana</t>
         </is>
       </c>
       <c r="C237" s="257" t="inlineStr">
@@ -16008,84 +16008,89 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="81" t="n"/>
-      <c r="B238" s="704" t="inlineStr">
+      <c r="A238" s="80" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="B238" s="364" t="inlineStr">
+        <is>
+          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
+        </is>
+      </c>
+      <c r="C238" s="257" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D238" s="258" t="n"/>
+      <c r="E238" s="1451" t="n"/>
+      <c r="F238" s="1453">
+        <f>D238*E238</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="81" t="n"/>
+      <c r="B239" s="704" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 22 - GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
-      <c r="C238" s="567" t="n"/>
-      <c r="D238" s="567" t="n"/>
-      <c r="E238" s="567" t="n"/>
-      <c r="F238" s="1454">
-        <f>SUM(F234:F237)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="82" t="n"/>
-      <c r="B239" s="716" t="n"/>
-      <c r="C239" s="716" t="n"/>
-      <c r="D239" s="716" t="n"/>
-      <c r="E239" s="716" t="n"/>
-      <c r="F239" s="708" t="n"/>
-    </row>
-    <row r="240" ht="15" customHeight="1" s="550">
-      <c r="A240" s="83" t="n"/>
-      <c r="B240" s="715" t="inlineStr">
+      <c r="C239" s="567" t="n"/>
+      <c r="D239" s="567" t="n"/>
+      <c r="E239" s="567" t="n"/>
+      <c r="F239" s="1454">
+        <f>SUM(F235:F238)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="82" t="n"/>
+      <c r="B240" s="716" t="n"/>
+      <c r="C240" s="716" t="n"/>
+      <c r="D240" s="716" t="n"/>
+      <c r="E240" s="716" t="n"/>
+      <c r="F240" s="708" t="n"/>
+    </row>
+    <row r="241" ht="15" customHeight="1" s="550">
+      <c r="A241" s="83" t="n"/>
+      <c r="B241" s="715" t="inlineStr">
         <is>
           <t>COSTO DIRECTO TOTAL (suma de capítulos 1 a 22)</t>
         </is>
       </c>
-      <c r="C240" s="567" t="n"/>
-      <c r="D240" s="567" t="n"/>
-      <c r="E240" s="567" t="n"/>
-      <c r="F240" s="1456">
-        <f>F25+F39+F49+F69+F81+F93+F100+F107+F121+F129+F140+F147+F162+F176+F185+F192+F198+F212+F219+F227+F231+F238</f>
-        <v/>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="84" t="n"/>
-      <c r="B241" s="28" t="n"/>
-      <c r="C241" s="28" t="n"/>
-      <c r="D241" s="28" t="n"/>
-      <c r="E241" s="28" t="n"/>
-      <c r="F241" s="85" t="n"/>
-    </row>
-    <row r="242" ht="15" customHeight="1" s="550">
-      <c r="A242" s="82" t="n"/>
-      <c r="B242" s="46" t="inlineStr">
-        <is>
-          <t>Administración (A)</t>
-        </is>
-      </c>
-      <c r="C242" s="716" t="n"/>
-      <c r="D242" s="716" t="n"/>
-      <c r="E242" s="1314">
-        <f>'Ficha Técnica del Proyecto'!$B$29</f>
-        <v/>
-      </c>
-      <c r="F242" s="1457">
-        <f>F240*E242</f>
-        <v/>
-      </c>
+      <c r="C241" s="567" t="n"/>
+      <c r="D241" s="567" t="n"/>
+      <c r="E241" s="567" t="n"/>
+      <c r="F241" s="1456">
+        <f>F25+F39+F49+F69+F81+F93+F100+F106+F120+F130+F141+F148+F163+F177+F186+F193+F199+F213+F220+F228+F232+F239</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="84" t="n"/>
+      <c r="B242" s="28" t="n"/>
+      <c r="C242" s="28" t="n"/>
+      <c r="D242" s="28" t="n"/>
+      <c r="E242" s="28" t="n"/>
+      <c r="F242" s="85" t="n"/>
     </row>
     <row r="243" ht="15" customHeight="1" s="550">
       <c r="A243" s="82" t="n"/>
       <c r="B243" s="46" t="inlineStr">
         <is>
-          <t>Imprevistos (I)</t>
+          <t>Administración (A)</t>
         </is>
       </c>
       <c r="C243" s="716" t="n"/>
       <c r="D243" s="716" t="n"/>
       <c r="E243" s="1314">
-        <f>'Ficha Técnica del Proyecto'!$B$30</f>
+        <f>'Ficha Técnica del Proyecto'!$B$29</f>
         <v/>
       </c>
       <c r="F243" s="1457">
-        <f>F240*E243</f>
+        <f>F241*E243</f>
         <v/>
       </c>
     </row>
@@ -16093,47 +16098,50 @@
       <c r="A244" s="82" t="n"/>
       <c r="B244" s="46" t="inlineStr">
         <is>
-          <t>Utilidad (U)</t>
+          <t>Imprevistos (I)</t>
         </is>
       </c>
       <c r="C244" s="716" t="n"/>
       <c r="D244" s="716" t="n"/>
       <c r="E244" s="1314">
+        <f>'Ficha Técnica del Proyecto'!$B$30</f>
+        <v/>
+      </c>
+      <c r="F244" s="1457">
+        <f>F241*E244</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245" ht="15" customHeight="1" s="550">
+      <c r="A245" s="82" t="n"/>
+      <c r="B245" s="46" t="inlineStr">
+        <is>
+          <t>Utilidad (U)</t>
+        </is>
+      </c>
+      <c r="C245" s="716" t="n"/>
+      <c r="D245" s="716" t="n"/>
+      <c r="E245" s="1314">
         <f>'Ficha Técnica del Proyecto'!$B$31</f>
         <v/>
       </c>
-      <c r="F244" s="1457">
-        <f>F240*E244</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245" ht="15" customHeight="1" s="550">
-      <c r="A245" s="81" t="n"/>
-      <c r="B245" s="704" t="inlineStr">
+      <c r="F245" s="1457">
+        <f>F241*E245</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246" ht="15" customHeight="1" s="550">
+      <c r="A246" s="81" t="n"/>
+      <c r="B246" s="704" t="inlineStr">
         <is>
           <t>SUBTOTAL AIU (A+I+U)</t>
         </is>
       </c>
-      <c r="C245" s="29" t="n"/>
-      <c r="D245" s="29" t="n"/>
-      <c r="E245" s="30" t="n"/>
-      <c r="F245" s="1454">
-        <f>F242+F243+F244</f>
-        <v/>
-      </c>
-    </row>
-    <row r="246" ht="15" customHeight="1" s="550">
-      <c r="A246" s="82" t="n"/>
-      <c r="B246" s="46" t="inlineStr">
-        <is>
-          <t>COSTO DIRECTO + AIU</t>
-        </is>
-      </c>
-      <c r="C246" s="716" t="n"/>
-      <c r="D246" s="716" t="n"/>
-      <c r="E246" s="47" t="n"/>
-      <c r="F246" s="1457">
-        <f>F240+F245</f>
+      <c r="C246" s="29" t="n"/>
+      <c r="D246" s="29" t="n"/>
+      <c r="E246" s="30" t="n"/>
+      <c r="F246" s="1454">
+        <f>F243+F244+F245</f>
         <v/>
       </c>
     </row>
@@ -16141,103 +16149,110 @@
       <c r="A247" s="82" t="n"/>
       <c r="B247" s="46" t="inlineStr">
         <is>
-          <t>IVA sobre Utilidad (19%)</t>
+          <t>COSTO DIRECTO + AIU</t>
         </is>
       </c>
       <c r="C247" s="716" t="n"/>
       <c r="D247" s="716" t="n"/>
-      <c r="E247" s="1314">
-        <f>'Ficha Técnica del Proyecto'!$B$32</f>
-        <v/>
-      </c>
+      <c r="E247" s="47" t="n"/>
       <c r="F247" s="1457">
-        <f>F244*E247</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248">
+        <f>F241+F246</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248" ht="15" customHeight="1" s="550">
       <c r="A248" s="82" t="n"/>
-      <c r="B248" s="716" t="n"/>
+      <c r="B248" s="46" t="inlineStr">
+        <is>
+          <t>IVA sobre Utilidad (19%)</t>
+        </is>
+      </c>
       <c r="C248" s="716" t="n"/>
       <c r="D248" s="716" t="n"/>
-      <c r="E248" s="716" t="n"/>
-      <c r="F248" s="708" t="n"/>
-    </row>
-    <row r="249" ht="24" customHeight="1" s="550">
-      <c r="A249" s="86" t="n"/>
-      <c r="B249" s="703" t="inlineStr">
+      <c r="E248" s="1314">
+        <f>'Ficha Técnica del Proyecto'!$B$32</f>
+        <v/>
+      </c>
+      <c r="F248" s="1457">
+        <f>F245*E248</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="82" t="n"/>
+      <c r="B249" s="716" t="n"/>
+      <c r="C249" s="716" t="n"/>
+      <c r="D249" s="716" t="n"/>
+      <c r="E249" s="716" t="n"/>
+      <c r="F249" s="708" t="n"/>
+    </row>
+    <row r="250" ht="24" customHeight="1" s="550">
+      <c r="A250" s="86" t="n"/>
+      <c r="B250" s="703" t="inlineStr">
         <is>
           <t>PRESUPUESTO TOTAL DE OBRA</t>
         </is>
       </c>
-      <c r="C249" s="567" t="n"/>
-      <c r="D249" s="567" t="n"/>
-      <c r="E249" s="567" t="n"/>
-      <c r="F249" s="1458">
-        <f>F246+F247</f>
-        <v/>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="87" t="n"/>
-      <c r="B250" s="203" t="inlineStr">
-        <is>
-          <t>REV. 10/09/2026</t>
-        </is>
-      </c>
-      <c r="C250" s="277" t="n"/>
-      <c r="D250" s="277" t="n"/>
-      <c r="E250" s="277" t="n"/>
-      <c r="F250" s="345">
-        <f>F6</f>
+      <c r="C250" s="567" t="n"/>
+      <c r="D250" s="567" t="n"/>
+      <c r="E250" s="567" t="n"/>
+      <c r="F250" s="1458">
+        <f>F247+F248</f>
         <v/>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="87" t="n"/>
-      <c r="B251" s="203" t="n"/>
+      <c r="B251" s="203" t="inlineStr">
+        <is>
+          <t>REV. 10/09/2026</t>
+        </is>
+      </c>
       <c r="C251" s="277" t="n"/>
       <c r="D251" s="277" t="n"/>
       <c r="E251" s="277" t="n"/>
-      <c r="F251" s="201" t="n"/>
-    </row>
-    <row r="252" ht="15" customHeight="1" s="550">
+      <c r="F251" s="345">
+        <f>F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252">
       <c r="A252" s="87" t="n"/>
-      <c r="B252" s="89" t="inlineStr">
+      <c r="B252" s="203" t="n"/>
+      <c r="C252" s="277" t="n"/>
+      <c r="D252" s="277" t="n"/>
+      <c r="E252" s="277" t="n"/>
+      <c r="F252" s="201" t="n"/>
+    </row>
+    <row r="253" ht="15" customHeight="1" s="550">
+      <c r="A253" s="87" t="n"/>
+      <c r="B253" s="89" t="inlineStr">
         <is>
           <t>Costo por m² construido (sobre Costo Directo Total)</t>
         </is>
       </c>
-      <c r="C252" s="90" t="n"/>
-      <c r="D252" s="90" t="n"/>
-      <c r="E252" s="90" t="n"/>
-      <c r="F252" s="1459">
-        <f>F240/'Ficha Técnica del Proyecto'!$B$21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253" ht="15" customHeight="1" s="550">
-      <c r="A253" s="88" t="n"/>
-      <c r="B253" s="91" t="inlineStr">
+      <c r="C253" s="90" t="n"/>
+      <c r="D253" s="90" t="n"/>
+      <c r="E253" s="90" t="n"/>
+      <c r="F253" s="1459">
+        <f>F241/'Ficha Técnica del Proyecto'!$B$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254" ht="15" customHeight="1" s="550">
+      <c r="A254" s="88" t="n"/>
+      <c r="B254" s="91" t="inlineStr">
         <is>
           <t>Costo por m² construido (sobre Presupuesto Total)</t>
         </is>
       </c>
-      <c r="C253" s="92" t="n"/>
-      <c r="D253" s="92" t="n"/>
-      <c r="E253" s="92" t="n"/>
-      <c r="F253" s="1460">
-        <f>F249/'Ficha Técnica del Proyecto'!$B$21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="27" t="n"/>
-      <c r="B254" s="277" t="n"/>
-      <c r="C254" s="277" t="n"/>
-      <c r="D254" s="277" t="n"/>
-      <c r="E254" s="277" t="n"/>
-      <c r="F254" s="277" t="n"/>
+      <c r="C254" s="92" t="n"/>
+      <c r="D254" s="92" t="n"/>
+      <c r="E254" s="92" t="n"/>
+      <c r="F254" s="1460">
+        <f>F250/'Ficha Técnica del Proyecto'!$B$21</f>
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="27" t="n"/>
@@ -16279,69 +16294,77 @@
       <c r="E259" s="277" t="n"/>
       <c r="F259" s="277" t="n"/>
     </row>
+    <row r="260">
+      <c r="A260" s="27" t="n"/>
+      <c r="B260" s="277" t="n"/>
+      <c r="C260" s="277" t="n"/>
+      <c r="D260" s="277" t="n"/>
+      <c r="E260" s="277" t="n"/>
+      <c r="F260" s="277" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="B233:F233"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="B109:F109"/>
     <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B200:F200"/>
-    <mergeCell ref="B194:F194"/>
-    <mergeCell ref="B192:E192"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B165:F165"/>
     <mergeCell ref="C5:D5"/>
+    <mergeCell ref="B150:F150"/>
     <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B177:E177"/>
+    <mergeCell ref="B241:E241"/>
+    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B215:F215"/>
     <mergeCell ref="B71:F71"/>
     <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B214:F214"/>
-    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B27:F27"/>
     <mergeCell ref="B102:F102"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B130:F130"/>
-    <mergeCell ref="B212:E212"/>
-    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="B213:E213"/>
+    <mergeCell ref="B163:E163"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B195:F195"/>
     <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B229:F229"/>
-    <mergeCell ref="B227:E227"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B185:E185"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B132:F132"/>
     <mergeCell ref="B81:E81"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B232:E232"/>
+    <mergeCell ref="B199:E199"/>
+    <mergeCell ref="B193:E193"/>
     <mergeCell ref="B93:E93"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B140:E140"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="B238:E238"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B176:E176"/>
-    <mergeCell ref="B219:E219"/>
+    <mergeCell ref="B234:F234"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B228:E228"/>
+    <mergeCell ref="B130:E130"/>
     <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B230:F230"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B240:E240"/>
-    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B143:F143"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="B101:E101"/>
     <mergeCell ref="B83:F83"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B201:F201"/>
+    <mergeCell ref="B148:E148"/>
     <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B250:E250"/>
     <mergeCell ref="C1:F3"/>
     <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="B222:F222"/>
     <mergeCell ref="B82:E82"/>
     <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B249:E249"/>
-    <mergeCell ref="B162:E162"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B221:F221"/>
+    <mergeCell ref="B186:E186"/>
     <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B188:F188"/>
   </mergeCells>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.5118110236220472" footer="0.5118110236220472"/>
   <pageSetup orientation="portrait" paperSize="9" scale="53" horizontalDpi="300" verticalDpi="300"/>

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Presupuesto " sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Presupuesto '!$A$13:$F$238</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -11282,13 +11284,13 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
   </mergeCells>
@@ -16303,6 +16305,7 @@
       <c r="F260" s="277" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A13:F238"/>
   <mergeCells count="61">
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="B49:E49"/>
@@ -16317,9 +16320,9 @@
     <mergeCell ref="B215:F215"/>
     <mergeCell ref="B71:F71"/>
     <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B27:F27"/>
     <mergeCell ref="B102:F102"/>
     <mergeCell ref="B213:E213"/>
+    <mergeCell ref="B27:F27"/>
     <mergeCell ref="B163:E163"/>
     <mergeCell ref="B106:E106"/>
     <mergeCell ref="B195:F195"/>

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -11253,6 +11253,7 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11284,13 +11285,12 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
   </mergeCells>
@@ -11306,7 +11306,7 @@
     <tabColor rgb="FF2E7D32"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F260"/>
+  <dimension ref="A1:F259"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" style="614" min="1" max="1"/>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="B42" s="364" t="inlineStr">
         <is>
-          <t>Concreto de limpieza / solado</t>
+          <t>Concreto de f'c = 175 kg/cm² (2500 PSI), incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="C42" s="257" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B43" s="364" t="inlineStr">
         <is>
-          <t>Concreto para zapatas</t>
+          <t>Concreto ciclópeo, incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="C43" s="257" t="inlineStr">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="B44" s="364" t="inlineStr">
         <is>
-          <t>Concreto para vigas de cimentación</t>
+          <t>Concreto de f'c = 210 kg/cm² (3000 PSI), incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="C44" s="257" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="B45" s="364" t="inlineStr">
         <is>
-          <t>Concreto para losas de cimentación</t>
+          <t>Concreto de f'c = 280 kg/cm² (4000 PSI), incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="C45" s="257" t="inlineStr">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="B46" s="364" t="inlineStr">
         <is>
-          <t>Concreto para pedestales</t>
+          <t>Concreto de f'c = 350 kg/cm² (5000 PSI), incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="C46" s="257" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="B47" s="364" t="inlineStr">
         <is>
-          <t>Acero de refuerzo en cimentación</t>
+          <t>Suministro, figurado y amarre de acero de refuerzo 60.000 PSI</t>
         </is>
       </c>
       <c r="C47" s="257" t="inlineStr">
@@ -12217,12 +12217,12 @@
       </c>
       <c r="B48" s="364" t="inlineStr">
         <is>
-          <t>Formaleta para elementos de cimentación</t>
+          <t>Suministro, figurado y amarre de acero de refuerzo 37.000 PSI</t>
         </is>
       </c>
       <c r="C48" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D48" s="258" t="n"/>
@@ -12233,76 +12233,76 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="81" t="n"/>
-      <c r="B49" s="704" t="inlineStr">
+      <c r="A49" s="80" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="B49" s="364" t="inlineStr">
+        <is>
+          <t>Formaleta para elementos de cimentación</t>
+        </is>
+      </c>
+      <c r="C49" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D49" s="258" t="n"/>
+      <c r="E49" s="1451" t="n"/>
+      <c r="F49" s="1453">
+        <f>D49*E49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="81" t="n"/>
+      <c r="B50" s="704" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 3 - CIMENTACIONES</t>
         </is>
       </c>
-      <c r="C49" s="567" t="n"/>
-      <c r="D49" s="567" t="n"/>
-      <c r="E49" s="567" t="n"/>
-      <c r="F49" s="1454">
-        <f>SUM(F42:F48)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="82" t="n"/>
-      <c r="B50" s="716" t="n"/>
-      <c r="C50" s="716" t="n"/>
-      <c r="D50" s="716" t="n"/>
-      <c r="E50" s="716" t="n"/>
-      <c r="F50" s="708" t="n"/>
+      <c r="C50" s="567" t="n"/>
+      <c r="D50" s="567" t="n"/>
+      <c r="E50" s="567" t="n"/>
+      <c r="F50" s="1454">
+        <f>SUM(F42:F49)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="182" t="inlineStr">
+      <c r="A51" s="82" t="n"/>
+      <c r="B51" s="716" t="n"/>
+      <c r="C51" s="716" t="n"/>
+      <c r="D51" s="716" t="n"/>
+      <c r="E51" s="716" t="n"/>
+      <c r="F51" s="708" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="182" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B51" s="703" t="inlineStr">
+      <c r="B52" s="703" t="inlineStr">
         <is>
           <t>ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C51" s="567" t="n"/>
-      <c r="D51" s="567" t="n"/>
-      <c r="E51" s="567" t="n"/>
-      <c r="F51" s="567" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="80" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="B52" s="364" t="inlineStr">
-        <is>
-          <t>Concreto para columnas</t>
-        </is>
-      </c>
-      <c r="C52" s="257" t="inlineStr">
-        <is>
-          <t>M³</t>
-        </is>
-      </c>
-      <c r="D52" s="258" t="n"/>
-      <c r="E52" s="1451" t="n"/>
-      <c r="F52" s="1453">
-        <f>D52*E52</f>
-        <v/>
-      </c>
+      <c r="C52" s="567" t="n"/>
+      <c r="D52" s="567" t="n"/>
+      <c r="E52" s="567" t="n"/>
+      <c r="F52" s="567" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="80" t="inlineStr">
         <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="B53" s="365" t="inlineStr">
-        <is>
-          <t>Concreto para vigas</t>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B53" s="364" t="inlineStr">
+        <is>
+          <t>Concreto de f'c = 210 kg/cm² (3000 PSI), incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="C53" s="257" t="inlineStr">
@@ -12310,9 +12310,9 @@
           <t>M³</t>
         </is>
       </c>
-      <c r="D53" s="1449" t="n"/>
-      <c r="E53" s="1452" t="n"/>
-      <c r="F53" s="1455">
+      <c r="D53" s="258" t="n"/>
+      <c r="E53" s="1451" t="n"/>
+      <c r="F53" s="1453">
         <f>D53*E53</f>
         <v/>
       </c>
@@ -12320,12 +12320,12 @@
     <row r="54">
       <c r="A54" s="80" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B54" s="364" t="inlineStr">
         <is>
-          <t>Concreto para losas</t>
+          <t>Concreto de f'c = 280 kg/cm² (4000 PSI), incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="C54" s="257" t="inlineStr">
@@ -12343,12 +12343,12 @@
     <row r="55">
       <c r="A55" s="80" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B55" s="364" t="inlineStr">
         <is>
-          <t>Concreto para escaleras</t>
+          <t>Concreto de f'c = 350 kg/cm² (5000 PSI), incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="C55" s="257" t="inlineStr">
@@ -12366,12 +12366,12 @@
     <row r="56">
       <c r="A56" s="80" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="B56" s="364" t="inlineStr">
         <is>
-          <t>Concreto para muros estructurales</t>
+          <t>Concreto de f'c = 420 kg/cm² (6000 PSI), incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="C56" s="257" t="inlineStr">
@@ -12389,12 +12389,12 @@
     <row r="57">
       <c r="A57" s="80" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="B57" s="364" t="inlineStr">
         <is>
-          <t>Acero de refuerzo de columnas</t>
+          <t>Suministro, figurado y amarre de acero de refuerzo 60.000 PSI</t>
         </is>
       </c>
       <c r="C57" s="257" t="inlineStr">
@@ -12412,12 +12412,12 @@
     <row r="58">
       <c r="A58" s="80" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="B58" s="364" t="inlineStr">
         <is>
-          <t>Acero de refuerzo de vigas</t>
+          <t>Suministro, figurado y amarre de acero de refuerzo 37.000 PSI</t>
         </is>
       </c>
       <c r="C58" s="257" t="inlineStr">
@@ -12435,21 +12435,21 @@
     <row r="59">
       <c r="A59" s="80" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="B59" s="364" t="inlineStr">
         <is>
-          <t>Acero de refuerzo de losas</t>
+          <t>Formaleta de columnas</t>
         </is>
       </c>
       <c r="C59" s="257" t="inlineStr">
         <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="D59" s="1449" t="n"/>
-      <c r="E59" s="1452" t="n"/>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D59" s="258" t="n"/>
+      <c r="E59" s="1451" t="n"/>
       <c r="F59" s="1453">
         <f>D59*E59</f>
         <v/>
@@ -12458,12 +12458,12 @@
     <row r="60">
       <c r="A60" s="80" t="inlineStr">
         <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="B60" s="364" t="inlineStr">
-        <is>
-          <t>Formaleta de columnas</t>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="B60" s="365" t="inlineStr">
+        <is>
+          <t>Formaleta de vigas</t>
         </is>
       </c>
       <c r="C60" s="257" t="inlineStr">
@@ -12471,9 +12471,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D60" s="258" t="n"/>
-      <c r="E60" s="1451" t="n"/>
-      <c r="F60" s="1453">
+      <c r="D60" s="1449" t="n"/>
+      <c r="E60" s="1452" t="n"/>
+      <c r="F60" s="1455">
         <f>D60*E60</f>
         <v/>
       </c>
@@ -12481,12 +12481,12 @@
     <row r="61">
       <c r="A61" s="80" t="inlineStr">
         <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="B61" s="365" t="inlineStr">
-        <is>
-          <t>Formaleta de vigas</t>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="B61" s="364" t="inlineStr">
+        <is>
+          <t>Formaleta de losas</t>
         </is>
       </c>
       <c r="C61" s="257" t="inlineStr">
@@ -12494,9 +12494,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D61" s="1449" t="n"/>
-      <c r="E61" s="1452" t="n"/>
-      <c r="F61" s="1455">
+      <c r="D61" s="258" t="n"/>
+      <c r="E61" s="1451" t="n"/>
+      <c r="F61" s="1453">
         <f>D61*E61</f>
         <v/>
       </c>
@@ -12504,12 +12504,12 @@
     <row r="62">
       <c r="A62" s="80" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="B62" s="364" t="inlineStr">
         <is>
-          <t>Formaleta de losas</t>
+          <t>Formaleta de escaleras</t>
         </is>
       </c>
       <c r="C62" s="257" t="inlineStr">
@@ -12527,17 +12527,17 @@
     <row r="63">
       <c r="A63" s="80" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="B63" s="364" t="inlineStr">
         <is>
-          <t>Formaleta de escaleras</t>
+          <t>Suministro y montaje de perfiles metálicos</t>
         </is>
       </c>
       <c r="C63" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D63" s="258" t="n"/>
@@ -12550,12 +12550,12 @@
     <row r="64">
       <c r="A64" s="80" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="B64" s="364" t="inlineStr">
         <is>
-          <t>Suministro y montaje de perfiles metálicos</t>
+          <t>Placas, pernos y conexiones metálicas</t>
         </is>
       </c>
       <c r="C64" s="257" t="inlineStr">
@@ -12573,17 +12573,17 @@
     <row r="65">
       <c r="A65" s="80" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="B65" s="364" t="inlineStr">
         <is>
-          <t>Placas, pernos y conexiones metálicas</t>
+          <t>Grouting cementoso para reparación estructural</t>
         </is>
       </c>
       <c r="C65" s="257" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D65" s="258" t="n"/>
@@ -12596,12 +12596,12 @@
     <row r="66">
       <c r="A66" s="80" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="B66" s="364" t="inlineStr">
         <is>
-          <t>Grouting cementoso para reparación estructural</t>
+          <t>Grouting epóxico para reparación estructural</t>
         </is>
       </c>
       <c r="C66" s="257" t="inlineStr">
@@ -12619,17 +12619,17 @@
     <row r="67">
       <c r="A67" s="80" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="B67" s="364" t="inlineStr">
         <is>
-          <t>Grouting epóxico para reparación estructural</t>
+          <t>Concreto premezclado o de planta (suministro)</t>
         </is>
       </c>
       <c r="C67" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D67" s="258" t="n"/>
@@ -12640,76 +12640,76 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="80" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="B68" s="364" t="inlineStr">
-        <is>
-          <t>Concreto premezclado o de planta (suministro)</t>
-        </is>
-      </c>
-      <c r="C68" s="257" t="inlineStr">
-        <is>
-          <t>M³</t>
-        </is>
-      </c>
-      <c r="D68" s="258" t="n"/>
-      <c r="E68" s="1451" t="n"/>
-      <c r="F68" s="1453">
-        <f>D68*E68</f>
+      <c r="A68" s="81" t="n"/>
+      <c r="B68" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 4 - ESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="C68" s="567" t="n"/>
+      <c r="D68" s="567" t="n"/>
+      <c r="E68" s="567" t="n"/>
+      <c r="F68" s="1454">
+        <f>SUM(F53:F67)</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="81" t="n"/>
-      <c r="B69" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 4 - ESTRUCTURA</t>
-        </is>
-      </c>
-      <c r="C69" s="567" t="n"/>
-      <c r="D69" s="567" t="n"/>
-      <c r="E69" s="567" t="n"/>
-      <c r="F69" s="1454">
-        <f>SUM(F51:F68)</f>
-        <v/>
-      </c>
+      <c r="A69" s="82" t="n"/>
+      <c r="B69" s="716" t="n"/>
+      <c r="C69" s="716" t="n"/>
+      <c r="D69" s="716" t="n"/>
+      <c r="E69" s="716" t="n"/>
+      <c r="F69" s="708" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="82" t="n"/>
-      <c r="B70" s="716" t="n"/>
-      <c r="C70" s="716" t="n"/>
-      <c r="D70" s="716" t="n"/>
-      <c r="E70" s="716" t="n"/>
-      <c r="F70" s="708" t="n"/>
+      <c r="A70" s="182" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B70" s="707" t="inlineStr">
+        <is>
+          <t>MAMPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="C70" s="609" t="n"/>
+      <c r="D70" s="609" t="n"/>
+      <c r="E70" s="609" t="n"/>
+      <c r="F70" s="610" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="182" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B71" s="707" t="inlineStr">
-        <is>
-          <t>MAMPOSTERÍA</t>
-        </is>
-      </c>
-      <c r="C71" s="609" t="n"/>
-      <c r="D71" s="609" t="n"/>
-      <c r="E71" s="609" t="n"/>
-      <c r="F71" s="610" t="n"/>
+      <c r="A71" s="80" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B71" s="364" t="inlineStr">
+        <is>
+          <t>Mampostería en bloque de concreto</t>
+        </is>
+      </c>
+      <c r="C71" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D71" s="258" t="n"/>
+      <c r="E71" s="1451" t="n"/>
+      <c r="F71" s="1453">
+        <f>D71*E71</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="80" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B72" s="364" t="inlineStr">
         <is>
-          <t>Mampostería en bloque de concreto</t>
+          <t>Mampostería en ladrillo</t>
         </is>
       </c>
       <c r="C72" s="257" t="inlineStr">
@@ -12727,12 +12727,12 @@
     <row r="73">
       <c r="A73" s="80" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B73" s="364" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo</t>
+          <t>Mampostería estructural</t>
         </is>
       </c>
       <c r="C73" s="257" t="inlineStr">
@@ -12750,12 +12750,12 @@
     <row r="74">
       <c r="A74" s="80" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="B74" s="364" t="inlineStr">
         <is>
-          <t>Mampostería estructural</t>
+          <t>Muros en sistema liviano / drywall</t>
         </is>
       </c>
       <c r="C74" s="257" t="inlineStr">
@@ -12773,17 +12773,17 @@
     <row r="75">
       <c r="A75" s="80" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="B75" s="364" t="inlineStr">
         <is>
-          <t>Muros en sistema liviano / drywall</t>
+          <t>Dinteles sobre vanos</t>
         </is>
       </c>
       <c r="C75" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D75" s="258" t="n"/>
@@ -12796,12 +12796,12 @@
     <row r="76">
       <c r="A76" s="80" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="B76" s="364" t="inlineStr">
         <is>
-          <t>Dinteles sobre vanos</t>
+          <t>Alfajías y remates</t>
         </is>
       </c>
       <c r="C76" s="257" t="inlineStr">
@@ -12819,17 +12819,17 @@
     <row r="77">
       <c r="A77" s="80" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="B77" s="364" t="inlineStr">
         <is>
-          <t>Alfajías y remates</t>
+          <t>Anclajes y refuerzos de mampostería</t>
         </is>
       </c>
       <c r="C77" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D77" s="258" t="n"/>
@@ -12842,17 +12842,17 @@
     <row r="78">
       <c r="A78" s="80" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="B78" s="364" t="inlineStr">
         <is>
-          <t>Anclajes y refuerzos de mampostería</t>
+          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
         </is>
       </c>
       <c r="C78" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D78" s="258" t="n"/>
@@ -12865,12 +12865,12 @@
     <row r="79">
       <c r="A79" s="80" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="B79" s="364" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
+          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
         </is>
       </c>
       <c r="C79" s="257" t="inlineStr">
@@ -12886,76 +12886,76 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="80" t="inlineStr">
-        <is>
-          <t>5.9</t>
-        </is>
-      </c>
-      <c r="B80" s="364" t="inlineStr">
-        <is>
-          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
-        </is>
-      </c>
-      <c r="C80" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D80" s="258" t="n"/>
-      <c r="E80" s="1451" t="n"/>
-      <c r="F80" s="1453">
-        <f>D80*E80</f>
+      <c r="A80" s="81" t="n"/>
+      <c r="B80" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 5 - MAMPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="C80" s="567" t="n"/>
+      <c r="D80" s="567" t="n"/>
+      <c r="E80" s="567" t="n"/>
+      <c r="F80" s="1454">
+        <f>SUM(F71:F79)</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="81" t="n"/>
-      <c r="B81" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 5 - MAMPOSTERÍA</t>
-        </is>
-      </c>
+      <c r="A81" s="82" t="n"/>
+      <c r="B81" s="716" t="n"/>
       <c r="C81" s="567" t="n"/>
       <c r="D81" s="567" t="n"/>
       <c r="E81" s="567" t="n"/>
-      <c r="F81" s="1454">
-        <f>SUM(F72:F80)</f>
-        <v/>
-      </c>
+      <c r="F81" s="708" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="82" t="n"/>
-      <c r="B82" s="716" t="n"/>
+      <c r="A82" s="182" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B82" s="717" t="inlineStr">
+        <is>
+          <t>CUBIERTAS</t>
+        </is>
+      </c>
       <c r="C82" s="567" t="n"/>
       <c r="D82" s="567" t="n"/>
       <c r="E82" s="567" t="n"/>
-      <c r="F82" s="708" t="n"/>
+      <c r="F82" s="567" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="182" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B83" s="717" t="inlineStr">
-        <is>
-          <t>CUBIERTAS</t>
-        </is>
-      </c>
-      <c r="C83" s="567" t="n"/>
-      <c r="D83" s="567" t="n"/>
-      <c r="E83" s="567" t="n"/>
-      <c r="F83" s="567" t="n"/>
+      <c r="A83" s="80" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B83" s="365" t="inlineStr">
+        <is>
+          <t>Estructura metálica o de madera para cubierta</t>
+        </is>
+      </c>
+      <c r="C83" s="257" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D83" s="1449" t="n"/>
+      <c r="E83" s="1452" t="n"/>
+      <c r="F83" s="1455">
+        <f>D83*E83</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="80" t="inlineStr">
         <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B84" s="365" t="inlineStr">
-        <is>
-          <t>Estructura metálica o de madera para cubierta</t>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B84" s="364" t="inlineStr">
+        <is>
+          <t>Cerchas y elementos estructurales</t>
         </is>
       </c>
       <c r="C84" s="257" t="inlineStr">
@@ -12963,9 +12963,9 @@
           <t>KG</t>
         </is>
       </c>
-      <c r="D84" s="1449" t="n"/>
-      <c r="E84" s="1452" t="n"/>
-      <c r="F84" s="1455">
+      <c r="D84" s="258" t="n"/>
+      <c r="E84" s="1451" t="n"/>
+      <c r="F84" s="1453">
         <f>D84*E84</f>
         <v/>
       </c>
@@ -12973,17 +12973,17 @@
     <row r="85">
       <c r="A85" s="80" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B85" s="364" t="inlineStr">
         <is>
-          <t>Cerchas y elementos estructurales</t>
+          <t>Suministro e instalación de teja</t>
         </is>
       </c>
       <c r="C85" s="257" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D85" s="258" t="n"/>
@@ -12996,12 +12996,12 @@
     <row r="86">
       <c r="A86" s="80" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="B86" s="364" t="inlineStr">
         <is>
-          <t>Suministro e instalación de teja</t>
+          <t>Impermeabilización de cubierta</t>
         </is>
       </c>
       <c r="C86" s="257" t="inlineStr">
@@ -13019,12 +13019,12 @@
     <row r="87">
       <c r="A87" s="80" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="B87" s="364" t="inlineStr">
         <is>
-          <t>Impermeabilización de cubierta</t>
+          <t>Aislamiento térmico/acústico</t>
         </is>
       </c>
       <c r="C87" s="257" t="inlineStr">
@@ -13042,17 +13042,17 @@
     <row r="88">
       <c r="A88" s="80" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="B88" s="364" t="inlineStr">
         <is>
-          <t>Aislamiento térmico/acústico</t>
+          <t>Canales de aguas lluvias</t>
         </is>
       </c>
       <c r="C88" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D88" s="258" t="n"/>
@@ -13065,12 +13065,12 @@
     <row r="89">
       <c r="A89" s="80" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="B89" s="364" t="inlineStr">
         <is>
-          <t>Canales de aguas lluvias</t>
+          <t>Bajantes de aguas lluvias</t>
         </is>
       </c>
       <c r="C89" s="257" t="inlineStr">
@@ -13088,17 +13088,17 @@
     <row r="90">
       <c r="A90" s="80" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="B90" s="364" t="inlineStr">
         <is>
-          <t>Bajantes de aguas lluvias</t>
+          <t>Cielo raso Dry Wall</t>
         </is>
       </c>
       <c r="C90" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D90" s="258" t="n"/>
@@ -13111,12 +13111,12 @@
     <row r="91">
       <c r="A91" s="80" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="B91" s="364" t="inlineStr">
         <is>
-          <t>Cielo raso Dry Wall</t>
+          <t>Cielo raso en lámina acústica de fibra mineral</t>
         </is>
       </c>
       <c r="C91" s="257" t="inlineStr">
@@ -13132,76 +13132,76 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="80" t="inlineStr">
-        <is>
-          <t>6.9</t>
-        </is>
-      </c>
-      <c r="B92" s="364" t="inlineStr">
-        <is>
-          <t>Cielo raso en lámina acústica de fibra mineral</t>
-        </is>
-      </c>
-      <c r="C92" s="257" t="inlineStr">
+      <c r="A92" s="81" t="n"/>
+      <c r="B92" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 6 - CUBIERTAS</t>
+        </is>
+      </c>
+      <c r="C92" s="567" t="n"/>
+      <c r="D92" s="567" t="n"/>
+      <c r="E92" s="567" t="n"/>
+      <c r="F92" s="1454">
+        <f>SUM(F83:F91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="82" t="n"/>
+      <c r="B93" s="716" t="n"/>
+      <c r="C93" s="716" t="n"/>
+      <c r="D93" s="716" t="n"/>
+      <c r="E93" s="716" t="n"/>
+      <c r="F93" s="708" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="182" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B94" s="703" t="inlineStr">
+        <is>
+          <t>IMPERMEABILIZACIONES</t>
+        </is>
+      </c>
+      <c r="C94" s="567" t="n"/>
+      <c r="D94" s="567" t="n"/>
+      <c r="E94" s="567" t="n"/>
+      <c r="F94" s="567" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="80" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="B95" s="364" t="inlineStr">
+        <is>
+          <t>Impermeabilización de losas y terrazas</t>
+        </is>
+      </c>
+      <c r="C95" s="257" t="inlineStr">
         <is>
           <t>M²</t>
         </is>
       </c>
-      <c r="D92" s="258" t="n"/>
-      <c r="E92" s="1451" t="n"/>
-      <c r="F92" s="1453">
-        <f>D92*E92</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="81" t="n"/>
-      <c r="B93" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 6 - CUBIERTAS</t>
-        </is>
-      </c>
-      <c r="C93" s="567" t="n"/>
-      <c r="D93" s="567" t="n"/>
-      <c r="E93" s="567" t="n"/>
-      <c r="F93" s="1454">
-        <f>SUM(F84:F92)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="82" t="n"/>
-      <c r="B94" s="716" t="n"/>
-      <c r="C94" s="716" t="n"/>
-      <c r="D94" s="716" t="n"/>
-      <c r="E94" s="716" t="n"/>
-      <c r="F94" s="708" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="182" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B95" s="703" t="inlineStr">
-        <is>
-          <t>IMPERMEABILIZACIONES</t>
-        </is>
-      </c>
-      <c r="C95" s="567" t="n"/>
-      <c r="D95" s="567" t="n"/>
-      <c r="E95" s="567" t="n"/>
-      <c r="F95" s="567" t="n"/>
+      <c r="D95" s="258" t="n"/>
+      <c r="E95" s="1451" t="n"/>
+      <c r="F95" s="1453">
+        <f>D95*E95</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="80" t="inlineStr">
         <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="B96" s="364" t="inlineStr">
-        <is>
-          <t>Impermeabilización de losas y terrazas</t>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B96" s="365" t="inlineStr">
+        <is>
+          <t>Impermeabilización de muros</t>
         </is>
       </c>
       <c r="C96" s="257" t="inlineStr">
@@ -13209,9 +13209,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D96" s="258" t="n"/>
-      <c r="E96" s="1451" t="n"/>
-      <c r="F96" s="1453">
+      <c r="D96" s="1449" t="n"/>
+      <c r="E96" s="1452" t="n"/>
+      <c r="F96" s="1455">
         <f>D96*E96</f>
         <v/>
       </c>
@@ -13219,12 +13219,12 @@
     <row r="97">
       <c r="A97" s="80" t="inlineStr">
         <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B97" s="365" t="inlineStr">
-        <is>
-          <t>Impermeabilización de muros</t>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="B97" s="364" t="inlineStr">
+        <is>
+          <t>Impermeabilización de zonas húmedas</t>
         </is>
       </c>
       <c r="C97" s="257" t="inlineStr">
@@ -13232,9 +13232,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D97" s="1449" t="n"/>
-      <c r="E97" s="1452" t="n"/>
-      <c r="F97" s="1455">
+      <c r="D97" s="258" t="n"/>
+      <c r="E97" s="1451" t="n"/>
+      <c r="F97" s="1453">
         <f>D97*E97</f>
         <v/>
       </c>
@@ -13242,12 +13242,12 @@
     <row r="98">
       <c r="A98" s="80" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="B98" s="364" t="inlineStr">
         <is>
-          <t>Impermeabilización de zonas húmedas</t>
+          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
         </is>
       </c>
       <c r="C98" s="257" t="inlineStr">
@@ -13263,76 +13263,76 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="80" t="inlineStr">
-        <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="B99" s="364" t="inlineStr">
-        <is>
-          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
-        </is>
-      </c>
-      <c r="C99" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D99" s="258" t="n"/>
-      <c r="E99" s="1451" t="n"/>
-      <c r="F99" s="1453">
-        <f>D99*E99</f>
+      <c r="A99" s="81" t="n"/>
+      <c r="B99" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 7 - IMPERMEABILIZACIONES</t>
+        </is>
+      </c>
+      <c r="C99" s="567" t="n"/>
+      <c r="D99" s="567" t="n"/>
+      <c r="E99" s="567" t="n"/>
+      <c r="F99" s="1454">
+        <f>SUM(F95:F98)</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="81" t="n"/>
-      <c r="B100" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 7 - IMPERMEABILIZACIONES</t>
-        </is>
-      </c>
+      <c r="A100" s="82" t="n"/>
+      <c r="B100" s="716" t="n"/>
       <c r="C100" s="567" t="n"/>
       <c r="D100" s="567" t="n"/>
       <c r="E100" s="567" t="n"/>
-      <c r="F100" s="1454">
-        <f>SUM(F96:F99)</f>
-        <v/>
-      </c>
+      <c r="F100" s="708" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="82" t="n"/>
-      <c r="B101" s="716" t="n"/>
+      <c r="A101" s="182" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B101" s="703" t="inlineStr">
+        <is>
+          <t>PAÑETES Y REVOQUES</t>
+        </is>
+      </c>
       <c r="C101" s="567" t="n"/>
       <c r="D101" s="567" t="n"/>
       <c r="E101" s="567" t="n"/>
-      <c r="F101" s="708" t="n"/>
+      <c r="F101" s="567" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="182" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B102" s="703" t="inlineStr">
-        <is>
-          <t>PAÑETES Y REVOQUES</t>
-        </is>
-      </c>
-      <c r="C102" s="567" t="n"/>
-      <c r="D102" s="567" t="n"/>
-      <c r="E102" s="567" t="n"/>
-      <c r="F102" s="567" t="n"/>
+      <c r="A102" s="80" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B102" s="365" t="inlineStr">
+        <is>
+          <t>Pañete / revoque interior</t>
+        </is>
+      </c>
+      <c r="C102" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D102" s="1449" t="n"/>
+      <c r="E102" s="1452" t="n"/>
+      <c r="F102" s="1455">
+        <f>D102*E102</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="80" t="inlineStr">
         <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="B103" s="365" t="inlineStr">
-        <is>
-          <t>Pañete / revoque interior</t>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="B103" s="364" t="inlineStr">
+        <is>
+          <t>Pañete / revoque exterior</t>
         </is>
       </c>
       <c r="C103" s="257" t="inlineStr">
@@ -13340,9 +13340,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D103" s="1449" t="n"/>
-      <c r="E103" s="1452" t="n"/>
-      <c r="F103" s="1455">
+      <c r="D103" s="258" t="n"/>
+      <c r="E103" s="1451" t="n"/>
+      <c r="F103" s="1453">
         <f>D103*E103</f>
         <v/>
       </c>
@@ -13350,12 +13350,12 @@
     <row r="104">
       <c r="A104" s="80" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="B104" s="364" t="inlineStr">
         <is>
-          <t>Pañete / revoque exterior</t>
+          <t>Pañete impermeabilizado</t>
         </is>
       </c>
       <c r="C104" s="257" t="inlineStr">
@@ -13371,76 +13371,76 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="80" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="B105" s="364" t="inlineStr">
-        <is>
-          <t>Pañete impermeabilizado</t>
-        </is>
-      </c>
-      <c r="C105" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D105" s="258" t="n"/>
-      <c r="E105" s="1451" t="n"/>
-      <c r="F105" s="1453">
-        <f>D105*E105</f>
+      <c r="A105" s="81" t="n"/>
+      <c r="B105" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 8 - PAÑETES Y REVOQUES</t>
+        </is>
+      </c>
+      <c r="C105" s="567" t="n"/>
+      <c r="D105" s="567" t="n"/>
+      <c r="E105" s="567" t="n"/>
+      <c r="F105" s="1454">
+        <f>SUM(F102:F104)</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="81" t="n"/>
-      <c r="B106" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 8 - PAÑETES Y REVOQUES</t>
-        </is>
-      </c>
+      <c r="A106" s="82" t="n"/>
+      <c r="B106" s="708" t="n"/>
       <c r="C106" s="567" t="n"/>
       <c r="D106" s="567" t="n"/>
       <c r="E106" s="567" t="n"/>
-      <c r="F106" s="1454">
-        <f>SUM(F103:F105)</f>
-        <v/>
-      </c>
+      <c r="F106" s="607" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="82" t="n"/>
-      <c r="B107" s="708" t="n"/>
+      <c r="A107" s="182" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B107" s="703" t="inlineStr">
+        <is>
+          <t>PISOS Y ENCHAPES</t>
+        </is>
+      </c>
       <c r="C107" s="567" t="n"/>
       <c r="D107" s="567" t="n"/>
       <c r="E107" s="567" t="n"/>
-      <c r="F107" s="607" t="n"/>
+      <c r="F107" s="567" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="182" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B108" s="703" t="inlineStr">
-        <is>
-          <t>PISOS Y ENCHAPES</t>
-        </is>
-      </c>
-      <c r="C108" s="567" t="n"/>
-      <c r="D108" s="567" t="n"/>
-      <c r="E108" s="567" t="n"/>
-      <c r="F108" s="567" t="n"/>
+      <c r="A108" s="80" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B108" s="364" t="inlineStr">
+        <is>
+          <t>Mortero de nivelación</t>
+        </is>
+      </c>
+      <c r="C108" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D108" s="258" t="n"/>
+      <c r="E108" s="1451" t="n"/>
+      <c r="F108" s="1453">
+        <f>D108*E108</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="80" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="B109" s="364" t="inlineStr">
         <is>
-          <t>Mortero de nivelación</t>
+          <t>Piso cerámico</t>
         </is>
       </c>
       <c r="C109" s="257" t="inlineStr">
@@ -13458,12 +13458,12 @@
     <row r="110">
       <c r="A110" s="80" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="B110" s="364" t="inlineStr">
         <is>
-          <t>Piso cerámico</t>
+          <t>Piso en porcelanato</t>
         </is>
       </c>
       <c r="C110" s="257" t="inlineStr">
@@ -13481,12 +13481,12 @@
     <row r="111">
       <c r="A111" s="80" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="B111" s="364" t="inlineStr">
         <is>
-          <t>Piso en porcelanato</t>
+          <t>Piso vinílico</t>
         </is>
       </c>
       <c r="C111" s="257" t="inlineStr">
@@ -13504,12 +13504,12 @@
     <row r="112">
       <c r="A112" s="80" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="B112" s="364" t="inlineStr">
         <is>
-          <t>Piso vinílico</t>
+          <t>Piso laminado</t>
         </is>
       </c>
       <c r="C112" s="257" t="inlineStr">
@@ -13527,12 +13527,12 @@
     <row r="113">
       <c r="A113" s="80" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="B113" s="364" t="inlineStr">
         <is>
-          <t>Piso laminado</t>
+          <t>Enchape cerámico en muros</t>
         </is>
       </c>
       <c r="C113" s="257" t="inlineStr">
@@ -13540,8 +13540,8 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D113" s="258" t="n"/>
-      <c r="E113" s="1451" t="n"/>
+      <c r="D113" s="1449" t="n"/>
+      <c r="E113" s="1452" t="n"/>
       <c r="F113" s="1453">
         <f>D113*E113</f>
         <v/>
@@ -13550,21 +13550,21 @@
     <row r="114">
       <c r="A114" s="80" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="B114" s="364" t="inlineStr">
         <is>
-          <t>Enchape cerámico en muros</t>
+          <t>Guardaescoba</t>
         </is>
       </c>
       <c r="C114" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D114" s="1449" t="n"/>
-      <c r="E114" s="1452" t="n"/>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D114" s="258" t="n"/>
+      <c r="E114" s="1451" t="n"/>
       <c r="F114" s="1453">
         <f>D114*E114</f>
         <v/>
@@ -13573,12 +13573,12 @@
     <row r="115">
       <c r="A115" s="80" t="inlineStr">
         <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="B115" s="364" t="inlineStr">
-        <is>
-          <t>Guardaescoba</t>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="B115" s="365" t="inlineStr">
+        <is>
+          <t>Juntas de dilatación / construcción</t>
         </is>
       </c>
       <c r="C115" s="257" t="inlineStr">
@@ -13586,9 +13586,9 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D115" s="258" t="n"/>
-      <c r="E115" s="1451" t="n"/>
-      <c r="F115" s="1453">
+      <c r="D115" s="1449" t="n"/>
+      <c r="E115" s="1452" t="n"/>
+      <c r="F115" s="1455">
         <f>D115*E115</f>
         <v/>
       </c>
@@ -13596,17 +13596,17 @@
     <row r="116">
       <c r="A116" s="80" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="B116" s="365" t="inlineStr">
         <is>
-          <t>Juntas de dilatación / construcción</t>
+          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
         </is>
       </c>
       <c r="C116" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D116" s="1449" t="n"/>
@@ -13619,12 +13619,12 @@
     <row r="117">
       <c r="A117" s="80" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="B117" s="365" t="inlineStr">
         <is>
-          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
+          <t>Baldosa de granito</t>
         </is>
       </c>
       <c r="C117" s="257" t="inlineStr">
@@ -13642,12 +13642,12 @@
     <row r="118">
       <c r="A118" s="80" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="B118" s="365" t="inlineStr">
         <is>
-          <t>Baldosa de granito</t>
+          <t>Enchape en granito pulido</t>
         </is>
       </c>
       <c r="C118" s="257" t="inlineStr">
@@ -13663,76 +13663,76 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="80" t="inlineStr">
-        <is>
-          <t>9.11</t>
-        </is>
-      </c>
-      <c r="B119" s="365" t="inlineStr">
-        <is>
-          <t>Enchape en granito pulido</t>
-        </is>
-      </c>
-      <c r="C119" s="257" t="inlineStr">
+      <c r="A119" s="81" t="n"/>
+      <c r="B119" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 9 - PISOS Y ENCHAPES</t>
+        </is>
+      </c>
+      <c r="C119" s="567" t="n"/>
+      <c r="D119" s="567" t="n"/>
+      <c r="E119" s="567" t="n"/>
+      <c r="F119" s="1454">
+        <f>SUM(F108:F118)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="82" t="n"/>
+      <c r="B120" s="716" t="n"/>
+      <c r="C120" s="716" t="n"/>
+      <c r="D120" s="716" t="n"/>
+      <c r="E120" s="716" t="n"/>
+      <c r="F120" s="708" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="182" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B121" s="703" t="inlineStr">
+        <is>
+          <t>PINTURA</t>
+        </is>
+      </c>
+      <c r="C121" s="567" t="n"/>
+      <c r="D121" s="567" t="n"/>
+      <c r="E121" s="567" t="n"/>
+      <c r="F121" s="567" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="80" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="B122" s="364" t="inlineStr">
+        <is>
+          <t>Pintura vinílica interior</t>
+        </is>
+      </c>
+      <c r="C122" s="257" t="inlineStr">
         <is>
           <t>M²</t>
         </is>
       </c>
-      <c r="D119" s="1449" t="n"/>
-      <c r="E119" s="1452" t="n"/>
-      <c r="F119" s="1455">
-        <f>D119*E119</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="81" t="n"/>
-      <c r="B120" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 9 - PISOS Y ENCHAPES</t>
-        </is>
-      </c>
-      <c r="C120" s="567" t="n"/>
-      <c r="D120" s="567" t="n"/>
-      <c r="E120" s="567" t="n"/>
-      <c r="F120" s="1454">
-        <f>SUM(F109:F119)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="82" t="n"/>
-      <c r="B121" s="716" t="n"/>
-      <c r="C121" s="716" t="n"/>
-      <c r="D121" s="716" t="n"/>
-      <c r="E121" s="716" t="n"/>
-      <c r="F121" s="708" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="182" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B122" s="703" t="inlineStr">
-        <is>
-          <t>PINTURA</t>
-        </is>
-      </c>
-      <c r="C122" s="567" t="n"/>
-      <c r="D122" s="567" t="n"/>
-      <c r="E122" s="567" t="n"/>
-      <c r="F122" s="567" t="n"/>
+      <c r="D122" s="258" t="n"/>
+      <c r="E122" s="1451" t="n"/>
+      <c r="F122" s="1453">
+        <f>D122*E122</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="80" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="B123" s="364" t="inlineStr">
         <is>
-          <t>Pintura vinílica interior</t>
+          <t>Pintura exterior</t>
         </is>
       </c>
       <c r="C123" s="257" t="inlineStr">
@@ -13750,12 +13750,12 @@
     <row r="124">
       <c r="A124" s="80" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="B124" s="364" t="inlineStr">
         <is>
-          <t>Pintura exterior</t>
+          <t>Pintura esmalte en superficies metálicas/madera</t>
         </is>
       </c>
       <c r="C124" s="257" t="inlineStr">
@@ -13773,12 +13773,12 @@
     <row r="125">
       <c r="A125" s="80" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="B125" s="364" t="inlineStr">
         <is>
-          <t>Pintura esmalte en superficies metálicas/madera</t>
+          <t>Pintura anticorrosiva</t>
         </is>
       </c>
       <c r="C125" s="257" t="inlineStr">
@@ -13796,12 +13796,12 @@
     <row r="126">
       <c r="A126" s="80" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="B126" s="364" t="inlineStr">
         <is>
-          <t>Pintura anticorrosiva</t>
+          <t>Sellador / imprimante</t>
         </is>
       </c>
       <c r="C126" s="257" t="inlineStr">
@@ -13809,8 +13809,8 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D126" s="258" t="n"/>
-      <c r="E126" s="1451" t="n"/>
+      <c r="D126" s="1449" t="n"/>
+      <c r="E126" s="1452" t="n"/>
       <c r="F126" s="1453">
         <f>D126*E126</f>
         <v/>
@@ -13819,12 +13819,12 @@
     <row r="127">
       <c r="A127" s="80" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="B127" s="364" t="inlineStr">
         <is>
-          <t>Sellador / imprimante</t>
+          <t>Estuco plástico</t>
         </is>
       </c>
       <c r="C127" s="257" t="inlineStr">
@@ -13842,12 +13842,12 @@
     <row r="128">
       <c r="A128" s="80" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="B128" s="364" t="inlineStr">
         <is>
-          <t>Estuco plástico</t>
+          <t>Estuco tradicional</t>
         </is>
       </c>
       <c r="C128" s="257" t="inlineStr">
@@ -13863,85 +13863,85 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="80" t="inlineStr">
-        <is>
-          <t>10.7</t>
-        </is>
-      </c>
-      <c r="B129" s="364" t="inlineStr">
-        <is>
-          <t>Estuco tradicional</t>
-        </is>
-      </c>
-      <c r="C129" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D129" s="1449" t="n"/>
-      <c r="E129" s="1452" t="n"/>
-      <c r="F129" s="1453">
-        <f>D129*E129</f>
+      <c r="A129" s="81" t="n"/>
+      <c r="B129" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 10 - PINTURA</t>
+        </is>
+      </c>
+      <c r="C129" s="567" t="n"/>
+      <c r="D129" s="567" t="n"/>
+      <c r="E129" s="567" t="n"/>
+      <c r="F129" s="1454">
+        <f>SUM(F122:F128)</f>
         <v/>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="81" t="n"/>
-      <c r="B130" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 10 - PINTURA</t>
-        </is>
-      </c>
+      <c r="A130" s="82" t="n"/>
+      <c r="B130" s="708" t="n"/>
       <c r="C130" s="567" t="n"/>
       <c r="D130" s="567" t="n"/>
       <c r="E130" s="567" t="n"/>
-      <c r="F130" s="1454">
-        <f>SUM(F123:F129)</f>
-        <v/>
-      </c>
+      <c r="F130" s="607" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="82" t="n"/>
-      <c r="B131" s="708" t="n"/>
+      <c r="A131" s="182" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B131" s="703" t="inlineStr">
+        <is>
+          <t>CARPINTERÍA</t>
+        </is>
+      </c>
       <c r="C131" s="567" t="n"/>
       <c r="D131" s="567" t="n"/>
       <c r="E131" s="567" t="n"/>
-      <c r="F131" s="607" t="n"/>
+      <c r="F131" s="567" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="182" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B132" s="703" t="inlineStr">
-        <is>
-          <t>CARPINTERÍA</t>
-        </is>
-      </c>
-      <c r="C132" s="567" t="n"/>
-      <c r="D132" s="567" t="n"/>
-      <c r="E132" s="567" t="n"/>
-      <c r="F132" s="567" t="n"/>
+      <c r="A132" s="80" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="B132" s="364" t="inlineStr">
+        <is>
+          <t>Puertas de madera</t>
+        </is>
+      </c>
+      <c r="C132" s="257" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D132" s="258" t="n"/>
+      <c r="E132" s="1451" t="n"/>
+      <c r="F132" s="1453">
+        <f>D132*E132</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="80" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="B133" s="364" t="inlineStr">
         <is>
-          <t>Puertas de madera</t>
+          <t>Muebles fijos de madera</t>
         </is>
       </c>
       <c r="C133" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D133" s="258" t="n"/>
-      <c r="E133" s="1451" t="n"/>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D133" s="1449" t="n"/>
+      <c r="E133" s="1452" t="n"/>
       <c r="F133" s="1453">
         <f>D133*E133</f>
         <v/>
@@ -13950,21 +13950,21 @@
     <row r="134">
       <c r="A134" s="80" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="B134" s="364" t="inlineStr">
         <is>
-          <t>Muebles fijos de madera</t>
+          <t>Puertas metálicas</t>
         </is>
       </c>
       <c r="C134" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D134" s="1449" t="n"/>
-      <c r="E134" s="1452" t="n"/>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D134" s="258" t="n"/>
+      <c r="E134" s="1451" t="n"/>
       <c r="F134" s="1453">
         <f>D134*E134</f>
         <v/>
@@ -13973,22 +13973,22 @@
     <row r="135">
       <c r="A135" s="80" t="inlineStr">
         <is>
-          <t>11.3</t>
-        </is>
-      </c>
-      <c r="B135" s="364" t="inlineStr">
-        <is>
-          <t>Puertas metálicas</t>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="B135" s="365" t="inlineStr">
+        <is>
+          <t>Barandas metálicas</t>
         </is>
       </c>
       <c r="C135" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D135" s="258" t="n"/>
-      <c r="E135" s="1451" t="n"/>
-      <c r="F135" s="1453">
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D135" s="1449" t="n"/>
+      <c r="E135" s="1452" t="n"/>
+      <c r="F135" s="1455">
         <f>D135*E135</f>
         <v/>
       </c>
@@ -13996,12 +13996,12 @@
     <row r="136">
       <c r="A136" s="80" t="inlineStr">
         <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="B136" s="365" t="inlineStr">
-        <is>
-          <t>Barandas metálicas</t>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="B136" s="364" t="inlineStr">
+        <is>
+          <t>Pasamanos</t>
         </is>
       </c>
       <c r="C136" s="257" t="inlineStr">
@@ -14009,9 +14009,9 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D136" s="1449" t="n"/>
-      <c r="E136" s="1452" t="n"/>
-      <c r="F136" s="1455">
+      <c r="D136" s="258" t="n"/>
+      <c r="E136" s="1451" t="n"/>
+      <c r="F136" s="1453">
         <f>D136*E136</f>
         <v/>
       </c>
@@ -14019,17 +14019,17 @@
     <row r="137">
       <c r="A137" s="80" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="B137" s="364" t="inlineStr">
         <is>
-          <t>Pasamanos</t>
+          <t>Ventanas de aluminio</t>
         </is>
       </c>
       <c r="C137" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D137" s="258" t="n"/>
@@ -14042,12 +14042,12 @@
     <row r="138">
       <c r="A138" s="80" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="B138" s="364" t="inlineStr">
         <is>
-          <t>Ventanas de aluminio</t>
+          <t>Divisiones de aluminio</t>
         </is>
       </c>
       <c r="C138" s="257" t="inlineStr">
@@ -14065,17 +14065,17 @@
     <row r="139">
       <c r="A139" s="80" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="B139" s="364" t="inlineStr">
         <is>
-          <t>Divisiones de aluminio</t>
+          <t>Puerta antipánico</t>
         </is>
       </c>
       <c r="C139" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D139" s="258" t="n"/>
@@ -14086,76 +14086,76 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="80" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="B140" s="364" t="inlineStr">
-        <is>
-          <t>Puerta antipánico</t>
-        </is>
-      </c>
-      <c r="C140" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D140" s="258" t="n"/>
-      <c r="E140" s="1451" t="n"/>
-      <c r="F140" s="1453">
-        <f>D140*E140</f>
+      <c r="A140" s="81" t="n"/>
+      <c r="B140" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 11 - CARPINTERÍA</t>
+        </is>
+      </c>
+      <c r="C140" s="567" t="n"/>
+      <c r="D140" s="567" t="n"/>
+      <c r="E140" s="567" t="n"/>
+      <c r="F140" s="1454">
+        <f>SUM(F132:F139)</f>
         <v/>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="81" t="n"/>
-      <c r="B141" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 11 - CARPINTERÍA</t>
-        </is>
-      </c>
-      <c r="C141" s="567" t="n"/>
-      <c r="D141" s="567" t="n"/>
-      <c r="E141" s="567" t="n"/>
-      <c r="F141" s="1454">
-        <f>SUM(F133:F140)</f>
-        <v/>
-      </c>
+      <c r="A141" s="82" t="n"/>
+      <c r="B141" s="716" t="n"/>
+      <c r="C141" s="716" t="n"/>
+      <c r="D141" s="716" t="n"/>
+      <c r="E141" s="716" t="n"/>
+      <c r="F141" s="708" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="82" t="n"/>
-      <c r="B142" s="716" t="n"/>
-      <c r="C142" s="716" t="n"/>
-      <c r="D142" s="716" t="n"/>
-      <c r="E142" s="716" t="n"/>
-      <c r="F142" s="708" t="n"/>
+      <c r="A142" s="182" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B142" s="703" t="inlineStr">
+        <is>
+          <t>VIDRIOS</t>
+        </is>
+      </c>
+      <c r="C142" s="567" t="n"/>
+      <c r="D142" s="567" t="n"/>
+      <c r="E142" s="567" t="n"/>
+      <c r="F142" s="567" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="182" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B143" s="703" t="inlineStr">
-        <is>
-          <t>VIDRIOS</t>
-        </is>
-      </c>
-      <c r="C143" s="567" t="n"/>
-      <c r="D143" s="567" t="n"/>
-      <c r="E143" s="567" t="n"/>
-      <c r="F143" s="567" t="n"/>
+      <c r="A143" s="80" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="B143" s="364" t="inlineStr">
+        <is>
+          <t>Vidrio templado</t>
+        </is>
+      </c>
+      <c r="C143" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D143" s="1449" t="n"/>
+      <c r="E143" s="1452" t="n"/>
+      <c r="F143" s="1453">
+        <f>D143*E143</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="80" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="B144" s="364" t="inlineStr">
         <is>
-          <t>Vidrio templado</t>
+          <t>Vidrio laminado</t>
         </is>
       </c>
       <c r="C144" s="257" t="inlineStr">
@@ -14163,8 +14163,8 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D144" s="1449" t="n"/>
-      <c r="E144" s="1452" t="n"/>
+      <c r="D144" s="258" t="n"/>
+      <c r="E144" s="1451" t="n"/>
       <c r="F144" s="1453">
         <f>D144*E144</f>
         <v/>
@@ -14173,12 +14173,12 @@
     <row r="145">
       <c r="A145" s="80" t="inlineStr">
         <is>
-          <t>12.2</t>
-        </is>
-      </c>
-      <c r="B145" s="364" t="inlineStr">
-        <is>
-          <t>Vidrio laminado</t>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="B145" s="365" t="inlineStr">
+        <is>
+          <t>Espejos</t>
         </is>
       </c>
       <c r="C145" s="257" t="inlineStr">
@@ -14186,9 +14186,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D145" s="258" t="n"/>
-      <c r="E145" s="1451" t="n"/>
-      <c r="F145" s="1453">
+      <c r="D145" s="1449" t="n"/>
+      <c r="E145" s="1452" t="n"/>
+      <c r="F145" s="1455">
         <f>D145*E145</f>
         <v/>
       </c>
@@ -14196,97 +14196,97 @@
     <row r="146">
       <c r="A146" s="80" t="inlineStr">
         <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="B146" s="365" t="inlineStr">
-        <is>
-          <t>Espejos</t>
+          <t>12.4</t>
+        </is>
+      </c>
+      <c r="B146" s="364" t="inlineStr">
+        <is>
+          <t>Sellos y silicona</t>
         </is>
       </c>
       <c r="C146" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D146" s="1449" t="n"/>
-      <c r="E146" s="1452" t="n"/>
-      <c r="F146" s="1455">
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D146" s="258" t="n"/>
+      <c r="E146" s="1451" t="n"/>
+      <c r="F146" s="1453">
         <f>D146*E146</f>
         <v/>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="80" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
-      </c>
-      <c r="B147" s="364" t="inlineStr">
-        <is>
-          <t>Sellos y silicona</t>
-        </is>
-      </c>
-      <c r="C147" s="257" t="inlineStr">
+      <c r="A147" s="81" t="n"/>
+      <c r="B147" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 12 - VIDRIOS</t>
+        </is>
+      </c>
+      <c r="C147" s="567" t="n"/>
+      <c r="D147" s="567" t="n"/>
+      <c r="E147" s="567" t="n"/>
+      <c r="F147" s="1454">
+        <f>SUM(F143:F146)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="82" t="n"/>
+      <c r="B148" s="716" t="n"/>
+      <c r="C148" s="716" t="n"/>
+      <c r="D148" s="716" t="n"/>
+      <c r="E148" s="716" t="n"/>
+      <c r="F148" s="708" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="182" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B149" s="703" t="inlineStr">
+        <is>
+          <t>INSTALACIONES HIDROSANITARIAS</t>
+        </is>
+      </c>
+      <c r="C149" s="567" t="n"/>
+      <c r="D149" s="567" t="n"/>
+      <c r="E149" s="567" t="n"/>
+      <c r="F149" s="567" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="80" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="B150" s="364" t="inlineStr">
+        <is>
+          <t>Tubería de agua fría</t>
+        </is>
+      </c>
+      <c r="C150" s="257" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="D147" s="258" t="n"/>
-      <c r="E147" s="1451" t="n"/>
-      <c r="F147" s="1453">
-        <f>D147*E147</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="81" t="n"/>
-      <c r="B148" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 12 - VIDRIOS</t>
-        </is>
-      </c>
-      <c r="C148" s="567" t="n"/>
-      <c r="D148" s="567" t="n"/>
-      <c r="E148" s="567" t="n"/>
-      <c r="F148" s="1454">
-        <f>SUM(F144:F147)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="82" t="n"/>
-      <c r="B149" s="716" t="n"/>
-      <c r="C149" s="716" t="n"/>
-      <c r="D149" s="716" t="n"/>
-      <c r="E149" s="716" t="n"/>
-      <c r="F149" s="708" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="182" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B150" s="703" t="inlineStr">
-        <is>
-          <t>INSTALACIONES HIDROSANITARIAS</t>
-        </is>
-      </c>
-      <c r="C150" s="567" t="n"/>
-      <c r="D150" s="567" t="n"/>
-      <c r="E150" s="567" t="n"/>
-      <c r="F150" s="567" t="n"/>
+      <c r="D150" s="1449" t="n"/>
+      <c r="E150" s="1452" t="n"/>
+      <c r="F150" s="1453">
+        <f>D150*E150</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="80" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="B151" s="364" t="inlineStr">
         <is>
-          <t>Tubería de agua fría</t>
+          <t>Tubería de agua caliente</t>
         </is>
       </c>
       <c r="C151" s="257" t="inlineStr">
@@ -14294,8 +14294,8 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D151" s="1449" t="n"/>
-      <c r="E151" s="1452" t="n"/>
+      <c r="D151" s="258" t="n"/>
+      <c r="E151" s="1451" t="n"/>
       <c r="F151" s="1453">
         <f>D151*E151</f>
         <v/>
@@ -14304,21 +14304,21 @@
     <row r="152">
       <c r="A152" s="80" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="B152" s="364" t="inlineStr">
         <is>
-          <t>Tubería de agua caliente</t>
+          <t>Válvulas y accesorios hidrosanitarios</t>
         </is>
       </c>
       <c r="C152" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D152" s="258" t="n"/>
-      <c r="E152" s="1451" t="n"/>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D152" s="1449" t="n"/>
+      <c r="E152" s="1452" t="n"/>
       <c r="F152" s="1453">
         <f>D152*E152</f>
         <v/>
@@ -14327,21 +14327,21 @@
     <row r="153">
       <c r="A153" s="80" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="B153" s="364" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios hidrosanitarios</t>
+          <t>Tubería sanitaria</t>
         </is>
       </c>
       <c r="C153" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D153" s="1449" t="n"/>
-      <c r="E153" s="1452" t="n"/>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D153" s="258" t="n"/>
+      <c r="E153" s="1451" t="n"/>
       <c r="F153" s="1453">
         <f>D153*E153</f>
         <v/>
@@ -14350,12 +14350,12 @@
     <row r="154">
       <c r="A154" s="80" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="B154" s="364" t="inlineStr">
         <is>
-          <t>Tubería sanitaria</t>
+          <t>Tubería de aguas lluvias</t>
         </is>
       </c>
       <c r="C154" s="257" t="inlineStr">
@@ -14373,17 +14373,17 @@
     <row r="155">
       <c r="A155" s="80" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="B155" s="364" t="inlineStr">
         <is>
-          <t>Tubería de aguas lluvias</t>
+          <t>Cajas de inspección</t>
         </is>
       </c>
       <c r="C155" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D155" s="258" t="n"/>
@@ -14396,12 +14396,12 @@
     <row r="156">
       <c r="A156" s="80" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="B156" s="364" t="inlineStr">
         <is>
-          <t>Cajas de inspección</t>
+          <t>Aparatos sanitarios</t>
         </is>
       </c>
       <c r="C156" s="257" t="inlineStr">
@@ -14419,12 +14419,12 @@
     <row r="157">
       <c r="A157" s="80" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="B157" s="364" t="inlineStr">
         <is>
-          <t>Aparatos sanitarios</t>
+          <t>Lavamanos</t>
         </is>
       </c>
       <c r="C157" s="257" t="inlineStr">
@@ -14442,12 +14442,12 @@
     <row r="158">
       <c r="A158" s="80" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="B158" s="364" t="inlineStr">
         <is>
-          <t>Lavamanos</t>
+          <t>Griferías</t>
         </is>
       </c>
       <c r="C158" s="257" t="inlineStr">
@@ -14465,12 +14465,12 @@
     <row r="159">
       <c r="A159" s="80" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="B159" s="364" t="inlineStr">
         <is>
-          <t>Griferías</t>
+          <t>Duchas</t>
         </is>
       </c>
       <c r="C159" s="257" t="inlineStr">
@@ -14488,17 +14488,17 @@
     <row r="160">
       <c r="A160" s="80" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="B160" s="364" t="inlineStr">
         <is>
-          <t>Duchas</t>
+          <t>Pruebas hidráulicas y de estanqueidad</t>
         </is>
       </c>
       <c r="C160" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D160" s="258" t="n"/>
@@ -14511,17 +14511,17 @@
     <row r="161">
       <c r="A161" s="80" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="B161" s="364" t="inlineStr">
         <is>
-          <t>Pruebas hidráulicas y de estanqueidad</t>
+          <t>Orinal institucional</t>
         </is>
       </c>
       <c r="C161" s="257" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D161" s="258" t="n"/>
@@ -14532,76 +14532,76 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="80" t="inlineStr">
-        <is>
-          <t>13.12</t>
-        </is>
-      </c>
-      <c r="B162" s="364" t="inlineStr">
-        <is>
-          <t>Orinal institucional</t>
-        </is>
-      </c>
-      <c r="C162" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D162" s="258" t="n"/>
-      <c r="E162" s="1451" t="n"/>
-      <c r="F162" s="1453">
-        <f>D162*E162</f>
+      <c r="A162" s="81" t="n"/>
+      <c r="B162" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 13 - INSTALACIONES HIDROSANITARIAS</t>
+        </is>
+      </c>
+      <c r="C162" s="567" t="n"/>
+      <c r="D162" s="567" t="n"/>
+      <c r="E162" s="567" t="n"/>
+      <c r="F162" s="1454">
+        <f>SUM(F150:F161)</f>
         <v/>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="81" t="n"/>
-      <c r="B163" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 13 - INSTALACIONES HIDROSANITARIAS</t>
-        </is>
-      </c>
-      <c r="C163" s="567" t="n"/>
-      <c r="D163" s="567" t="n"/>
-      <c r="E163" s="567" t="n"/>
-      <c r="F163" s="1454">
-        <f>SUM(F151:F162)</f>
-        <v/>
-      </c>
+      <c r="A163" s="82" t="n"/>
+      <c r="B163" s="716" t="n"/>
+      <c r="C163" s="716" t="n"/>
+      <c r="D163" s="716" t="n"/>
+      <c r="E163" s="716" t="n"/>
+      <c r="F163" s="708" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="82" t="n"/>
-      <c r="B164" s="716" t="n"/>
-      <c r="C164" s="716" t="n"/>
-      <c r="D164" s="716" t="n"/>
-      <c r="E164" s="716" t="n"/>
-      <c r="F164" s="708" t="n"/>
+      <c r="A164" s="182" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B164" s="703" t="inlineStr">
+        <is>
+          <t>INSTALACIONES ELÉCTRICAS</t>
+        </is>
+      </c>
+      <c r="C164" s="567" t="n"/>
+      <c r="D164" s="567" t="n"/>
+      <c r="E164" s="567" t="n"/>
+      <c r="F164" s="567" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="182" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B165" s="703" t="inlineStr">
-        <is>
-          <t>INSTALACIONES ELÉCTRICAS</t>
-        </is>
-      </c>
-      <c r="C165" s="567" t="n"/>
-      <c r="D165" s="567" t="n"/>
-      <c r="E165" s="567" t="n"/>
-      <c r="F165" s="567" t="n"/>
+      <c r="A165" s="80" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="B165" s="364" t="inlineStr">
+        <is>
+          <t>Tubería/conduit eléctrica</t>
+        </is>
+      </c>
+      <c r="C165" s="257" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D165" s="258" t="n"/>
+      <c r="E165" s="1451" t="n"/>
+      <c r="F165" s="1453">
+        <f>D165*E165</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="80" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="B166" s="364" t="inlineStr">
         <is>
-          <t>Tubería/conduit eléctrica</t>
+          <t>Bandejas portacables</t>
         </is>
       </c>
       <c r="C166" s="257" t="inlineStr">
@@ -14619,17 +14619,17 @@
     <row r="167">
       <c r="A167" s="80" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="B167" s="364" t="inlineStr">
         <is>
-          <t>Bandejas portacables</t>
+          <t>Cajas eléctricas</t>
         </is>
       </c>
       <c r="C167" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D167" s="258" t="n"/>
@@ -14642,17 +14642,17 @@
     <row r="168">
       <c r="A168" s="80" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="B168" s="364" t="inlineStr">
         <is>
-          <t>Cajas eléctricas</t>
+          <t>Cableado de fuerza</t>
         </is>
       </c>
       <c r="C168" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D168" s="258" t="n"/>
@@ -14665,12 +14665,12 @@
     <row r="169">
       <c r="A169" s="80" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="B169" s="364" t="inlineStr">
         <is>
-          <t>Cableado de fuerza</t>
+          <t>Cableado de iluminación</t>
         </is>
       </c>
       <c r="C169" s="257" t="inlineStr">
@@ -14688,17 +14688,17 @@
     <row r="170">
       <c r="A170" s="80" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="B170" s="364" t="inlineStr">
         <is>
-          <t>Cableado de iluminación</t>
+          <t>Tableros eléctricos</t>
         </is>
       </c>
       <c r="C170" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D170" s="258" t="n"/>
@@ -14711,12 +14711,12 @@
     <row r="171">
       <c r="A171" s="80" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="B171" s="364" t="inlineStr">
         <is>
-          <t>Tableros eléctricos</t>
+          <t>Tomacorrientes</t>
         </is>
       </c>
       <c r="C171" s="257" t="inlineStr">
@@ -14734,12 +14734,12 @@
     <row r="172">
       <c r="A172" s="80" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="B172" s="364" t="inlineStr">
         <is>
-          <t>Tomacorrientes</t>
+          <t>Interruptores</t>
         </is>
       </c>
       <c r="C172" s="257" t="inlineStr">
@@ -14757,12 +14757,12 @@
     <row r="173">
       <c r="A173" s="80" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="B173" s="364" t="inlineStr">
         <is>
-          <t>Interruptores</t>
+          <t>Luminarias</t>
         </is>
       </c>
       <c r="C173" s="257" t="inlineStr">
@@ -14780,17 +14780,17 @@
     <row r="174">
       <c r="A174" s="80" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="B174" s="364" t="inlineStr">
         <is>
-          <t>Luminarias</t>
+          <t>Sistema de puesta a tierra</t>
         </is>
       </c>
       <c r="C174" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D174" s="258" t="n"/>
@@ -14803,12 +14803,12 @@
     <row r="175">
       <c r="A175" s="80" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="B175" s="364" t="inlineStr">
         <is>
-          <t>Sistema de puesta a tierra</t>
+          <t>Pruebas y certificaciones</t>
         </is>
       </c>
       <c r="C175" s="257" t="inlineStr">
@@ -14824,81 +14824,81 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="80" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
-      </c>
-      <c r="B176" s="364" t="inlineStr">
-        <is>
-          <t>Pruebas y certificaciones</t>
-        </is>
-      </c>
-      <c r="C176" s="257" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D176" s="258" t="n"/>
-      <c r="E176" s="1451" t="n"/>
-      <c r="F176" s="1453">
-        <f>D176*E176</f>
+      <c r="A176" s="81" t="n"/>
+      <c r="B176" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 14 - INSTALACIONES ELÉCTRICAS</t>
+        </is>
+      </c>
+      <c r="C176" s="567" t="n"/>
+      <c r="D176" s="567" t="n"/>
+      <c r="E176" s="567" t="n"/>
+      <c r="F176" s="1454">
+        <f>SUM(F165:F175)</f>
         <v/>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="81" t="n"/>
-      <c r="B177" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 14 - INSTALACIONES ELÉCTRICAS</t>
-        </is>
-      </c>
-      <c r="C177" s="567" t="n"/>
-      <c r="D177" s="567" t="n"/>
-      <c r="E177" s="567" t="n"/>
-      <c r="F177" s="1454">
-        <f>SUM(F166:F176)</f>
-        <v/>
-      </c>
+      <c r="A177" s="82" t="n"/>
+      <c r="B177" s="716" t="n"/>
+      <c r="C177" s="716" t="n"/>
+      <c r="D177" s="716" t="n"/>
+      <c r="E177" s="716" t="n"/>
+      <c r="F177" s="708" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="82" t="n"/>
-      <c r="B178" s="716" t="n"/>
-      <c r="C178" s="716" t="n"/>
-      <c r="D178" s="716" t="n"/>
-      <c r="E178" s="716" t="n"/>
-      <c r="F178" s="708" t="n"/>
+      <c r="A178" s="182" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B178" s="703" t="inlineStr">
+        <is>
+          <t>COMUNICACIONES Y SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="C178" s="567" t="n"/>
+      <c r="D178" s="567" t="n"/>
+      <c r="E178" s="567" t="n"/>
+      <c r="F178" s="567" t="n"/>
     </row>
     <row r="179">
-      <c r="A179" s="182" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B179" s="703" t="inlineStr">
-        <is>
-          <t>COMUNICACIONES Y SEGURIDAD</t>
-        </is>
-      </c>
-      <c r="C179" s="567" t="n"/>
-      <c r="D179" s="567" t="n"/>
-      <c r="E179" s="567" t="n"/>
-      <c r="F179" s="567" t="n"/>
+      <c r="A179" s="80" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="B179" s="364" t="inlineStr">
+        <is>
+          <t>Cableado estructurado de datos</t>
+        </is>
+      </c>
+      <c r="C179" s="257" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D179" s="258" t="n"/>
+      <c r="E179" s="1451" t="n"/>
+      <c r="F179" s="1453">
+        <f>D179*E179</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="80" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="B180" s="364" t="inlineStr">
         <is>
-          <t>Cableado estructurado de datos</t>
+          <t>Rack de comunicaciones</t>
         </is>
       </c>
       <c r="C180" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D180" s="258" t="n"/>
@@ -14911,12 +14911,12 @@
     <row r="181">
       <c r="A181" s="80" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="B181" s="364" t="inlineStr">
         <is>
-          <t>Rack de comunicaciones</t>
+          <t>Cámaras y sistema CCTV</t>
         </is>
       </c>
       <c r="C181" s="257" t="inlineStr">
@@ -14934,12 +14934,12 @@
     <row r="182">
       <c r="A182" s="80" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="B182" s="364" t="inlineStr">
         <is>
-          <t>Cámaras y sistema CCTV</t>
+          <t>Control de acceso</t>
         </is>
       </c>
       <c r="C182" s="257" t="inlineStr">
@@ -14957,12 +14957,12 @@
     <row r="183">
       <c r="A183" s="80" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="B183" s="364" t="inlineStr">
         <is>
-          <t>Control de acceso</t>
+          <t>Sistema de citofonía</t>
         </is>
       </c>
       <c r="C183" s="257" t="inlineStr">
@@ -14980,17 +14980,17 @@
     <row r="184">
       <c r="A184" s="80" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.6</t>
         </is>
       </c>
       <c r="B184" s="364" t="inlineStr">
         <is>
-          <t>Sistema de citofonía</t>
+          <t>Sistema de detección de incendios</t>
         </is>
       </c>
       <c r="C184" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D184" s="258" t="n"/>
@@ -15001,81 +15001,81 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="80" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="B185" s="364" t="inlineStr">
-        <is>
-          <t>Sistema de detección de incendios</t>
-        </is>
-      </c>
-      <c r="C185" s="257" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D185" s="258" t="n"/>
-      <c r="E185" s="1451" t="n"/>
-      <c r="F185" s="1453">
-        <f>D185*E185</f>
+      <c r="A185" s="81" t="n"/>
+      <c r="B185" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 15 - COMUNICACIONES Y SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="C185" s="567" t="n"/>
+      <c r="D185" s="567" t="n"/>
+      <c r="E185" s="567" t="n"/>
+      <c r="F185" s="1454">
+        <f>SUM(F179:F184)</f>
         <v/>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="81" t="n"/>
-      <c r="B186" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 15 - COMUNICACIONES Y SEGURIDAD</t>
-        </is>
-      </c>
-      <c r="C186" s="567" t="n"/>
-      <c r="D186" s="567" t="n"/>
-      <c r="E186" s="567" t="n"/>
-      <c r="F186" s="1454">
-        <f>SUM(F180:F185)</f>
-        <v/>
-      </c>
+      <c r="A186" s="82" t="n"/>
+      <c r="B186" s="716" t="n"/>
+      <c r="C186" s="716" t="n"/>
+      <c r="D186" s="716" t="n"/>
+      <c r="E186" s="716" t="n"/>
+      <c r="F186" s="708" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="82" t="n"/>
-      <c r="B187" s="716" t="n"/>
-      <c r="C187" s="716" t="n"/>
-      <c r="D187" s="716" t="n"/>
-      <c r="E187" s="716" t="n"/>
-      <c r="F187" s="708" t="n"/>
+      <c r="A187" s="182" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B187" s="703" t="inlineStr">
+        <is>
+          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
+        </is>
+      </c>
+      <c r="C187" s="567" t="n"/>
+      <c r="D187" s="567" t="n"/>
+      <c r="E187" s="567" t="n"/>
+      <c r="F187" s="567" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="182" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B188" s="703" t="inlineStr">
-        <is>
-          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
-        </is>
-      </c>
-      <c r="C188" s="567" t="n"/>
-      <c r="D188" s="567" t="n"/>
-      <c r="E188" s="567" t="n"/>
-      <c r="F188" s="567" t="n"/>
+      <c r="A188" s="80" t="inlineStr">
+        <is>
+          <t>16.1</t>
+        </is>
+      </c>
+      <c r="B188" s="364" t="inlineStr">
+        <is>
+          <t>Equipos de aire acondicionado</t>
+        </is>
+      </c>
+      <c r="C188" s="257" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D188" s="258" t="n"/>
+      <c r="E188" s="1451" t="n"/>
+      <c r="F188" s="1453">
+        <f>D188*E188</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="80" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="B189" s="364" t="inlineStr">
         <is>
-          <t>Equipos de aire acondicionado</t>
+          <t>Ductos de ventilación</t>
         </is>
       </c>
       <c r="C189" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D189" s="258" t="n"/>
@@ -15088,17 +15088,17 @@
     <row r="190">
       <c r="A190" s="80" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="B190" s="364" t="inlineStr">
         <is>
-          <t>Ductos de ventilación</t>
+          <t>Tubería de refrigerante</t>
         </is>
       </c>
       <c r="C190" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D190" s="258" t="n"/>
@@ -15111,17 +15111,17 @@
     <row r="191">
       <c r="A191" s="80" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="B191" s="364" t="inlineStr">
         <is>
-          <t>Tubería de refrigerante</t>
+          <t>Rejillas y difusores</t>
         </is>
       </c>
       <c r="C191" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D191" s="258" t="n"/>
@@ -15132,81 +15132,81 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="80" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
-      <c r="B192" s="364" t="inlineStr">
-        <is>
-          <t>Rejillas y difusores</t>
-        </is>
-      </c>
-      <c r="C192" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D192" s="258" t="n"/>
-      <c r="E192" s="1451" t="n"/>
-      <c r="F192" s="1453">
-        <f>D192*E192</f>
+      <c r="A192" s="81" t="n"/>
+      <c r="B192" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 16 - CLIMATIZACIÓN Y VENTILACIÓN</t>
+        </is>
+      </c>
+      <c r="C192" s="567" t="n"/>
+      <c r="D192" s="567" t="n"/>
+      <c r="E192" s="567" t="n"/>
+      <c r="F192" s="1454">
+        <f>SUM(F188:F191)</f>
         <v/>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="81" t="n"/>
-      <c r="B193" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 16 - CLIMATIZACIÓN Y VENTILACIÓN</t>
-        </is>
-      </c>
-      <c r="C193" s="567" t="n"/>
-      <c r="D193" s="567" t="n"/>
-      <c r="E193" s="567" t="n"/>
-      <c r="F193" s="1454">
-        <f>SUM(F189:F192)</f>
-        <v/>
-      </c>
+      <c r="A193" s="82" t="n"/>
+      <c r="B193" s="716" t="n"/>
+      <c r="C193" s="716" t="n"/>
+      <c r="D193" s="716" t="n"/>
+      <c r="E193" s="716" t="n"/>
+      <c r="F193" s="708" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" s="82" t="n"/>
-      <c r="B194" s="716" t="n"/>
-      <c r="C194" s="716" t="n"/>
-      <c r="D194" s="716" t="n"/>
-      <c r="E194" s="716" t="n"/>
-      <c r="F194" s="708" t="n"/>
+      <c r="A194" s="182" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B194" s="703" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="C194" s="567" t="n"/>
+      <c r="D194" s="567" t="n"/>
+      <c r="E194" s="567" t="n"/>
+      <c r="F194" s="567" t="n"/>
     </row>
     <row r="195">
-      <c r="A195" s="182" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B195" s="703" t="inlineStr">
-        <is>
-          <t>GAS</t>
-        </is>
-      </c>
-      <c r="C195" s="567" t="n"/>
-      <c r="D195" s="567" t="n"/>
-      <c r="E195" s="567" t="n"/>
-      <c r="F195" s="567" t="n"/>
+      <c r="A195" s="80" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="B195" s="364" t="inlineStr">
+        <is>
+          <t>Red interna de gas</t>
+        </is>
+      </c>
+      <c r="C195" s="257" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D195" s="258" t="n"/>
+      <c r="E195" s="1451" t="n"/>
+      <c r="F195" s="1453">
+        <f>D195*E195</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="80" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="B196" s="364" t="inlineStr">
         <is>
-          <t>Red interna de gas</t>
+          <t>Válvulas y accesorios de gas</t>
         </is>
       </c>
       <c r="C196" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D196" s="258" t="n"/>
@@ -15219,17 +15219,17 @@
     <row r="197">
       <c r="A197" s="80" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="B197" s="364" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios de gas</t>
+          <t>Pruebas y certificación</t>
         </is>
       </c>
       <c r="C197" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D197" s="258" t="n"/>
@@ -15240,81 +15240,81 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="80" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="B198" s="364" t="inlineStr">
-        <is>
-          <t>Pruebas y certificación</t>
-        </is>
-      </c>
-      <c r="C198" s="257" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D198" s="258" t="n"/>
-      <c r="E198" s="1451" t="n"/>
-      <c r="F198" s="1453">
-        <f>D198*E198</f>
+      <c r="A198" s="81" t="n"/>
+      <c r="B198" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 17 - GAS</t>
+        </is>
+      </c>
+      <c r="C198" s="567" t="n"/>
+      <c r="D198" s="567" t="n"/>
+      <c r="E198" s="567" t="n"/>
+      <c r="F198" s="1454">
+        <f>SUM(F195:F197)</f>
         <v/>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="81" t="n"/>
-      <c r="B199" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 17 - GAS</t>
-        </is>
-      </c>
-      <c r="C199" s="567" t="n"/>
-      <c r="D199" s="567" t="n"/>
-      <c r="E199" s="567" t="n"/>
-      <c r="F199" s="1454">
-        <f>SUM(F196:F198)</f>
-        <v/>
-      </c>
+      <c r="A199" s="82" t="n"/>
+      <c r="B199" s="716" t="n"/>
+      <c r="C199" s="716" t="n"/>
+      <c r="D199" s="716" t="n"/>
+      <c r="E199" s="716" t="n"/>
+      <c r="F199" s="708" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="82" t="n"/>
-      <c r="B200" s="716" t="n"/>
-      <c r="C200" s="716" t="n"/>
-      <c r="D200" s="716" t="n"/>
-      <c r="E200" s="716" t="n"/>
-      <c r="F200" s="708" t="n"/>
+      <c r="A200" s="182" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B200" s="703" t="inlineStr">
+        <is>
+          <t>URBANISMO Y EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C200" s="567" t="n"/>
+      <c r="D200" s="567" t="n"/>
+      <c r="E200" s="567" t="n"/>
+      <c r="F200" s="567" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="182" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B201" s="703" t="inlineStr">
-        <is>
-          <t>URBANISMO Y EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C201" s="567" t="n"/>
-      <c r="D201" s="567" t="n"/>
-      <c r="E201" s="567" t="n"/>
-      <c r="F201" s="567" t="n"/>
+      <c r="A201" s="80" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="B201" s="364" t="inlineStr">
+        <is>
+          <t>Construcción de andenes</t>
+        </is>
+      </c>
+      <c r="C201" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D201" s="258" t="n"/>
+      <c r="E201" s="1451" t="n"/>
+      <c r="F201" s="1453">
+        <f>D201*E201</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="80" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="B202" s="364" t="inlineStr">
         <is>
-          <t>Construcción de andenes</t>
+          <t>Placas de concreto exteriores</t>
         </is>
       </c>
       <c r="C202" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D202" s="258" t="n"/>
@@ -15327,17 +15327,17 @@
     <row r="203">
       <c r="A203" s="80" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="B203" s="364" t="inlineStr">
         <is>
-          <t>Placas de concreto exteriores</t>
+          <t>Pavimento en adoquín</t>
         </is>
       </c>
       <c r="C203" s="257" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D203" s="258" t="n"/>
@@ -15350,17 +15350,17 @@
     <row r="204">
       <c r="A204" s="80" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="B204" s="364" t="inlineStr">
         <is>
-          <t>Pavimento en adoquín</t>
+          <t>Sardineles y bordillos</t>
         </is>
       </c>
       <c r="C204" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D204" s="258" t="n"/>
@@ -15373,17 +15373,17 @@
     <row r="205">
       <c r="A205" s="80" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="B205" s="364" t="inlineStr">
         <is>
-          <t>Sardineles y bordillos</t>
+          <t>Sumideros exteriores</t>
         </is>
       </c>
       <c r="C205" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D205" s="258" t="n"/>
@@ -15396,17 +15396,17 @@
     <row r="206">
       <c r="A206" s="80" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="B206" s="364" t="inlineStr">
         <is>
-          <t>Sumideros exteriores</t>
+          <t>Suministro y extendido de tierra vegetal</t>
         </is>
       </c>
       <c r="C206" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D206" s="258" t="n"/>
@@ -15419,17 +15419,17 @@
     <row r="207">
       <c r="A207" s="80" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="B207" s="364" t="inlineStr">
         <is>
-          <t>Suministro y extendido de tierra vegetal</t>
+          <t>Siembra y jardinería</t>
         </is>
       </c>
       <c r="C207" s="257" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D207" s="258" t="n"/>
@@ -15442,12 +15442,12 @@
     <row r="208">
       <c r="A208" s="80" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="B208" s="364" t="inlineStr">
         <is>
-          <t>Siembra y jardinería</t>
+          <t>Geotextil para drenaje y filtración</t>
         </is>
       </c>
       <c r="C208" s="257" t="inlineStr">
@@ -15465,17 +15465,17 @@
     <row r="209">
       <c r="A209" s="80" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="B209" s="364" t="inlineStr">
         <is>
-          <t>Geotextil para drenaje y filtración</t>
+          <t>Gaviones para obras de contención</t>
         </is>
       </c>
       <c r="C209" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D209" s="258" t="n"/>
@@ -15488,17 +15488,17 @@
     <row r="210">
       <c r="A210" s="80" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="B210" s="364" t="inlineStr">
         <is>
-          <t>Gaviones para obras de contención</t>
+          <t>Filtro francés (drenaje de terrenos)</t>
         </is>
       </c>
       <c r="C210" s="257" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D210" s="258" t="n"/>
@@ -15511,17 +15511,17 @@
     <row r="211">
       <c r="A211" s="80" t="inlineStr">
         <is>
-          <t>18.10</t>
+          <t>18.11</t>
         </is>
       </c>
       <c r="B211" s="364" t="inlineStr">
         <is>
-          <t>Filtro francés (drenaje de terrenos)</t>
+          <t>Revegetalización / empradización</t>
         </is>
       </c>
       <c r="C211" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D211" s="258" t="n"/>
@@ -15532,81 +15532,81 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="80" t="inlineStr">
-        <is>
-          <t>18.11</t>
-        </is>
-      </c>
-      <c r="B212" s="364" t="inlineStr">
-        <is>
-          <t>Revegetalización / empradización</t>
-        </is>
-      </c>
-      <c r="C212" s="257" t="inlineStr">
+      <c r="A212" s="81" t="n"/>
+      <c r="B212" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 18 - URBANISMO Y EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C212" s="567" t="n"/>
+      <c r="D212" s="567" t="n"/>
+      <c r="E212" s="567" t="n"/>
+      <c r="F212" s="1454">
+        <f>SUM(F201:F211)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="82" t="n"/>
+      <c r="B213" s="716" t="n"/>
+      <c r="C213" s="716" t="n"/>
+      <c r="D213" s="716" t="n"/>
+      <c r="E213" s="716" t="n"/>
+      <c r="F213" s="708" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="182" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B214" s="703" t="inlineStr">
+        <is>
+          <t>OBRAS COMPLEMENTARIAS</t>
+        </is>
+      </c>
+      <c r="C214" s="567" t="n"/>
+      <c r="D214" s="567" t="n"/>
+      <c r="E214" s="567" t="n"/>
+      <c r="F214" s="567" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="80" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="B215" s="364" t="inlineStr">
+        <is>
+          <t>Rejas metálicas</t>
+        </is>
+      </c>
+      <c r="C215" s="257" t="inlineStr">
         <is>
           <t>M²</t>
         </is>
       </c>
-      <c r="D212" s="258" t="n"/>
-      <c r="E212" s="1451" t="n"/>
-      <c r="F212" s="1453">
-        <f>D212*E212</f>
-        <v/>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="81" t="n"/>
-      <c r="B213" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 18 - URBANISMO Y EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C213" s="567" t="n"/>
-      <c r="D213" s="567" t="n"/>
-      <c r="E213" s="567" t="n"/>
-      <c r="F213" s="1454">
-        <f>SUM(F202:F212)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="82" t="n"/>
-      <c r="B214" s="716" t="n"/>
-      <c r="C214" s="716" t="n"/>
-      <c r="D214" s="716" t="n"/>
-      <c r="E214" s="716" t="n"/>
-      <c r="F214" s="708" t="n"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="182" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B215" s="703" t="inlineStr">
-        <is>
-          <t>OBRAS COMPLEMENTARIAS</t>
-        </is>
-      </c>
-      <c r="C215" s="567" t="n"/>
-      <c r="D215" s="567" t="n"/>
-      <c r="E215" s="567" t="n"/>
-      <c r="F215" s="567" t="n"/>
+      <c r="D215" s="258" t="n"/>
+      <c r="E215" s="1451" t="n"/>
+      <c r="F215" s="1453">
+        <f>D215*E215</f>
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="80" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="B216" s="364" t="inlineStr">
         <is>
-          <t>Rejas metálicas</t>
+          <t>Escaleras metálicas</t>
         </is>
       </c>
       <c r="C216" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D216" s="258" t="n"/>
@@ -15619,12 +15619,12 @@
     <row r="217">
       <c r="A217" s="80" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="B217" s="364" t="inlineStr">
         <is>
-          <t>Escaleras metálicas</t>
+          <t>Elementos metálicos especiales</t>
         </is>
       </c>
       <c r="C217" s="257" t="inlineStr">
@@ -15642,17 +15642,17 @@
     <row r="218">
       <c r="A218" s="80" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="B218" s="364" t="inlineStr">
         <is>
-          <t>Elementos metálicos especiales</t>
+          <t>Mobiliario fijo de obra</t>
         </is>
       </c>
       <c r="C218" s="257" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D218" s="258" t="n"/>
@@ -15663,76 +15663,76 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="80" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="B219" s="364" t="inlineStr">
-        <is>
-          <t>Mobiliario fijo de obra</t>
-        </is>
-      </c>
-      <c r="C219" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D219" s="258" t="n"/>
-      <c r="E219" s="1451" t="n"/>
-      <c r="F219" s="1453">
-        <f>D219*E219</f>
+      <c r="A219" s="81" t="n"/>
+      <c r="B219" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 19 - OBRAS COMPLEMENTARIAS</t>
+        </is>
+      </c>
+      <c r="C219" s="567" t="n"/>
+      <c r="D219" s="567" t="n"/>
+      <c r="E219" s="567" t="n"/>
+      <c r="F219" s="1454">
+        <f>SUM(F215:F218)</f>
         <v/>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="81" t="n"/>
-      <c r="B220" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 19 - OBRAS COMPLEMENTARIAS</t>
-        </is>
-      </c>
-      <c r="C220" s="567" t="n"/>
-      <c r="D220" s="567" t="n"/>
-      <c r="E220" s="567" t="n"/>
-      <c r="F220" s="1454">
-        <f>SUM(F216:F219)</f>
-        <v/>
-      </c>
+      <c r="A220" s="82" t="n"/>
+      <c r="B220" s="716" t="n"/>
+      <c r="C220" s="716" t="n"/>
+      <c r="D220" s="716" t="n"/>
+      <c r="E220" s="716" t="n"/>
+      <c r="F220" s="708" t="n"/>
     </row>
     <row r="221">
-      <c r="A221" s="82" t="n"/>
-      <c r="B221" s="716" t="n"/>
-      <c r="C221" s="716" t="n"/>
-      <c r="D221" s="716" t="n"/>
-      <c r="E221" s="716" t="n"/>
-      <c r="F221" s="708" t="n"/>
+      <c r="A221" s="182" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B221" s="703" t="inlineStr">
+        <is>
+          <t>ASEO, ENTREGA Y CIERRE</t>
+        </is>
+      </c>
+      <c r="C221" s="567" t="n"/>
+      <c r="D221" s="567" t="n"/>
+      <c r="E221" s="567" t="n"/>
+      <c r="F221" s="567" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="182" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B222" s="703" t="inlineStr">
-        <is>
-          <t>ASEO, ENTREGA Y CIERRE</t>
-        </is>
-      </c>
-      <c r="C222" s="567" t="n"/>
-      <c r="D222" s="567" t="n"/>
-      <c r="E222" s="567" t="n"/>
-      <c r="F222" s="567" t="n"/>
+      <c r="A222" s="80" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="B222" s="364" t="inlineStr">
+        <is>
+          <t>Limpieza gruesa y fina de obra</t>
+        </is>
+      </c>
+      <c r="C222" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D222" s="258" t="n"/>
+      <c r="E222" s="1451" t="n"/>
+      <c r="F222" s="1453">
+        <f>D222*E222</f>
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="80" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="B223" s="364" t="inlineStr">
         <is>
-          <t>Limpieza gruesa y fina de obra</t>
+          <t>Limpieza final para entrega</t>
         </is>
       </c>
       <c r="C223" s="257" t="inlineStr">
@@ -15750,17 +15750,17 @@
     <row r="224">
       <c r="A224" s="80" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="B224" s="364" t="inlineStr">
         <is>
-          <t>Limpieza final para entrega</t>
+          <t>Pruebas, puesta en marcha y ajustes</t>
         </is>
       </c>
       <c r="C224" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D224" s="258" t="n"/>
@@ -15773,12 +15773,12 @@
     <row r="225">
       <c r="A225" s="80" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="B225" s="364" t="inlineStr">
         <is>
-          <t>Pruebas, puesta en marcha y ajustes</t>
+          <t>Actualización de planos récord / as-built</t>
         </is>
       </c>
       <c r="C225" s="257" t="inlineStr">
@@ -15796,12 +15796,12 @@
     <row r="226">
       <c r="A226" s="80" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="B226" s="364" t="inlineStr">
         <is>
-          <t>Actualización de planos récord / as-built</t>
+          <t>Entrega, manuales y acta de recibo</t>
         </is>
       </c>
       <c r="C226" s="257" t="inlineStr">
@@ -15817,138 +15817,138 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="80" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="B227" s="364" t="inlineStr">
-        <is>
-          <t>Entrega, manuales y acta de recibo</t>
-        </is>
-      </c>
-      <c r="C227" s="257" t="inlineStr">
+      <c r="A227" s="81" t="n"/>
+      <c r="B227" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 20 - ASEO, ENTREGA Y CIERRE</t>
+        </is>
+      </c>
+      <c r="C227" s="567" t="n"/>
+      <c r="D227" s="567" t="n"/>
+      <c r="E227" s="567" t="n"/>
+      <c r="F227" s="1454">
+        <f>SUM(F222:F226)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="82" t="n"/>
+      <c r="B228" s="716" t="n"/>
+      <c r="C228" s="716" t="n"/>
+      <c r="D228" s="716" t="n"/>
+      <c r="E228" s="716" t="n"/>
+      <c r="F228" s="708" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="182" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B229" s="703" t="inlineStr">
+        <is>
+          <t>ASCENSORES</t>
+        </is>
+      </c>
+      <c r="C229" s="567" t="n"/>
+      <c r="D229" s="567" t="n"/>
+      <c r="E229" s="567" t="n"/>
+      <c r="F229" s="567" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="80" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="B230" s="364" t="inlineStr">
+        <is>
+          <t>Suministro e instalación de ascensor eléctrico</t>
+        </is>
+      </c>
+      <c r="C230" s="257" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D230" s="258" t="n"/>
+      <c r="E230" s="1451" t="n"/>
+      <c r="F230" s="1453">
+        <f>D230*E230</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="81" t="n"/>
+      <c r="B231" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 21 - ASCENSORES</t>
+        </is>
+      </c>
+      <c r="C231" s="567" t="n"/>
+      <c r="D231" s="567" t="n"/>
+      <c r="E231" s="567" t="n"/>
+      <c r="F231" s="1454">
+        <f>SUM(F230:F230)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="82" t="n"/>
+      <c r="B232" s="716" t="n"/>
+      <c r="C232" s="716" t="n"/>
+      <c r="D232" s="716" t="n"/>
+      <c r="E232" s="716" t="n"/>
+      <c r="F232" s="708" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="182" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B233" s="703" t="inlineStr">
+        <is>
+          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="C233" s="567" t="n"/>
+      <c r="D233" s="567" t="n"/>
+      <c r="E233" s="567" t="n"/>
+      <c r="F233" s="567" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="80" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="B234" s="364" t="inlineStr">
+        <is>
+          <t>Estudio de suelos y geotecnia</t>
+        </is>
+      </c>
+      <c r="C234" s="257" t="inlineStr">
         <is>
           <t>GL</t>
         </is>
       </c>
-      <c r="D227" s="258" t="n"/>
-      <c r="E227" s="1451" t="n"/>
-      <c r="F227" s="1453">
-        <f>D227*E227</f>
-        <v/>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="81" t="n"/>
-      <c r="B228" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 20 - ASEO, ENTREGA Y CIERRE</t>
-        </is>
-      </c>
-      <c r="C228" s="567" t="n"/>
-      <c r="D228" s="567" t="n"/>
-      <c r="E228" s="567" t="n"/>
-      <c r="F228" s="1454">
-        <f>SUM(F223:F227)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="82" t="n"/>
-      <c r="B229" s="716" t="n"/>
-      <c r="C229" s="716" t="n"/>
-      <c r="D229" s="716" t="n"/>
-      <c r="E229" s="716" t="n"/>
-      <c r="F229" s="708" t="n"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="182" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B230" s="703" t="inlineStr">
-        <is>
-          <t>ASCENSORES</t>
-        </is>
-      </c>
-      <c r="C230" s="567" t="n"/>
-      <c r="D230" s="567" t="n"/>
-      <c r="E230" s="567" t="n"/>
-      <c r="F230" s="567" t="n"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="80" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
-      <c r="B231" s="364" t="inlineStr">
-        <is>
-          <t>Suministro e instalación de ascensor eléctrico</t>
-        </is>
-      </c>
-      <c r="C231" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D231" s="258" t="n"/>
-      <c r="E231" s="1451" t="n"/>
-      <c r="F231" s="1453">
-        <f>D231*E231</f>
-        <v/>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="81" t="n"/>
-      <c r="B232" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 21 - ASCENSORES</t>
-        </is>
-      </c>
-      <c r="C232" s="567" t="n"/>
-      <c r="D232" s="567" t="n"/>
-      <c r="E232" s="567" t="n"/>
-      <c r="F232" s="1454">
-        <f>SUM(F231:F231)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="82" t="n"/>
-      <c r="B233" s="716" t="n"/>
-      <c r="C233" s="716" t="n"/>
-      <c r="D233" s="716" t="n"/>
-      <c r="E233" s="716" t="n"/>
-      <c r="F233" s="708" t="n"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="182" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B234" s="703" t="inlineStr">
-        <is>
-          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
-        </is>
-      </c>
-      <c r="C234" s="567" t="n"/>
-      <c r="D234" s="567" t="n"/>
-      <c r="E234" s="567" t="n"/>
-      <c r="F234" s="567" t="n"/>
+      <c r="D234" s="258" t="n"/>
+      <c r="E234" s="1451" t="n"/>
+      <c r="F234" s="1453">
+        <f>D234*E234</f>
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="80" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="B235" s="364" t="inlineStr">
         <is>
-          <t>Estudio de suelos y geotecnia</t>
+          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
         </is>
       </c>
       <c r="C235" s="257" t="inlineStr">
@@ -15966,12 +15966,12 @@
     <row r="236">
       <c r="A236" s="80" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="B236" s="364" t="inlineStr">
         <is>
-          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
+          <t>Licencia de construcción y trámites de curaduría urbana</t>
         </is>
       </c>
       <c r="C236" s="257" t="inlineStr">
@@ -15989,12 +15989,12 @@
     <row r="237">
       <c r="A237" s="80" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="B237" s="364" t="inlineStr">
         <is>
-          <t>Licencia de construcción y trámites de curaduría urbana</t>
+          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
         </is>
       </c>
       <c r="C237" s="257" t="inlineStr">
@@ -16010,89 +16010,84 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="80" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="B238" s="364" t="inlineStr">
-        <is>
-          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
-        </is>
-      </c>
-      <c r="C238" s="257" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D238" s="258" t="n"/>
-      <c r="E238" s="1451" t="n"/>
-      <c r="F238" s="1453">
-        <f>D238*E238</f>
+      <c r="A238" s="81" t="n"/>
+      <c r="B238" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 22 - GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="C238" s="567" t="n"/>
+      <c r="D238" s="567" t="n"/>
+      <c r="E238" s="567" t="n"/>
+      <c r="F238" s="1454">
+        <f>SUM(F234:F237)</f>
         <v/>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="81" t="n"/>
-      <c r="B239" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 22 - GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
-        </is>
-      </c>
-      <c r="C239" s="567" t="n"/>
-      <c r="D239" s="567" t="n"/>
-      <c r="E239" s="567" t="n"/>
-      <c r="F239" s="1454">
-        <f>SUM(F235:F238)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="82" t="n"/>
-      <c r="B240" s="716" t="n"/>
-      <c r="C240" s="716" t="n"/>
-      <c r="D240" s="716" t="n"/>
-      <c r="E240" s="716" t="n"/>
-      <c r="F240" s="708" t="n"/>
-    </row>
-    <row r="241" ht="15" customHeight="1" s="550">
-      <c r="A241" s="83" t="n"/>
-      <c r="B241" s="715" t="inlineStr">
+      <c r="A239" s="82" t="n"/>
+      <c r="B239" s="716" t="n"/>
+      <c r="C239" s="716" t="n"/>
+      <c r="D239" s="716" t="n"/>
+      <c r="E239" s="716" t="n"/>
+      <c r="F239" s="708" t="n"/>
+    </row>
+    <row r="240" ht="15" customHeight="1" s="550">
+      <c r="A240" s="83" t="n"/>
+      <c r="B240" s="715" t="inlineStr">
         <is>
           <t>COSTO DIRECTO TOTAL (suma de capítulos 1 a 22)</t>
         </is>
       </c>
-      <c r="C241" s="567" t="n"/>
-      <c r="D241" s="567" t="n"/>
-      <c r="E241" s="567" t="n"/>
-      <c r="F241" s="1456">
-        <f>F25+F39+F49+F69+F81+F93+F100+F106+F120+F130+F141+F148+F163+F177+F186+F193+F199+F213+F220+F228+F232+F239</f>
-        <v/>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="84" t="n"/>
-      <c r="B242" s="28" t="n"/>
-      <c r="C242" s="28" t="n"/>
-      <c r="D242" s="28" t="n"/>
-      <c r="E242" s="28" t="n"/>
-      <c r="F242" s="85" t="n"/>
+      <c r="C240" s="567" t="n"/>
+      <c r="D240" s="567" t="n"/>
+      <c r="E240" s="567" t="n"/>
+      <c r="F240" s="1456">
+        <f>F25+F39+F50+F68+F80+F92+F99+F105+F119+F129+F140+F147+F162+F176+F185+F192+F198+F212+F219+F227+F231+F238</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="84" t="n"/>
+      <c r="B241" s="28" t="n"/>
+      <c r="C241" s="28" t="n"/>
+      <c r="D241" s="28" t="n"/>
+      <c r="E241" s="28" t="n"/>
+      <c r="F241" s="85" t="n"/>
+    </row>
+    <row r="242" ht="15" customHeight="1" s="550">
+      <c r="A242" s="82" t="n"/>
+      <c r="B242" s="46" t="inlineStr">
+        <is>
+          <t>Administración (A)</t>
+        </is>
+      </c>
+      <c r="C242" s="716" t="n"/>
+      <c r="D242" s="716" t="n"/>
+      <c r="E242" s="1314">
+        <f>'Ficha Técnica del Proyecto'!$B$29</f>
+        <v/>
+      </c>
+      <c r="F242" s="1457">
+        <f>F240*E242</f>
+        <v/>
+      </c>
     </row>
     <row r="243" ht="15" customHeight="1" s="550">
       <c r="A243" s="82" t="n"/>
       <c r="B243" s="46" t="inlineStr">
         <is>
-          <t>Administración (A)</t>
+          <t>Imprevistos (I)</t>
         </is>
       </c>
       <c r="C243" s="716" t="n"/>
       <c r="D243" s="716" t="n"/>
       <c r="E243" s="1314">
-        <f>'Ficha Técnica del Proyecto'!$B$29</f>
+        <f>'Ficha Técnica del Proyecto'!$B$30</f>
         <v/>
       </c>
       <c r="F243" s="1457">
-        <f>F241*E243</f>
+        <f>F240*E243</f>
         <v/>
       </c>
     </row>
@@ -16100,50 +16095,47 @@
       <c r="A244" s="82" t="n"/>
       <c r="B244" s="46" t="inlineStr">
         <is>
-          <t>Imprevistos (I)</t>
+          <t>Utilidad (U)</t>
         </is>
       </c>
       <c r="C244" s="716" t="n"/>
       <c r="D244" s="716" t="n"/>
       <c r="E244" s="1314">
-        <f>'Ficha Técnica del Proyecto'!$B$30</f>
+        <f>'Ficha Técnica del Proyecto'!$B$31</f>
         <v/>
       </c>
       <c r="F244" s="1457">
-        <f>F241*E244</f>
+        <f>F240*E244</f>
         <v/>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1" s="550">
-      <c r="A245" s="82" t="n"/>
-      <c r="B245" s="46" t="inlineStr">
-        <is>
-          <t>Utilidad (U)</t>
-        </is>
-      </c>
-      <c r="C245" s="716" t="n"/>
-      <c r="D245" s="716" t="n"/>
-      <c r="E245" s="1314">
-        <f>'Ficha Técnica del Proyecto'!$B$31</f>
-        <v/>
-      </c>
-      <c r="F245" s="1457">
-        <f>F241*E245</f>
+      <c r="A245" s="81" t="n"/>
+      <c r="B245" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL AIU (A+I+U)</t>
+        </is>
+      </c>
+      <c r="C245" s="29" t="n"/>
+      <c r="D245" s="29" t="n"/>
+      <c r="E245" s="30" t="n"/>
+      <c r="F245" s="1454">
+        <f>F242+F243+F244</f>
         <v/>
       </c>
     </row>
     <row r="246" ht="15" customHeight="1" s="550">
-      <c r="A246" s="81" t="n"/>
-      <c r="B246" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL AIU (A+I+U)</t>
-        </is>
-      </c>
-      <c r="C246" s="29" t="n"/>
-      <c r="D246" s="29" t="n"/>
-      <c r="E246" s="30" t="n"/>
-      <c r="F246" s="1454">
-        <f>F243+F244+F245</f>
+      <c r="A246" s="82" t="n"/>
+      <c r="B246" s="46" t="inlineStr">
+        <is>
+          <t>COSTO DIRECTO + AIU</t>
+        </is>
+      </c>
+      <c r="C246" s="716" t="n"/>
+      <c r="D246" s="716" t="n"/>
+      <c r="E246" s="47" t="n"/>
+      <c r="F246" s="1457">
+        <f>F240+F245</f>
         <v/>
       </c>
     </row>
@@ -16151,110 +16143,103 @@
       <c r="A247" s="82" t="n"/>
       <c r="B247" s="46" t="inlineStr">
         <is>
-          <t>COSTO DIRECTO + AIU</t>
+          <t>IVA sobre Utilidad (19%)</t>
         </is>
       </c>
       <c r="C247" s="716" t="n"/>
       <c r="D247" s="716" t="n"/>
-      <c r="E247" s="47" t="n"/>
+      <c r="E247" s="1314">
+        <f>'Ficha Técnica del Proyecto'!$B$32</f>
+        <v/>
+      </c>
       <c r="F247" s="1457">
-        <f>F241+F246</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248" ht="15" customHeight="1" s="550">
+        <f>F244*E247</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248">
       <c r="A248" s="82" t="n"/>
-      <c r="B248" s="46" t="inlineStr">
-        <is>
-          <t>IVA sobre Utilidad (19%)</t>
-        </is>
-      </c>
+      <c r="B248" s="716" t="n"/>
       <c r="C248" s="716" t="n"/>
       <c r="D248" s="716" t="n"/>
-      <c r="E248" s="1314">
-        <f>'Ficha Técnica del Proyecto'!$B$32</f>
-        <v/>
-      </c>
-      <c r="F248" s="1457">
-        <f>F245*E248</f>
-        <v/>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="82" t="n"/>
-      <c r="B249" s="716" t="n"/>
-      <c r="C249" s="716" t="n"/>
-      <c r="D249" s="716" t="n"/>
-      <c r="E249" s="716" t="n"/>
-      <c r="F249" s="708" t="n"/>
-    </row>
-    <row r="250" ht="24" customHeight="1" s="550">
-      <c r="A250" s="86" t="n"/>
-      <c r="B250" s="703" t="inlineStr">
+      <c r="E248" s="716" t="n"/>
+      <c r="F248" s="708" t="n"/>
+    </row>
+    <row r="249" ht="24" customHeight="1" s="550">
+      <c r="A249" s="86" t="n"/>
+      <c r="B249" s="703" t="inlineStr">
         <is>
           <t>PRESUPUESTO TOTAL DE OBRA</t>
         </is>
       </c>
-      <c r="C250" s="567" t="n"/>
-      <c r="D250" s="567" t="n"/>
-      <c r="E250" s="567" t="n"/>
-      <c r="F250" s="1458">
-        <f>F247+F248</f>
+      <c r="C249" s="567" t="n"/>
+      <c r="D249" s="567" t="n"/>
+      <c r="E249" s="567" t="n"/>
+      <c r="F249" s="1458">
+        <f>F246+F247</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="87" t="n"/>
+      <c r="B250" s="203" t="inlineStr">
+        <is>
+          <t>REV. 10/09/2026</t>
+        </is>
+      </c>
+      <c r="C250" s="277" t="n"/>
+      <c r="D250" s="277" t="n"/>
+      <c r="E250" s="277" t="n"/>
+      <c r="F250" s="345">
+        <f>F6</f>
         <v/>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="87" t="n"/>
-      <c r="B251" s="203" t="inlineStr">
-        <is>
-          <t>REV. 10/09/2026</t>
-        </is>
-      </c>
+      <c r="B251" s="203" t="n"/>
       <c r="C251" s="277" t="n"/>
       <c r="D251" s="277" t="n"/>
       <c r="E251" s="277" t="n"/>
-      <c r="F251" s="345">
-        <f>F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252">
+      <c r="F251" s="201" t="n"/>
+    </row>
+    <row r="252" ht="15" customHeight="1" s="550">
       <c r="A252" s="87" t="n"/>
-      <c r="B252" s="203" t="n"/>
-      <c r="C252" s="277" t="n"/>
-      <c r="D252" s="277" t="n"/>
-      <c r="E252" s="277" t="n"/>
-      <c r="F252" s="201" t="n"/>
+      <c r="B252" s="89" t="inlineStr">
+        <is>
+          <t>Costo por m² construido (sobre Costo Directo Total)</t>
+        </is>
+      </c>
+      <c r="C252" s="90" t="n"/>
+      <c r="D252" s="90" t="n"/>
+      <c r="E252" s="90" t="n"/>
+      <c r="F252" s="1459">
+        <f>F240/'Ficha Técnica del Proyecto'!$B$21</f>
+        <v/>
+      </c>
     </row>
     <row r="253" ht="15" customHeight="1" s="550">
-      <c r="A253" s="87" t="n"/>
-      <c r="B253" s="89" t="inlineStr">
-        <is>
-          <t>Costo por m² construido (sobre Costo Directo Total)</t>
-        </is>
-      </c>
-      <c r="C253" s="90" t="n"/>
-      <c r="D253" s="90" t="n"/>
-      <c r="E253" s="90" t="n"/>
-      <c r="F253" s="1459">
-        <f>F241/'Ficha Técnica del Proyecto'!$B$21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="254" ht="15" customHeight="1" s="550">
-      <c r="A254" s="88" t="n"/>
-      <c r="B254" s="91" t="inlineStr">
+      <c r="A253" s="88" t="n"/>
+      <c r="B253" s="91" t="inlineStr">
         <is>
           <t>Costo por m² construido (sobre Presupuesto Total)</t>
         </is>
       </c>
-      <c r="C254" s="92" t="n"/>
-      <c r="D254" s="92" t="n"/>
-      <c r="E254" s="92" t="n"/>
-      <c r="F254" s="1460">
-        <f>F250/'Ficha Técnica del Proyecto'!$B$21</f>
-        <v/>
-      </c>
+      <c r="C253" s="92" t="n"/>
+      <c r="D253" s="92" t="n"/>
+      <c r="E253" s="92" t="n"/>
+      <c r="F253" s="1460">
+        <f>F249/'Ficha Técnica del Proyecto'!$B$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="27" t="n"/>
+      <c r="B254" s="277" t="n"/>
+      <c r="C254" s="277" t="n"/>
+      <c r="D254" s="277" t="n"/>
+      <c r="E254" s="277" t="n"/>
+      <c r="F254" s="277" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="27" t="n"/>
@@ -16296,78 +16281,70 @@
       <c r="E259" s="277" t="n"/>
       <c r="F259" s="277" t="n"/>
     </row>
-    <row r="260">
-      <c r="A260" s="27" t="n"/>
-      <c r="B260" s="277" t="n"/>
-      <c r="C260" s="277" t="n"/>
-      <c r="D260" s="277" t="n"/>
-      <c r="E260" s="277" t="n"/>
-      <c r="F260" s="277" t="n"/>
-    </row>
   </sheetData>
   <autoFilter ref="A13:F238"/>
   <mergeCells count="61">
+    <mergeCell ref="B233:F233"/>
+    <mergeCell ref="B106:F106"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B165:F165"/>
+    <mergeCell ref="B200:F200"/>
+    <mergeCell ref="B194:F194"/>
+    <mergeCell ref="B192:E192"/>
+    <mergeCell ref="B92:E92"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B68:E68"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B177:E177"/>
-    <mergeCell ref="B241:E241"/>
-    <mergeCell ref="B122:F122"/>
-    <mergeCell ref="B215:F215"/>
-    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B121:F121"/>
+    <mergeCell ref="B80:E80"/>
     <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B102:F102"/>
-    <mergeCell ref="B213:E213"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B214:F214"/>
+    <mergeCell ref="B198:E198"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B163:E163"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B195:F195"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B130:F130"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B129:E129"/>
     <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B229:F229"/>
+    <mergeCell ref="B227:E227"/>
+    <mergeCell ref="B185:E185"/>
+    <mergeCell ref="B107:F107"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B81:E81"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B141:E141"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B232:E232"/>
-    <mergeCell ref="B199:E199"/>
-    <mergeCell ref="B193:E193"/>
-    <mergeCell ref="B93:E93"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="B82:F82"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B140:E140"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="B234:F234"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B228:E228"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B230:F230"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B219:E219"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B240:E240"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B187:F187"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="B201:F201"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B250:E250"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B119:E119"/>
     <mergeCell ref="C1:F3"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B222:F222"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B186:E186"/>
+    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B249:E249"/>
+    <mergeCell ref="B162:E162"/>
+    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="B221:F221"/>
     <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B188:F188"/>
   </mergeCells>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.5118110236220472" footer="0.5118110236220472"/>
   <pageSetup orientation="portrait" paperSize="9" scale="53" horizontalDpi="300" verticalDpi="300"/>

--- a/public/plantilla-presupuesto.xlsx
+++ b/public/plantilla-presupuesto.xlsx
@@ -11253,7 +11253,6 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11285,12 +11284,13 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
   </mergeCells>
@@ -11306,7 +11306,7 @@
     <tabColor rgb="FF2E7D32"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F259"/>
+  <dimension ref="A1:F253"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" style="614" min="1" max="1"/>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="B42" s="364" t="inlineStr">
         <is>
-          <t>Concreto de f'c = 175 kg/cm² (2500 PSI), incluye vaciado y vibrado</t>
+          <t>Concreto de f'c = 175 kg/cm² (2500 PSI), incluye vaciado</t>
         </is>
       </c>
       <c r="C42" s="257" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B43" s="364" t="inlineStr">
         <is>
-          <t>Concreto ciclópeo, incluye vaciado y vibrado</t>
+          <t>Concreto ciclópeo, incluye vaciado</t>
         </is>
       </c>
       <c r="C43" s="257" t="inlineStr">
@@ -12233,76 +12233,76 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="80" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="B49" s="364" t="inlineStr">
-        <is>
-          <t>Formaleta para elementos de cimentación</t>
-        </is>
-      </c>
-      <c r="C49" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D49" s="258" t="n"/>
-      <c r="E49" s="1451" t="n"/>
-      <c r="F49" s="1453">
-        <f>D49*E49</f>
+      <c r="A49" s="81" t="n"/>
+      <c r="B49" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 3 - CIMENTACIONES</t>
+        </is>
+      </c>
+      <c r="C49" s="567" t="n"/>
+      <c r="D49" s="567" t="n"/>
+      <c r="E49" s="567" t="n"/>
+      <c r="F49" s="1454">
+        <f>SUM(F42:F48)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="81" t="n"/>
-      <c r="B50" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 3 - CIMENTACIONES</t>
-        </is>
-      </c>
-      <c r="C50" s="567" t="n"/>
-      <c r="D50" s="567" t="n"/>
-      <c r="E50" s="567" t="n"/>
-      <c r="F50" s="1454">
-        <f>SUM(F42:F49)</f>
-        <v/>
-      </c>
+      <c r="A50" s="82" t="n"/>
+      <c r="B50" s="716" t="n"/>
+      <c r="C50" s="716" t="n"/>
+      <c r="D50" s="716" t="n"/>
+      <c r="E50" s="716" t="n"/>
+      <c r="F50" s="708" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="82" t="n"/>
-      <c r="B51" s="716" t="n"/>
-      <c r="C51" s="716" t="n"/>
-      <c r="D51" s="716" t="n"/>
-      <c r="E51" s="716" t="n"/>
-      <c r="F51" s="708" t="n"/>
+      <c r="A51" s="182" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B51" s="703" t="inlineStr">
+        <is>
+          <t>ESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="C51" s="567" t="n"/>
+      <c r="D51" s="567" t="n"/>
+      <c r="E51" s="567" t="n"/>
+      <c r="F51" s="567" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="182" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B52" s="703" t="inlineStr">
-        <is>
-          <t>ESTRUCTURA</t>
-        </is>
-      </c>
-      <c r="C52" s="567" t="n"/>
-      <c r="D52" s="567" t="n"/>
-      <c r="E52" s="567" t="n"/>
-      <c r="F52" s="567" t="n"/>
+      <c r="A52" s="80" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B52" s="364" t="inlineStr">
+        <is>
+          <t>Concreto de f'c = 210 kg/cm² (3000 PSI), incluye vaciado y vibrado</t>
+        </is>
+      </c>
+      <c r="C52" s="257" t="inlineStr">
+        <is>
+          <t>M³</t>
+        </is>
+      </c>
+      <c r="D52" s="258" t="n"/>
+      <c r="E52" s="1451" t="n"/>
+      <c r="F52" s="1453">
+        <f>D52*E52</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="80" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B53" s="364" t="inlineStr">
         <is>
-          <t>Concreto de f'c = 210 kg/cm² (3000 PSI), incluye vaciado y vibrado</t>
+          <t>Concreto de f'c = 280 kg/cm² (4000 PSI), incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="C53" s="257" t="inlineStr">
@@ -12320,12 +12320,12 @@
     <row r="54">
       <c r="A54" s="80" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="B54" s="364" t="inlineStr">
         <is>
-          <t>Concreto de f'c = 280 kg/cm² (4000 PSI), incluye vaciado y vibrado</t>
+          <t>Concreto de f'c = 350 kg/cm² (5000 PSI), incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="C54" s="257" t="inlineStr">
@@ -12343,12 +12343,12 @@
     <row r="55">
       <c r="A55" s="80" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="B55" s="364" t="inlineStr">
         <is>
-          <t>Concreto de f'c = 350 kg/cm² (5000 PSI), incluye vaciado y vibrado</t>
+          <t>Concreto de f'c = 420 kg/cm² (6000 PSI), incluye vaciado y vibrado</t>
         </is>
       </c>
       <c r="C55" s="257" t="inlineStr">
@@ -12366,17 +12366,17 @@
     <row r="56">
       <c r="A56" s="80" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="B56" s="364" t="inlineStr">
         <is>
-          <t>Concreto de f'c = 420 kg/cm² (6000 PSI), incluye vaciado y vibrado</t>
+          <t>Suministro, figurado y amarre de acero de refuerzo 60.000 PSI</t>
         </is>
       </c>
       <c r="C56" s="257" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D56" s="258" t="n"/>
@@ -12389,12 +12389,12 @@
     <row r="57">
       <c r="A57" s="80" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="B57" s="364" t="inlineStr">
         <is>
-          <t>Suministro, figurado y amarre de acero de refuerzo 60.000 PSI</t>
+          <t>Suministro, figurado y amarre de acero de refuerzo 37.000 PSI</t>
         </is>
       </c>
       <c r="C57" s="257" t="inlineStr">
@@ -12412,12 +12412,12 @@
     <row r="58">
       <c r="A58" s="80" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="B58" s="364" t="inlineStr">
         <is>
-          <t>Suministro, figurado y amarre de acero de refuerzo 37.000 PSI</t>
+          <t>Suministro y montaje de perfiles metálicos</t>
         </is>
       </c>
       <c r="C58" s="257" t="inlineStr">
@@ -12435,17 +12435,17 @@
     <row r="59">
       <c r="A59" s="80" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="B59" s="364" t="inlineStr">
         <is>
-          <t>Formaleta de columnas</t>
+          <t>Placas, pernos y conexiones metálicas</t>
         </is>
       </c>
       <c r="C59" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D59" s="258" t="n"/>
@@ -12458,12 +12458,12 @@
     <row r="60">
       <c r="A60" s="80" t="inlineStr">
         <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="B60" s="365" t="inlineStr">
-        <is>
-          <t>Formaleta de vigas</t>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="B60" s="364" t="inlineStr">
+        <is>
+          <t>Grouting cementoso para reparación estructural</t>
         </is>
       </c>
       <c r="C60" s="257" t="inlineStr">
@@ -12471,9 +12471,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D60" s="1449" t="n"/>
-      <c r="E60" s="1452" t="n"/>
-      <c r="F60" s="1455">
+      <c r="D60" s="258" t="n"/>
+      <c r="E60" s="1451" t="n"/>
+      <c r="F60" s="1453">
         <f>D60*E60</f>
         <v/>
       </c>
@@ -12481,12 +12481,12 @@
     <row r="61">
       <c r="A61" s="80" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="B61" s="364" t="inlineStr">
         <is>
-          <t>Formaleta de losas</t>
+          <t>Grouting epóxico para reparación estructural</t>
         </is>
       </c>
       <c r="C61" s="257" t="inlineStr">
@@ -12502,83 +12502,53 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="80" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="B62" s="364" t="inlineStr">
-        <is>
-          <t>Formaleta de escaleras</t>
-        </is>
-      </c>
-      <c r="C62" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D62" s="258" t="n"/>
-      <c r="E62" s="1451" t="n"/>
-      <c r="F62" s="1453">
-        <f>D62*E62</f>
+      <c r="A62" s="81" t="n"/>
+      <c r="B62" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 4 - ESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="C62" s="567" t="n"/>
+      <c r="D62" s="567" t="n"/>
+      <c r="E62" s="567" t="n"/>
+      <c r="F62" s="1454">
+        <f>SUM(F52:F61)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="80" t="inlineStr">
-        <is>
-          <t>4.11</t>
-        </is>
-      </c>
-      <c r="B63" s="364" t="inlineStr">
-        <is>
-          <t>Suministro y montaje de perfiles metálicos</t>
-        </is>
-      </c>
-      <c r="C63" s="257" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="D63" s="258" t="n"/>
-      <c r="E63" s="1451" t="n"/>
-      <c r="F63" s="1453">
-        <f>D63*E63</f>
-        <v/>
-      </c>
+      <c r="A63" s="82" t="n"/>
+      <c r="B63" s="716" t="n"/>
+      <c r="C63" s="716" t="n"/>
+      <c r="D63" s="716" t="n"/>
+      <c r="E63" s="716" t="n"/>
+      <c r="F63" s="708" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="80" t="inlineStr">
-        <is>
-          <t>4.12</t>
-        </is>
-      </c>
-      <c r="B64" s="364" t="inlineStr">
-        <is>
-          <t>Placas, pernos y conexiones metálicas</t>
-        </is>
-      </c>
-      <c r="C64" s="257" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="D64" s="258" t="n"/>
-      <c r="E64" s="1451" t="n"/>
-      <c r="F64" s="1453">
-        <f>D64*E64</f>
-        <v/>
-      </c>
+      <c r="A64" s="182" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B64" s="707" t="inlineStr">
+        <is>
+          <t>MAMPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="C64" s="609" t="n"/>
+      <c r="D64" s="609" t="n"/>
+      <c r="E64" s="609" t="n"/>
+      <c r="F64" s="610" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="80" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B65" s="364" t="inlineStr">
         <is>
-          <t>Grouting cementoso para reparación estructural</t>
+          <t>Mampostería en bloque de concreto</t>
         </is>
       </c>
       <c r="C65" s="257" t="inlineStr">
@@ -12596,12 +12566,12 @@
     <row r="66">
       <c r="A66" s="80" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B66" s="364" t="inlineStr">
         <is>
-          <t>Grouting epóxico para reparación estructural</t>
+          <t>Mampostería en ladrillo</t>
         </is>
       </c>
       <c r="C66" s="257" t="inlineStr">
@@ -12619,17 +12589,17 @@
     <row r="67">
       <c r="A67" s="80" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B67" s="364" t="inlineStr">
         <is>
-          <t>Concreto premezclado o de planta (suministro)</t>
+          <t>Mampostería estructural</t>
         </is>
       </c>
       <c r="C67" s="257" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D67" s="258" t="n"/>
@@ -12640,58 +12610,88 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="81" t="n"/>
-      <c r="B68" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 4 - ESTRUCTURA</t>
-        </is>
-      </c>
-      <c r="C68" s="567" t="n"/>
-      <c r="D68" s="567" t="n"/>
-      <c r="E68" s="567" t="n"/>
-      <c r="F68" s="1454">
-        <f>SUM(F53:F67)</f>
+      <c r="A68" s="80" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="B68" s="364" t="inlineStr">
+        <is>
+          <t>Muros en sistema liviano / drywall</t>
+        </is>
+      </c>
+      <c r="C68" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D68" s="258" t="n"/>
+      <c r="E68" s="1451" t="n"/>
+      <c r="F68" s="1453">
+        <f>D68*E68</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="82" t="n"/>
-      <c r="B69" s="716" t="n"/>
-      <c r="C69" s="716" t="n"/>
-      <c r="D69" s="716" t="n"/>
-      <c r="E69" s="716" t="n"/>
-      <c r="F69" s="708" t="n"/>
+      <c r="A69" s="80" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="B69" s="364" t="inlineStr">
+        <is>
+          <t>Dinteles sobre vanos</t>
+        </is>
+      </c>
+      <c r="C69" s="257" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D69" s="258" t="n"/>
+      <c r="E69" s="1451" t="n"/>
+      <c r="F69" s="1453">
+        <f>D69*E69</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="182" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B70" s="707" t="inlineStr">
-        <is>
-          <t>MAMPOSTERÍA</t>
-        </is>
-      </c>
-      <c r="C70" s="609" t="n"/>
-      <c r="D70" s="609" t="n"/>
-      <c r="E70" s="609" t="n"/>
-      <c r="F70" s="610" t="n"/>
+      <c r="A70" s="80" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="B70" s="364" t="inlineStr">
+        <is>
+          <t>Alfajías y remates</t>
+        </is>
+      </c>
+      <c r="C70" s="257" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D70" s="258" t="n"/>
+      <c r="E70" s="1451" t="n"/>
+      <c r="F70" s="1453">
+        <f>D70*E70</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="80" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="B71" s="364" t="inlineStr">
         <is>
-          <t>Mampostería en bloque de concreto</t>
+          <t>Anclajes y refuerzos de mampostería</t>
         </is>
       </c>
       <c r="C71" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D71" s="258" t="n"/>
@@ -12704,12 +12704,12 @@
     <row r="72">
       <c r="A72" s="80" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="B72" s="364" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo</t>
+          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
         </is>
       </c>
       <c r="C72" s="257" t="inlineStr">
@@ -12727,12 +12727,12 @@
     <row r="73">
       <c r="A73" s="80" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="B73" s="364" t="inlineStr">
         <is>
-          <t>Mampostería estructural</t>
+          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
         </is>
       </c>
       <c r="C73" s="257" t="inlineStr">
@@ -12748,93 +12748,63 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="80" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="B74" s="364" t="inlineStr">
-        <is>
-          <t>Muros en sistema liviano / drywall</t>
-        </is>
-      </c>
-      <c r="C74" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D74" s="258" t="n"/>
-      <c r="E74" s="1451" t="n"/>
-      <c r="F74" s="1453">
-        <f>D74*E74</f>
+      <c r="A74" s="81" t="n"/>
+      <c r="B74" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 5 - MAMPOSTERÍA</t>
+        </is>
+      </c>
+      <c r="C74" s="567" t="n"/>
+      <c r="D74" s="567" t="n"/>
+      <c r="E74" s="567" t="n"/>
+      <c r="F74" s="1454">
+        <f>SUM(F65:F73)</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="80" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="B75" s="364" t="inlineStr">
-        <is>
-          <t>Dinteles sobre vanos</t>
-        </is>
-      </c>
-      <c r="C75" s="257" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D75" s="258" t="n"/>
-      <c r="E75" s="1451" t="n"/>
-      <c r="F75" s="1453">
-        <f>D75*E75</f>
-        <v/>
-      </c>
+      <c r="A75" s="82" t="n"/>
+      <c r="B75" s="716" t="n"/>
+      <c r="C75" s="567" t="n"/>
+      <c r="D75" s="567" t="n"/>
+      <c r="E75" s="567" t="n"/>
+      <c r="F75" s="708" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="80" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="B76" s="364" t="inlineStr">
-        <is>
-          <t>Alfajías y remates</t>
-        </is>
-      </c>
-      <c r="C76" s="257" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D76" s="258" t="n"/>
-      <c r="E76" s="1451" t="n"/>
-      <c r="F76" s="1453">
-        <f>D76*E76</f>
-        <v/>
-      </c>
+      <c r="A76" s="182" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B76" s="717" t="inlineStr">
+        <is>
+          <t>CUBIERTAS</t>
+        </is>
+      </c>
+      <c r="C76" s="567" t="n"/>
+      <c r="D76" s="567" t="n"/>
+      <c r="E76" s="567" t="n"/>
+      <c r="F76" s="567" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="80" t="inlineStr">
         <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="B77" s="364" t="inlineStr">
-        <is>
-          <t>Anclajes y refuerzos de mampostería</t>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B77" s="365" t="inlineStr">
+        <is>
+          <t>Estructura metálica o de madera para cubierta</t>
         </is>
       </c>
       <c r="C77" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D77" s="258" t="n"/>
-      <c r="E77" s="1451" t="n"/>
-      <c r="F77" s="1453">
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D77" s="1449" t="n"/>
+      <c r="E77" s="1452" t="n"/>
+      <c r="F77" s="1455">
         <f>D77*E77</f>
         <v/>
       </c>
@@ -12842,17 +12812,17 @@
     <row r="78">
       <c r="A78" s="80" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B78" s="364" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
+          <t>Cerchas y elementos estructurales</t>
         </is>
       </c>
       <c r="C78" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D78" s="258" t="n"/>
@@ -12865,12 +12835,12 @@
     <row r="79">
       <c r="A79" s="80" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B79" s="364" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
+          <t>Suministro e instalación de teja</t>
         </is>
       </c>
       <c r="C79" s="257" t="inlineStr">
@@ -12886,63 +12856,93 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="81" t="n"/>
-      <c r="B80" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 5 - MAMPOSTERÍA</t>
-        </is>
-      </c>
-      <c r="C80" s="567" t="n"/>
-      <c r="D80" s="567" t="n"/>
-      <c r="E80" s="567" t="n"/>
-      <c r="F80" s="1454">
-        <f>SUM(F71:F79)</f>
+      <c r="A80" s="80" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="B80" s="364" t="inlineStr">
+        <is>
+          <t>Impermeabilización de cubierta</t>
+        </is>
+      </c>
+      <c r="C80" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D80" s="258" t="n"/>
+      <c r="E80" s="1451" t="n"/>
+      <c r="F80" s="1453">
+        <f>D80*E80</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="82" t="n"/>
-      <c r="B81" s="716" t="n"/>
-      <c r="C81" s="567" t="n"/>
-      <c r="D81" s="567" t="n"/>
-      <c r="E81" s="567" t="n"/>
-      <c r="F81" s="708" t="n"/>
+      <c r="A81" s="80" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="B81" s="364" t="inlineStr">
+        <is>
+          <t>Aislamiento térmico/acústico</t>
+        </is>
+      </c>
+      <c r="C81" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D81" s="258" t="n"/>
+      <c r="E81" s="1451" t="n"/>
+      <c r="F81" s="1453">
+        <f>D81*E81</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="182" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B82" s="717" t="inlineStr">
-        <is>
-          <t>CUBIERTAS</t>
-        </is>
-      </c>
-      <c r="C82" s="567" t="n"/>
-      <c r="D82" s="567" t="n"/>
-      <c r="E82" s="567" t="n"/>
-      <c r="F82" s="567" t="n"/>
+      <c r="A82" s="80" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="B82" s="364" t="inlineStr">
+        <is>
+          <t>Canales de aguas lluvias</t>
+        </is>
+      </c>
+      <c r="C82" s="257" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D82" s="258" t="n"/>
+      <c r="E82" s="1451" t="n"/>
+      <c r="F82" s="1453">
+        <f>D82*E82</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="80" t="inlineStr">
         <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B83" s="365" t="inlineStr">
-        <is>
-          <t>Estructura metálica o de madera para cubierta</t>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="B83" s="364" t="inlineStr">
+        <is>
+          <t>Bajantes de aguas lluvias</t>
         </is>
       </c>
       <c r="C83" s="257" t="inlineStr">
         <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="D83" s="1449" t="n"/>
-      <c r="E83" s="1452" t="n"/>
-      <c r="F83" s="1455">
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D83" s="258" t="n"/>
+      <c r="E83" s="1451" t="n"/>
+      <c r="F83" s="1453">
         <f>D83*E83</f>
         <v/>
       </c>
@@ -12950,17 +12950,17 @@
     <row r="84">
       <c r="A84" s="80" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="B84" s="364" t="inlineStr">
         <is>
-          <t>Cerchas y elementos estructurales</t>
+          <t>Cielo raso Dry Wall</t>
         </is>
       </c>
       <c r="C84" s="257" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D84" s="258" t="n"/>
@@ -12973,12 +12973,12 @@
     <row r="85">
       <c r="A85" s="80" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="B85" s="364" t="inlineStr">
         <is>
-          <t>Suministro e instalación de teja</t>
+          <t>Cielo raso en lámina acústica de fibra mineral</t>
         </is>
       </c>
       <c r="C85" s="257" t="inlineStr">
@@ -12994,88 +12994,58 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="80" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="B86" s="364" t="inlineStr">
-        <is>
-          <t>Impermeabilización de cubierta</t>
-        </is>
-      </c>
-      <c r="C86" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D86" s="258" t="n"/>
-      <c r="E86" s="1451" t="n"/>
-      <c r="F86" s="1453">
-        <f>D86*E86</f>
+      <c r="A86" s="81" t="n"/>
+      <c r="B86" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 6 - CUBIERTAS</t>
+        </is>
+      </c>
+      <c r="C86" s="567" t="n"/>
+      <c r="D86" s="567" t="n"/>
+      <c r="E86" s="567" t="n"/>
+      <c r="F86" s="1454">
+        <f>SUM(F77:F85)</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="80" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="B87" s="364" t="inlineStr">
-        <is>
-          <t>Aislamiento térmico/acústico</t>
-        </is>
-      </c>
-      <c r="C87" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D87" s="258" t="n"/>
-      <c r="E87" s="1451" t="n"/>
-      <c r="F87" s="1453">
-        <f>D87*E87</f>
-        <v/>
-      </c>
+      <c r="A87" s="82" t="n"/>
+      <c r="B87" s="716" t="n"/>
+      <c r="C87" s="716" t="n"/>
+      <c r="D87" s="716" t="n"/>
+      <c r="E87" s="716" t="n"/>
+      <c r="F87" s="708" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="80" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="B88" s="364" t="inlineStr">
-        <is>
-          <t>Canales de aguas lluvias</t>
-        </is>
-      </c>
-      <c r="C88" s="257" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D88" s="258" t="n"/>
-      <c r="E88" s="1451" t="n"/>
-      <c r="F88" s="1453">
-        <f>D88*E88</f>
-        <v/>
-      </c>
+      <c r="A88" s="182" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B88" s="703" t="inlineStr">
+        <is>
+          <t>IMPERMEABILIZACIONES</t>
+        </is>
+      </c>
+      <c r="C88" s="567" t="n"/>
+      <c r="D88" s="567" t="n"/>
+      <c r="E88" s="567" t="n"/>
+      <c r="F88" s="567" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="80" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B89" s="364" t="inlineStr">
         <is>
-          <t>Bajantes de aguas lluvias</t>
+          <t>Impermeabilización de losas y terrazas</t>
         </is>
       </c>
       <c r="C89" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D89" s="258" t="n"/>
@@ -13088,12 +13058,12 @@
     <row r="90">
       <c r="A90" s="80" t="inlineStr">
         <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="B90" s="364" t="inlineStr">
-        <is>
-          <t>Cielo raso Dry Wall</t>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B90" s="365" t="inlineStr">
+        <is>
+          <t>Impermeabilización de muros</t>
         </is>
       </c>
       <c r="C90" s="257" t="inlineStr">
@@ -13101,9 +13071,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D90" s="258" t="n"/>
-      <c r="E90" s="1451" t="n"/>
-      <c r="F90" s="1453">
+      <c r="D90" s="1449" t="n"/>
+      <c r="E90" s="1452" t="n"/>
+      <c r="F90" s="1455">
         <f>D90*E90</f>
         <v/>
       </c>
@@ -13111,12 +13081,12 @@
     <row r="91">
       <c r="A91" s="80" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B91" s="364" t="inlineStr">
         <is>
-          <t>Cielo raso en lámina acústica de fibra mineral</t>
+          <t>Impermeabilización de zonas húmedas</t>
         </is>
       </c>
       <c r="C91" s="257" t="inlineStr">
@@ -13132,76 +13102,76 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="81" t="n"/>
-      <c r="B92" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 6 - CUBIERTAS</t>
-        </is>
-      </c>
-      <c r="C92" s="567" t="n"/>
-      <c r="D92" s="567" t="n"/>
-      <c r="E92" s="567" t="n"/>
-      <c r="F92" s="1454">
-        <f>SUM(F83:F91)</f>
+      <c r="A92" s="80" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="B92" s="364" t="inlineStr">
+        <is>
+          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
+        </is>
+      </c>
+      <c r="C92" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D92" s="258" t="n"/>
+      <c r="E92" s="1451" t="n"/>
+      <c r="F92" s="1453">
+        <f>D92*E92</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="82" t="n"/>
-      <c r="B93" s="716" t="n"/>
-      <c r="C93" s="716" t="n"/>
-      <c r="D93" s="716" t="n"/>
-      <c r="E93" s="716" t="n"/>
-      <c r="F93" s="708" t="n"/>
+      <c r="A93" s="81" t="n"/>
+      <c r="B93" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 7 - IMPERMEABILIZACIONES</t>
+        </is>
+      </c>
+      <c r="C93" s="567" t="n"/>
+      <c r="D93" s="567" t="n"/>
+      <c r="E93" s="567" t="n"/>
+      <c r="F93" s="1454">
+        <f>SUM(F89:F92)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="182" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B94" s="703" t="inlineStr">
-        <is>
-          <t>IMPERMEABILIZACIONES</t>
-        </is>
-      </c>
+      <c r="A94" s="82" t="n"/>
+      <c r="B94" s="716" t="n"/>
       <c r="C94" s="567" t="n"/>
       <c r="D94" s="567" t="n"/>
       <c r="E94" s="567" t="n"/>
-      <c r="F94" s="567" t="n"/>
+      <c r="F94" s="708" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="80" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="B95" s="364" t="inlineStr">
-        <is>
-          <t>Impermeabilización de losas y terrazas</t>
-        </is>
-      </c>
-      <c r="C95" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D95" s="258" t="n"/>
-      <c r="E95" s="1451" t="n"/>
-      <c r="F95" s="1453">
-        <f>D95*E95</f>
-        <v/>
-      </c>
+      <c r="A95" s="182" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B95" s="703" t="inlineStr">
+        <is>
+          <t>PAÑETES Y REVOQUES</t>
+        </is>
+      </c>
+      <c r="C95" s="567" t="n"/>
+      <c r="D95" s="567" t="n"/>
+      <c r="E95" s="567" t="n"/>
+      <c r="F95" s="567" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="80" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="B96" s="365" t="inlineStr">
         <is>
-          <t>Impermeabilización de muros</t>
+          <t>Pañete / revoque interior</t>
         </is>
       </c>
       <c r="C96" s="257" t="inlineStr">
@@ -13219,12 +13189,12 @@
     <row r="97">
       <c r="A97" s="80" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="B97" s="364" t="inlineStr">
         <is>
-          <t>Impermeabilización de zonas húmedas</t>
+          <t>Pañete / revoque exterior</t>
         </is>
       </c>
       <c r="C97" s="257" t="inlineStr">
@@ -13242,12 +13212,12 @@
     <row r="98">
       <c r="A98" s="80" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="B98" s="364" t="inlineStr">
         <is>
-          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
+          <t>Pañete impermeabilizado</t>
         </is>
       </c>
       <c r="C98" s="257" t="inlineStr">
@@ -13266,34 +13236,34 @@
       <c r="A99" s="81" t="n"/>
       <c r="B99" s="704" t="inlineStr">
         <is>
-          <t>SUBTOTAL CAPÍTULO 7 - IMPERMEABILIZACIONES</t>
+          <t>SUBTOTAL CAPÍTULO 8 - PAÑETES Y REVOQUES</t>
         </is>
       </c>
       <c r="C99" s="567" t="n"/>
       <c r="D99" s="567" t="n"/>
       <c r="E99" s="567" t="n"/>
       <c r="F99" s="1454">
-        <f>SUM(F95:F98)</f>
+        <f>SUM(F96:F98)</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="82" t="n"/>
-      <c r="B100" s="716" t="n"/>
+      <c r="B100" s="708" t="n"/>
       <c r="C100" s="567" t="n"/>
       <c r="D100" s="567" t="n"/>
       <c r="E100" s="567" t="n"/>
-      <c r="F100" s="708" t="n"/>
+      <c r="F100" s="607" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="182" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B101" s="703" t="inlineStr">
         <is>
-          <t>PAÑETES Y REVOQUES</t>
+          <t>PISOS Y ENCHAPES</t>
         </is>
       </c>
       <c r="C101" s="567" t="n"/>
@@ -13304,12 +13274,12 @@
     <row r="102">
       <c r="A102" s="80" t="inlineStr">
         <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="B102" s="365" t="inlineStr">
-        <is>
-          <t>Pañete / revoque interior</t>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B102" s="364" t="inlineStr">
+        <is>
+          <t>Mortero de nivelación</t>
         </is>
       </c>
       <c r="C102" s="257" t="inlineStr">
@@ -13317,9 +13287,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D102" s="1449" t="n"/>
-      <c r="E102" s="1452" t="n"/>
-      <c r="F102" s="1455">
+      <c r="D102" s="258" t="n"/>
+      <c r="E102" s="1451" t="n"/>
+      <c r="F102" s="1453">
         <f>D102*E102</f>
         <v/>
       </c>
@@ -13327,12 +13297,12 @@
     <row r="103">
       <c r="A103" s="80" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="B103" s="364" t="inlineStr">
         <is>
-          <t>Pañete / revoque exterior</t>
+          <t>Piso cerámico</t>
         </is>
       </c>
       <c r="C103" s="257" t="inlineStr">
@@ -13350,12 +13320,12 @@
     <row r="104">
       <c r="A104" s="80" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="B104" s="364" t="inlineStr">
         <is>
-          <t>Pañete impermeabilizado</t>
+          <t>Piso en porcelanato</t>
         </is>
       </c>
       <c r="C104" s="257" t="inlineStr">
@@ -13371,58 +13341,88 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="81" t="n"/>
-      <c r="B105" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 8 - PAÑETES Y REVOQUES</t>
-        </is>
-      </c>
-      <c r="C105" s="567" t="n"/>
-      <c r="D105" s="567" t="n"/>
-      <c r="E105" s="567" t="n"/>
-      <c r="F105" s="1454">
-        <f>SUM(F102:F104)</f>
+      <c r="A105" s="80" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="B105" s="364" t="inlineStr">
+        <is>
+          <t>Piso vinílico</t>
+        </is>
+      </c>
+      <c r="C105" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D105" s="258" t="n"/>
+      <c r="E105" s="1451" t="n"/>
+      <c r="F105" s="1453">
+        <f>D105*E105</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="82" t="n"/>
-      <c r="B106" s="708" t="n"/>
-      <c r="C106" s="567" t="n"/>
-      <c r="D106" s="567" t="n"/>
-      <c r="E106" s="567" t="n"/>
-      <c r="F106" s="607" t="n"/>
+      <c r="A106" s="80" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="B106" s="364" t="inlineStr">
+        <is>
+          <t>Piso laminado</t>
+        </is>
+      </c>
+      <c r="C106" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D106" s="258" t="n"/>
+      <c r="E106" s="1451" t="n"/>
+      <c r="F106" s="1453">
+        <f>D106*E106</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="182" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B107" s="703" t="inlineStr">
-        <is>
-          <t>PISOS Y ENCHAPES</t>
-        </is>
-      </c>
-      <c r="C107" s="567" t="n"/>
-      <c r="D107" s="567" t="n"/>
-      <c r="E107" s="567" t="n"/>
-      <c r="F107" s="567" t="n"/>
+      <c r="A107" s="80" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="B107" s="364" t="inlineStr">
+        <is>
+          <t>Enchape cerámico en muros</t>
+        </is>
+      </c>
+      <c r="C107" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D107" s="1449" t="n"/>
+      <c r="E107" s="1452" t="n"/>
+      <c r="F107" s="1453">
+        <f>D107*E107</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="80" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="B108" s="364" t="inlineStr">
         <is>
-          <t>Mortero de nivelación</t>
+          <t>Guardaescoba</t>
         </is>
       </c>
       <c r="C108" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D108" s="258" t="n"/>
@@ -13435,22 +13435,22 @@
     <row r="109">
       <c r="A109" s="80" t="inlineStr">
         <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="B109" s="364" t="inlineStr">
-        <is>
-          <t>Piso cerámico</t>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="B109" s="365" t="inlineStr">
+        <is>
+          <t>Juntas de dilatación / construcción</t>
         </is>
       </c>
       <c r="C109" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D109" s="258" t="n"/>
-      <c r="E109" s="1451" t="n"/>
-      <c r="F109" s="1453">
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D109" s="1449" t="n"/>
+      <c r="E109" s="1452" t="n"/>
+      <c r="F109" s="1455">
         <f>D109*E109</f>
         <v/>
       </c>
@@ -13458,12 +13458,12 @@
     <row r="110">
       <c r="A110" s="80" t="inlineStr">
         <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="B110" s="364" t="inlineStr">
-        <is>
-          <t>Piso en porcelanato</t>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="B110" s="365" t="inlineStr">
+        <is>
+          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
         </is>
       </c>
       <c r="C110" s="257" t="inlineStr">
@@ -13471,9 +13471,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D110" s="258" t="n"/>
-      <c r="E110" s="1451" t="n"/>
-      <c r="F110" s="1453">
+      <c r="D110" s="1449" t="n"/>
+      <c r="E110" s="1452" t="n"/>
+      <c r="F110" s="1455">
         <f>D110*E110</f>
         <v/>
       </c>
@@ -13481,12 +13481,12 @@
     <row r="111">
       <c r="A111" s="80" t="inlineStr">
         <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="B111" s="364" t="inlineStr">
-        <is>
-          <t>Piso vinílico</t>
+          <t>9.10</t>
+        </is>
+      </c>
+      <c r="B111" s="365" t="inlineStr">
+        <is>
+          <t>Baldosa de granito</t>
         </is>
       </c>
       <c r="C111" s="257" t="inlineStr">
@@ -13494,9 +13494,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D111" s="258" t="n"/>
-      <c r="E111" s="1451" t="n"/>
-      <c r="F111" s="1453">
+      <c r="D111" s="1449" t="n"/>
+      <c r="E111" s="1452" t="n"/>
+      <c r="F111" s="1455">
         <f>D111*E111</f>
         <v/>
       </c>
@@ -13504,12 +13504,12 @@
     <row r="112">
       <c r="A112" s="80" t="inlineStr">
         <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="B112" s="364" t="inlineStr">
-        <is>
-          <t>Piso laminado</t>
+          <t>9.11</t>
+        </is>
+      </c>
+      <c r="B112" s="365" t="inlineStr">
+        <is>
+          <t>Enchape en granito pulido</t>
         </is>
       </c>
       <c r="C112" s="257" t="inlineStr">
@@ -13517,91 +13517,61 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D112" s="258" t="n"/>
-      <c r="E112" s="1451" t="n"/>
-      <c r="F112" s="1453">
+      <c r="D112" s="1449" t="n"/>
+      <c r="E112" s="1452" t="n"/>
+      <c r="F112" s="1455">
         <f>D112*E112</f>
         <v/>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="80" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="B113" s="364" t="inlineStr">
-        <is>
-          <t>Enchape cerámico en muros</t>
-        </is>
-      </c>
-      <c r="C113" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D113" s="1449" t="n"/>
-      <c r="E113" s="1452" t="n"/>
-      <c r="F113" s="1453">
-        <f>D113*E113</f>
+      <c r="A113" s="81" t="n"/>
+      <c r="B113" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 9 - PISOS Y ENCHAPES</t>
+        </is>
+      </c>
+      <c r="C113" s="567" t="n"/>
+      <c r="D113" s="567" t="n"/>
+      <c r="E113" s="567" t="n"/>
+      <c r="F113" s="1454">
+        <f>SUM(F102:F112)</f>
         <v/>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="80" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="B114" s="364" t="inlineStr">
-        <is>
-          <t>Guardaescoba</t>
-        </is>
-      </c>
-      <c r="C114" s="257" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D114" s="258" t="n"/>
-      <c r="E114" s="1451" t="n"/>
-      <c r="F114" s="1453">
-        <f>D114*E114</f>
-        <v/>
-      </c>
+      <c r="A114" s="82" t="n"/>
+      <c r="B114" s="716" t="n"/>
+      <c r="C114" s="716" t="n"/>
+      <c r="D114" s="716" t="n"/>
+      <c r="E114" s="716" t="n"/>
+      <c r="F114" s="708" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="80" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="B115" s="365" t="inlineStr">
-        <is>
-          <t>Juntas de dilatación / construcción</t>
-        </is>
-      </c>
-      <c r="C115" s="257" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D115" s="1449" t="n"/>
-      <c r="E115" s="1452" t="n"/>
-      <c r="F115" s="1455">
-        <f>D115*E115</f>
-        <v/>
-      </c>
+      <c r="A115" s="182" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B115" s="703" t="inlineStr">
+        <is>
+          <t>PINTURA</t>
+        </is>
+      </c>
+      <c r="C115" s="567" t="n"/>
+      <c r="D115" s="567" t="n"/>
+      <c r="E115" s="567" t="n"/>
+      <c r="F115" s="567" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="80" t="inlineStr">
         <is>
-          <t>9.9</t>
-        </is>
-      </c>
-      <c r="B116" s="365" t="inlineStr">
-        <is>
-          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="B116" s="364" t="inlineStr">
+        <is>
+          <t>Pintura vinílica interior</t>
         </is>
       </c>
       <c r="C116" s="257" t="inlineStr">
@@ -13609,9 +13579,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D116" s="1449" t="n"/>
-      <c r="E116" s="1452" t="n"/>
-      <c r="F116" s="1455">
+      <c r="D116" s="258" t="n"/>
+      <c r="E116" s="1451" t="n"/>
+      <c r="F116" s="1453">
         <f>D116*E116</f>
         <v/>
       </c>
@@ -13619,12 +13589,12 @@
     <row r="117">
       <c r="A117" s="80" t="inlineStr">
         <is>
-          <t>9.10</t>
-        </is>
-      </c>
-      <c r="B117" s="365" t="inlineStr">
-        <is>
-          <t>Baldosa de granito</t>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="B117" s="364" t="inlineStr">
+        <is>
+          <t>Pintura exterior</t>
         </is>
       </c>
       <c r="C117" s="257" t="inlineStr">
@@ -13632,9 +13602,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D117" s="1449" t="n"/>
-      <c r="E117" s="1452" t="n"/>
-      <c r="F117" s="1455">
+      <c r="D117" s="258" t="n"/>
+      <c r="E117" s="1451" t="n"/>
+      <c r="F117" s="1453">
         <f>D117*E117</f>
         <v/>
       </c>
@@ -13642,12 +13612,12 @@
     <row r="118">
       <c r="A118" s="80" t="inlineStr">
         <is>
-          <t>9.11</t>
-        </is>
-      </c>
-      <c r="B118" s="365" t="inlineStr">
-        <is>
-          <t>Enchape en granito pulido</t>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="B118" s="364" t="inlineStr">
+        <is>
+          <t>Pintura esmalte en superficies metálicas/madera</t>
         </is>
       </c>
       <c r="C118" s="257" t="inlineStr">
@@ -13655,61 +13625,91 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D118" s="1449" t="n"/>
-      <c r="E118" s="1452" t="n"/>
-      <c r="F118" s="1455">
+      <c r="D118" s="258" t="n"/>
+      <c r="E118" s="1451" t="n"/>
+      <c r="F118" s="1453">
         <f>D118*E118</f>
         <v/>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="81" t="n"/>
-      <c r="B119" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 9 - PISOS Y ENCHAPES</t>
-        </is>
-      </c>
-      <c r="C119" s="567" t="n"/>
-      <c r="D119" s="567" t="n"/>
-      <c r="E119" s="567" t="n"/>
-      <c r="F119" s="1454">
-        <f>SUM(F108:F118)</f>
+      <c r="A119" s="80" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="B119" s="364" t="inlineStr">
+        <is>
+          <t>Pintura anticorrosiva</t>
+        </is>
+      </c>
+      <c r="C119" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D119" s="258" t="n"/>
+      <c r="E119" s="1451" t="n"/>
+      <c r="F119" s="1453">
+        <f>D119*E119</f>
         <v/>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="82" t="n"/>
-      <c r="B120" s="716" t="n"/>
-      <c r="C120" s="716" t="n"/>
-      <c r="D120" s="716" t="n"/>
-      <c r="E120" s="716" t="n"/>
-      <c r="F120" s="708" t="n"/>
+      <c r="A120" s="80" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="B120" s="364" t="inlineStr">
+        <is>
+          <t>Sellador / imprimante</t>
+        </is>
+      </c>
+      <c r="C120" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D120" s="1449" t="n"/>
+      <c r="E120" s="1452" t="n"/>
+      <c r="F120" s="1453">
+        <f>D120*E120</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="182" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B121" s="703" t="inlineStr">
-        <is>
-          <t>PINTURA</t>
-        </is>
-      </c>
-      <c r="C121" s="567" t="n"/>
-      <c r="D121" s="567" t="n"/>
-      <c r="E121" s="567" t="n"/>
-      <c r="F121" s="567" t="n"/>
+      <c r="A121" s="80" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="B121" s="364" t="inlineStr">
+        <is>
+          <t>Estuco plástico</t>
+        </is>
+      </c>
+      <c r="C121" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D121" s="1449" t="n"/>
+      <c r="E121" s="1452" t="n"/>
+      <c r="F121" s="1453">
+        <f>D121*E121</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="80" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="B122" s="364" t="inlineStr">
         <is>
-          <t>Pintura vinílica interior</t>
+          <t>Estuco tradicional</t>
         </is>
       </c>
       <c r="C122" s="257" t="inlineStr">
@@ -13717,100 +13717,70 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D122" s="258" t="n"/>
-      <c r="E122" s="1451" t="n"/>
+      <c r="D122" s="1449" t="n"/>
+      <c r="E122" s="1452" t="n"/>
       <c r="F122" s="1453">
         <f>D122*E122</f>
         <v/>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="80" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="B123" s="364" t="inlineStr">
-        <is>
-          <t>Pintura exterior</t>
-        </is>
-      </c>
-      <c r="C123" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D123" s="258" t="n"/>
-      <c r="E123" s="1451" t="n"/>
-      <c r="F123" s="1453">
-        <f>D123*E123</f>
+      <c r="A123" s="81" t="n"/>
+      <c r="B123" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 10 - PINTURA</t>
+        </is>
+      </c>
+      <c r="C123" s="567" t="n"/>
+      <c r="D123" s="567" t="n"/>
+      <c r="E123" s="567" t="n"/>
+      <c r="F123" s="1454">
+        <f>SUM(F116:F122)</f>
         <v/>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="80" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="B124" s="364" t="inlineStr">
-        <is>
-          <t>Pintura esmalte en superficies metálicas/madera</t>
-        </is>
-      </c>
-      <c r="C124" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D124" s="258" t="n"/>
-      <c r="E124" s="1451" t="n"/>
-      <c r="F124" s="1453">
-        <f>D124*E124</f>
-        <v/>
-      </c>
+      <c r="A124" s="82" t="n"/>
+      <c r="B124" s="708" t="n"/>
+      <c r="C124" s="567" t="n"/>
+      <c r="D124" s="567" t="n"/>
+      <c r="E124" s="567" t="n"/>
+      <c r="F124" s="607" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="80" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
-      </c>
-      <c r="B125" s="364" t="inlineStr">
-        <is>
-          <t>Pintura anticorrosiva</t>
-        </is>
-      </c>
-      <c r="C125" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D125" s="258" t="n"/>
-      <c r="E125" s="1451" t="n"/>
-      <c r="F125" s="1453">
-        <f>D125*E125</f>
-        <v/>
-      </c>
+      <c r="A125" s="182" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B125" s="703" t="inlineStr">
+        <is>
+          <t>CARPINTERÍA</t>
+        </is>
+      </c>
+      <c r="C125" s="567" t="n"/>
+      <c r="D125" s="567" t="n"/>
+      <c r="E125" s="567" t="n"/>
+      <c r="F125" s="567" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="80" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="B126" s="364" t="inlineStr">
         <is>
-          <t>Sellador / imprimante</t>
+          <t>Puertas de madera</t>
         </is>
       </c>
       <c r="C126" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D126" s="1449" t="n"/>
-      <c r="E126" s="1452" t="n"/>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D126" s="258" t="n"/>
+      <c r="E126" s="1451" t="n"/>
       <c r="F126" s="1453">
         <f>D126*E126</f>
         <v/>
@@ -13819,17 +13789,17 @@
     <row r="127">
       <c r="A127" s="80" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="B127" s="364" t="inlineStr">
         <is>
-          <t>Estuco plástico</t>
+          <t>Muebles fijos de madera</t>
         </is>
       </c>
       <c r="C127" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D127" s="1449" t="n"/>
@@ -13842,79 +13812,109 @@
     <row r="128">
       <c r="A128" s="80" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="B128" s="364" t="inlineStr">
         <is>
-          <t>Estuco tradicional</t>
+          <t>Puertas metálicas</t>
         </is>
       </c>
       <c r="C128" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D128" s="1449" t="n"/>
-      <c r="E128" s="1452" t="n"/>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D128" s="258" t="n"/>
+      <c r="E128" s="1451" t="n"/>
       <c r="F128" s="1453">
         <f>D128*E128</f>
         <v/>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="81" t="n"/>
-      <c r="B129" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 10 - PINTURA</t>
-        </is>
-      </c>
-      <c r="C129" s="567" t="n"/>
-      <c r="D129" s="567" t="n"/>
-      <c r="E129" s="567" t="n"/>
-      <c r="F129" s="1454">
-        <f>SUM(F122:F128)</f>
+      <c r="A129" s="80" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="B129" s="365" t="inlineStr">
+        <is>
+          <t>Barandas metálicas</t>
+        </is>
+      </c>
+      <c r="C129" s="257" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D129" s="1449" t="n"/>
+      <c r="E129" s="1452" t="n"/>
+      <c r="F129" s="1455">
+        <f>D129*E129</f>
         <v/>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="82" t="n"/>
-      <c r="B130" s="708" t="n"/>
-      <c r="C130" s="567" t="n"/>
-      <c r="D130" s="567" t="n"/>
-      <c r="E130" s="567" t="n"/>
-      <c r="F130" s="607" t="n"/>
+      <c r="A130" s="80" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="B130" s="364" t="inlineStr">
+        <is>
+          <t>Pasamanos</t>
+        </is>
+      </c>
+      <c r="C130" s="257" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D130" s="258" t="n"/>
+      <c r="E130" s="1451" t="n"/>
+      <c r="F130" s="1453">
+        <f>D130*E130</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="182" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B131" s="703" t="inlineStr">
-        <is>
-          <t>CARPINTERÍA</t>
-        </is>
-      </c>
-      <c r="C131" s="567" t="n"/>
-      <c r="D131" s="567" t="n"/>
-      <c r="E131" s="567" t="n"/>
-      <c r="F131" s="567" t="n"/>
+      <c r="A131" s="80" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="B131" s="364" t="inlineStr">
+        <is>
+          <t>Ventanas de aluminio</t>
+        </is>
+      </c>
+      <c r="C131" s="257" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D131" s="258" t="n"/>
+      <c r="E131" s="1451" t="n"/>
+      <c r="F131" s="1453">
+        <f>D131*E131</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="80" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="B132" s="364" t="inlineStr">
         <is>
-          <t>Puertas de madera</t>
+          <t>Divisiones de aluminio</t>
         </is>
       </c>
       <c r="C132" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D132" s="258" t="n"/>
@@ -13927,104 +13927,74 @@
     <row r="133">
       <c r="A133" s="80" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="B133" s="364" t="inlineStr">
         <is>
-          <t>Muebles fijos de madera</t>
+          <t>Puerta antipánico</t>
         </is>
       </c>
       <c r="C133" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D133" s="1449" t="n"/>
-      <c r="E133" s="1452" t="n"/>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D133" s="258" t="n"/>
+      <c r="E133" s="1451" t="n"/>
       <c r="F133" s="1453">
         <f>D133*E133</f>
         <v/>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="80" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
-      <c r="B134" s="364" t="inlineStr">
-        <is>
-          <t>Puertas metálicas</t>
-        </is>
-      </c>
-      <c r="C134" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D134" s="258" t="n"/>
-      <c r="E134" s="1451" t="n"/>
-      <c r="F134" s="1453">
-        <f>D134*E134</f>
+      <c r="A134" s="81" t="n"/>
+      <c r="B134" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 11 - CARPINTERÍA</t>
+        </is>
+      </c>
+      <c r="C134" s="567" t="n"/>
+      <c r="D134" s="567" t="n"/>
+      <c r="E134" s="567" t="n"/>
+      <c r="F134" s="1454">
+        <f>SUM(F126:F133)</f>
         <v/>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="80" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="B135" s="365" t="inlineStr">
-        <is>
-          <t>Barandas metálicas</t>
-        </is>
-      </c>
-      <c r="C135" s="257" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D135" s="1449" t="n"/>
-      <c r="E135" s="1452" t="n"/>
-      <c r="F135" s="1455">
-        <f>D135*E135</f>
-        <v/>
-      </c>
+      <c r="A135" s="82" t="n"/>
+      <c r="B135" s="716" t="n"/>
+      <c r="C135" s="716" t="n"/>
+      <c r="D135" s="716" t="n"/>
+      <c r="E135" s="716" t="n"/>
+      <c r="F135" s="708" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="80" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="B136" s="364" t="inlineStr">
-        <is>
-          <t>Pasamanos</t>
-        </is>
-      </c>
-      <c r="C136" s="257" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D136" s="258" t="n"/>
-      <c r="E136" s="1451" t="n"/>
-      <c r="F136" s="1453">
-        <f>D136*E136</f>
-        <v/>
-      </c>
+      <c r="A136" s="182" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B136" s="703" t="inlineStr">
+        <is>
+          <t>VIDRIOS</t>
+        </is>
+      </c>
+      <c r="C136" s="567" t="n"/>
+      <c r="D136" s="567" t="n"/>
+      <c r="E136" s="567" t="n"/>
+      <c r="F136" s="567" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="80" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="B137" s="364" t="inlineStr">
         <is>
-          <t>Ventanas de aluminio</t>
+          <t>Vidrio templado</t>
         </is>
       </c>
       <c r="C137" s="257" t="inlineStr">
@@ -14032,8 +14002,8 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D137" s="258" t="n"/>
-      <c r="E137" s="1451" t="n"/>
+      <c r="D137" s="1449" t="n"/>
+      <c r="E137" s="1452" t="n"/>
       <c r="F137" s="1453">
         <f>D137*E137</f>
         <v/>
@@ -14042,12 +14012,12 @@
     <row r="138">
       <c r="A138" s="80" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="B138" s="364" t="inlineStr">
         <is>
-          <t>Divisiones de aluminio</t>
+          <t>Vidrio laminado</t>
         </is>
       </c>
       <c r="C138" s="257" t="inlineStr">
@@ -14065,106 +14035,106 @@
     <row r="139">
       <c r="A139" s="80" t="inlineStr">
         <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="B139" s="364" t="inlineStr">
-        <is>
-          <t>Puerta antipánico</t>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="B139" s="365" t="inlineStr">
+        <is>
+          <t>Espejos</t>
         </is>
       </c>
       <c r="C139" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D139" s="258" t="n"/>
-      <c r="E139" s="1451" t="n"/>
-      <c r="F139" s="1453">
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D139" s="1449" t="n"/>
+      <c r="E139" s="1452" t="n"/>
+      <c r="F139" s="1455">
         <f>D139*E139</f>
         <v/>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="81" t="n"/>
-      <c r="B140" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 11 - CARPINTERÍA</t>
-        </is>
-      </c>
-      <c r="C140" s="567" t="n"/>
-      <c r="D140" s="567" t="n"/>
-      <c r="E140" s="567" t="n"/>
-      <c r="F140" s="1454">
-        <f>SUM(F132:F139)</f>
+      <c r="A140" s="80" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
+      </c>
+      <c r="B140" s="364" t="inlineStr">
+        <is>
+          <t>Sellos y silicona</t>
+        </is>
+      </c>
+      <c r="C140" s="257" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D140" s="258" t="n"/>
+      <c r="E140" s="1451" t="n"/>
+      <c r="F140" s="1453">
+        <f>D140*E140</f>
         <v/>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="82" t="n"/>
-      <c r="B141" s="716" t="n"/>
-      <c r="C141" s="716" t="n"/>
-      <c r="D141" s="716" t="n"/>
-      <c r="E141" s="716" t="n"/>
-      <c r="F141" s="708" t="n"/>
+      <c r="A141" s="81" t="n"/>
+      <c r="B141" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 12 - VIDRIOS</t>
+        </is>
+      </c>
+      <c r="C141" s="567" t="n"/>
+      <c r="D141" s="567" t="n"/>
+      <c r="E141" s="567" t="n"/>
+      <c r="F141" s="1454">
+        <f>SUM(F137:F140)</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="182" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B142" s="703" t="inlineStr">
-        <is>
-          <t>VIDRIOS</t>
-        </is>
-      </c>
-      <c r="C142" s="567" t="n"/>
-      <c r="D142" s="567" t="n"/>
-      <c r="E142" s="567" t="n"/>
-      <c r="F142" s="567" t="n"/>
+      <c r="A142" s="82" t="n"/>
+      <c r="B142" s="716" t="n"/>
+      <c r="C142" s="716" t="n"/>
+      <c r="D142" s="716" t="n"/>
+      <c r="E142" s="716" t="n"/>
+      <c r="F142" s="708" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="80" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="B143" s="364" t="inlineStr">
-        <is>
-          <t>Vidrio templado</t>
-        </is>
-      </c>
-      <c r="C143" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D143" s="1449" t="n"/>
-      <c r="E143" s="1452" t="n"/>
-      <c r="F143" s="1453">
-        <f>D143*E143</f>
-        <v/>
-      </c>
+      <c r="A143" s="182" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B143" s="703" t="inlineStr">
+        <is>
+          <t>INSTALACIONES HIDROSANITARIAS</t>
+        </is>
+      </c>
+      <c r="C143" s="567" t="n"/>
+      <c r="D143" s="567" t="n"/>
+      <c r="E143" s="567" t="n"/>
+      <c r="F143" s="567" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="80" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="B144" s="364" t="inlineStr">
         <is>
-          <t>Vidrio laminado</t>
+          <t>Tubería de agua fría</t>
         </is>
       </c>
       <c r="C144" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D144" s="258" t="n"/>
-      <c r="E144" s="1451" t="n"/>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D144" s="1449" t="n"/>
+      <c r="E144" s="1452" t="n"/>
       <c r="F144" s="1453">
         <f>D144*E144</f>
         <v/>
@@ -14173,22 +14143,22 @@
     <row r="145">
       <c r="A145" s="80" t="inlineStr">
         <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="B145" s="365" t="inlineStr">
-        <is>
-          <t>Espejos</t>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="B145" s="364" t="inlineStr">
+        <is>
+          <t>Tubería de agua caliente</t>
         </is>
       </c>
       <c r="C145" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D145" s="1449" t="n"/>
-      <c r="E145" s="1452" t="n"/>
-      <c r="F145" s="1455">
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D145" s="258" t="n"/>
+      <c r="E145" s="1451" t="n"/>
+      <c r="F145" s="1453">
         <f>D145*E145</f>
         <v/>
       </c>
@@ -14196,83 +14166,113 @@
     <row r="146">
       <c r="A146" s="80" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="B146" s="364" t="inlineStr">
         <is>
-          <t>Sellos y silicona</t>
+          <t>Válvulas y accesorios hidrosanitarios</t>
         </is>
       </c>
       <c r="C146" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D146" s="258" t="n"/>
-      <c r="E146" s="1451" t="n"/>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D146" s="1449" t="n"/>
+      <c r="E146" s="1452" t="n"/>
       <c r="F146" s="1453">
         <f>D146*E146</f>
         <v/>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="81" t="n"/>
-      <c r="B147" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 12 - VIDRIOS</t>
-        </is>
-      </c>
-      <c r="C147" s="567" t="n"/>
-      <c r="D147" s="567" t="n"/>
-      <c r="E147" s="567" t="n"/>
-      <c r="F147" s="1454">
-        <f>SUM(F143:F146)</f>
+      <c r="A147" s="80" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="B147" s="364" t="inlineStr">
+        <is>
+          <t>Tubería sanitaria</t>
+        </is>
+      </c>
+      <c r="C147" s="257" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D147" s="258" t="n"/>
+      <c r="E147" s="1451" t="n"/>
+      <c r="F147" s="1453">
+        <f>D147*E147</f>
         <v/>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="82" t="n"/>
-      <c r="B148" s="716" t="n"/>
-      <c r="C148" s="716" t="n"/>
-      <c r="D148" s="716" t="n"/>
-      <c r="E148" s="716" t="n"/>
-      <c r="F148" s="708" t="n"/>
+      <c r="A148" s="80" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="B148" s="364" t="inlineStr">
+        <is>
+          <t>Tubería de aguas lluvias</t>
+        </is>
+      </c>
+      <c r="C148" s="257" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D148" s="258" t="n"/>
+      <c r="E148" s="1451" t="n"/>
+      <c r="F148" s="1453">
+        <f>D148*E148</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="182" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B149" s="703" t="inlineStr">
-        <is>
-          <t>INSTALACIONES HIDROSANITARIAS</t>
-        </is>
-      </c>
-      <c r="C149" s="567" t="n"/>
-      <c r="D149" s="567" t="n"/>
-      <c r="E149" s="567" t="n"/>
-      <c r="F149" s="567" t="n"/>
+      <c r="A149" s="80" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="B149" s="364" t="inlineStr">
+        <is>
+          <t>Cajas de inspección</t>
+        </is>
+      </c>
+      <c r="C149" s="257" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D149" s="258" t="n"/>
+      <c r="E149" s="1451" t="n"/>
+      <c r="F149" s="1453">
+        <f>D149*E149</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="80" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="B150" s="364" t="inlineStr">
         <is>
-          <t>Tubería de agua fría</t>
+          <t>Aparatos sanitarios</t>
         </is>
       </c>
       <c r="C150" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D150" s="1449" t="n"/>
-      <c r="E150" s="1452" t="n"/>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D150" s="258" t="n"/>
+      <c r="E150" s="1451" t="n"/>
       <c r="F150" s="1453">
         <f>D150*E150</f>
         <v/>
@@ -14281,17 +14281,17 @@
     <row r="151">
       <c r="A151" s="80" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="B151" s="364" t="inlineStr">
         <is>
-          <t>Tubería de agua caliente</t>
+          <t>Lavamanos</t>
         </is>
       </c>
       <c r="C151" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D151" s="258" t="n"/>
@@ -14304,12 +14304,12 @@
     <row r="152">
       <c r="A152" s="80" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="B152" s="364" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios hidrosanitarios</t>
+          <t>Griferías</t>
         </is>
       </c>
       <c r="C152" s="257" t="inlineStr">
@@ -14317,8 +14317,8 @@
           <t>UND</t>
         </is>
       </c>
-      <c r="D152" s="1449" t="n"/>
-      <c r="E152" s="1452" t="n"/>
+      <c r="D152" s="258" t="n"/>
+      <c r="E152" s="1451" t="n"/>
       <c r="F152" s="1453">
         <f>D152*E152</f>
         <v/>
@@ -14327,17 +14327,17 @@
     <row r="153">
       <c r="A153" s="80" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="B153" s="364" t="inlineStr">
         <is>
-          <t>Tubería sanitaria</t>
+          <t>Duchas</t>
         </is>
       </c>
       <c r="C153" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D153" s="258" t="n"/>
@@ -14350,17 +14350,17 @@
     <row r="154">
       <c r="A154" s="80" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="B154" s="364" t="inlineStr">
         <is>
-          <t>Tubería de aguas lluvias</t>
+          <t>Pruebas hidráulicas y de estanqueidad</t>
         </is>
       </c>
       <c r="C154" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D154" s="258" t="n"/>
@@ -14373,12 +14373,12 @@
     <row r="155">
       <c r="A155" s="80" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="B155" s="364" t="inlineStr">
         <is>
-          <t>Cajas de inspección</t>
+          <t>Orinal institucional</t>
         </is>
       </c>
       <c r="C155" s="257" t="inlineStr">
@@ -14394,88 +14394,58 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="80" t="inlineStr">
-        <is>
-          <t>13.7</t>
-        </is>
-      </c>
-      <c r="B156" s="364" t="inlineStr">
-        <is>
-          <t>Aparatos sanitarios</t>
-        </is>
-      </c>
-      <c r="C156" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D156" s="258" t="n"/>
-      <c r="E156" s="1451" t="n"/>
-      <c r="F156" s="1453">
-        <f>D156*E156</f>
+      <c r="A156" s="81" t="n"/>
+      <c r="B156" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 13 - INSTALACIONES HIDROSANITARIAS</t>
+        </is>
+      </c>
+      <c r="C156" s="567" t="n"/>
+      <c r="D156" s="567" t="n"/>
+      <c r="E156" s="567" t="n"/>
+      <c r="F156" s="1454">
+        <f>SUM(F144:F155)</f>
         <v/>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="80" t="inlineStr">
-        <is>
-          <t>13.8</t>
-        </is>
-      </c>
-      <c r="B157" s="364" t="inlineStr">
-        <is>
-          <t>Lavamanos</t>
-        </is>
-      </c>
-      <c r="C157" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D157" s="258" t="n"/>
-      <c r="E157" s="1451" t="n"/>
-      <c r="F157" s="1453">
-        <f>D157*E157</f>
-        <v/>
-      </c>
+      <c r="A157" s="82" t="n"/>
+      <c r="B157" s="716" t="n"/>
+      <c r="C157" s="716" t="n"/>
+      <c r="D157" s="716" t="n"/>
+      <c r="E157" s="716" t="n"/>
+      <c r="F157" s="708" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="80" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
-      </c>
-      <c r="B158" s="364" t="inlineStr">
-        <is>
-          <t>Griferías</t>
-        </is>
-      </c>
-      <c r="C158" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D158" s="258" t="n"/>
-      <c r="E158" s="1451" t="n"/>
-      <c r="F158" s="1453">
-        <f>D158*E158</f>
-        <v/>
-      </c>
+      <c r="A158" s="182" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B158" s="703" t="inlineStr">
+        <is>
+          <t>INSTALACIONES ELÉCTRICAS</t>
+        </is>
+      </c>
+      <c r="C158" s="567" t="n"/>
+      <c r="D158" s="567" t="n"/>
+      <c r="E158" s="567" t="n"/>
+      <c r="F158" s="567" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="80" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="B159" s="364" t="inlineStr">
         <is>
-          <t>Duchas</t>
+          <t>Tubería/conduit eléctrica</t>
         </is>
       </c>
       <c r="C159" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D159" s="258" t="n"/>
@@ -14488,17 +14458,17 @@
     <row r="160">
       <c r="A160" s="80" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="B160" s="364" t="inlineStr">
         <is>
-          <t>Pruebas hidráulicas y de estanqueidad</t>
+          <t>Bandejas portacables</t>
         </is>
       </c>
       <c r="C160" s="257" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D160" s="258" t="n"/>
@@ -14511,12 +14481,12 @@
     <row r="161">
       <c r="A161" s="80" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="B161" s="364" t="inlineStr">
         <is>
-          <t>Orinal institucional</t>
+          <t>Cajas eléctricas</t>
         </is>
       </c>
       <c r="C161" s="257" t="inlineStr">
@@ -14532,58 +14502,88 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="81" t="n"/>
-      <c r="B162" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 13 - INSTALACIONES HIDROSANITARIAS</t>
-        </is>
-      </c>
-      <c r="C162" s="567" t="n"/>
-      <c r="D162" s="567" t="n"/>
-      <c r="E162" s="567" t="n"/>
-      <c r="F162" s="1454">
-        <f>SUM(F150:F161)</f>
+      <c r="A162" s="80" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="B162" s="364" t="inlineStr">
+        <is>
+          <t>Cableado de fuerza</t>
+        </is>
+      </c>
+      <c r="C162" s="257" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D162" s="258" t="n"/>
+      <c r="E162" s="1451" t="n"/>
+      <c r="F162" s="1453">
+        <f>D162*E162</f>
         <v/>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="82" t="n"/>
-      <c r="B163" s="716" t="n"/>
-      <c r="C163" s="716" t="n"/>
-      <c r="D163" s="716" t="n"/>
-      <c r="E163" s="716" t="n"/>
-      <c r="F163" s="708" t="n"/>
+      <c r="A163" s="80" t="inlineStr">
+        <is>
+          <t>14.5</t>
+        </is>
+      </c>
+      <c r="B163" s="364" t="inlineStr">
+        <is>
+          <t>Cableado de iluminación</t>
+        </is>
+      </c>
+      <c r="C163" s="257" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D163" s="258" t="n"/>
+      <c r="E163" s="1451" t="n"/>
+      <c r="F163" s="1453">
+        <f>D163*E163</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="182" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B164" s="703" t="inlineStr">
-        <is>
-          <t>INSTALACIONES ELÉCTRICAS</t>
-        </is>
-      </c>
-      <c r="C164" s="567" t="n"/>
-      <c r="D164" s="567" t="n"/>
-      <c r="E164" s="567" t="n"/>
-      <c r="F164" s="567" t="n"/>
+      <c r="A164" s="80" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="B164" s="364" t="inlineStr">
+        <is>
+          <t>Tableros eléctricos</t>
+        </is>
+      </c>
+      <c r="C164" s="257" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D164" s="258" t="n"/>
+      <c r="E164" s="1451" t="n"/>
+      <c r="F164" s="1453">
+        <f>D164*E164</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="80" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="B165" s="364" t="inlineStr">
         <is>
-          <t>Tubería/conduit eléctrica</t>
+          <t>Tomacorrientes</t>
         </is>
       </c>
       <c r="C165" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D165" s="258" t="n"/>
@@ -14596,17 +14596,17 @@
     <row r="166">
       <c r="A166" s="80" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="B166" s="364" t="inlineStr">
         <is>
-          <t>Bandejas portacables</t>
+          <t>Interruptores</t>
         </is>
       </c>
       <c r="C166" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D166" s="258" t="n"/>
@@ -14619,12 +14619,12 @@
     <row r="167">
       <c r="A167" s="80" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="B167" s="364" t="inlineStr">
         <is>
-          <t>Cajas eléctricas</t>
+          <t>Luminarias</t>
         </is>
       </c>
       <c r="C167" s="257" t="inlineStr">
@@ -14642,17 +14642,17 @@
     <row r="168">
       <c r="A168" s="80" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="B168" s="364" t="inlineStr">
         <is>
-          <t>Cableado de fuerza</t>
+          <t>Sistema de puesta a tierra</t>
         </is>
       </c>
       <c r="C168" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D168" s="258" t="n"/>
@@ -14665,17 +14665,17 @@
     <row r="169">
       <c r="A169" s="80" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="B169" s="364" t="inlineStr">
         <is>
-          <t>Cableado de iluminación</t>
+          <t>Pruebas y certificaciones</t>
         </is>
       </c>
       <c r="C169" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D169" s="258" t="n"/>
@@ -14686,88 +14686,58 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="80" t="inlineStr">
-        <is>
-          <t>14.6</t>
-        </is>
-      </c>
-      <c r="B170" s="364" t="inlineStr">
-        <is>
-          <t>Tableros eléctricos</t>
-        </is>
-      </c>
-      <c r="C170" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D170" s="258" t="n"/>
-      <c r="E170" s="1451" t="n"/>
-      <c r="F170" s="1453">
-        <f>D170*E170</f>
+      <c r="A170" s="81" t="n"/>
+      <c r="B170" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 14 - INSTALACIONES ELÉCTRICAS</t>
+        </is>
+      </c>
+      <c r="C170" s="567" t="n"/>
+      <c r="D170" s="567" t="n"/>
+      <c r="E170" s="567" t="n"/>
+      <c r="F170" s="1454">
+        <f>SUM(F159:F169)</f>
         <v/>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="80" t="inlineStr">
-        <is>
-          <t>14.7</t>
-        </is>
-      </c>
-      <c r="B171" s="364" t="inlineStr">
-        <is>
-          <t>Tomacorrientes</t>
-        </is>
-      </c>
-      <c r="C171" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D171" s="258" t="n"/>
-      <c r="E171" s="1451" t="n"/>
-      <c r="F171" s="1453">
-        <f>D171*E171</f>
-        <v/>
-      </c>
+      <c r="A171" s="82" t="n"/>
+      <c r="B171" s="716" t="n"/>
+      <c r="C171" s="716" t="n"/>
+      <c r="D171" s="716" t="n"/>
+      <c r="E171" s="716" t="n"/>
+      <c r="F171" s="708" t="n"/>
     </row>
     <row r="172">
-      <c r="A172" s="80" t="inlineStr">
-        <is>
-          <t>14.8</t>
-        </is>
-      </c>
-      <c r="B172" s="364" t="inlineStr">
-        <is>
-          <t>Interruptores</t>
-        </is>
-      </c>
-      <c r="C172" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D172" s="258" t="n"/>
-      <c r="E172" s="1451" t="n"/>
-      <c r="F172" s="1453">
-        <f>D172*E172</f>
-        <v/>
-      </c>
+      <c r="A172" s="182" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B172" s="703" t="inlineStr">
+        <is>
+          <t>COMUNICACIONES Y SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="C172" s="567" t="n"/>
+      <c r="D172" s="567" t="n"/>
+      <c r="E172" s="567" t="n"/>
+      <c r="F172" s="567" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="80" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="B173" s="364" t="inlineStr">
         <is>
-          <t>Luminarias</t>
+          <t>Cableado estructurado de datos</t>
         </is>
       </c>
       <c r="C173" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D173" s="258" t="n"/>
@@ -14780,17 +14750,17 @@
     <row r="174">
       <c r="A174" s="80" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="B174" s="364" t="inlineStr">
         <is>
-          <t>Sistema de puesta a tierra</t>
+          <t>Rack de comunicaciones</t>
         </is>
       </c>
       <c r="C174" s="257" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D174" s="258" t="n"/>
@@ -14803,17 +14773,17 @@
     <row r="175">
       <c r="A175" s="80" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="B175" s="364" t="inlineStr">
         <is>
-          <t>Pruebas y certificaciones</t>
+          <t>Cámaras y sistema CCTV</t>
         </is>
       </c>
       <c r="C175" s="257" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D175" s="258" t="n"/>
@@ -14824,122 +14794,122 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="81" t="n"/>
-      <c r="B176" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 14 - INSTALACIONES ELÉCTRICAS</t>
-        </is>
-      </c>
-      <c r="C176" s="567" t="n"/>
-      <c r="D176" s="567" t="n"/>
-      <c r="E176" s="567" t="n"/>
-      <c r="F176" s="1454">
-        <f>SUM(F165:F175)</f>
+      <c r="A176" s="80" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="B176" s="364" t="inlineStr">
+        <is>
+          <t>Control de acceso</t>
+        </is>
+      </c>
+      <c r="C176" s="257" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D176" s="258" t="n"/>
+      <c r="E176" s="1451" t="n"/>
+      <c r="F176" s="1453">
+        <f>D176*E176</f>
         <v/>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="82" t="n"/>
-      <c r="B177" s="716" t="n"/>
-      <c r="C177" s="716" t="n"/>
-      <c r="D177" s="716" t="n"/>
-      <c r="E177" s="716" t="n"/>
-      <c r="F177" s="708" t="n"/>
+      <c r="A177" s="80" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="B177" s="364" t="inlineStr">
+        <is>
+          <t>Sistema de citofonía</t>
+        </is>
+      </c>
+      <c r="C177" s="257" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D177" s="258" t="n"/>
+      <c r="E177" s="1451" t="n"/>
+      <c r="F177" s="1453">
+        <f>D177*E177</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
-      <c r="A178" s="182" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B178" s="703" t="inlineStr">
-        <is>
-          <t>COMUNICACIONES Y SEGURIDAD</t>
-        </is>
-      </c>
-      <c r="C178" s="567" t="n"/>
-      <c r="D178" s="567" t="n"/>
-      <c r="E178" s="567" t="n"/>
-      <c r="F178" s="567" t="n"/>
+      <c r="A178" s="80" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="B178" s="364" t="inlineStr">
+        <is>
+          <t>Sistema de detección de incendios</t>
+        </is>
+      </c>
+      <c r="C178" s="257" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D178" s="258" t="n"/>
+      <c r="E178" s="1451" t="n"/>
+      <c r="F178" s="1453">
+        <f>D178*E178</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
-      <c r="A179" s="80" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="B179" s="364" t="inlineStr">
-        <is>
-          <t>Cableado estructurado de datos</t>
-        </is>
-      </c>
-      <c r="C179" s="257" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D179" s="258" t="n"/>
-      <c r="E179" s="1451" t="n"/>
-      <c r="F179" s="1453">
-        <f>D179*E179</f>
+      <c r="A179" s="81" t="n"/>
+      <c r="B179" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 15 - COMUNICACIONES Y SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="C179" s="567" t="n"/>
+      <c r="D179" s="567" t="n"/>
+      <c r="E179" s="567" t="n"/>
+      <c r="F179" s="1454">
+        <f>SUM(F173:F178)</f>
         <v/>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="80" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
-      <c r="B180" s="364" t="inlineStr">
-        <is>
-          <t>Rack de comunicaciones</t>
-        </is>
-      </c>
-      <c r="C180" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D180" s="258" t="n"/>
-      <c r="E180" s="1451" t="n"/>
-      <c r="F180" s="1453">
-        <f>D180*E180</f>
-        <v/>
-      </c>
+      <c r="A180" s="82" t="n"/>
+      <c r="B180" s="716" t="n"/>
+      <c r="C180" s="716" t="n"/>
+      <c r="D180" s="716" t="n"/>
+      <c r="E180" s="716" t="n"/>
+      <c r="F180" s="708" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="80" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
-      </c>
-      <c r="B181" s="364" t="inlineStr">
-        <is>
-          <t>Cámaras y sistema CCTV</t>
-        </is>
-      </c>
-      <c r="C181" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D181" s="258" t="n"/>
-      <c r="E181" s="1451" t="n"/>
-      <c r="F181" s="1453">
-        <f>D181*E181</f>
-        <v/>
-      </c>
+      <c r="A181" s="182" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B181" s="703" t="inlineStr">
+        <is>
+          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
+        </is>
+      </c>
+      <c r="C181" s="567" t="n"/>
+      <c r="D181" s="567" t="n"/>
+      <c r="E181" s="567" t="n"/>
+      <c r="F181" s="567" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="80" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="B182" s="364" t="inlineStr">
         <is>
-          <t>Control de acceso</t>
+          <t>Equipos de aire acondicionado</t>
         </is>
       </c>
       <c r="C182" s="257" t="inlineStr">
@@ -14957,17 +14927,17 @@
     <row r="183">
       <c r="A183" s="80" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="B183" s="364" t="inlineStr">
         <is>
-          <t>Sistema de citofonía</t>
+          <t>Ductos de ventilación</t>
         </is>
       </c>
       <c r="C183" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D183" s="258" t="n"/>
@@ -14980,17 +14950,17 @@
     <row r="184">
       <c r="A184" s="80" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="B184" s="364" t="inlineStr">
         <is>
-          <t>Sistema de detección de incendios</t>
+          <t>Tubería de refrigerante</t>
         </is>
       </c>
       <c r="C184" s="257" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D184" s="258" t="n"/>
@@ -15001,81 +14971,81 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="81" t="n"/>
-      <c r="B185" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 15 - COMUNICACIONES Y SEGURIDAD</t>
-        </is>
-      </c>
-      <c r="C185" s="567" t="n"/>
-      <c r="D185" s="567" t="n"/>
-      <c r="E185" s="567" t="n"/>
-      <c r="F185" s="1454">
-        <f>SUM(F179:F184)</f>
+      <c r="A185" s="80" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="B185" s="364" t="inlineStr">
+        <is>
+          <t>Rejillas y difusores</t>
+        </is>
+      </c>
+      <c r="C185" s="257" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D185" s="258" t="n"/>
+      <c r="E185" s="1451" t="n"/>
+      <c r="F185" s="1453">
+        <f>D185*E185</f>
         <v/>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="82" t="n"/>
-      <c r="B186" s="716" t="n"/>
-      <c r="C186" s="716" t="n"/>
-      <c r="D186" s="716" t="n"/>
-      <c r="E186" s="716" t="n"/>
-      <c r="F186" s="708" t="n"/>
+      <c r="A186" s="81" t="n"/>
+      <c r="B186" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 16 - CLIMATIZACIÓN Y VENTILACIÓN</t>
+        </is>
+      </c>
+      <c r="C186" s="567" t="n"/>
+      <c r="D186" s="567" t="n"/>
+      <c r="E186" s="567" t="n"/>
+      <c r="F186" s="1454">
+        <f>SUM(F182:F185)</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
-      <c r="A187" s="182" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B187" s="703" t="inlineStr">
-        <is>
-          <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
-        </is>
-      </c>
-      <c r="C187" s="567" t="n"/>
-      <c r="D187" s="567" t="n"/>
-      <c r="E187" s="567" t="n"/>
-      <c r="F187" s="567" t="n"/>
+      <c r="A187" s="82" t="n"/>
+      <c r="B187" s="716" t="n"/>
+      <c r="C187" s="716" t="n"/>
+      <c r="D187" s="716" t="n"/>
+      <c r="E187" s="716" t="n"/>
+      <c r="F187" s="708" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="80" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="B188" s="364" t="inlineStr">
-        <is>
-          <t>Equipos de aire acondicionado</t>
-        </is>
-      </c>
-      <c r="C188" s="257" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D188" s="258" t="n"/>
-      <c r="E188" s="1451" t="n"/>
-      <c r="F188" s="1453">
-        <f>D188*E188</f>
-        <v/>
-      </c>
+      <c r="A188" s="182" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B188" s="703" t="inlineStr">
+        <is>
+          <t>GAS</t>
+        </is>
+      </c>
+      <c r="C188" s="567" t="n"/>
+      <c r="D188" s="567" t="n"/>
+      <c r="E188" s="567" t="n"/>
+      <c r="F188" s="567" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="80" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="B189" s="364" t="inlineStr">
         <is>
-          <t>Ductos de ventilación</t>
+          <t>Red interna de gas</t>
         </is>
       </c>
       <c r="C189" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D189" s="258" t="n"/>
@@ -15088,17 +15058,17 @@
     <row r="190">
       <c r="A190" s="80" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="B190" s="364" t="inlineStr">
         <is>
-          <t>Tubería de refrigerante</t>
+          <t>Válvulas y accesorios de gas</t>
         </is>
       </c>
       <c r="C190" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D190" s="258" t="n"/>
@@ -15111,17 +15081,17 @@
     <row r="191">
       <c r="A191" s="80" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="B191" s="364" t="inlineStr">
         <is>
-          <t>Rejillas y difusores</t>
+          <t>Pruebas y certificación</t>
         </is>
       </c>
       <c r="C191" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D191" s="258" t="n"/>
@@ -15135,14 +15105,14 @@
       <c r="A192" s="81" t="n"/>
       <c r="B192" s="704" t="inlineStr">
         <is>
-          <t>SUBTOTAL CAPÍTULO 16 - CLIMATIZACIÓN Y VENTILACIÓN</t>
+          <t>SUBTOTAL CAPÍTULO 17 - GAS</t>
         </is>
       </c>
       <c r="C192" s="567" t="n"/>
       <c r="D192" s="567" t="n"/>
       <c r="E192" s="567" t="n"/>
       <c r="F192" s="1454">
-        <f>SUM(F188:F191)</f>
+        <f>SUM(F189:F191)</f>
         <v/>
       </c>
     </row>
@@ -15157,12 +15127,12 @@
     <row r="194">
       <c r="A194" s="182" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B194" s="703" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
       <c r="C194" s="567" t="n"/>
@@ -15173,17 +15143,17 @@
     <row r="195">
       <c r="A195" s="80" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="B195" s="364" t="inlineStr">
         <is>
-          <t>Red interna de gas</t>
+          <t>Construcción de andenes</t>
         </is>
       </c>
       <c r="C195" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D195" s="258" t="n"/>
@@ -15196,17 +15166,17 @@
     <row r="196">
       <c r="A196" s="80" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="B196" s="364" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios de gas</t>
+          <t>Placas de concreto exteriores</t>
         </is>
       </c>
       <c r="C196" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D196" s="258" t="n"/>
@@ -15219,17 +15189,17 @@
     <row r="197">
       <c r="A197" s="80" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="B197" s="364" t="inlineStr">
         <is>
-          <t>Pruebas y certificación</t>
+          <t>Pavimento en adoquín</t>
         </is>
       </c>
       <c r="C197" s="257" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D197" s="258" t="n"/>
@@ -15240,53 +15210,83 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="81" t="n"/>
-      <c r="B198" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 17 - GAS</t>
-        </is>
-      </c>
-      <c r="C198" s="567" t="n"/>
-      <c r="D198" s="567" t="n"/>
-      <c r="E198" s="567" t="n"/>
-      <c r="F198" s="1454">
-        <f>SUM(F195:F197)</f>
+      <c r="A198" s="80" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="B198" s="364" t="inlineStr">
+        <is>
+          <t>Sardineles y bordillos</t>
+        </is>
+      </c>
+      <c r="C198" s="257" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D198" s="258" t="n"/>
+      <c r="E198" s="1451" t="n"/>
+      <c r="F198" s="1453">
+        <f>D198*E198</f>
         <v/>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="82" t="n"/>
-      <c r="B199" s="716" t="n"/>
-      <c r="C199" s="716" t="n"/>
-      <c r="D199" s="716" t="n"/>
-      <c r="E199" s="716" t="n"/>
-      <c r="F199" s="708" t="n"/>
+      <c r="A199" s="80" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="B199" s="364" t="inlineStr">
+        <is>
+          <t>Sumideros exteriores</t>
+        </is>
+      </c>
+      <c r="C199" s="257" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D199" s="258" t="n"/>
+      <c r="E199" s="1451" t="n"/>
+      <c r="F199" s="1453">
+        <f>D199*E199</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
-      <c r="A200" s="182" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B200" s="703" t="inlineStr">
-        <is>
-          <t>URBANISMO Y EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C200" s="567" t="n"/>
-      <c r="D200" s="567" t="n"/>
-      <c r="E200" s="567" t="n"/>
-      <c r="F200" s="567" t="n"/>
+      <c r="A200" s="80" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="B200" s="364" t="inlineStr">
+        <is>
+          <t>Suministro y extendido de tierra vegetal</t>
+        </is>
+      </c>
+      <c r="C200" s="257" t="inlineStr">
+        <is>
+          <t>M³</t>
+        </is>
+      </c>
+      <c r="D200" s="258" t="n"/>
+      <c r="E200" s="1451" t="n"/>
+      <c r="F200" s="1453">
+        <f>D200*E200</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="80" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="B201" s="364" t="inlineStr">
         <is>
-          <t>Construcción de andenes</t>
+          <t>Siembra y jardinería</t>
         </is>
       </c>
       <c r="C201" s="257" t="inlineStr">
@@ -15304,17 +15304,17 @@
     <row r="202">
       <c r="A202" s="80" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="B202" s="364" t="inlineStr">
         <is>
-          <t>Placas de concreto exteriores</t>
+          <t>Geotextil para drenaje y filtración</t>
         </is>
       </c>
       <c r="C202" s="257" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D202" s="258" t="n"/>
@@ -15327,17 +15327,17 @@
     <row r="203">
       <c r="A203" s="80" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="B203" s="364" t="inlineStr">
         <is>
-          <t>Pavimento en adoquín</t>
+          <t>Gaviones para obras de contención</t>
         </is>
       </c>
       <c r="C203" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D203" s="258" t="n"/>
@@ -15350,12 +15350,12 @@
     <row r="204">
       <c r="A204" s="80" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="B204" s="364" t="inlineStr">
         <is>
-          <t>Sardineles y bordillos</t>
+          <t>Filtro francés (drenaje de terrenos)</t>
         </is>
       </c>
       <c r="C204" s="257" t="inlineStr">
@@ -15373,17 +15373,17 @@
     <row r="205">
       <c r="A205" s="80" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.11</t>
         </is>
       </c>
       <c r="B205" s="364" t="inlineStr">
         <is>
-          <t>Sumideros exteriores</t>
+          <t>Revegetalización / empradización</t>
         </is>
       </c>
       <c r="C205" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D205" s="258" t="n"/>
@@ -15394,88 +15394,58 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="80" t="inlineStr">
-        <is>
-          <t>18.6</t>
-        </is>
-      </c>
-      <c r="B206" s="364" t="inlineStr">
-        <is>
-          <t>Suministro y extendido de tierra vegetal</t>
-        </is>
-      </c>
-      <c r="C206" s="257" t="inlineStr">
-        <is>
-          <t>M³</t>
-        </is>
-      </c>
-      <c r="D206" s="258" t="n"/>
-      <c r="E206" s="1451" t="n"/>
-      <c r="F206" s="1453">
-        <f>D206*E206</f>
+      <c r="A206" s="81" t="n"/>
+      <c r="B206" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 18 - URBANISMO Y EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C206" s="567" t="n"/>
+      <c r="D206" s="567" t="n"/>
+      <c r="E206" s="567" t="n"/>
+      <c r="F206" s="1454">
+        <f>SUM(F195:F205)</f>
         <v/>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="80" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="B207" s="364" t="inlineStr">
-        <is>
-          <t>Siembra y jardinería</t>
-        </is>
-      </c>
-      <c r="C207" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D207" s="258" t="n"/>
-      <c r="E207" s="1451" t="n"/>
-      <c r="F207" s="1453">
-        <f>D207*E207</f>
-        <v/>
-      </c>
+      <c r="A207" s="82" t="n"/>
+      <c r="B207" s="716" t="n"/>
+      <c r="C207" s="716" t="n"/>
+      <c r="D207" s="716" t="n"/>
+      <c r="E207" s="716" t="n"/>
+      <c r="F207" s="708" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="80" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="B208" s="364" t="inlineStr">
-        <is>
-          <t>Geotextil para drenaje y filtración</t>
-        </is>
-      </c>
-      <c r="C208" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D208" s="258" t="n"/>
-      <c r="E208" s="1451" t="n"/>
-      <c r="F208" s="1453">
-        <f>D208*E208</f>
-        <v/>
-      </c>
+      <c r="A208" s="182" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B208" s="703" t="inlineStr">
+        <is>
+          <t>OBRAS COMPLEMENTARIAS</t>
+        </is>
+      </c>
+      <c r="C208" s="567" t="n"/>
+      <c r="D208" s="567" t="n"/>
+      <c r="E208" s="567" t="n"/>
+      <c r="F208" s="567" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="80" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="B209" s="364" t="inlineStr">
         <is>
-          <t>Gaviones para obras de contención</t>
+          <t>Rejas metálicas</t>
         </is>
       </c>
       <c r="C209" s="257" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D209" s="258" t="n"/>
@@ -15488,17 +15458,17 @@
     <row r="210">
       <c r="A210" s="80" t="inlineStr">
         <is>
-          <t>18.10</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="B210" s="364" t="inlineStr">
         <is>
-          <t>Filtro francés (drenaje de terrenos)</t>
+          <t>Escaleras metálicas</t>
         </is>
       </c>
       <c r="C210" s="257" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D210" s="258" t="n"/>
@@ -15511,17 +15481,17 @@
     <row r="211">
       <c r="A211" s="80" t="inlineStr">
         <is>
-          <t>18.11</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="B211" s="364" t="inlineStr">
         <is>
-          <t>Revegetalización / empradización</t>
+          <t>Elementos metálicos especiales</t>
         </is>
       </c>
       <c r="C211" s="257" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D211" s="258" t="n"/>
@@ -15532,81 +15502,81 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="81" t="n"/>
-      <c r="B212" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 18 - URBANISMO Y EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C212" s="567" t="n"/>
-      <c r="D212" s="567" t="n"/>
-      <c r="E212" s="567" t="n"/>
-      <c r="F212" s="1454">
-        <f>SUM(F201:F211)</f>
+      <c r="A212" s="80" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="B212" s="364" t="inlineStr">
+        <is>
+          <t>Mobiliario fijo de obra</t>
+        </is>
+      </c>
+      <c r="C212" s="257" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D212" s="258" t="n"/>
+      <c r="E212" s="1451" t="n"/>
+      <c r="F212" s="1453">
+        <f>D212*E212</f>
         <v/>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="82" t="n"/>
-      <c r="B213" s="716" t="n"/>
-      <c r="C213" s="716" t="n"/>
-      <c r="D213" s="716" t="n"/>
-      <c r="E213" s="716" t="n"/>
-      <c r="F213" s="708" t="n"/>
+      <c r="A213" s="81" t="n"/>
+      <c r="B213" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 19 - OBRAS COMPLEMENTARIAS</t>
+        </is>
+      </c>
+      <c r="C213" s="567" t="n"/>
+      <c r="D213" s="567" t="n"/>
+      <c r="E213" s="567" t="n"/>
+      <c r="F213" s="1454">
+        <f>SUM(F209:F212)</f>
+        <v/>
+      </c>
     </row>
     <row r="214">
-      <c r="A214" s="182" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B214" s="703" t="inlineStr">
-        <is>
-          <t>OBRAS COMPLEMENTARIAS</t>
-        </is>
-      </c>
-      <c r="C214" s="567" t="n"/>
-      <c r="D214" s="567" t="n"/>
-      <c r="E214" s="567" t="n"/>
-      <c r="F214" s="567" t="n"/>
+      <c r="A214" s="82" t="n"/>
+      <c r="B214" s="716" t="n"/>
+      <c r="C214" s="716" t="n"/>
+      <c r="D214" s="716" t="n"/>
+      <c r="E214" s="716" t="n"/>
+      <c r="F214" s="708" t="n"/>
     </row>
     <row r="215">
-      <c r="A215" s="80" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="B215" s="364" t="inlineStr">
-        <is>
-          <t>Rejas metálicas</t>
-        </is>
-      </c>
-      <c r="C215" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D215" s="258" t="n"/>
-      <c r="E215" s="1451" t="n"/>
-      <c r="F215" s="1453">
-        <f>D215*E215</f>
-        <v/>
-      </c>
+      <c r="A215" s="182" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B215" s="703" t="inlineStr">
+        <is>
+          <t>ASEO, ENTREGA Y CIERRE</t>
+        </is>
+      </c>
+      <c r="C215" s="567" t="n"/>
+      <c r="D215" s="567" t="n"/>
+      <c r="E215" s="567" t="n"/>
+      <c r="F215" s="567" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="80" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="B216" s="364" t="inlineStr">
         <is>
-          <t>Escaleras metálicas</t>
+          <t>Limpieza gruesa y fina de obra</t>
         </is>
       </c>
       <c r="C216" s="257" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D216" s="258" t="n"/>
@@ -15619,17 +15589,17 @@
     <row r="217">
       <c r="A217" s="80" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="B217" s="364" t="inlineStr">
         <is>
-          <t>Elementos metálicos especiales</t>
+          <t>Limpieza final para entrega</t>
         </is>
       </c>
       <c r="C217" s="257" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D217" s="258" t="n"/>
@@ -15642,17 +15612,17 @@
     <row r="218">
       <c r="A218" s="80" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="B218" s="364" t="inlineStr">
         <is>
-          <t>Mobiliario fijo de obra</t>
+          <t>Pruebas, puesta en marcha y ajustes</t>
         </is>
       </c>
       <c r="C218" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D218" s="258" t="n"/>
@@ -15663,104 +15633,104 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="81" t="n"/>
-      <c r="B219" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 19 - OBRAS COMPLEMENTARIAS</t>
-        </is>
-      </c>
-      <c r="C219" s="567" t="n"/>
-      <c r="D219" s="567" t="n"/>
-      <c r="E219" s="567" t="n"/>
-      <c r="F219" s="1454">
-        <f>SUM(F215:F218)</f>
+      <c r="A219" s="80" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="B219" s="364" t="inlineStr">
+        <is>
+          <t>Actualización de planos récord / as-built</t>
+        </is>
+      </c>
+      <c r="C219" s="257" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D219" s="258" t="n"/>
+      <c r="E219" s="1451" t="n"/>
+      <c r="F219" s="1453">
+        <f>D219*E219</f>
         <v/>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="82" t="n"/>
-      <c r="B220" s="716" t="n"/>
-      <c r="C220" s="716" t="n"/>
-      <c r="D220" s="716" t="n"/>
-      <c r="E220" s="716" t="n"/>
-      <c r="F220" s="708" t="n"/>
+      <c r="A220" s="80" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="B220" s="364" t="inlineStr">
+        <is>
+          <t>Entrega, manuales y acta de recibo</t>
+        </is>
+      </c>
+      <c r="C220" s="257" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D220" s="258" t="n"/>
+      <c r="E220" s="1451" t="n"/>
+      <c r="F220" s="1453">
+        <f>D220*E220</f>
+        <v/>
+      </c>
     </row>
     <row r="221">
-      <c r="A221" s="182" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B221" s="703" t="inlineStr">
-        <is>
-          <t>ASEO, ENTREGA Y CIERRE</t>
+      <c r="A221" s="81" t="n"/>
+      <c r="B221" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 20 - ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
       <c r="C221" s="567" t="n"/>
       <c r="D221" s="567" t="n"/>
       <c r="E221" s="567" t="n"/>
-      <c r="F221" s="567" t="n"/>
+      <c r="F221" s="1454">
+        <f>SUM(F216:F220)</f>
+        <v/>
+      </c>
     </row>
     <row r="222">
-      <c r="A222" s="80" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="B222" s="364" t="inlineStr">
-        <is>
-          <t>Limpieza gruesa y fina de obra</t>
-        </is>
-      </c>
-      <c r="C222" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D222" s="258" t="n"/>
-      <c r="E222" s="1451" t="n"/>
-      <c r="F222" s="1453">
-        <f>D222*E222</f>
-        <v/>
-      </c>
+      <c r="A222" s="82" t="n"/>
+      <c r="B222" s="716" t="n"/>
+      <c r="C222" s="716" t="n"/>
+      <c r="D222" s="716" t="n"/>
+      <c r="E222" s="716" t="n"/>
+      <c r="F222" s="708" t="n"/>
     </row>
     <row r="223">
-      <c r="A223" s="80" t="inlineStr">
-        <is>
-          <t>20.2</t>
-        </is>
-      </c>
-      <c r="B223" s="364" t="inlineStr">
-        <is>
-          <t>Limpieza final para entrega</t>
-        </is>
-      </c>
-      <c r="C223" s="257" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D223" s="258" t="n"/>
-      <c r="E223" s="1451" t="n"/>
-      <c r="F223" s="1453">
-        <f>D223*E223</f>
-        <v/>
-      </c>
+      <c r="A223" s="182" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B223" s="703" t="inlineStr">
+        <is>
+          <t>ASCENSORES</t>
+        </is>
+      </c>
+      <c r="C223" s="567" t="n"/>
+      <c r="D223" s="567" t="n"/>
+      <c r="E223" s="567" t="n"/>
+      <c r="F223" s="567" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="80" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="B224" s="364" t="inlineStr">
         <is>
-          <t>Pruebas, puesta en marcha y ajustes</t>
+          <t>Suministro e instalación de ascensor eléctrico</t>
         </is>
       </c>
       <c r="C224" s="257" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D224" s="258" t="n"/>
@@ -15771,104 +15741,104 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="80" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="B225" s="364" t="inlineStr">
-        <is>
-          <t>Actualización de planos récord / as-built</t>
-        </is>
-      </c>
-      <c r="C225" s="257" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D225" s="258" t="n"/>
-      <c r="E225" s="1451" t="n"/>
-      <c r="F225" s="1453">
-        <f>D225*E225</f>
+      <c r="A225" s="81" t="n"/>
+      <c r="B225" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 21 - ASCENSORES</t>
+        </is>
+      </c>
+      <c r="C225" s="567" t="n"/>
+      <c r="D225" s="567" t="n"/>
+      <c r="E225" s="567" t="n"/>
+      <c r="F225" s="1454">
+        <f>SUM(F224:F224)</f>
         <v/>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="80" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="B226" s="364" t="inlineStr">
-        <is>
-          <t>Entrega, manuales y acta de recibo</t>
-        </is>
-      </c>
-      <c r="C226" s="257" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D226" s="258" t="n"/>
-      <c r="E226" s="1451" t="n"/>
-      <c r="F226" s="1453">
-        <f>D226*E226</f>
-        <v/>
-      </c>
+      <c r="A226" s="82" t="n"/>
+      <c r="B226" s="716" t="n"/>
+      <c r="C226" s="716" t="n"/>
+      <c r="D226" s="716" t="n"/>
+      <c r="E226" s="716" t="n"/>
+      <c r="F226" s="708" t="n"/>
     </row>
     <row r="227">
-      <c r="A227" s="81" t="n"/>
-      <c r="B227" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 20 - ASEO, ENTREGA Y CIERRE</t>
+      <c r="A227" s="182" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B227" s="703" t="inlineStr">
+        <is>
+          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
       <c r="C227" s="567" t="n"/>
       <c r="D227" s="567" t="n"/>
       <c r="E227" s="567" t="n"/>
-      <c r="F227" s="1454">
-        <f>SUM(F222:F226)</f>
-        <v/>
-      </c>
+      <c r="F227" s="567" t="n"/>
     </row>
     <row r="228">
-      <c r="A228" s="82" t="n"/>
-      <c r="B228" s="716" t="n"/>
-      <c r="C228" s="716" t="n"/>
-      <c r="D228" s="716" t="n"/>
-      <c r="E228" s="716" t="n"/>
-      <c r="F228" s="708" t="n"/>
+      <c r="A228" s="80" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="B228" s="364" t="inlineStr">
+        <is>
+          <t>Estudio de suelos y geotecnia</t>
+        </is>
+      </c>
+      <c r="C228" s="257" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D228" s="258" t="n"/>
+      <c r="E228" s="1451" t="n"/>
+      <c r="F228" s="1453">
+        <f>D228*E228</f>
+        <v/>
+      </c>
     </row>
     <row r="229">
-      <c r="A229" s="182" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B229" s="703" t="inlineStr">
-        <is>
-          <t>ASCENSORES</t>
-        </is>
-      </c>
-      <c r="C229" s="567" t="n"/>
-      <c r="D229" s="567" t="n"/>
-      <c r="E229" s="567" t="n"/>
-      <c r="F229" s="567" t="n"/>
+      <c r="A229" s="80" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="B229" s="364" t="inlineStr">
+        <is>
+          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
+        </is>
+      </c>
+      <c r="C229" s="257" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D229" s="258" t="n"/>
+      <c r="E229" s="1451" t="n"/>
+      <c r="F229" s="1453">
+        <f>D229*E229</f>
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="80" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="B230" s="364" t="inlineStr">
         <is>
-          <t>Suministro e instalación de ascensor eléctrico</t>
+          <t>Licencia de construcción y trámites de curaduría urbana</t>
         </is>
       </c>
       <c r="C230" s="257" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D230" s="258" t="n"/>
@@ -15879,472 +15849,364 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="81" t="n"/>
-      <c r="B231" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 21 - ASCENSORES</t>
-        </is>
-      </c>
-      <c r="C231" s="567" t="n"/>
-      <c r="D231" s="567" t="n"/>
-      <c r="E231" s="567" t="n"/>
-      <c r="F231" s="1454">
-        <f>SUM(F230:F230)</f>
+      <c r="A231" s="80" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="B231" s="364" t="inlineStr">
+        <is>
+          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
+        </is>
+      </c>
+      <c r="C231" s="257" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D231" s="258" t="n"/>
+      <c r="E231" s="1451" t="n"/>
+      <c r="F231" s="1453">
+        <f>D231*E231</f>
         <v/>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="82" t="n"/>
-      <c r="B232" s="716" t="n"/>
-      <c r="C232" s="716" t="n"/>
-      <c r="D232" s="716" t="n"/>
-      <c r="E232" s="716" t="n"/>
-      <c r="F232" s="708" t="n"/>
+      <c r="A232" s="81" t="n"/>
+      <c r="B232" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL CAPÍTULO 22 - GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="C232" s="567" t="n"/>
+      <c r="D232" s="567" t="n"/>
+      <c r="E232" s="567" t="n"/>
+      <c r="F232" s="1454">
+        <f>SUM(F228:F231)</f>
+        <v/>
+      </c>
     </row>
     <row r="233">
-      <c r="A233" s="182" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B233" s="703" t="inlineStr">
-        <is>
-          <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
-        </is>
-      </c>
-      <c r="C233" s="567" t="n"/>
-      <c r="D233" s="567" t="n"/>
-      <c r="E233" s="567" t="n"/>
-      <c r="F233" s="567" t="n"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="80" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="B234" s="364" t="inlineStr">
-        <is>
-          <t>Estudio de suelos y geotecnia</t>
-        </is>
-      </c>
-      <c r="C234" s="257" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D234" s="258" t="n"/>
-      <c r="E234" s="1451" t="n"/>
-      <c r="F234" s="1453">
-        <f>D234*E234</f>
+      <c r="A233" s="82" t="n"/>
+      <c r="B233" s="716" t="n"/>
+      <c r="C233" s="716" t="n"/>
+      <c r="D233" s="716" t="n"/>
+      <c r="E233" s="716" t="n"/>
+      <c r="F233" s="708" t="n"/>
+    </row>
+    <row r="234" ht="15" customHeight="1" s="550">
+      <c r="A234" s="83" t="n"/>
+      <c r="B234" s="715" t="inlineStr">
+        <is>
+          <t>COSTO DIRECTO TOTAL (suma de capítulos 1 a 22)</t>
+        </is>
+      </c>
+      <c r="C234" s="567" t="n"/>
+      <c r="D234" s="567" t="n"/>
+      <c r="E234" s="567" t="n"/>
+      <c r="F234" s="1456">
+        <f>F25+F39+F49+F62+F74+F86+F93+F99+F113+F123+F134+F141+F156+F170+F179+F186+F192+F206+F213+F221+F225+F232</f>
         <v/>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="80" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="B235" s="364" t="inlineStr">
-        <is>
-          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
-        </is>
-      </c>
-      <c r="C235" s="257" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D235" s="258" t="n"/>
-      <c r="E235" s="1451" t="n"/>
-      <c r="F235" s="1453">
-        <f>D235*E235</f>
-        <v/>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="80" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
-      <c r="B236" s="364" t="inlineStr">
-        <is>
-          <t>Licencia de construcción y trámites de curaduría urbana</t>
-        </is>
-      </c>
-      <c r="C236" s="257" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D236" s="258" t="n"/>
-      <c r="E236" s="1451" t="n"/>
-      <c r="F236" s="1453">
-        <f>D236*E236</f>
-        <v/>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="80" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="B237" s="364" t="inlineStr">
-        <is>
-          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
-        </is>
-      </c>
-      <c r="C237" s="257" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D237" s="258" t="n"/>
-      <c r="E237" s="1451" t="n"/>
-      <c r="F237" s="1453">
-        <f>D237*E237</f>
-        <v/>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="81" t="n"/>
-      <c r="B238" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL CAPÍTULO 22 - GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
-        </is>
-      </c>
-      <c r="C238" s="567" t="n"/>
-      <c r="D238" s="567" t="n"/>
-      <c r="E238" s="567" t="n"/>
-      <c r="F238" s="1454">
-        <f>SUM(F234:F237)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="82" t="n"/>
-      <c r="B239" s="716" t="n"/>
-      <c r="C239" s="716" t="n"/>
-      <c r="D239" s="716" t="n"/>
-      <c r="E239" s="716" t="n"/>
-      <c r="F239" s="708" t="n"/>
+      <c r="A235" s="84" t="n"/>
+      <c r="B235" s="28" t="n"/>
+      <c r="C235" s="28" t="n"/>
+      <c r="D235" s="28" t="n"/>
+      <c r="E235" s="28" t="n"/>
+      <c r="F235" s="85" t="n"/>
+    </row>
+    <row r="236" ht="15" customHeight="1" s="550">
+      <c r="A236" s="82" t="n"/>
+      <c r="B236" s="46" t="inlineStr">
+        <is>
+          <t>Administración (A)</t>
+        </is>
+      </c>
+      <c r="C236" s="716" t="n"/>
+      <c r="D236" s="716" t="n"/>
+      <c r="E236" s="1314">
+        <f>'Ficha Técnica del Proyecto'!$B$29</f>
+        <v/>
+      </c>
+      <c r="F236" s="1457">
+        <f>F234*E236</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237" ht="15" customHeight="1" s="550">
+      <c r="A237" s="82" t="n"/>
+      <c r="B237" s="46" t="inlineStr">
+        <is>
+          <t>Imprevistos (I)</t>
+        </is>
+      </c>
+      <c r="C237" s="716" t="n"/>
+      <c r="D237" s="716" t="n"/>
+      <c r="E237" s="1314">
+        <f>'Ficha Técnica del Proyecto'!$B$30</f>
+        <v/>
+      </c>
+      <c r="F237" s="1457">
+        <f>F234*E237</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238" ht="15" customHeight="1" s="550">
+      <c r="A238" s="82" t="n"/>
+      <c r="B238" s="46" t="inlineStr">
+        <is>
+          <t>Utilidad (U)</t>
+        </is>
+      </c>
+      <c r="C238" s="716" t="n"/>
+      <c r="D238" s="716" t="n"/>
+      <c r="E238" s="1314">
+        <f>'Ficha Técnica del Proyecto'!$B$31</f>
+        <v/>
+      </c>
+      <c r="F238" s="1457">
+        <f>F234*E238</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239" ht="15" customHeight="1" s="550">
+      <c r="A239" s="81" t="n"/>
+      <c r="B239" s="704" t="inlineStr">
+        <is>
+          <t>SUBTOTAL AIU (A+I+U)</t>
+        </is>
+      </c>
+      <c r="C239" s="29" t="n"/>
+      <c r="D239" s="29" t="n"/>
+      <c r="E239" s="30" t="n"/>
+      <c r="F239" s="1454">
+        <f>F236+F237+F238</f>
+        <v/>
+      </c>
     </row>
     <row r="240" ht="15" customHeight="1" s="550">
-      <c r="A240" s="83" t="n"/>
-      <c r="B240" s="715" t="inlineStr">
-        <is>
-          <t>COSTO DIRECTO TOTAL (suma de capítulos 1 a 22)</t>
-        </is>
-      </c>
-      <c r="C240" s="567" t="n"/>
-      <c r="D240" s="567" t="n"/>
-      <c r="E240" s="567" t="n"/>
-      <c r="F240" s="1456">
-        <f>F25+F39+F50+F68+F80+F92+F99+F105+F119+F129+F140+F147+F162+F176+F185+F192+F198+F212+F219+F227+F231+F238</f>
-        <v/>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="84" t="n"/>
-      <c r="B241" s="28" t="n"/>
-      <c r="C241" s="28" t="n"/>
-      <c r="D241" s="28" t="n"/>
-      <c r="E241" s="28" t="n"/>
-      <c r="F241" s="85" t="n"/>
-    </row>
-    <row r="242" ht="15" customHeight="1" s="550">
+      <c r="A240" s="82" t="n"/>
+      <c r="B240" s="46" t="inlineStr">
+        <is>
+          <t>COSTO DIRECTO + AIU</t>
+        </is>
+      </c>
+      <c r="C240" s="716" t="n"/>
+      <c r="D240" s="716" t="n"/>
+      <c r="E240" s="47" t="n"/>
+      <c r="F240" s="1457">
+        <f>F234+F239</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241" ht="15" customHeight="1" s="550">
+      <c r="A241" s="82" t="n"/>
+      <c r="B241" s="46" t="inlineStr">
+        <is>
+          <t>IVA sobre Utilidad (19%)</t>
+        </is>
+      </c>
+      <c r="C241" s="716" t="n"/>
+      <c r="D241" s="716" t="n"/>
+      <c r="E241" s="1314">
+        <f>'Ficha Técnica del Proyecto'!$B$32</f>
+        <v/>
+      </c>
+      <c r="F241" s="1457">
+        <f>F238*E241</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242">
       <c r="A242" s="82" t="n"/>
-      <c r="B242" s="46" t="inlineStr">
-        <is>
-          <t>Administración (A)</t>
-        </is>
-      </c>
+      <c r="B242" s="716" t="n"/>
       <c r="C242" s="716" t="n"/>
       <c r="D242" s="716" t="n"/>
-      <c r="E242" s="1314">
-        <f>'Ficha Técnica del Proyecto'!$B$29</f>
-        <v/>
-      </c>
-      <c r="F242" s="1457">
-        <f>F240*E242</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243" ht="15" customHeight="1" s="550">
-      <c r="A243" s="82" t="n"/>
-      <c r="B243" s="46" t="inlineStr">
-        <is>
-          <t>Imprevistos (I)</t>
-        </is>
-      </c>
-      <c r="C243" s="716" t="n"/>
-      <c r="D243" s="716" t="n"/>
-      <c r="E243" s="1314">
-        <f>'Ficha Técnica del Proyecto'!$B$30</f>
-        <v/>
-      </c>
-      <c r="F243" s="1457">
-        <f>F240*E243</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244" ht="15" customHeight="1" s="550">
-      <c r="A244" s="82" t="n"/>
-      <c r="B244" s="46" t="inlineStr">
-        <is>
-          <t>Utilidad (U)</t>
-        </is>
-      </c>
-      <c r="C244" s="716" t="n"/>
-      <c r="D244" s="716" t="n"/>
-      <c r="E244" s="1314">
-        <f>'Ficha Técnica del Proyecto'!$B$31</f>
-        <v/>
-      </c>
-      <c r="F244" s="1457">
-        <f>F240*E244</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245" ht="15" customHeight="1" s="550">
-      <c r="A245" s="81" t="n"/>
-      <c r="B245" s="704" t="inlineStr">
-        <is>
-          <t>SUBTOTAL AIU (A+I+U)</t>
-        </is>
-      </c>
-      <c r="C245" s="29" t="n"/>
-      <c r="D245" s="29" t="n"/>
-      <c r="E245" s="30" t="n"/>
-      <c r="F245" s="1454">
-        <f>F242+F243+F244</f>
-        <v/>
-      </c>
+      <c r="E242" s="716" t="n"/>
+      <c r="F242" s="708" t="n"/>
+    </row>
+    <row r="243" ht="24" customHeight="1" s="550">
+      <c r="A243" s="86" t="n"/>
+      <c r="B243" s="703" t="inlineStr">
+        <is>
+          <t>PRESUPUESTO TOTAL DE OBRA</t>
+        </is>
+      </c>
+      <c r="C243" s="567" t="n"/>
+      <c r="D243" s="567" t="n"/>
+      <c r="E243" s="567" t="n"/>
+      <c r="F243" s="1458">
+        <f>F240+F241</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="87" t="n"/>
+      <c r="B244" s="203" t="inlineStr">
+        <is>
+          <t>REV. 10/09/2026</t>
+        </is>
+      </c>
+      <c r="C244" s="277" t="n"/>
+      <c r="D244" s="277" t="n"/>
+      <c r="E244" s="277" t="n"/>
+      <c r="F244" s="345">
+        <f>F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="87" t="n"/>
+      <c r="B245" s="203" t="n"/>
+      <c r="C245" s="277" t="n"/>
+      <c r="D245" s="277" t="n"/>
+      <c r="E245" s="277" t="n"/>
+      <c r="F245" s="201" t="n"/>
     </row>
     <row r="246" ht="15" customHeight="1" s="550">
-      <c r="A246" s="82" t="n"/>
-      <c r="B246" s="46" t="inlineStr">
-        <is>
-          <t>COSTO DIRECTO + AIU</t>
-        </is>
-      </c>
-      <c r="C246" s="716" t="n"/>
-      <c r="D246" s="716" t="n"/>
-      <c r="E246" s="47" t="n"/>
-      <c r="F246" s="1457">
-        <f>F240+F245</f>
+      <c r="A246" s="87" t="n"/>
+      <c r="B246" s="89" t="inlineStr">
+        <is>
+          <t>Costo por m² construido (sobre Costo Directo Total)</t>
+        </is>
+      </c>
+      <c r="C246" s="90" t="n"/>
+      <c r="D246" s="90" t="n"/>
+      <c r="E246" s="90" t="n"/>
+      <c r="F246" s="1459">
+        <f>F234/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
     </row>
     <row r="247" ht="15" customHeight="1" s="550">
-      <c r="A247" s="82" t="n"/>
-      <c r="B247" s="46" t="inlineStr">
-        <is>
-          <t>IVA sobre Utilidad (19%)</t>
-        </is>
-      </c>
-      <c r="C247" s="716" t="n"/>
-      <c r="D247" s="716" t="n"/>
-      <c r="E247" s="1314">
-        <f>'Ficha Técnica del Proyecto'!$B$32</f>
-        <v/>
-      </c>
-      <c r="F247" s="1457">
-        <f>F244*E247</f>
+      <c r="A247" s="88" t="n"/>
+      <c r="B247" s="91" t="inlineStr">
+        <is>
+          <t>Costo por m² construido (sobre Presupuesto Total)</t>
+        </is>
+      </c>
+      <c r="C247" s="92" t="n"/>
+      <c r="D247" s="92" t="n"/>
+      <c r="E247" s="92" t="n"/>
+      <c r="F247" s="1460">
+        <f>F243/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="82" t="n"/>
-      <c r="B248" s="716" t="n"/>
-      <c r="C248" s="716" t="n"/>
-      <c r="D248" s="716" t="n"/>
-      <c r="E248" s="716" t="n"/>
-      <c r="F248" s="708" t="n"/>
-    </row>
-    <row r="249" ht="24" customHeight="1" s="550">
-      <c r="A249" s="86" t="n"/>
-      <c r="B249" s="703" t="inlineStr">
-        <is>
-          <t>PRESUPUESTO TOTAL DE OBRA</t>
-        </is>
-      </c>
-      <c r="C249" s="567" t="n"/>
-      <c r="D249" s="567" t="n"/>
-      <c r="E249" s="567" t="n"/>
-      <c r="F249" s="1458">
-        <f>F246+F247</f>
-        <v/>
-      </c>
+      <c r="A248" s="27" t="n"/>
+      <c r="B248" s="277" t="n"/>
+      <c r="C248" s="277" t="n"/>
+      <c r="D248" s="277" t="n"/>
+      <c r="E248" s="277" t="n"/>
+      <c r="F248" s="277" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="27" t="n"/>
+      <c r="B249" s="277" t="n"/>
+      <c r="C249" s="277" t="n"/>
+      <c r="D249" s="277" t="n"/>
+      <c r="E249" s="277" t="n"/>
+      <c r="F249" s="277" t="n"/>
     </row>
     <row r="250">
-      <c r="A250" s="87" t="n"/>
-      <c r="B250" s="203" t="inlineStr">
-        <is>
-          <t>REV. 10/09/2026</t>
-        </is>
-      </c>
+      <c r="A250" s="27" t="n"/>
+      <c r="B250" s="277" t="n"/>
       <c r="C250" s="277" t="n"/>
       <c r="D250" s="277" t="n"/>
       <c r="E250" s="277" t="n"/>
-      <c r="F250" s="345">
-        <f>F6</f>
-        <v/>
-      </c>
+      <c r="F250" s="277" t="n"/>
     </row>
     <row r="251">
-      <c r="A251" s="87" t="n"/>
-      <c r="B251" s="203" t="n"/>
+      <c r="A251" s="27" t="n"/>
+      <c r="B251" s="277" t="n"/>
       <c r="C251" s="277" t="n"/>
       <c r="D251" s="277" t="n"/>
       <c r="E251" s="277" t="n"/>
-      <c r="F251" s="201" t="n"/>
-    </row>
-    <row r="252" ht="15" customHeight="1" s="550">
-      <c r="A252" s="87" t="n"/>
-      <c r="B252" s="89" t="inlineStr">
-        <is>
-          <t>Costo por m² construido (sobre Costo Directo Total)</t>
-        </is>
-      </c>
-      <c r="C252" s="90" t="n"/>
-      <c r="D252" s="90" t="n"/>
-      <c r="E252" s="90" t="n"/>
-      <c r="F252" s="1459">
-        <f>F240/'Ficha Técnica del Proyecto'!$B$21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253" ht="15" customHeight="1" s="550">
-      <c r="A253" s="88" t="n"/>
-      <c r="B253" s="91" t="inlineStr">
-        <is>
-          <t>Costo por m² construido (sobre Presupuesto Total)</t>
-        </is>
-      </c>
-      <c r="C253" s="92" t="n"/>
-      <c r="D253" s="92" t="n"/>
-      <c r="E253" s="92" t="n"/>
-      <c r="F253" s="1460">
-        <f>F249/'Ficha Técnica del Proyecto'!$B$21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="27" t="n"/>
-      <c r="B254" s="277" t="n"/>
-      <c r="C254" s="277" t="n"/>
-      <c r="D254" s="277" t="n"/>
-      <c r="E254" s="277" t="n"/>
-      <c r="F254" s="277" t="n"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="27" t="n"/>
-      <c r="B255" s="277" t="n"/>
-      <c r="C255" s="277" t="n"/>
-      <c r="D255" s="277" t="n"/>
-      <c r="E255" s="277" t="n"/>
-      <c r="F255" s="277" t="n"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="27" t="n"/>
-      <c r="B256" s="277" t="n"/>
-      <c r="C256" s="277" t="n"/>
-      <c r="D256" s="277" t="n"/>
-      <c r="E256" s="277" t="n"/>
-      <c r="F256" s="277" t="n"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="27" t="n"/>
-      <c r="B257" s="277" t="n"/>
-      <c r="C257" s="277" t="n"/>
-      <c r="D257" s="277" t="n"/>
-      <c r="E257" s="277" t="n"/>
-      <c r="F257" s="277" t="n"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="27" t="n"/>
-      <c r="B258" s="277" t="n"/>
-      <c r="C258" s="277" t="n"/>
-      <c r="D258" s="277" t="n"/>
-      <c r="E258" s="277" t="n"/>
-      <c r="F258" s="277" t="n"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="27" t="n"/>
-      <c r="B259" s="277" t="n"/>
-      <c r="C259" s="277" t="n"/>
-      <c r="D259" s="277" t="n"/>
-      <c r="E259" s="277" t="n"/>
-      <c r="F259" s="277" t="n"/>
+      <c r="F251" s="277" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="27" t="n"/>
+      <c r="B252" s="277" t="n"/>
+      <c r="C252" s="277" t="n"/>
+      <c r="D252" s="277" t="n"/>
+      <c r="E252" s="277" t="n"/>
+      <c r="F252" s="277" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="27" t="n"/>
+      <c r="B253" s="277" t="n"/>
+      <c r="C253" s="277" t="n"/>
+      <c r="D253" s="277" t="n"/>
+      <c r="E253" s="277" t="n"/>
+      <c r="F253" s="277" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A13:F238"/>
   <mergeCells count="61">
-    <mergeCell ref="B233:F233"/>
-    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B227:F227"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="B200:F200"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B100:F100"/>
     <mergeCell ref="B194:F194"/>
+    <mergeCell ref="B125:F125"/>
+    <mergeCell ref="B74:E74"/>
     <mergeCell ref="B192:E192"/>
-    <mergeCell ref="B92:E92"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="B68:E68"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B121:F121"/>
-    <mergeCell ref="B80:E80"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B214:F214"/>
-    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B208:F208"/>
+    <mergeCell ref="B215:F215"/>
+    <mergeCell ref="B115:F115"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B70:F70"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B130:F130"/>
-    <mergeCell ref="B212:E212"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B129:E129"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B229:F229"/>
-    <mergeCell ref="B227:E227"/>
-    <mergeCell ref="B185:E185"/>
-    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="B213:E213"/>
+    <mergeCell ref="B223:F223"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B221:E221"/>
+    <mergeCell ref="B206:E206"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="B113:E113"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B136:F136"/>
     <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B134:E134"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B81:E81"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B232:E232"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="B156:E156"/>
+    <mergeCell ref="B88:F88"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="B93:E93"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B140:E140"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="B238:E238"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B176:E176"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B219:E219"/>
+    <mergeCell ref="B172:F172"/>
+    <mergeCell ref="B86:E86"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B231:E231"/>
     <mergeCell ref="B99:E99"/>
-    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B143:F143"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B179:E179"/>
+    <mergeCell ref="B225:E225"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B170:E170"/>
+    <mergeCell ref="B158:F158"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B119:E119"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="C1:F3"/>
-    <mergeCell ref="B142:F142"/>
-    <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B249:E249"/>
-    <mergeCell ref="B162:E162"/>
-    <mergeCell ref="B94:F94"/>
-    <mergeCell ref="B221:F221"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B76:F76"/>
+    <mergeCell ref="B243:E243"/>
+    <mergeCell ref="B234:E234"/>
+    <mergeCell ref="B186:E186"/>
     <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B188:F188"/>
   </mergeCells>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.5118110236220472" footer="0.5118110236220472"/>
   <pageSetup orientation="portrait" paperSize="9" scale="53" horizontalDpi="300" verticalDpi="300"/>
